--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="426">
   <si>
     <t>Rank</t>
   </si>
@@ -85,7 +85,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>Current official site advertises same-day and emergency electrical service, EV chargers, panel upgrades, Tesla Powerwall work, free estimates and typically responding within a few hours.</t>
+    <t>Official site crawled Sep 12-13 advertises free estimates, same-day service, EV chargers, panel upgrades, Tesla Powerwall work, active EV/panel promotions and PG&amp;E rebate assistance.</t>
   </si>
   <si>
     <t>(415) 676-0598</t>
@@ -97,219 +97,309 @@
     <t>Direct email; same-day/emergency service</t>
   </si>
   <si>
-    <t>Turn panel, EV and battery work into an electrical-readiness decision funnel.</t>
-  </si>
-  <si>
-    <t>Same-day electrical decision-flow idea for Hertz Electric</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Hertz Electric’s current services and noticed you combine same-day work with panel upgrades, EV chargers and Powerwall projects. Campaign angle: ‘Before adding an EV charger or battery, make sure the electrical system underneath it is ready.’ I’d turn that into FAQs, upgrade-readiness posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Hertz-specific examples first?</t>
+    <t>Turn panel capacity, EV charging and rebate navigation into an electrical-readiness decision funnel.</t>
+  </si>
+  <si>
+    <t>EV + panel readiness campaign idea for Hertz Electric</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Hertz Electric’s current San Jose pages and saw you combine EV chargers, panel upgrades, Powerwall work, free estimates and rebate guidance. Campaign angle: ‘Before adding an EV charger or battery, make sure the electrical system underneath it is ready — and know which incentives may apply.’ I’d turn that into readiness FAQs, rebate explainer posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Hertz-specific examples first?</t>
   </si>
   <si>
     <t>https://thehertzelectric.com/</t>
   </si>
   <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>1-800 WATER DAMAGE of West San Jose &amp; Sunnyvale</t>
+  </si>
+  <si>
+    <t>Water / Fire / Mold / Sewage Restoration</t>
+  </si>
+  <si>
+    <t>West San Jose / Sunnyvale, CA</t>
+  </si>
+  <si>
+    <t>Current local franchise content publishes direct local email, 24/7 emergency service, residential/commercial restoration and a mitigation-to-reconstruction workflow.</t>
+  </si>
+  <si>
+    <t>(408) 834-7773</t>
+  </si>
+  <si>
+    <t>Murali.Sridharane@1800waterdamage.com</t>
+  </si>
+  <si>
+    <t>Direct local email; 24/7 emergency business</t>
+  </si>
+  <si>
+    <t>Market first-hour mitigation plus documentation and reconstruction as one calm recovery path.</t>
+  </si>
+  <si>
+    <t>First-hour restoration campaign idea for 1-800 WATER DAMAGE</t>
+  </si>
+  <si>
+    <t>Hi Murali — I reviewed the West San Jose / Sunnyvale restoration content and saw your local team handles water, fire, mold and sewage emergencies around the clock. Campaign angle: ‘The first hour is about stopping the damage and documenting what happens next.’ I’d turn that into emergency checklists, homeowner FAQs and insurance/reconstruction follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two location-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.1800waterdamage.com/west-jose-sunnyvale/</t>
+  </si>
+  <si>
+    <t>Ozone Service</t>
+  </si>
+  <si>
+    <t>HVAC / Electrical / Panel / EV</t>
+  </si>
+  <si>
+    <t>Current official pages publish 24/7 service, free estimates/diagnostics, written scope and price, panel upgrades, EV chargers, heat pumps, financing and rebate assistance.</t>
+  </si>
+  <si>
+    <t>(669) 323-7077</t>
+  </si>
+  <si>
+    <t>go@serviceozone.com</t>
+  </si>
+  <si>
+    <t>Direct email; 24/7 service; free estimate</t>
+  </si>
+  <si>
+    <t>Make written scope, rebates and cross-trade HVAC/electrical readiness the trust campaign.</t>
+  </si>
+  <si>
+    <t>Written-scope + rebate campaign idea for Ozone Service</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Ozone Service’s current pages and noticed you already solve several objections: free diagnostics, written scope before work, financing and rebate support across HVAC and electrical upgrades. I’d turn that into upgrade-readiness posts, rebate FAQs and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Ozone-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://serviceozone.com/</t>
+  </si>
+  <si>
+    <t>Silicon Valley Building Service and Repair</t>
+  </si>
+  <si>
+    <t>Remodeling / ADU / Additions</t>
+  </si>
+  <si>
+    <t>San Jose / South Bay, CA</t>
+  </si>
+  <si>
+    <t>Official pages crawled Sep 12-13 publish free estimates, fixed-price written scopes, same-day replies during business hours, remodeling, ADUs and additions.</t>
+  </si>
+  <si>
+    <t>(408) 667-4946</t>
+  </si>
+  <si>
+    <t>info@siliconvalleybuilding.com</t>
+  </si>
+  <si>
+    <t>Direct email; usually same-day reply; free estimate</t>
+  </si>
+  <si>
+    <t>Turn scope-first fixed pricing into a high-ticket remodeling decision campaign.</t>
+  </si>
+  <si>
+    <t>Fixed-price remodeling decision-flow idea for SVBSR</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed SVBSR’s current process and noticed a strong trust angle: free estimate, written scope and fixed price before the work starts. Campaign idea: ‘Before committing to a remodel or ADU, make the scope and price understandable.’ I’d build planning FAQs, ADU/remodel posts and estimate follow-ups. $150 flat. Want two SVBSR-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://siliconvalleybuilding.com/</t>
+  </si>
+  <si>
+    <t>Shefer Builder</t>
+  </si>
+  <si>
+    <t>Remodeling / ADU / Additions / New Construction</t>
+  </si>
+  <si>
+    <t>Official site crawled Sep 12-13 publishes direct email, free estimates, ADU/garage conversion, room and second-story additions, general remodeling and Sunday hours 9 AM-7 PM.</t>
+  </si>
+  <si>
+    <t>510-571-0060</t>
+  </si>
+  <si>
+    <t>sheferbuilder@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; open Sunday; free estimate</t>
+  </si>
+  <si>
+    <t>Use one-contractor continuity across remodel, ADU and addition work to simplify a complex project decision.</t>
+  </si>
+  <si>
+    <t>ADU + addition decision-flow idea for Shefer Builder</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Shefer Builder’s current services and saw you handle remodeling, ADUs, garage conversions and room/second-story additions. Campaign angle: ‘Before choosing finishes, make the project path — scope, added space and build sequence — easy to understand.’ I’d turn that into ADU/addition FAQs, project-planning posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Shefer-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://sheferbuilder.com/</t>
+  </si>
+  <si>
+    <t>California Bay Builders &amp; Remodeling</t>
+  </si>
+  <si>
+    <t>ADU / Remodeling / Design-Build</t>
+  </si>
+  <si>
+    <t>Official San Jose ADU pages crawled Sep 11 publish a direct email, free consultation, turnkey design-build service, permitting support and owner-led delivery.</t>
+  </si>
+  <si>
+    <t>(800) 209-0051</t>
+  </si>
+  <si>
+    <t>info@californiabaybuildersandremodeling.com</t>
+  </si>
+  <si>
+    <t>Direct email; free consultation</t>
+  </si>
+  <si>
+    <t>Turn lot feasibility, permitting and turnkey delivery into a pre-design decision funnel.</t>
+  </si>
+  <si>
+    <t>San Jose ADU feasibility campaign idea</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed your San Jose ADU pages and noticed the free consultation already answers the right first question: what can actually be built on this lot before the owner spends money on design. I’d turn that into feasibility FAQs, permit/process posts and consultation follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two California Bay Builders-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://californiabaybuildersandremodeling.com/adu-builder-san-jose/</t>
+  </si>
+  <si>
+    <t>Atra Construction</t>
+  </si>
+  <si>
+    <t>ADU / Design / Construction Management</t>
+  </si>
+  <si>
+    <t>Current official site publishes direct email, free ADU consultations, design options, permit/concept planning and construction management for Bay Area ADU projects.</t>
+  </si>
+  <si>
+    <t>925-238-3141</t>
+  </si>
+  <si>
+    <t>info@atraconstruction.com</t>
+  </si>
+  <si>
+    <t>Use concept-to-permit-to-build continuity to reduce uncertainty before an ADU project begins.</t>
+  </si>
+  <si>
+    <t>Concept-to-build ADU campaign idea for Atra</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Atra Construction’s current ADU process and saw a strong customer story in the sequence itself: free consultation, design options, permit planning and construction management. I’d turn that into feasibility FAQs, project-stage posts and consultation follow-ups so prospects understand the path before committing. Same-Day Customer Growth Pack: $150 flat. Want two Atra-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.atraconstruction.com/</t>
+  </si>
+  <si>
+    <t>South San Jose Electric</t>
+  </si>
+  <si>
+    <t>Residential / Commercial Electrical</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>Current official site publishes direct email, free estimates, Monday-Sunday availability and high-value panel upgrades, rewiring and EV charger work.</t>
+  </si>
+  <si>
+    <t>(669) 371-5273</t>
+  </si>
+  <si>
+    <t>contact@southsanjoseelectric.com</t>
+  </si>
+  <si>
+    <t>Direct email; seven-day availability; free estimate</t>
+  </si>
+  <si>
+    <t>Build an electrical-capacity readiness campaign around panels, rewiring and EV additions.</t>
+  </si>
+  <si>
+    <t>Electrical-capacity campaign idea for South San Jose Electric</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed South San Jose Electric’s current services. Panel upgrades, rewiring and EV chargers all answer the same question: ‘Is the electrical system ready for what I want to add next?’ I’d turn that into capacity-readiness posts, FAQs and estimate follow-ups. $150 flat. Want two business-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://southsanjoseelectric.com/</t>
+  </si>
+  <si>
+    <t>RoofCraft Inc</t>
+  </si>
+  <si>
+    <t>Roofing</t>
+  </si>
+  <si>
+    <t>Sunnyvale / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official financing page crawled Sep 10 publishes free estimates/inspections, financing from $1,000-$100,000, typical Bay Area roof-replacement ranges around $12,000-$40,000 and financing decisions often within minutes.</t>
+  </si>
+  <si>
+    <t>(408) 904-8900</t>
+  </si>
+  <si>
+    <t>info@roofcraftcompany.com</t>
+  </si>
+  <si>
+    <t>Direct email; high-ticket roofing; financing</t>
+  </si>
+  <si>
+    <t>Use inspection, realistic project ranges and financing education to reduce replacement uncertainty.</t>
+  </si>
+  <si>
+    <t>High-ticket roof decision campaign idea for RoofCraft</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed RoofCraft’s current financing information. Publishing inspection guidance, realistic replacement ranges and financing options creates a strong trust angle: ‘Understand the roof condition, project range and payment options before committing.’ I’d build inspection posts, repair-vs-replacement FAQs and estimate follow-ups. $150 flat. Want two RoofCraft-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://roofcraftcompany.com/financing/</t>
+  </si>
+  <si>
+    <t>SERVPRO of Mountain View, Los Altos</t>
+  </si>
+  <si>
+    <t>Water / Fire / Mold / Storm / Construction</t>
+  </si>
+  <si>
+    <t>Sunnyvale / Mountain View / Los Altos, CA</t>
+  </si>
+  <si>
+    <t>Local SERVPRO pages publish 24/7 emergency restoration, construction and commercial services, a Sunnyvale office and a direct office email.</t>
+  </si>
+  <si>
+    <t>(650) 770-2992</t>
+  </si>
+  <si>
+    <t>office@SERVPROmtview.com</t>
+  </si>
+  <si>
+    <t>Direct office email; 24/7 emergency service</t>
+  </si>
+  <si>
+    <t>Explain mitigation-to-reconstruction continuity and commercial response in plain language.</t>
+  </si>
+  <si>
+    <t>Mitigation-to-rebuild campaign idea for SERVPRO Mountain View</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed your local SERVPRO services and noticed the team handles emergency mitigation, commercial losses and reconstruction. Campaign angle: ‘Stop the damage first, then keep recovery moving without making the customer restart the process.’ I’d build first-hour checklists, commercial-response posts and reconstruction FAQs. $150 flat. Want two local examples first?</t>
+  </si>
+  <si>
+    <t>https://www.servpromountainviewlosaltos.com/</t>
+  </si>
+  <si>
     <t>2026-09-12</t>
   </si>
   <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
-    <t>1-800 WATER DAMAGE of West San Jose &amp; Sunnyvale</t>
-  </si>
-  <si>
-    <t>Water / Fire / Mold / Sewage Restoration</t>
-  </si>
-  <si>
-    <t>West San Jose / Sunnyvale, CA</t>
-  </si>
-  <si>
-    <t>Current local franchise pages publish a direct owner email, 24/7 emergency restoration, residential/commercial service, water/fire/mold/sewage work and insurance assistance.</t>
-  </si>
-  <si>
-    <t>(408) 834-7773</t>
-  </si>
-  <si>
-    <t>Murali.Sridharane@1800waterdamage.com</t>
-  </si>
-  <si>
-    <t>Direct owner email; 24/7 emergency business</t>
-  </si>
-  <si>
-    <t>Market first-hour mitigation plus insurance documentation as a calm local decision path.</t>
-  </si>
-  <si>
-    <t>First-hour restoration campaign idea for 1-800 WATER DAMAGE</t>
-  </si>
-  <si>
-    <t>Hi Murali — I reviewed the West San Jose / Sunnyvale pages and saw your local team handles water, fire, mold and sewage emergencies 24/7. Campaign angle: ‘The first hour is about stopping the damage and documenting what happens next.’ I’d turn that into emergency checklists, FAQs and insurance-documentation follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two location-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.1800waterdamage.com/west-san-jose-sunnyvale/</t>
-  </si>
-  <si>
-    <t>Ozone Service</t>
-  </si>
-  <si>
-    <t>Electrical / Panel Upgrades</t>
-  </si>
-  <si>
-    <t>Current site advertises 24/7 Bay Area electrical service, free panel-upgrade estimates, no trip/diagnostic fee positioning and written scope/price before work.</t>
-  </si>
-  <si>
-    <t>(669) 323-7077</t>
-  </si>
-  <si>
-    <t>go@serviceozone.com</t>
-  </si>
-  <si>
-    <t>Direct email; 24/7 service; free estimate</t>
-  </si>
-  <si>
-    <t>Make written scope and pricing the trust campaign for upgrades.</t>
-  </si>
-  <si>
-    <t>Panel-upgrade trust campaign idea for Ozone Service</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Ozone Service’s current electrical pages. You already reduce several homeowner objections with 24/7 availability, free panel-upgrade estimates and written scope before work. I’d turn that into panel-readiness posts, EV/upgrade FAQs and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Ozone-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://serviceozone.com/</t>
-  </si>
-  <si>
-    <t>Silicon Valley Building Service and Repair</t>
-  </si>
-  <si>
-    <t>Remodeling / ADU / Additions</t>
-  </si>
-  <si>
-    <t>San Jose / Silicon Valley, CA</t>
-  </si>
-  <si>
-    <t>Official site is current with kitchen/bath/whole-home remodeling, ADUs, additions and garage conversions, free estimates, written fixed-price proposals and a same-day reply expectation.</t>
-  </si>
-  <si>
-    <t>(408) 667-4946</t>
-  </si>
-  <si>
-    <t>info@siliconvalleybuilding.com</t>
-  </si>
-  <si>
-    <t>Direct email; usually same-day reply; free estimate</t>
-  </si>
-  <si>
-    <t>Turn scope-first, fixed-price proposals into a high-ticket remodeling decision campaign.</t>
-  </si>
-  <si>
-    <t>Fixed-price remodeling decision-flow idea for SVBSR</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed SVBSR’s current process and noticed a strong trust angle: free estimate, written scope and fixed-price proposal. Campaign idea: ‘Before committing to a remodel or ADU, make the scope and price understandable.’ I’d build project-planning FAQs, ADU/remodel posts and estimate follow-ups. $150 flat. Want two SVBSR-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://siliconvalleybuilding.com/</t>
-  </si>
-  <si>
-    <t>South San Jose Electric</t>
-  </si>
-  <si>
-    <t>Residential / Commercial Electrical</t>
-  </si>
-  <si>
-    <t>San Jose, CA</t>
-  </si>
-  <si>
-    <t>Current official site publishes a direct email, free estimates and residential/commercial work including panel upgrades, full rewiring and EV chargers, with seven-day availability.</t>
-  </si>
-  <si>
-    <t>(669) 371-5273</t>
-  </si>
-  <si>
-    <t>contact@southsanjoseelectric.com</t>
-  </si>
-  <si>
-    <t>Direct email; seven-day availability; free estimate</t>
-  </si>
-  <si>
-    <t>Build an electrical-capacity readiness campaign around panels, rewiring and EV additions.</t>
-  </si>
-  <si>
-    <t>Electrical-capacity campaign idea for South San Jose Electric</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed South San Jose Electric’s current services. Panel upgrades, rewiring and EV chargers all answer the same question: ‘Is the electrical system ready for what I want to add next?’ I’d turn that into capacity-readiness posts, FAQs and estimate follow-ups. $150 flat. Want two business-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://southsanjoseelectric.com/</t>
-  </si>
-  <si>
-    <t>RoofCraft Inc</t>
-  </si>
-  <si>
-    <t>Roofing</t>
-  </si>
-  <si>
-    <t>Sunnyvale / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official pages are current with free estimates/inspections, financing from $1,000 to $100,000, published Bay Area replacement ranges around $12,000–$40,000 and payment after project completion.</t>
-  </si>
-  <si>
-    <t>(408) 904-8900</t>
-  </si>
-  <si>
-    <t>info@roofcraftcompany.com</t>
-  </si>
-  <si>
-    <t>Direct email; high-ticket roofing; financing</t>
-  </si>
-  <si>
-    <t>Use inspection, realistic project ranges and financing education to reduce replacement uncertainty.</t>
-  </si>
-  <si>
-    <t>High-ticket roof decision campaign idea for RoofCraft</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed RoofCraft’s current estimate and financing pages. Publishing inspection guidance and realistic project ranges creates a strong trust angle: ‘Understand the roof condition, project range and financing options before committing.’ I’d build inspection posts, repair-vs-replacement FAQs and estimate follow-ups. $150 flat. Want two RoofCraft-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://roofcraftcompany.com/</t>
-  </si>
-  <si>
-    <t>SERVPRO of Mountain View, Los Altos</t>
-  </si>
-  <si>
-    <t>Water / Fire / Mold / Storm / Construction</t>
-  </si>
-  <si>
-    <t>Sunnyvale / Mountain View / Los Altos, CA</t>
-  </si>
-  <si>
-    <t>Current local SERVPRO pages publish 24/7 emergency service, fire/water/mold/storm restoration, construction and commercial services, a Sunnyvale office and direct office email.</t>
-  </si>
-  <si>
-    <t>(650) 770-2992</t>
-  </si>
-  <si>
-    <t>office@SERVPROmtview.com</t>
-  </si>
-  <si>
-    <t>Direct office email; 24/7 emergency service</t>
-  </si>
-  <si>
-    <t>Explain mitigation-to-reconstruction continuity and commercial response in plain language.</t>
-  </si>
-  <si>
-    <t>Mitigation-to-rebuild campaign idea for SERVPRO Mountain View</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed your local SERVPRO pages and noticed the team handles both emergency mitigation and reconstruction, plus commercial losses. Campaign angle: ‘Stop the damage first, then keep recovery moving without making the customer restart the process.’ I’d build first-hour checklists, commercial-response posts and reconstruction FAQs. $150 flat. Want two local examples first?</t>
-  </si>
-  <si>
-    <t>https://www.servpromountainviewlosaltos.com/</t>
-  </si>
-  <si>
     <t>Courtesy Electric</t>
   </si>
   <si>
@@ -319,7 +409,7 @@
     <t>Sunnyvale / South Bay, CA</t>
   </si>
   <si>
-    <t>Official site publishes owner-operated electrical service, free estimates, new construction, remodeling, service upgrades and lighting, plus a direct business email.</t>
+    <t>Official site publishes owner-operated electrical service, free estimates, new construction, remodeling, service upgrades and a direct business email.</t>
   </si>
   <si>
     <t>(408) 509-1017</t>
@@ -376,7 +466,7 @@
     <t>AYH Remodeling &amp; Construction Inc</t>
   </si>
   <si>
-    <t>Current site publishes free estimates, remodeling, ADUs/additions, structural and permit services, a direct email and Monday–Saturday 7 AM–7 PM hours.</t>
+    <t>Current site publishes free estimates, remodeling, ADUs/additions, structural and permit services, a direct email and Monday-Saturday 7 AM-7 PM hours.</t>
   </si>
   <si>
     <t>833-408-5179</t>
@@ -385,7 +475,7 @@
     <t>ayhremodelingandconstruction@gmail.com</t>
   </si>
   <si>
-    <t>Direct email; Mon–Sat; free estimate</t>
+    <t>Direct email; Mon-Sat; free estimate</t>
   </si>
   <si>
     <t>Use permit, structural and build coordination to simplify the ADU/addition decision.</t>
@@ -406,7 +496,7 @@
     <t>Remodeling / ADU / Design-Build</t>
   </si>
   <si>
-    <t>Current site publishes premium remodeling/ADU services, free in-home consultations, a current 2026 ADU cost guide and direct business email.</t>
+    <t>Current pages publish high-ticket 2024-2026 remodeling/ADU ranges, free in-home consultations and a fixed-price proposal process.</t>
   </si>
   <si>
     <t>(650) 800-9755</t>
@@ -418,16 +508,16 @@
     <t>Direct email; free in-home consultation</t>
   </si>
   <si>
-    <t>Turn the current 2026 ADU cost guide into consultation-driving education.</t>
-  </si>
-  <si>
-    <t>2026 ADU cost-guide campaign idea for Pylon Builders</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Pylon Builders’ current ADU content and saw the 2026 cost guide alongside your free in-home consultation. Campaign angle: ‘Use real planning ranges to decide whether an ADU is worth designing before you commit.’ I’d build cost/feasibility posts, ADU FAQs and consultation follow-ups. $150 flat. Want two Pylon-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://pylonbuilders.com/</t>
+    <t>Turn current local project ranges into consultation-driving budget education.</t>
+  </si>
+  <si>
+    <t>Bay Area ADU budget campaign idea for Pylon Builders</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Pylon Builders’ current remodeling/ADU information and saw you publish realistic local project ranges alongside a free in-home consultation. Campaign angle: ‘Use planning ranges to decide what is feasible before committing to design.’ I’d build cost/feasibility posts, ADU FAQs and consultation follow-ups. $150 flat. Want two Pylon-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://pylonbuilders.com/home-remodeling-santa-clara</t>
   </si>
   <si>
     <t>Home Pro Roofing and Solar</t>
@@ -436,7 +526,7 @@
     <t>Roofing / Solar / Battery / EV</t>
   </si>
   <si>
-    <t>Current contact page advertises free estimates within 24 hours and offers through Sep 15, 2026: $250 off a full roof replacement and $1,500 off a roof + solar combo.</t>
+    <t>Current contact page advertises free estimates within 24 hours and offers through Sep 15, 2026, including roof-replacement and roof-plus-solar savings.</t>
   </si>
   <si>
     <t>(800) 650-3134</t>
@@ -463,7 +553,7 @@
     <t>Foundation / Concrete / Crawl Space</t>
   </si>
   <si>
-    <t>Current San Jose pages advertise free expert inspections, financing, concrete/foundation services and current qualifying-project savings; financing pages describe large-project lender options.</t>
+    <t>Current San Jose pages advertise free expert inspections, financing and foundation/concrete services.</t>
   </si>
   <si>
     <t>(925) 961-9012</t>
@@ -472,13 +562,13 @@
     <t>Phone/web form; free inspection; financing</t>
   </si>
   <si>
-    <t>Build inspection-first education around cracks, settlement and financing without fear-based claims.</t>
+    <t>Build inspection-first education around cracks and settlement without fear-based claims.</t>
   </si>
   <si>
     <t>Foundation inspection decision-flow idea</t>
   </si>
   <si>
-    <t>Hi — I reviewed your current San Jose pages and think the free inspection can support a stronger campaign than generic foundation-problem advertising. Angle: ‘Start with evidence of what is moving, why, and what actually needs repair.’ I’d build symptom FAQs, inspection-prep posts and estimate follow-ups. $150 flat. Want two business-specific examples first?</t>
+    <t>Hi — I reviewed your San Jose pages and think the free inspection can support a stronger campaign than generic foundation-problem advertising. Angle: ‘Start with evidence of what is moving, why, and what actually needs repair.’ I’d build symptom FAQs, inspection-prep posts and estimate follow-ups. $150 flat. Want two business-specific examples first?</t>
   </si>
   <si>
     <t>https://www.foundationrepairofca.com/service-areas/san-jose-ca/</t>
@@ -493,7 +583,7 @@
     <t>San Jose / Campbell / Sunnyvale, CA</t>
   </si>
   <si>
-    <t>Current official pages publish free in-home estimates, itemized estimates typically within 24 hours, flexible financing including qualified 0% APR promotions and limited savings for 5+ windows.</t>
+    <t>Current official pages publish free in-home estimates, itemized estimates typically within 24 hours and flexible financing for larger replacement projects.</t>
   </si>
   <si>
     <t>(408) 479-7960</t>
@@ -514,94 +604,13 @@
     <t>https://bentsonwindows.com/</t>
   </si>
   <si>
-    <t>Trio Roofers</t>
-  </si>
-  <si>
-    <t>Residential / Commercial Roofing</t>
-  </si>
-  <si>
-    <t>Current San Jose pages advertise free inspections, residential/commercial/emergency roofing, 24/7 emergency availability and $0-upfront financing positioning. No tax-credit claim is used.</t>
-  </si>
-  <si>
-    <t>(408) 886-9287</t>
-  </si>
-  <si>
-    <t>Phone/web form; 24/7 emergency; free inspection</t>
-  </si>
-  <si>
-    <t>Use free inspection plus financing as a proof-before-purchase sequence.</t>
-  </si>
-  <si>
-    <t>Free-inspection roofing funnel idea for Trio</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Trio Roofers’ current San Jose pages. The strongest customer story is the decision sequence: ‘Inspect first. See the scope. Then decide how to fund the project.’ I’d build inspection posts, repair-vs-replacement FAQs and financing follow-ups. $150 flat. Want two Trio-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://trioroofers.com/san-jose/</t>
-  </si>
-  <si>
-    <t>Foundation Strategies &amp; Construction</t>
-  </si>
-  <si>
-    <t>Foundation / Waterproofing / Structural</t>
-  </si>
-  <si>
-    <t>San Jose / Sunnyvale, CA</t>
-  </si>
-  <si>
-    <t>Current pages publish free no-pressure inspections/estimates, foundation and waterproofing services, financing options and structural/new-foundation work in the South Bay.</t>
-  </si>
-  <si>
-    <t>(408) 320-7433</t>
-  </si>
-  <si>
-    <t>Turn no-pressure inspection plus structural explanation into trust-focused content.</t>
-  </si>
-  <si>
-    <t>No-pressure foundation inspection campaign idea</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Foundation Strategies’ current South Bay pages and noticed you emphasize free, no-pressure inspections alongside structural and waterproofing work. Campaign angle: ‘Understand the cause and repair options before deciding whether a foundation project is actually necessary.’ I’d build crack/settlement FAQs and estimate follow-ups. $150 flat. Want two examples first?</t>
-  </si>
-  <si>
-    <t>https://foundationstrategies.com/</t>
-  </si>
-  <si>
-    <t>Jackson Electric</t>
-  </si>
-  <si>
-    <t>Electrical / Panel / EV</t>
-  </si>
-  <si>
-    <t>Current site says emergency calls are prioritized, panel-upgrade and EV-charger quotes are usually returned within one business day, and the company has operated locally since 1989.</t>
-  </si>
-  <si>
-    <t>(408) 266-5351</t>
-  </si>
-  <si>
-    <t>Phone/web form; one-business-day quote target</t>
-  </si>
-  <si>
-    <t>Use long local history plus fast quotes to clarify panel/EV upgrades.</t>
-  </si>
-  <si>
-    <t>One-day electrical quote campaign idea for Jackson Electric</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Jackson Electric’s current services and noticed you pair long local history with a practical advantage: panel-upgrade and EV-charger quotes are usually turned around within one business day. I’d build panel/EV FAQs, quote follow-ups and capacity-readiness posts. $150 flat. Want two Jackson-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://jacksonelectric.com/</t>
-  </si>
-  <si>
     <t>Atlas Trillo</t>
   </si>
   <si>
     <t>HVAC / Plumbing</t>
   </si>
   <si>
-    <t>Current site has September residential offers through Sep 30, including a $59 seasonal HVAC tune-up and $50 off qualifying service repair, alongside HVAC and plumbing services.</t>
+    <t>Current site has September residential offers through Sep 30, including a seasonal HVAC tune-up and qualifying service-repair savings.</t>
   </si>
   <si>
     <t>(408) 444-9511</t>
@@ -616,7 +625,7 @@
     <t>September HVAC tune-up campaign idea for Atlas Trillo</t>
   </si>
   <si>
-    <t>Hi — I checked Atlas Trillo’s current September offers and saw the seasonal HVAC tune-up and repair savings are live through September 30. Campaign angle: ‘Use the tune-up to learn what actually needs attention before peak heating season.’ I’d build symptom posts, tune-up FAQs and repair follow-ups. $150 flat. Want two examples first?</t>
+    <t>Hi — I checked Atlas Trillo’s September offers and saw the seasonal HVAC tune-up and repair savings are live through September 30. Campaign angle: ‘Use the tune-up to learn what actually needs attention before peak heating season.’ I’d build symptom posts, tune-up FAQs and repair follow-ups. $150 flat. Want two examples first?</t>
   </si>
   <si>
     <t>https://www.atlastrillo.com/specials/</t>
@@ -628,7 +637,7 @@
     <t>Plumbing / Drain / HVAC</t>
   </si>
   <si>
-    <t>Current San Jose pages publish 24/7 service and active Sep 1–30 residential promotions including drain/camera-inspection and qualifying repair savings. Expired commercial promotions are excluded.</t>
+    <t>Current San Jose pages publish 24/7 service and active September residential promotions including drain/camera-inspection and qualifying repair savings.</t>
   </si>
   <si>
     <t>(408) 703-6715</t>
@@ -643,7 +652,7 @@
     <t>Drain-camera decision campaign idea for Rooter Hero</t>
   </si>
   <si>
-    <t>Hi — I reviewed Rooter Hero San Jose’s current September residential offers and think the camera-inspection angle supports a better campaign than discount-only messaging: ‘See what is causing the drain problem before choosing the repair.’ I’d build diagnosis posts, FAQs and service follow-ups. $150 flat. Want two San Jose-specific examples first?</t>
+    <t>Hi — I reviewed Rooter Hero San Jose’s September residential offers and think the camera-inspection angle supports a better campaign than discount-only messaging: ‘See what is causing the drain problem before choosing the repair.’ I’d build diagnosis posts, FAQs and service follow-ups. $150 flat. Want two San Jose-specific examples first?</t>
   </si>
   <si>
     <t>https://rooterhero.com/san-jose/</t>
@@ -655,25 +664,25 @@
     <t>Home Additions / ADU / Remodeling</t>
   </si>
   <si>
-    <t>Current site publishes free estimates, home additions, ADUs and second-story work, a direct email, Monday–Saturday service and Sunday appointments.</t>
+    <t>Official site crawled today publishes direct email, free itemized on-site estimates, design-build ADUs/additions/second stories, permit handling and Sunday appointments.</t>
   </si>
   <si>
     <t>info@homeadditionssanjose.com</t>
   </si>
   <si>
-    <t>Direct email; free estimate; Mon–Sat + Sunday by appointment</t>
-  </si>
-  <si>
-    <t>Use feasibility-to-estimate planning as a high-ticket addition/ADU funnel.</t>
+    <t>Direct email; free estimate; Sunday by appointment</t>
+  </si>
+  <si>
+    <t>Use feasibility-to-itemized-estimate planning as a high-ticket addition/ADU funnel.</t>
   </si>
   <si>
     <t>Addition + ADU feasibility campaign idea</t>
   </si>
   <si>
-    <t>Hi — I reviewed Home Additions San Jose’s current services and saw you cover additions, ADUs and second-story projects with free estimates. Campaign angle: ‘Before designing a major addition, establish what is feasible, what needs permitting and what the project scope should include.’ I’d build feasibility FAQs and estimate follow-ups. $150 flat. Want two examples first?</t>
-  </si>
-  <si>
-    <t>https://homeadditionssanjose.com/</t>
+    <t>Hi — I reviewed Home Additions San Jose today and saw you handle additions, ADUs and second-story projects with design, permits and free itemized estimates. Campaign angle: ‘Before designing a major addition, establish what is feasible, what needs permitting and what the project scope should include.’ I’d build feasibility FAQs and estimate follow-ups. $150 flat. Want two examples first?</t>
+  </si>
+  <si>
+    <t>https://www.homeadditionssanjose.com/</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -2035,34 +2044,34 @@
         <v>62</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -2076,40 +2085,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -2123,40 +2132,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -2170,40 +2179,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -2217,40 +2226,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -2264,43 +2273,43 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -2317,37 +2326,37 @@
         <v>125</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -2358,41 +2367,43 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H13" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="I13" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>28</v>
@@ -2403,10 +2414,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>144</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>17</v>
@@ -2415,29 +2426,31 @@
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H14" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="I14" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -2448,38 +2461,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H15" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>158</v>
+      </c>
       <c r="I15" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>27</v>
@@ -2493,41 +2508,41 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -2538,41 +2553,41 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -2583,41 +2598,41 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -2628,41 +2643,41 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -2673,41 +2688,41 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -2718,38 +2733,38 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>27</v>
@@ -2804,142 +2819,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -2973,58 +2988,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -3054,7 +3069,7 @@
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
@@ -3094,7 +3109,7 @@
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
@@ -3134,7 +3149,7 @@
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
@@ -3174,7 +3189,7 @@
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
@@ -3195,7 +3210,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3213,15 +3228,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2" t="s">
-        <v>273</v>
-      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R6" s="3">
         <v>150</v>
@@ -3229,13 +3242,13 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3253,15 +3266,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="2" t="s">
-        <v>273</v>
-      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -3269,13 +3280,13 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -3293,15 +3304,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="2" t="s">
-        <v>273</v>
-      </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="R8" s="3">
         <v>150</v>
@@ -3309,13 +3318,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -3334,14 +3343,14 @@
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="R9" s="3">
         <v>150</v>
@@ -3349,13 +3358,13 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3374,14 +3383,14 @@
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -3389,13 +3398,13 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3414,14 +3423,14 @@
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R11" s="3">
         <v>150</v>
@@ -3435,7 +3444,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -3454,14 +3463,14 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="R12" s="3">
         <v>150</v>
@@ -3469,13 +3478,13 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B13" s="2">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -3494,14 +3503,14 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="R13" s="3">
         <v>150</v>
@@ -3509,13 +3518,13 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B14" s="2">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -3534,14 +3543,14 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R14" s="3">
         <v>150</v>
@@ -3549,13 +3558,13 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B15" s="2">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -3574,14 +3583,14 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="R15" s="3">
         <v>150</v>
@@ -3589,13 +3598,13 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B16" s="2">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -3614,14 +3623,14 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="R16" s="3">
         <v>150</v>
@@ -3629,13 +3638,13 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -3654,14 +3663,14 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="R17" s="3">
         <v>150</v>
@@ -3669,13 +3678,13 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B18" s="2">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -3694,14 +3703,14 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="R18" s="3">
         <v>150</v>
@@ -3709,13 +3718,13 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B19" s="2">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -3734,14 +3743,14 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="R19" s="3">
         <v>150</v>
@@ -3749,13 +3758,13 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B20" s="2">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -3774,14 +3783,14 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R20" s="3">
         <v>150</v>
@@ -3789,13 +3798,13 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B21" s="2">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -3814,14 +3823,14 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="R21" s="3">
         <v>150</v>
@@ -3829,28 +3838,28 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3860,7 +3869,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3871,32 +3880,32 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3906,7 +3915,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3917,26 +3926,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3946,7 +3955,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3957,26 +3966,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -3986,7 +3995,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3997,26 +4006,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -4026,7 +4035,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -4037,26 +4046,26 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -4066,7 +4075,7 @@
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -4077,26 +4086,26 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
@@ -4106,7 +4115,7 @@
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -4117,26 +4126,26 @@
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -4146,7 +4155,7 @@
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -4157,26 +4166,26 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K30" s="3">
         <v>0</v>
@@ -4186,7 +4195,7 @@
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -4197,26 +4206,26 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K31" s="3">
         <v>0</v>
@@ -4226,7 +4235,7 @@
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -4237,28 +4246,28 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -4268,7 +4277,7 @@
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -4279,26 +4288,26 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -4308,7 +4317,7 @@
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -4319,26 +4328,26 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -4348,7 +4357,7 @@
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -4359,26 +4368,26 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -4388,7 +4397,7 @@
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -4399,26 +4408,26 @@
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K36" s="3">
         <v>0</v>
@@ -4428,7 +4437,7 @@
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -4502,67 +4511,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -4571,13 +4580,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -4585,10 +4594,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -4597,13 +4606,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -4611,10 +4620,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -4623,28 +4632,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -4653,13 +4662,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -4667,10 +4676,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -4679,13 +4688,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -4693,10 +4702,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -4705,13 +4714,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -4719,10 +4728,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -4731,28 +4740,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -4761,13 +4770,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -4775,10 +4784,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -4787,13 +4796,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -4801,10 +4810,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -4813,13 +4822,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -4827,10 +4836,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -4839,13 +4848,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -4853,10 +4862,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -4865,13 +4874,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -4879,10 +4888,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -4891,13 +4900,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -4905,10 +4914,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -4917,13 +4926,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -4931,10 +4940,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -4943,13 +4952,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -4957,10 +4966,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -4992,33 +5001,33 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -5032,16 +5041,16 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -5055,14 +5064,14 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -5076,20 +5085,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -5099,16 +5108,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
@@ -5122,14 +5131,14 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -5143,14 +5152,14 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
@@ -5164,14 +5173,14 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
@@ -5185,14 +5194,14 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -5206,16 +5215,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
@@ -5229,14 +5238,14 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>28</v>
@@ -5250,14 +5259,14 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>28</v>
@@ -5271,14 +5280,14 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>28</v>
@@ -5292,16 +5301,16 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>28</v>
@@ -5315,14 +5324,14 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>28</v>
@@ -5336,14 +5345,14 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>28</v>
@@ -5357,14 +5366,14 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>28</v>
@@ -5378,16 +5387,16 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>28</v>
@@ -5401,16 +5410,16 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>28</v>
@@ -5424,16 +5433,16 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>28</v>
@@ -5447,16 +5456,16 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>28</v>
@@ -5470,11 +5479,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -5506,13 +5515,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5532,7 +5541,7 @@
         <v>21</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5552,7 +5561,7 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5572,7 +5581,7 @@
         <v>44</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5592,7 +5601,7 @@
         <v>55</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5600,119 +5609,119 @@
         <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="C11" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5720,199 +5729,199 @@
         <v>124</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -5957,7 +5966,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5967,20 +5976,20 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5992,95 +6001,95 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -6106,98 +6115,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -6216,19 +6225,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -6245,7 +6254,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="431">
   <si>
     <t>Rank</t>
   </si>
@@ -73,18 +73,174 @@
     <t>Status</t>
   </si>
   <si>
+    <t>RCK Development</t>
+  </si>
+  <si>
+    <t>Remodeling / ADU / Additions / HVAC / Plumbing</t>
+  </si>
+  <si>
+    <t>San Jose / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Official site crawled Sep 14 publishes direct email, free estimates, same-day message response, realistic estimate/timeline promises, permit coordination and high-ticket remodel/ADU work.</t>
+  </si>
+  <si>
+    <t>(408) 982-7586</t>
+  </si>
+  <si>
+    <t>therckdevelopment@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; same-day message response; free estimate</t>
+  </si>
+  <si>
+    <t>Turn realistic scope, timeline and permit coordination into a no-pressure pre-estimate decision funnel.</t>
+  </si>
+  <si>
+    <t>Realistic remodel estimate campaign idea for RCK</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed RCK Development’s current site and noticed you make a useful promise most contractors avoid: realistic estimates and timelines, with permits and changes handled clearly. Campaign angle: ‘Before choosing finishes, know what the project can realistically cost, how long it can take, and what has to happen first.’ I’d turn that into planning FAQs, ADU/remodel posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two RCK-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.rckdevelopment.com/</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>Fox Electric</t>
+  </si>
+  <si>
+    <t>Electrical / EV Charger / Panel Upgrade</t>
+  </si>
+  <si>
+    <t>Current San Jose EV page advertises free on-site estimates, a 2-hour quote response, same-day availability, written fixed pricing, permit handling, PG&amp;E coordination and panel/load-management options.</t>
+  </si>
+  <si>
+    <t>(650) 550-0719</t>
+  </si>
+  <si>
+    <t>info@foxelectrician.com</t>
+  </si>
+  <si>
+    <t>Direct email; 2-hour quote response; same-day slots</t>
+  </si>
+  <si>
+    <t>Use EV load calculation and panel-readiness education to prevent unnecessary upgrades and make the estimate feel trustworthy.</t>
+  </si>
+  <si>
+    <t>2-hour EV + panel readiness campaign idea for Fox Electric</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Fox Electric’s San Jose EV page and the strongest marketing angle may be that you check whether a home actually needs a panel upgrade before selling one. Campaign idea: ‘Before upgrading the panel, calculate what the home and charger really require.’ I’d turn that into EV-readiness FAQs, load-management education, permit/PG&amp;E posts and estimate follow-ups. $150 flat. Want two Fox-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://foxelectrician.com/services/ev-charger-installation/san-jose/</t>
+  </si>
+  <si>
+    <t>EMC Remodels</t>
+  </si>
+  <si>
+    <t>Remodeling / ADU / Additions / Structural</t>
+  </si>
+  <si>
+    <t>Official site crawled Sep 14 publishes direct estimate email, free estimates, detailed proposals, ADUs/additions, structural and seismic work, permit experience and response within one business day.</t>
+  </si>
+  <si>
+    <t>(510) 650-5555</t>
+  </si>
+  <si>
+    <t>estimates@emcremodels.com</t>
+  </si>
+  <si>
+    <t>Direct estimates email; response within one business day</t>
+  </si>
+  <si>
+    <t>Turn project type, budget, structural risk and permitting into an estimate-readiness campaign.</t>
+  </si>
+  <si>
+    <t>Estimate-readiness campaign idea for EMC Remodels</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed EMC Remodels’ current estimate flow and noticed you already ask the questions that determine whether a project is ready to move: scope, budget, start timing and structural needs. I’d turn that into an ‘Is your remodel or ADU ready for an estimate?’ campaign with permit FAQs, structural-risk education and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two EMC-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.emcremodels.com/</t>
+  </si>
+  <si>
+    <t>Primework Construction</t>
+  </si>
+  <si>
+    <t>Remodeling / Renovation / Design-Build</t>
+  </si>
+  <si>
+    <t>Current official pages publish direct email, free quotes, 24/7 service hours, full-house/kitchen/bath/exterior renovation and a design-build process with budget proposals and timelines.</t>
+  </si>
+  <si>
+    <t>669-345-7070</t>
+  </si>
+  <si>
+    <t>info@primeworkconstructionca.com</t>
+  </si>
+  <si>
+    <t>Direct email; 24/7 listed service hours; free quote</t>
+  </si>
+  <si>
+    <t>Use design-first planning, budget breakdown and timeline clarity to reduce fear of change orders and renovation uncertainty.</t>
+  </si>
+  <si>
+    <t>Design-to-budget campaign idea for Primework Construction</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Primework Construction’s current process and noticed a strong decision-making story: design first, then a detailed budget proposal and timeline before the renovation moves forward. I’d turn that into planning posts, ‘avoid costly change-order’ FAQs and free-quote follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Primework-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://primeworkconstructionca.com/</t>
+  </si>
+  <si>
+    <t>Bayco Builders &amp; Restoration</t>
+  </si>
+  <si>
+    <t>Water / Fire / Mold / Sewage / Remodeling</t>
+  </si>
+  <si>
+    <t>Official site crawled Sep 14 publishes direct email, 24/7 emergency response, IICRC-certified restoration, insurance coordination, free estimates and mitigation-to-remodel/rebuild capability.</t>
+  </si>
+  <si>
+    <t>(669) 770-5373</t>
+  </si>
+  <si>
+    <t>baycobuildersandrestoration@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; 24/7 emergency response; free estimate</t>
+  </si>
+  <si>
+    <t>Explain the first-hour mitigation, insurance documentation and rebuild path in calm plain language.</t>
+  </si>
+  <si>
+    <t>First-hour restoration campaign idea for Bayco</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Bayco’s current San Jose restoration pages and think the strongest campaign is the full path after an emergency: ‘Stop the damage first, document what happened, then keep the rebuild moving without starting over.’ I’d turn that into first-hour checklists, insurance FAQs, emergency posts and rebuild follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Bayco-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://baycobuildersandrestoration.com/</t>
+  </si>
+  <si>
     <t>Hertz Electric Inc</t>
   </si>
   <si>
     <t>Electrical / EV / Panel / Battery</t>
   </si>
   <si>
-    <t>San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>Official site crawled Sep 12-13 advertises free estimates, same-day service, EV chargers, panel upgrades, Tesla Powerwall work, active EV/panel promotions and PG&amp;E rebate assistance.</t>
   </si>
   <si>
@@ -112,9 +268,6 @@
     <t>2026-09-13</t>
   </si>
   <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
     <t>1-800 WATER DAMAGE of West San Jose &amp; Sunnyvale</t>
   </si>
   <si>
@@ -187,7 +340,7 @@
     <t>San Jose / South Bay, CA</t>
   </si>
   <si>
-    <t>Official pages crawled Sep 12-13 publish free estimates, fixed-price written scopes, same-day replies during business hours, remodeling, ADUs and additions.</t>
+    <t>Official pages publish free estimates, fixed-price written scopes, same-day replies during business hours, remodeling, ADUs and additions.</t>
   </si>
   <si>
     <t>(408) 667-4946</t>
@@ -217,7 +370,7 @@
     <t>Remodeling / ADU / Additions / New Construction</t>
   </si>
   <si>
-    <t>Official site crawled Sep 12-13 publishes direct email, free estimates, ADU/garage conversion, room and second-story additions, general remodeling and Sunday hours 9 AM-7 PM.</t>
+    <t>Official site publishes direct email, free estimates, ADU/garage conversion, room and second-story additions, general remodeling and Sunday hours 9 AM-7 PM.</t>
   </si>
   <si>
     <t>510-571-0060</t>
@@ -247,7 +400,7 @@
     <t>ADU / Remodeling / Design-Build</t>
   </si>
   <si>
-    <t>Official San Jose ADU pages crawled Sep 11 publish a direct email, free consultation, turnkey design-build service, permitting support and owner-led delivery.</t>
+    <t>Official San Jose ADU pages publish a direct email, free consultation, turnkey design-build service, permitting support and owner-led delivery.</t>
   </si>
   <si>
     <t>(800) 209-0051</t>
@@ -340,7 +493,7 @@
     <t>Sunnyvale / Bay Area, CA</t>
   </si>
   <si>
-    <t>Official financing page crawled Sep 10 publishes free estimates/inspections, financing from $1,000-$100,000, typical Bay Area roof-replacement ranges around $12,000-$40,000 and financing decisions often within minutes.</t>
+    <t>Official financing page publishes free estimates/inspections, financing from $1,000-$100,000, typical Bay Area roof-replacement ranges around $12,000-$40,000 and financing decisions often within minutes.</t>
   </si>
   <si>
     <t>(408) 904-8900</t>
@@ -520,151 +673,13 @@
     <t>https://pylonbuilders.com/home-remodeling-santa-clara</t>
   </si>
   <si>
-    <t>Home Pro Roofing and Solar</t>
-  </si>
-  <si>
-    <t>Roofing / Solar / Battery / EV</t>
-  </si>
-  <si>
-    <t>Current contact page advertises free estimates within 24 hours and offers through Sep 15, 2026, including roof-replacement and roof-plus-solar savings.</t>
-  </si>
-  <si>
-    <t>(800) 650-3134</t>
-  </si>
-  <si>
-    <t>Phone/web form; seven-day availability; Sep 15 deadline</t>
-  </si>
-  <si>
-    <t>Use the Sep 15 roof+solar deadline to explain bundling readiness rather than repeating a discount.</t>
-  </si>
-  <si>
-    <t>Sep 15 roof + solar campaign idea for Home Pro</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Home Pro’s current page and saw the roof and roof-plus-solar offers run through September 15. Campaign angle: ‘If the roof and solar system will live together for years, plan them as one project before installation.’ I’d build roof-readiness posts, solar/battery FAQs and offer follow-ups. $150 flat. Want two Home Pro-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://homeproroofingandsolar.com/contact/</t>
-  </si>
-  <si>
-    <t>Foundation Repair of California</t>
-  </si>
-  <si>
-    <t>Foundation / Concrete / Crawl Space</t>
-  </si>
-  <si>
-    <t>Current San Jose pages advertise free expert inspections, financing and foundation/concrete services.</t>
-  </si>
-  <si>
-    <t>(925) 961-9012</t>
-  </si>
-  <si>
-    <t>Phone/web form; free inspection; financing</t>
-  </si>
-  <si>
-    <t>Build inspection-first education around cracks and settlement without fear-based claims.</t>
-  </si>
-  <si>
-    <t>Foundation inspection decision-flow idea</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed your San Jose pages and think the free inspection can support a stronger campaign than generic foundation-problem advertising. Angle: ‘Start with evidence of what is moving, why, and what actually needs repair.’ I’d build symptom FAQs, inspection-prep posts and estimate follow-ups. $150 flat. Want two business-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.foundationrepairofca.com/service-areas/san-jose-ca/</t>
-  </si>
-  <si>
-    <t>Bentson Window &amp; Door</t>
-  </si>
-  <si>
-    <t>Windows / Doors</t>
-  </si>
-  <si>
-    <t>San Jose / Campbell / Sunnyvale, CA</t>
-  </si>
-  <si>
-    <t>Current official pages publish free in-home estimates, itemized estimates typically within 24 hours and flexible financing for larger replacement projects.</t>
-  </si>
-  <si>
-    <t>(408) 479-7960</t>
-  </si>
-  <si>
-    <t>Phone/web form; 24-hour estimate target; financing</t>
-  </si>
-  <si>
-    <t>Use the itemized 24-hour estimate as the trust hook for multi-window replacement.</t>
-  </si>
-  <si>
-    <t>24-hour window-estimate campaign idea</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Bentson’s current estimate process and noticed you typically provide an itemized estimate within 24 hours. Campaign angle: ‘Before replacing several windows, know the itemized scope, efficiency choices and financing options.’ I’d build comparison FAQs, estimate follow-ups and financing education. $150 flat. Want two Bentson-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://bentsonwindows.com/</t>
-  </si>
-  <si>
-    <t>Atlas Trillo</t>
-  </si>
-  <si>
-    <t>HVAC / Plumbing</t>
-  </si>
-  <si>
-    <t>Current site has September residential offers through Sep 30, including a seasonal HVAC tune-up and qualifying service-repair savings.</t>
-  </si>
-  <si>
-    <t>(408) 444-9511</t>
-  </si>
-  <si>
-    <t>Phone/web form; active Sep 30 offers</t>
-  </si>
-  <si>
-    <t>Use the tune-up as a diagnostic/decision campaign rather than coupon-only advertising.</t>
-  </si>
-  <si>
-    <t>September HVAC tune-up campaign idea for Atlas Trillo</t>
-  </si>
-  <si>
-    <t>Hi — I checked Atlas Trillo’s September offers and saw the seasonal HVAC tune-up and repair savings are live through September 30. Campaign angle: ‘Use the tune-up to learn what actually needs attention before peak heating season.’ I’d build symptom posts, tune-up FAQs and repair follow-ups. $150 flat. Want two examples first?</t>
-  </si>
-  <si>
-    <t>https://www.atlastrillo.com/specials/</t>
-  </si>
-  <si>
-    <t>Rooter Hero Plumbing &amp; Air of San Jose</t>
-  </si>
-  <si>
-    <t>Plumbing / Drain / HVAC</t>
-  </si>
-  <si>
-    <t>Current San Jose pages publish 24/7 service and active September residential promotions including drain/camera-inspection and qualifying repair savings.</t>
-  </si>
-  <si>
-    <t>(408) 703-6715</t>
-  </si>
-  <si>
-    <t>24/7 phone/web; active Sep 30 residential offers</t>
-  </si>
-  <si>
-    <t>Turn drain-camera and repair offers into see-the-problem-before-choosing-the-repair education.</t>
-  </si>
-  <si>
-    <t>Drain-camera decision campaign idea for Rooter Hero</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Rooter Hero San Jose’s September residential offers and think the camera-inspection angle supports a better campaign than discount-only messaging: ‘See what is causing the drain problem before choosing the repair.’ I’d build diagnosis posts, FAQs and service follow-ups. $150 flat. Want two San Jose-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://rooterhero.com/san-jose/</t>
-  </si>
-  <si>
     <t>Home Additions San Jose</t>
   </si>
   <si>
     <t>Home Additions / ADU / Remodeling</t>
   </si>
   <si>
-    <t>Official site crawled today publishes direct email, free itemized on-site estimates, design-build ADUs/additions/second stories, permit handling and Sunday appointments.</t>
+    <t>Official site publishes direct email, free itemized on-site estimates, design-build ADUs/additions/second stories, permit handling and Sunday appointments.</t>
   </si>
   <si>
     <t>info@homeadditionssanjose.com</t>
@@ -679,7 +694,7 @@
     <t>Addition + ADU feasibility campaign idea</t>
   </si>
   <si>
-    <t>Hi — I reviewed Home Additions San Jose today and saw you handle additions, ADUs and second-story projects with design, permits and free itemized estimates. Campaign angle: ‘Before designing a major addition, establish what is feasible, what needs permitting and what the project scope should include.’ I’d build feasibility FAQs and estimate follow-ups. $150 flat. Want two examples first?</t>
+    <t>Hi — I reviewed Home Additions San Jose and saw you handle additions, ADUs and second-story projects with design, permits and free itemized estimates. Campaign angle: ‘Before designing a major addition, establish what is feasible, what needs permitting and what the project scope should include.’ I’d build feasibility FAQs and estimate follow-ups. $150 flat. Want two examples first?</t>
   </si>
   <si>
     <t>https://www.homeadditionssanjose.com/</t>
@@ -1903,34 +1918,34 @@
         <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
@@ -1944,10 +1959,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>17</v>
@@ -1956,28 +1971,28 @@
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>27</v>
@@ -1991,40 +2006,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>27</v>
@@ -2038,10 +2053,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>17</v>
@@ -2050,28 +2065,28 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -2085,10 +2100,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>17</v>
@@ -2097,31 +2112,31 @@
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -2132,13 +2147,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
@@ -2153,22 +2168,22 @@
         <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -2179,13 +2194,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
@@ -2215,7 +2230,7 @@
         <v>100</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -2262,7 +2277,7 @@
         <v>111</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -2279,37 +2294,37 @@
         <v>113</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="N11" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -2320,43 +2335,43 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="N12" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -2367,43 +2382,43 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="L13" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="N13" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>28</v>
@@ -2414,43 +2429,43 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="N14" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -2461,43 +2476,43 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="M15" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="N15" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -2508,13 +2523,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>18</v>
@@ -2525,24 +2540,26 @@
       <c r="G16" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="H16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>168</v>
+      </c>
       <c r="I16" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -2553,41 +2570,43 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>17</v>
+        <v>177</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H17" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="I17" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -2598,41 +2617,43 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="H18" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="I18" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -2643,41 +2664,43 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="H19" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="I19" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -2688,41 +2711,43 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>92</v>
+        <v>154</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="H20" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="I20" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -2733,41 +2758,41 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -2819,142 +2844,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -2988,58 +3013,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -3068,9 +3093,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
-        <v>276</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
         <v>27</v>
@@ -3090,7 +3113,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3108,15 +3131,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="2"/>
-      <c r="N3" s="2" t="s">
-        <v>276</v>
-      </c>
+      <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R3" s="3">
         <v>150</v>
@@ -3124,13 +3145,13 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3148,15 +3169,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="2"/>
-      <c r="N4" s="2" t="s">
-        <v>276</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R4" s="3">
         <v>150</v>
@@ -3164,13 +3183,13 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -3188,15 +3207,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="2"/>
-      <c r="N5" s="2" t="s">
-        <v>276</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R5" s="3">
         <v>150</v>
@@ -3204,13 +3221,13 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3234,7 +3251,7 @@
         <v>27</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R6" s="3">
         <v>150</v>
@@ -3242,13 +3259,13 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3266,13 +3283,15 @@
         <v>0</v>
       </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+      <c r="N7" s="2" t="s">
+        <v>281</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -3280,7 +3299,7 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
@@ -3304,13 +3323,15 @@
         <v>0</v>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>281</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="R8" s="3">
         <v>150</v>
@@ -3318,7 +3339,7 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
@@ -3343,11 +3364,11 @@
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>100</v>
@@ -3383,11 +3404,11 @@
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>111</v>
@@ -3404,7 +3425,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3422,15 +3443,13 @@
         <v>0</v>
       </c>
       <c r="M11" s="2"/>
-      <c r="N11" s="2" t="s">
-        <v>276</v>
-      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R11" s="3">
         <v>150</v>
@@ -3438,13 +3457,13 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B12" s="2">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -3462,15 +3481,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="2"/>
-      <c r="N12" s="2" t="s">
-        <v>276</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R12" s="3">
         <v>150</v>
@@ -3478,13 +3495,13 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B13" s="2">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -3502,15 +3519,13 @@
         <v>0</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="N13" s="2" t="s">
-        <v>276</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="R13" s="3">
         <v>150</v>
@@ -3518,13 +3533,13 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B14" s="2">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -3543,14 +3558,14 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="R14" s="3">
         <v>150</v>
@@ -3558,13 +3573,13 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B15" s="2">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -3583,14 +3598,14 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R15" s="3">
         <v>150</v>
@@ -3598,13 +3613,13 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B16" s="2">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -3623,14 +3638,14 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R16" s="3">
         <v>150</v>
@@ -3638,13 +3653,13 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B17" s="2">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -3663,14 +3678,14 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="R17" s="3">
         <v>150</v>
@@ -3678,13 +3693,13 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B18" s="2">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -3703,14 +3718,14 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="R18" s="3">
         <v>150</v>
@@ -3718,13 +3733,13 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B19" s="2">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -3743,14 +3758,14 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="R19" s="3">
         <v>150</v>
@@ -3758,13 +3773,13 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B20" s="2">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -3783,14 +3798,14 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="R20" s="3">
         <v>150</v>
@@ -3798,13 +3813,13 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B21" s="2">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -3823,14 +3838,14 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="R21" s="3">
         <v>150</v>
@@ -3838,28 +3853,28 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3869,7 +3884,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3880,32 +3895,32 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3915,7 +3930,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3926,26 +3941,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3955,7 +3970,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3966,26 +3981,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -3995,7 +4010,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -4006,26 +4021,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -4035,7 +4050,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -4046,26 +4061,26 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -4075,7 +4090,7 @@
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -4086,26 +4101,26 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
@@ -4115,7 +4130,7 @@
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -4126,26 +4141,26 @@
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -4155,7 +4170,7 @@
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -4166,26 +4181,26 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K30" s="3">
         <v>0</v>
@@ -4195,7 +4210,7 @@
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -4206,26 +4221,26 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K31" s="3">
         <v>0</v>
@@ -4235,7 +4250,7 @@
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -4246,28 +4261,28 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -4277,7 +4292,7 @@
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -4288,26 +4303,26 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -4317,7 +4332,7 @@
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -4328,26 +4343,26 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -4357,7 +4372,7 @@
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -4368,26 +4383,26 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -4397,7 +4412,7 @@
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -4408,26 +4423,26 @@
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K36" s="3">
         <v>0</v>
@@ -4437,7 +4452,7 @@
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -4511,67 +4526,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -4580,13 +4595,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -4594,10 +4609,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -4606,13 +4621,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -4620,10 +4635,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -4632,28 +4647,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -4662,13 +4677,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -4676,10 +4691,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -4688,13 +4703,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -4702,10 +4717,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -4714,13 +4729,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -4728,10 +4743,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -4740,28 +4755,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -4770,13 +4785,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -4784,10 +4799,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -4796,13 +4811,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -4810,10 +4825,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -4822,13 +4837,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -4836,10 +4851,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -4848,13 +4863,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -4862,10 +4877,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -4874,13 +4889,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -4888,10 +4903,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -4900,13 +4915,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -4914,10 +4929,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -4926,13 +4941,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -4940,10 +4955,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -4952,13 +4967,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -4966,10 +4981,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -5001,33 +5016,33 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -5041,16 +5056,16 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -5064,14 +5079,14 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -5085,20 +5100,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -5108,16 +5123,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
@@ -5131,14 +5146,14 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -5152,14 +5167,14 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
@@ -5173,14 +5188,14 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
@@ -5194,14 +5209,14 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -5215,16 +5230,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
@@ -5238,14 +5253,14 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>28</v>
@@ -5259,14 +5274,14 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>28</v>
@@ -5280,14 +5295,14 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>28</v>
@@ -5301,16 +5316,16 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>28</v>
@@ -5324,14 +5339,14 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>28</v>
@@ -5345,14 +5360,14 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>28</v>
@@ -5366,14 +5381,14 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>28</v>
@@ -5387,16 +5402,16 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>28</v>
@@ -5410,16 +5425,16 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>28</v>
@@ -5433,16 +5448,16 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>28</v>
@@ -5456,16 +5471,16 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>28</v>
@@ -5479,11 +5494,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -5515,13 +5530,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5541,7 +5556,7 @@
         <v>21</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5549,124 +5564,124 @@
         <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>93</v>
@@ -5675,13 +5690,13 @@
         <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>95</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -5695,13 +5710,13 @@
         <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>106</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -5709,219 +5724,219 @@
         <v>112</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -5966,7 +5981,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5976,20 +5991,20 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6001,95 +6016,95 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -6115,98 +6130,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -6225,19 +6240,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -6254,7 +6269,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -18,15 +18,15 @@
     <sheet name="Refresh Log" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'New Lead Queue'!$A$1:$O$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Pipeline!$A$1:$R$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'New Lead Queue'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Pipeline!$A$1:$R$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="330">
   <si>
     <t>Rank</t>
   </si>
@@ -73,19 +73,118 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Amex Roofing</t>
+  </si>
+  <si>
+    <t>Roofing / Repair / Replacement / Inspection</t>
+  </si>
+  <si>
+    <t>San Jose / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Official site crawled within two weeks publishes a direct email, free roof inspections, written estimates, project photos, a public license record and 300+ permitted projects referenced through BuildZoom.</t>
+  </si>
+  <si>
+    <t>(510) 761-8120</t>
+  </si>
+  <si>
+    <t>amexroofingca@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free inspection; written quote</t>
+  </si>
+  <si>
+    <t>Turn inspect-first documentation, written scope and completed-project photos into a proof-before-purchase campaign.</t>
+  </si>
+  <si>
+    <t>Proof-before-purchase roofing campaign idea for Amex</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Amex Roofing’s current site and noticed you already have the ingredients for a strong trust campaign: free inspection, written scope, clear pricing and completed-project photos. Campaign angle: ‘Inspect it. Put the scope in writing. See the work before you decide.’ I’d turn that into inspection posts, repair-vs-replacement FAQs, estimate follow-ups and project-proof content. Same-Day Customer Growth Pack: $150 flat. Want two Amex-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://amex-roofing.com/</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>Valle Construction</t>
+  </si>
+  <si>
+    <t>Remodeling / ADU / Kitchen / Bathroom</t>
+  </si>
+  <si>
+    <t>San Jose / Santa Clara County, CA</t>
+  </si>
+  <si>
+    <t>Official San Jose page crawled Sep 13 publishes direct email, free estimates, ADU/kitchen/bath remodeling, local permit-process familiarity and a stated response within one business day.</t>
+  </si>
+  <si>
+    <t>(669) 225-3277</t>
+  </si>
+  <si>
+    <t>info@valle.construction</t>
+  </si>
+  <si>
+    <t>Direct email; one-business-day response; free estimate</t>
+  </si>
+  <si>
+    <t>Turn San Jose permit familiarity and project feasibility into a pre-estimate planning funnel for ADUs and remodels.</t>
+  </si>
+  <si>
+    <t>San Jose permit-to-estimate campaign idea for Valle</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Valle Construction’s San Jose page and noticed a useful marketing advantage: you handle ADUs and remodels while already understanding the local permit process. Campaign angle: ‘Before choosing finishes, know what the project can realistically permit, require and cost.’ I’d turn that into permit FAQs, ADU/remodel planning posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Valle-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://valle.construction/services/san-jose</t>
+  </si>
+  <si>
+    <t>California Bay Roofing Inc</t>
+  </si>
+  <si>
+    <t>Residential / Commercial Roofing / Gutters</t>
+  </si>
+  <si>
+    <t>Official San Jose page crawled Sep 14 publishes two direct email addresses, a free inspection, residential and commercial roofing, flat-roof systems, coatings and seamless-gutter work.</t>
+  </si>
+  <si>
+    <t>(415) 684-4498</t>
+  </si>
+  <si>
+    <t>californiabayroofinginc@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free inspection</t>
+  </si>
+  <si>
+    <t>Use roof-system diagnosis across shingles, flat roofs, coatings and drainage to create a repair-path decision campaign instead of generic replacement advertising.</t>
+  </si>
+  <si>
+    <t>Roof-system diagnosis campaign idea for California Bay Roofing</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed California Bay Roofing’s San Jose services and noticed you work across shingles, flat roofs, coatings and seamless gutters. That supports a stronger campaign than generic roof replacement: ‘Find where the roof system is actually failing before choosing the repair.’ I’d build inspection posts, repair-path FAQs, drainage content and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two California Bay Roofing-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.californiabayroofinginc.net/san-jose-roofing</t>
+  </si>
+  <si>
     <t>RCK Development</t>
   </si>
   <si>
     <t>Remodeling / ADU / Additions / HVAC / Plumbing</t>
   </si>
   <si>
-    <t>San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Official site crawled Sep 14 publishes direct email, free estimates, same-day message response, realistic estimate/timeline promises, permit coordination and high-ticket remodel/ADU work.</t>
+    <t>Previously verified Sep 14 with direct email, free estimates, realistic estimate/timeline positioning, permit coordination and high-ticket remodel/ADU work.</t>
   </si>
   <si>
     <t>(408) 982-7586</t>
@@ -112,16 +211,13 @@
     <t>2026-09-14</t>
   </si>
   <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
     <t>Fox Electric</t>
   </si>
   <si>
     <t>Electrical / EV Charger / Panel Upgrade</t>
   </si>
   <si>
-    <t>Current San Jose EV page advertises free on-site estimates, a 2-hour quote response, same-day availability, written fixed pricing, permit handling, PG&amp;E coordination and panel/load-management options.</t>
+    <t>Official San Jose panel page re-crawled Sep 11 publishes direct email, free on-site estimates, panel upgrades, EV charging and licensed C-10 service.</t>
   </si>
   <si>
     <t>(650) 550-0719</t>
@@ -130,79 +226,49 @@
     <t>info@foxelectrician.com</t>
   </si>
   <si>
-    <t>Direct email; 2-hour quote response; same-day slots</t>
-  </si>
-  <si>
-    <t>Use EV load calculation and panel-readiness education to prevent unnecessary upgrades and make the estimate feel trustworthy.</t>
-  </si>
-  <si>
-    <t>2-hour EV + panel readiness campaign idea for Fox Electric</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Fox Electric’s San Jose EV page and the strongest marketing angle may be that you check whether a home actually needs a panel upgrade before selling one. Campaign idea: ‘Before upgrading the panel, calculate what the home and charger really require.’ I’d turn that into EV-readiness FAQs, load-management education, permit/PG&amp;E posts and estimate follow-ups. $150 flat. Want two Fox-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://foxelectrician.com/services/ev-charger-installation/san-jose/</t>
-  </si>
-  <si>
-    <t>EMC Remodels</t>
-  </si>
-  <si>
-    <t>Remodeling / ADU / Additions / Structural</t>
-  </si>
-  <si>
-    <t>Official site crawled Sep 14 publishes direct estimate email, free estimates, detailed proposals, ADUs/additions, structural and seismic work, permit experience and response within one business day.</t>
-  </si>
-  <si>
-    <t>(510) 650-5555</t>
-  </si>
-  <si>
-    <t>estimates@emcremodels.com</t>
-  </si>
-  <si>
-    <t>Direct estimates email; response within one business day</t>
-  </si>
-  <si>
-    <t>Turn project type, budget, structural risk and permitting into an estimate-readiness campaign.</t>
-  </si>
-  <si>
-    <t>Estimate-readiness campaign idea for EMC Remodels</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed EMC Remodels’ current estimate flow and noticed you already ask the questions that determine whether a project is ready to move: scope, budget, start timing and structural needs. I’d turn that into an ‘Is your remodel or ADU ready for an estimate?’ campaign with permit FAQs, structural-risk education and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two EMC-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.emcremodels.com/</t>
-  </si>
-  <si>
-    <t>Primework Construction</t>
-  </si>
-  <si>
-    <t>Remodeling / Renovation / Design-Build</t>
-  </si>
-  <si>
-    <t>Current official pages publish direct email, free quotes, 24/7 service hours, full-house/kitchen/bath/exterior renovation and a design-build process with budget proposals and timelines.</t>
-  </si>
-  <si>
-    <t>669-345-7070</t>
-  </si>
-  <si>
-    <t>info@primeworkconstructionca.com</t>
-  </si>
-  <si>
-    <t>Direct email; 24/7 listed service hours; free quote</t>
-  </si>
-  <si>
-    <t>Use design-first planning, budget breakdown and timeline clarity to reduce fear of change orders and renovation uncertainty.</t>
-  </si>
-  <si>
-    <t>Design-to-budget campaign idea for Primework Construction</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Primework Construction’s current process and noticed a strong decision-making story: design first, then a detailed budget proposal and timeline before the renovation moves forward. I’d turn that into planning posts, ‘avoid costly change-order’ FAQs and free-quote follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Primework-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://primeworkconstructionca.com/</t>
+    <t>Direct email; free on-site estimate</t>
+  </si>
+  <si>
+    <t>Use load calculation and panel-readiness education to make EV/panel estimates more trustworthy.</t>
+  </si>
+  <si>
+    <t>EV + panel readiness campaign idea for Fox Electric</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Fox Electric’s San Jose panel and EV services and think the strongest customer question is simple: ‘Does this home actually need a panel upgrade for the next electrical load?’ I’d turn that into EV-readiness FAQs, load-management education, permit posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Fox-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://foxelectrician.com/services/panel-upgrade/san-jose/</t>
+  </si>
+  <si>
+    <t>Hertz Electric Inc</t>
+  </si>
+  <si>
+    <t>Electrical / EV / Panel / Battery</t>
+  </si>
+  <si>
+    <t>Official site crawled today publishes direct email, same-day/emergency service, free estimates, EV charger and panel work, and PG&amp;E rebate/incentive assistance.</t>
+  </si>
+  <si>
+    <t>(415) 676-0598</t>
+  </si>
+  <si>
+    <t>arash@thehertzelectric.com</t>
+  </si>
+  <si>
+    <t>Direct email; same-day service; free estimate</t>
+  </si>
+  <si>
+    <t>Turn EV charger readiness plus rebate navigation into a fast, high-intent estimate funnel.</t>
+  </si>
+  <si>
+    <t>Same-day EV + rebate campaign idea for Hertz Electric</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Hertz Electric’s current San Jose page today and saw you combine same-day service, EV charger expertise, panel work and PG&amp;E rebate guidance. Campaign angle: ‘Before installing the charger, know whether the panel is ready and which incentives may reduce the project cost.’ I’d turn that into readiness FAQs, rebate explainer posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Hertz-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://thehertzelectric.com/</t>
   </si>
   <si>
     <t>Bayco Builders &amp; Restoration</t>
@@ -211,7 +277,7 @@
     <t>Water / Fire / Mold / Sewage / Remodeling</t>
   </si>
   <si>
-    <t>Official site crawled Sep 14 publishes direct email, 24/7 emergency response, IICRC-certified restoration, insurance coordination, free estimates and mitigation-to-remodel/rebuild capability.</t>
+    <t>Official site reverified this week with direct email, 24/7 emergency response and restoration-to-rebuild positioning.</t>
   </si>
   <si>
     <t>(669) 770-5373</t>
@@ -220,85 +286,49 @@
     <t>baycobuildersandrestoration@gmail.com</t>
   </si>
   <si>
-    <t>Direct email; 24/7 emergency response; free estimate</t>
-  </si>
-  <si>
-    <t>Explain the first-hour mitigation, insurance documentation and rebuild path in calm plain language.</t>
+    <t>Direct email; 24/7 emergency response</t>
+  </si>
+  <si>
+    <t>Explain first-hour mitigation and the rebuild path in calm plain language.</t>
   </si>
   <si>
     <t>First-hour restoration campaign idea for Bayco</t>
   </si>
   <si>
-    <t>Hi — I reviewed Bayco’s current San Jose restoration pages and think the strongest campaign is the full path after an emergency: ‘Stop the damage first, document what happened, then keep the rebuild moving without starting over.’ I’d turn that into first-hour checklists, insurance FAQs, emergency posts and rebuild follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Bayco-specific examples first?</t>
+    <t>Hi — I reviewed Bayco’s current restoration pages and think the strongest campaign is the full path after an emergency: ‘Stop the damage first, document what happened, then keep the rebuild moving without starting over.’ I’d turn that into first-hour checklists, insurance FAQs, emergency posts and rebuild follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Bayco-specific examples first?</t>
   </si>
   <si>
     <t>https://baycobuildersandrestoration.com/</t>
   </si>
   <si>
-    <t>Hertz Electric Inc</t>
-  </si>
-  <si>
-    <t>Electrical / EV / Panel / Battery</t>
-  </si>
-  <si>
-    <t>Official site crawled Sep 12-13 advertises free estimates, same-day service, EV chargers, panel upgrades, Tesla Powerwall work, active EV/panel promotions and PG&amp;E rebate assistance.</t>
-  </si>
-  <si>
-    <t>(415) 676-0598</t>
-  </si>
-  <si>
-    <t>arash@thehertzelectric.com</t>
-  </si>
-  <si>
-    <t>Direct email; same-day/emergency service</t>
-  </si>
-  <si>
-    <t>Turn panel capacity, EV charging and rebate navigation into an electrical-readiness decision funnel.</t>
-  </si>
-  <si>
-    <t>EV + panel readiness campaign idea for Hertz Electric</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Hertz Electric’s current San Jose pages and saw you combine EV chargers, panel upgrades, Powerwall work, free estimates and rebate guidance. Campaign angle: ‘Before adding an EV charger or battery, make sure the electrical system underneath it is ready — and know which incentives may apply.’ I’d turn that into readiness FAQs, rebate explainer posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Hertz-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://thehertzelectric.com/</t>
-  </si>
-  <si>
-    <t>2026-09-13</t>
-  </si>
-  <si>
-    <t>1-800 WATER DAMAGE of West San Jose &amp; Sunnyvale</t>
-  </si>
-  <si>
-    <t>Water / Fire / Mold / Sewage Restoration</t>
-  </si>
-  <si>
-    <t>West San Jose / Sunnyvale, CA</t>
-  </si>
-  <si>
-    <t>Current local franchise content publishes direct local email, 24/7 emergency service, residential/commercial restoration and a mitigation-to-reconstruction workflow.</t>
-  </si>
-  <si>
-    <t>(408) 834-7773</t>
-  </si>
-  <si>
-    <t>Murali.Sridharane@1800waterdamage.com</t>
-  </si>
-  <si>
-    <t>Direct local email; 24/7 emergency business</t>
-  </si>
-  <si>
-    <t>Market first-hour mitigation plus documentation and reconstruction as one calm recovery path.</t>
-  </si>
-  <si>
-    <t>First-hour restoration campaign idea for 1-800 WATER DAMAGE</t>
-  </si>
-  <si>
-    <t>Hi Murali — I reviewed the West San Jose / Sunnyvale restoration content and saw your local team handles water, fire, mold and sewage emergencies around the clock. Campaign angle: ‘The first hour is about stopping the damage and documenting what happens next.’ I’d turn that into emergency checklists, homeowner FAQs and insurance/reconstruction follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two location-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.1800waterdamage.com/west-jose-sunnyvale/</t>
+    <t>Shefer Builder</t>
+  </si>
+  <si>
+    <t>Remodeling / ADU / Additions / New Construction</t>
+  </si>
+  <si>
+    <t>Official contact page reverified this week publishes direct email, free estimates, ADU/garage conversion, room additions and seven-day hours.</t>
+  </si>
+  <si>
+    <t>510-571-0060</t>
+  </si>
+  <si>
+    <t>sheferbuilder@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; seven-day hours; free estimate</t>
+  </si>
+  <si>
+    <t>Use one-contractor continuity across remodel, ADU and addition work to simplify a complex project decision.</t>
+  </si>
+  <si>
+    <t>ADU + addition decision-flow idea for Shefer Builder</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Shefer Builder’s current services and saw you handle remodeling, ADUs, garage conversions and room additions. Campaign angle: ‘Before choosing finishes, make the project path — scope, added space and build sequence — easy to understand.’ I’d turn that into ADU/addition FAQs, planning posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Shefer-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://sheferbuilder.com/contact-us/</t>
   </si>
   <si>
     <t>Ozone Service</t>
@@ -307,28 +337,28 @@
     <t>HVAC / Electrical / Panel / EV</t>
   </si>
   <si>
-    <t>Current official pages publish 24/7 service, free estimates/diagnostics, written scope and price, panel upgrades, EV chargers, heat pumps, financing and rebate assistance.</t>
-  </si>
-  <si>
-    <t>(669) 323-7077</t>
-  </si>
-  <si>
-    <t>go@serviceozone.com</t>
-  </si>
-  <si>
-    <t>Direct email; 24/7 service; free estimate</t>
-  </si>
-  <si>
-    <t>Make written scope, rebates and cross-trade HVAC/electrical readiness the trust campaign.</t>
-  </si>
-  <si>
-    <t>Written-scope + rebate campaign idea for Ozone Service</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Ozone Service’s current pages and noticed you already solve several objections: free diagnostics, written scope before work, financing and rebate support across HVAC and electrical upgrades. I’d turn that into upgrade-readiness posts, rebate FAQs and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Ozone-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://serviceozone.com/</t>
+    <t>Official HVAC/electrical page reverified this week publishes direct email, free estimate, written scope/price, panel upgrades, EV chargers and heat pumps handled under one licensed team.</t>
+  </si>
+  <si>
+    <t>(310) 743-3364</t>
+  </si>
+  <si>
+    <t>info@serviceozone.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; 24/7 phone</t>
+  </si>
+  <si>
+    <t>Market one-team HVAC/electrical coordination for electrification projects that otherwise require multiple contractors.</t>
+  </si>
+  <si>
+    <t>One-team heat-pump + electrical campaign idea for Ozone</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Ozone’s current HVAC and electrical page and noticed a strong coordination angle: heat pumps, panel upgrades and EV charging can stay with one licensed team instead of being split between contractors. I’d turn that into electrification-readiness FAQs, scope explainers and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Ozone-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://serviceozone.com/ozone-hvac-electrical/</t>
   </si>
   <si>
     <t>Silicon Valley Building Service and Repair</t>
@@ -340,7 +370,7 @@
     <t>San Jose / South Bay, CA</t>
   </si>
   <si>
-    <t>Official pages publish free estimates, fixed-price written scopes, same-day replies during business hours, remodeling, ADUs and additions.</t>
+    <t>Previously verified official pages publish free estimates, fixed-price written scopes, same-day replies during business hours, remodeling, ADUs and additions.</t>
   </si>
   <si>
     <t>(408) 667-4946</t>
@@ -358,346 +388,10 @@
     <t>Fixed-price remodeling decision-flow idea for SVBSR</t>
   </si>
   <si>
-    <t>Hi — I reviewed SVBSR’s current process and noticed a strong trust angle: free estimate, written scope and fixed price before the work starts. Campaign idea: ‘Before committing to a remodel or ADU, make the scope and price understandable.’ I’d build planning FAQs, ADU/remodel posts and estimate follow-ups. $150 flat. Want two SVBSR-specific examples first?</t>
+    <t>Hi — I reviewed SVBSR’s current process and noticed a strong trust angle: free estimate, written scope and fixed price before the work starts. Campaign idea: ‘Before committing to a remodel or ADU, make the scope and price understandable.’ I’d build planning FAQs, ADU/remodel posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two SVBSR-specific examples first?</t>
   </si>
   <si>
     <t>https://siliconvalleybuilding.com/</t>
-  </si>
-  <si>
-    <t>Shefer Builder</t>
-  </si>
-  <si>
-    <t>Remodeling / ADU / Additions / New Construction</t>
-  </si>
-  <si>
-    <t>Official site publishes direct email, free estimates, ADU/garage conversion, room and second-story additions, general remodeling and Sunday hours 9 AM-7 PM.</t>
-  </si>
-  <si>
-    <t>510-571-0060</t>
-  </si>
-  <si>
-    <t>sheferbuilder@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; open Sunday; free estimate</t>
-  </si>
-  <si>
-    <t>Use one-contractor continuity across remodel, ADU and addition work to simplify a complex project decision.</t>
-  </si>
-  <si>
-    <t>ADU + addition decision-flow idea for Shefer Builder</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Shefer Builder’s current services and saw you handle remodeling, ADUs, garage conversions and room/second-story additions. Campaign angle: ‘Before choosing finishes, make the project path — scope, added space and build sequence — easy to understand.’ I’d turn that into ADU/addition FAQs, project-planning posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Shefer-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://sheferbuilder.com/</t>
-  </si>
-  <si>
-    <t>California Bay Builders &amp; Remodeling</t>
-  </si>
-  <si>
-    <t>ADU / Remodeling / Design-Build</t>
-  </si>
-  <si>
-    <t>Official San Jose ADU pages publish a direct email, free consultation, turnkey design-build service, permitting support and owner-led delivery.</t>
-  </si>
-  <si>
-    <t>(800) 209-0051</t>
-  </si>
-  <si>
-    <t>info@californiabaybuildersandremodeling.com</t>
-  </si>
-  <si>
-    <t>Direct email; free consultation</t>
-  </si>
-  <si>
-    <t>Turn lot feasibility, permitting and turnkey delivery into a pre-design decision funnel.</t>
-  </si>
-  <si>
-    <t>San Jose ADU feasibility campaign idea</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed your San Jose ADU pages and noticed the free consultation already answers the right first question: what can actually be built on this lot before the owner spends money on design. I’d turn that into feasibility FAQs, permit/process posts and consultation follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two California Bay Builders-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://californiabaybuildersandremodeling.com/adu-builder-san-jose/</t>
-  </si>
-  <si>
-    <t>Atra Construction</t>
-  </si>
-  <si>
-    <t>ADU / Design / Construction Management</t>
-  </si>
-  <si>
-    <t>Current official site publishes direct email, free ADU consultations, design options, permit/concept planning and construction management for Bay Area ADU projects.</t>
-  </si>
-  <si>
-    <t>925-238-3141</t>
-  </si>
-  <si>
-    <t>info@atraconstruction.com</t>
-  </si>
-  <si>
-    <t>Use concept-to-permit-to-build continuity to reduce uncertainty before an ADU project begins.</t>
-  </si>
-  <si>
-    <t>Concept-to-build ADU campaign idea for Atra</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Atra Construction’s current ADU process and saw a strong customer story in the sequence itself: free consultation, design options, permit planning and construction management. I’d turn that into feasibility FAQs, project-stage posts and consultation follow-ups so prospects understand the path before committing. Same-Day Customer Growth Pack: $150 flat. Want two Atra-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.atraconstruction.com/</t>
-  </si>
-  <si>
-    <t>South San Jose Electric</t>
-  </si>
-  <si>
-    <t>Residential / Commercial Electrical</t>
-  </si>
-  <si>
-    <t>San Jose, CA</t>
-  </si>
-  <si>
-    <t>Current official site publishes direct email, free estimates, Monday-Sunday availability and high-value panel upgrades, rewiring and EV charger work.</t>
-  </si>
-  <si>
-    <t>(669) 371-5273</t>
-  </si>
-  <si>
-    <t>contact@southsanjoseelectric.com</t>
-  </si>
-  <si>
-    <t>Direct email; seven-day availability; free estimate</t>
-  </si>
-  <si>
-    <t>Build an electrical-capacity readiness campaign around panels, rewiring and EV additions.</t>
-  </si>
-  <si>
-    <t>Electrical-capacity campaign idea for South San Jose Electric</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed South San Jose Electric’s current services. Panel upgrades, rewiring and EV chargers all answer the same question: ‘Is the electrical system ready for what I want to add next?’ I’d turn that into capacity-readiness posts, FAQs and estimate follow-ups. $150 flat. Want two business-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://southsanjoseelectric.com/</t>
-  </si>
-  <si>
-    <t>RoofCraft Inc</t>
-  </si>
-  <si>
-    <t>Roofing</t>
-  </si>
-  <si>
-    <t>Sunnyvale / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official financing page publishes free estimates/inspections, financing from $1,000-$100,000, typical Bay Area roof-replacement ranges around $12,000-$40,000 and financing decisions often within minutes.</t>
-  </si>
-  <si>
-    <t>(408) 904-8900</t>
-  </si>
-  <si>
-    <t>info@roofcraftcompany.com</t>
-  </si>
-  <si>
-    <t>Direct email; high-ticket roofing; financing</t>
-  </si>
-  <si>
-    <t>Use inspection, realistic project ranges and financing education to reduce replacement uncertainty.</t>
-  </si>
-  <si>
-    <t>High-ticket roof decision campaign idea for RoofCraft</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed RoofCraft’s current financing information. Publishing inspection guidance, realistic replacement ranges and financing options creates a strong trust angle: ‘Understand the roof condition, project range and payment options before committing.’ I’d build inspection posts, repair-vs-replacement FAQs and estimate follow-ups. $150 flat. Want two RoofCraft-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://roofcraftcompany.com/financing/</t>
-  </si>
-  <si>
-    <t>SERVPRO of Mountain View, Los Altos</t>
-  </si>
-  <si>
-    <t>Water / Fire / Mold / Storm / Construction</t>
-  </si>
-  <si>
-    <t>Sunnyvale / Mountain View / Los Altos, CA</t>
-  </si>
-  <si>
-    <t>Local SERVPRO pages publish 24/7 emergency restoration, construction and commercial services, a Sunnyvale office and a direct office email.</t>
-  </si>
-  <si>
-    <t>(650) 770-2992</t>
-  </si>
-  <si>
-    <t>office@SERVPROmtview.com</t>
-  </si>
-  <si>
-    <t>Direct office email; 24/7 emergency service</t>
-  </si>
-  <si>
-    <t>Explain mitigation-to-reconstruction continuity and commercial response in plain language.</t>
-  </si>
-  <si>
-    <t>Mitigation-to-rebuild campaign idea for SERVPRO Mountain View</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed your local SERVPRO services and noticed the team handles emergency mitigation, commercial losses and reconstruction. Campaign angle: ‘Stop the damage first, then keep recovery moving without making the customer restart the process.’ I’d build first-hour checklists, commercial-response posts and reconstruction FAQs. $150 flat. Want two local examples first?</t>
-  </si>
-  <si>
-    <t>https://www.servpromountainviewlosaltos.com/</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>Courtesy Electric</t>
-  </si>
-  <si>
-    <t>Electrical / Remodel / Service Upgrades</t>
-  </si>
-  <si>
-    <t>Sunnyvale / South Bay, CA</t>
-  </si>
-  <si>
-    <t>Official site publishes owner-operated electrical service, free estimates, new construction, remodeling, service upgrades and a direct business email.</t>
-  </si>
-  <si>
-    <t>(408) 509-1017</t>
-  </si>
-  <si>
-    <t>mike@courtesyelectric.us</t>
-  </si>
-  <si>
-    <t>Direct owner/business email; free estimate</t>
-  </si>
-  <si>
-    <t>Use owner-operated accountability plus upgrade/remodel scope clarity.</t>
-  </si>
-  <si>
-    <t>Service-upgrade campaign idea for Courtesy Electric</t>
-  </si>
-  <si>
-    <t>Hi Mike — I reviewed Courtesy Electric’s current services and think the owner-operated positioning can do more work in the marketing. Campaign angle: ‘For a remodel or service upgrade, know who is responsible for the electrical scope from estimate through completion.’ I’d build upgrade FAQs, remodel posts and estimate follow-ups. $150 flat. Want two Courtesy-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://courtesyelectric.us/</t>
-  </si>
-  <si>
-    <t>408 Builders Inc</t>
-  </si>
-  <si>
-    <t>Remodeling / ADU / New Construction</t>
-  </si>
-  <si>
-    <t>Official pages publish kitchen/bath remodeling, ADUs and new-home construction, free on-site estimates, detailed proposals and a stated reply within one business day.</t>
-  </si>
-  <si>
-    <t>(408) 609-1643</t>
-  </si>
-  <si>
-    <t>info@408buildersinc.com</t>
-  </si>
-  <si>
-    <t>Direct email; reply within one business day; free estimate</t>
-  </si>
-  <si>
-    <t>Build a consultation-to-detailed-proposal funnel for high-ticket ADU/remodel leads.</t>
-  </si>
-  <si>
-    <t>ADU + remodeling proposal-funnel idea for 408 Builders</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed 408 Builders’ current process and noticed you already give prospects a useful path: free on-site estimate followed by a detailed proposal. I’d turn that into ADU FAQs, project-planning posts and consultation follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two 408 Builders-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://408buildersinc.com/</t>
-  </si>
-  <si>
-    <t>AYH Remodeling &amp; Construction Inc</t>
-  </si>
-  <si>
-    <t>Current site publishes free estimates, remodeling, ADUs/additions, structural and permit services, a direct email and Monday-Saturday 7 AM-7 PM hours.</t>
-  </si>
-  <si>
-    <t>833-408-5179</t>
-  </si>
-  <si>
-    <t>ayhremodelingandconstruction@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; Mon-Sat; free estimate</t>
-  </si>
-  <si>
-    <t>Use permit, structural and build coordination to simplify the ADU/addition decision.</t>
-  </si>
-  <si>
-    <t>ADU permit-to-build campaign idea for AYH</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed AYH’s current services and noticed you cover the parts homeowners often find most confusing on an ADU or addition: structural work, permits and construction. I’d turn that into ADU FAQs, permit/process posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two AYH-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://ayhremodeling.com/</t>
-  </si>
-  <si>
-    <t>Pylon Builders</t>
-  </si>
-  <si>
-    <t>Remodeling / ADU / Design-Build</t>
-  </si>
-  <si>
-    <t>Current pages publish high-ticket 2024-2026 remodeling/ADU ranges, free in-home consultations and a fixed-price proposal process.</t>
-  </si>
-  <si>
-    <t>(650) 800-9755</t>
-  </si>
-  <si>
-    <t>info@pylonbuilders.com</t>
-  </si>
-  <si>
-    <t>Direct email; free in-home consultation</t>
-  </si>
-  <si>
-    <t>Turn current local project ranges into consultation-driving budget education.</t>
-  </si>
-  <si>
-    <t>Bay Area ADU budget campaign idea for Pylon Builders</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Pylon Builders’ current remodeling/ADU information and saw you publish realistic local project ranges alongside a free in-home consultation. Campaign angle: ‘Use planning ranges to decide what is feasible before committing to design.’ I’d build cost/feasibility posts, ADU FAQs and consultation follow-ups. $150 flat. Want two Pylon-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://pylonbuilders.com/home-remodeling-santa-clara</t>
-  </si>
-  <si>
-    <t>Home Additions San Jose</t>
-  </si>
-  <si>
-    <t>Home Additions / ADU / Remodeling</t>
-  </si>
-  <si>
-    <t>Official site publishes direct email, free itemized on-site estimates, design-build ADUs/additions/second stories, permit handling and Sunday appointments.</t>
-  </si>
-  <si>
-    <t>info@homeadditionssanjose.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; Sunday by appointment</t>
-  </si>
-  <si>
-    <t>Use feasibility-to-itemized-estimate planning as a high-ticket addition/ADU funnel.</t>
-  </si>
-  <si>
-    <t>Addition + ADU feasibility campaign idea</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Home Additions San Jose and saw you handle additions, ADUs and second-story projects with design, permits and free itemized estimates. Campaign angle: ‘Before designing a major addition, establish what is feasible, what needs permitting and what the project scope should include.’ I’d build feasibility FAQs and estimate follow-ups. $150 flat. Want two examples first?</t>
-  </si>
-  <si>
-    <t>https://www.homeadditionssanjose.com/</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -1099,6 +793,9 @@
   </si>
   <si>
     <t>Leader Restoration</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
   </si>
   <si>
     <t>Rotated out of fresh queue 2026-09-12; no outreach found in connected Gmail checks.</t>
@@ -1793,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -1918,34 +1615,34 @@
         <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
@@ -1959,10 +1656,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>17</v>
@@ -1971,28 +1668,28 @@
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>27</v>
@@ -2006,10 +1703,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>17</v>
@@ -2018,31 +1715,31 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -2053,10 +1750,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>17</v>
@@ -2065,28 +1762,28 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -2100,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>17</v>
@@ -2112,31 +1809,31 @@
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -2147,13 +1844,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
@@ -2183,7 +1880,7 @@
         <v>90</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -2230,7 +1927,7 @@
         <v>100</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -2247,37 +1944,37 @@
         <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="N10" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -2288,13 +1985,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
@@ -2324,483 +2021,15 @@
         <v>121</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O21"/>
-  <conditionalFormatting sqref="E2:E21">
+  <autoFilter ref="A1:O11"/>
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",E2)))</formula>
     </cfRule>
@@ -2816,16 +2045,6 @@
     <hyperlink ref="M9" r:id="rId8"/>
     <hyperlink ref="M10" r:id="rId9"/>
     <hyperlink ref="M11" r:id="rId10"/>
-    <hyperlink ref="M12" r:id="rId11"/>
-    <hyperlink ref="M13" r:id="rId12"/>
-    <hyperlink ref="M14" r:id="rId13"/>
-    <hyperlink ref="M15" r:id="rId14"/>
-    <hyperlink ref="M16" r:id="rId15"/>
-    <hyperlink ref="M17" r:id="rId16"/>
-    <hyperlink ref="M18" r:id="rId17"/>
-    <hyperlink ref="M19" r:id="rId18"/>
-    <hyperlink ref="M20" r:id="rId19"/>
-    <hyperlink ref="M21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2844,142 +2063,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>225</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>226</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>227</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>228</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>229</v>
+        <v>127</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>230</v>
+        <v>128</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>231</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>232</v>
+        <v>130</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>233</v>
+        <v>131</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>234</v>
+        <v>132</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>235</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>236</v>
+        <v>134</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>237</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>238</v>
+        <v>136</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>239</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>240</v>
+        <v>138</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>242</v>
+        <v>140</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>243</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>244</v>
+        <v>142</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>245</v>
+        <v>143</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>246</v>
+        <v>144</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>247</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>248</v>
+        <v>146</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>249</v>
+        <v>147</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>250</v>
+        <v>148</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>251</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>252</v>
+        <v>150</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>253</v>
+        <v>151</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>254</v>
+        <v>152</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>255</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>256</v>
+        <v>154</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>257</v>
+        <v>155</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>259</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>260</v>
+        <v>158</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>261</v>
+        <v>159</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>262</v>
+        <v>160</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>263</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2989,7 +2208,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -3013,58 +2232,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>162</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>265</v>
+        <v>163</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>164</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>165</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>268</v>
+        <v>166</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>269</v>
+        <v>167</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>270</v>
+        <v>168</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>271</v>
+        <v>169</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>272</v>
+        <v>170</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>225</v>
+        <v>123</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>273</v>
+        <v>171</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>274</v>
+        <v>172</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>275</v>
+        <v>173</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>276</v>
+        <v>174</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>277</v>
+        <v>175</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>278</v>
+        <v>176</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>279</v>
+        <v>177</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>280</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -3113,7 +2332,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3137,7 +2356,7 @@
         <v>27</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R3" s="3">
         <v>150</v>
@@ -3145,13 +2364,13 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3175,7 +2394,7 @@
         <v>27</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R4" s="3">
         <v>150</v>
@@ -3183,13 +2402,13 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -3210,10 +2429,10 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R5" s="3">
         <v>150</v>
@@ -3221,13 +2440,13 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3251,7 +2470,7 @@
         <v>27</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="R6" s="3">
         <v>150</v>
@@ -3259,13 +2478,13 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3284,14 +2503,14 @@
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>281</v>
+        <v>179</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -3299,7 +2518,7 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
@@ -3323,12 +2542,10 @@
         <v>0</v>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="2" t="s">
-        <v>281</v>
-      </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>90</v>
@@ -3363,12 +2580,10 @@
         <v>0</v>
       </c>
       <c r="M9" s="2"/>
-      <c r="N9" s="2" t="s">
-        <v>281</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>100</v>
@@ -3385,7 +2600,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3404,14 +2619,14 @@
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2" t="s">
-        <v>281</v>
+        <v>179</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -3419,7 +2634,7 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
@@ -3443,10 +2658,12 @@
         <v>0</v>
       </c>
       <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+      <c r="N11" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>121</v>
@@ -3457,22 +2674,28 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="2">
-        <v>11</v>
+        <v>180</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>185</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -3481,36 +2704,44 @@
         <v>0</v>
       </c>
       <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="N12" s="2" t="s">
+        <v>187</v>
+      </c>
       <c r="O12" s="2"/>
-      <c r="P12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
       <c r="R12" s="3">
         <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B13" s="2">
-        <v>12</v>
+        <v>188</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -3519,36 +2750,38 @@
         <v>0</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+      <c r="N13" s="2" t="s">
+        <v>193</v>
+      </c>
       <c r="O13" s="2"/>
-      <c r="P13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>140</v>
-      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
       <c r="R13" s="3">
         <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14" s="2">
-        <v>13</v>
+        <v>194</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -3558,37 +2791,37 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>281</v>
+        <v>197</v>
       </c>
       <c r="O14" s="2"/>
-      <c r="P14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
       <c r="R14" s="3">
         <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B15" s="2">
-        <v>14</v>
+        <v>198</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -3598,37 +2831,37 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>281</v>
+        <v>197</v>
       </c>
       <c r="O15" s="2"/>
-      <c r="P15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>162</v>
-      </c>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
       <c r="R15" s="3">
         <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B16" s="2">
-        <v>15</v>
+        <v>200</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -3638,37 +2871,37 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="O16" s="2"/>
-      <c r="P16" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>173</v>
-      </c>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
       <c r="R16" s="3">
         <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B17" s="2">
-        <v>16</v>
+        <v>203</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -3678,37 +2911,37 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="O17" s="2"/>
-      <c r="P17" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
       <c r="R17" s="3">
         <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B18" s="2">
-        <v>17</v>
+        <v>206</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -3718,37 +2951,37 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="O18" s="2"/>
-      <c r="P18" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
       <c r="R18" s="3">
         <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B19" s="2">
-        <v>18</v>
+        <v>208</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -3758,37 +2991,37 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="O19" s="2"/>
-      <c r="P19" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>204</v>
-      </c>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
       <c r="R19" s="3">
         <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B20" s="2">
-        <v>19</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -3798,37 +3031,37 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="O20" s="2"/>
-      <c r="P20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>214</v>
-      </c>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
       <c r="R20" s="3">
         <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B21" s="2">
-        <v>20</v>
+        <v>212</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -3838,43 +3071,39 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="O21" s="2"/>
-      <c r="P21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>223</v>
-      </c>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
       <c r="R21" s="3">
         <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>282</v>
+        <v>214</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>283</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>284</v>
+        <v>182</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>285</v>
+        <v>215</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>286</v>
+        <v>196</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>287</v>
+        <v>216</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3884,7 +3113,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>289</v>
+        <v>217</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3895,32 +3124,26 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>290</v>
+        <v>218</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>283</v>
+        <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>284</v>
+        <v>182</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>291</v>
+        <v>219</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>294</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3930,7 +3153,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>295</v>
+        <v>202</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3941,26 +3164,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>296</v>
+        <v>220</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>283</v>
+        <v>181</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>284</v>
+        <v>182</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>297</v>
+        <v>221</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>298</v>
+        <v>196</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3970,7 +3193,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>299</v>
+        <v>202</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3981,26 +3204,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>300</v>
+        <v>222</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>283</v>
+        <v>181</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>284</v>
+        <v>182</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>301</v>
+        <v>223</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>298</v>
+        <v>196</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -4010,7 +3233,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>299</v>
+        <v>202</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -4021,26 +3244,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>302</v>
+        <v>224</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>283</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>284</v>
+        <v>182</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>303</v>
+        <v>225</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>298</v>
+        <v>196</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -4050,7 +3273,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -4059,410 +3282,8 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="A28" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K28" s="3">
-        <v>0</v>
-      </c>
-      <c r="L28" s="3">
-        <v>0</v>
-      </c>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="A29" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
-      <c r="A30" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K30" s="3">
-        <v>0</v>
-      </c>
-      <c r="L30" s="3">
-        <v>0</v>
-      </c>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
-      <c r="A31" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K31" s="3">
-        <v>0</v>
-      </c>
-      <c r="L31" s="3">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
-      <c r="A32" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18">
-      <c r="A33" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18">
-      <c r="A34" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K34" s="3">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3">
-        <v>0</v>
-      </c>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18">
-      <c r="A35" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18">
-      <c r="A36" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K36" s="3">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3">
-        <v>0</v>
-      </c>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O36" s="2"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="3">
-        <v>150</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:R36"/>
+  <autoFilter ref="A1:R26"/>
   <conditionalFormatting sqref="J2:J501">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Won/Paid">
       <formula>NOT(ISERROR(SEARCH("Won/Paid",J2)))</formula>
@@ -4487,16 +3308,6 @@
     <hyperlink ref="Q9" r:id="rId8"/>
     <hyperlink ref="Q10" r:id="rId9"/>
     <hyperlink ref="Q11" r:id="rId10"/>
-    <hyperlink ref="Q12" r:id="rId11"/>
-    <hyperlink ref="Q13" r:id="rId12"/>
-    <hyperlink ref="Q14" r:id="rId13"/>
-    <hyperlink ref="Q15" r:id="rId14"/>
-    <hyperlink ref="Q16" r:id="rId15"/>
-    <hyperlink ref="Q17" r:id="rId16"/>
-    <hyperlink ref="Q18" r:id="rId17"/>
-    <hyperlink ref="Q19" r:id="rId18"/>
-    <hyperlink ref="Q20" r:id="rId19"/>
-    <hyperlink ref="Q21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4526,67 +3337,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>267</v>
+        <v>165</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>328</v>
+        <v>226</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>269</v>
+        <v>167</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>329</v>
+        <v>227</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>271</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>330</v>
+        <v>228</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>272</v>
+        <v>170</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>225</v>
+        <v>123</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>276</v>
+        <v>174</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>274</v>
+        <v>172</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>275</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>290</v>
+        <v>188</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>291</v>
+        <v>189</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>331</v>
+        <v>229</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>293</v>
+        <v>191</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>332</v>
+        <v>230</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>294</v>
+        <v>192</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>333</v>
+        <v>231</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>295</v>
+        <v>193</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -4595,13 +3406,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>326</v>
+        <v>224</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>327</v>
+        <v>225</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>334</v>
+        <v>232</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -4609,10 +3420,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -4621,13 +3432,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>300</v>
+        <v>198</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>301</v>
+        <v>199</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>335</v>
+        <v>233</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -4635,10 +3446,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>299</v>
+        <v>197</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -4647,28 +3458,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>316</v>
+        <v>214</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>317</v>
+        <v>215</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>336</v>
+        <v>234</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>318</v>
+        <v>216</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>337</v>
+        <v>235</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>319</v>
+        <v>217</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -4677,13 +3488,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>324</v>
+        <v>222</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>325</v>
+        <v>223</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>338</v>
+        <v>236</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -4691,10 +3502,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -4703,13 +3514,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>322</v>
+        <v>220</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>323</v>
+        <v>221</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>339</v>
+        <v>237</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -4717,10 +3528,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -4729,13 +3540,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>296</v>
+        <v>194</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>297</v>
+        <v>195</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>340</v>
+        <v>238</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -4743,10 +3554,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>299</v>
+        <v>197</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -4755,28 +3566,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>282</v>
+        <v>180</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>285</v>
+        <v>183</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>341</v>
+        <v>239</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>287</v>
+        <v>185</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>342</v>
+        <v>240</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>289</v>
+        <v>187</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -4785,13 +3596,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>302</v>
+        <v>200</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>303</v>
+        <v>201</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>343</v>
+        <v>241</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -4799,10 +3610,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -4811,13 +3622,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>320</v>
+        <v>218</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>321</v>
+        <v>219</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>344</v>
+        <v>242</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -4825,10 +3636,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -4837,13 +3648,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>345</v>
+        <v>243</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>346</v>
+        <v>244</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>347</v>
+        <v>245</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -4851,10 +3662,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>348</v>
+        <v>246</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -4863,13 +3674,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>310</v>
+        <v>208</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>311</v>
+        <v>209</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>349</v>
+        <v>247</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -4877,10 +3688,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -4889,13 +3700,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>305</v>
+        <v>203</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>306</v>
+        <v>204</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>350</v>
+        <v>248</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -4903,10 +3714,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -4915,13 +3726,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>312</v>
+        <v>210</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>313</v>
+        <v>211</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>351</v>
+        <v>249</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -4929,10 +3740,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -4941,13 +3752,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>314</v>
+        <v>212</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>315</v>
+        <v>213</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>352</v>
+        <v>250</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -4955,10 +3766,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -4967,13 +3778,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>308</v>
+        <v>206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>309</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>353</v>
+        <v>251</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -4981,10 +3792,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -5016,33 +3827,33 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>225</v>
+        <v>123</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>267</v>
+        <v>165</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>272</v>
+        <v>170</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>273</v>
+        <v>171</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>274</v>
+        <v>172</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>354</v>
+        <v>252</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>277</v>
+        <v>175</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>276</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>355</v>
+        <v>253</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -5056,16 +3867,16 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>356</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>357</v>
+        <v>256</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -5079,14 +3890,14 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>358</v>
+        <v>257</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>359</v>
+        <v>258</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -5100,20 +3911,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>358</v>
+        <v>257</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>345</v>
+        <v>243</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>346</v>
+        <v>244</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -5123,16 +3934,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>358</v>
+        <v>257</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>348</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
@@ -5146,14 +3957,14 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>358</v>
+        <v>257</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>361</v>
+        <v>260</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -5167,14 +3978,14 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>358</v>
+        <v>257</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>362</v>
+        <v>261</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
@@ -5188,14 +3999,14 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>358</v>
+        <v>257</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>363</v>
+        <v>262</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
@@ -5209,14 +4020,14 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>292</v>
+        <v>190</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>364</v>
+        <v>263</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -5230,16 +4041,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>307</v>
+        <v>205</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>365</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>366</v>
+        <v>265</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
@@ -5253,14 +4064,14 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>292</v>
+        <v>190</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>367</v>
+        <v>266</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>28</v>
@@ -5274,14 +4085,14 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>298</v>
+        <v>196</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>368</v>
+        <v>267</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>28</v>
@@ -5295,14 +4106,14 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>286</v>
+        <v>184</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>369</v>
+        <v>268</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>28</v>
@@ -5316,16 +4127,16 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>356</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>370</v>
+        <v>269</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>28</v>
@@ -5339,14 +4150,14 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>292</v>
+        <v>190</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>371</v>
+        <v>270</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>28</v>
@@ -5360,14 +4171,14 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>292</v>
+        <v>190</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>372</v>
+        <v>271</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>28</v>
@@ -5381,14 +4192,14 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>298</v>
+        <v>196</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>373</v>
+        <v>272</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>28</v>
@@ -5402,16 +4213,16 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>356</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>374</v>
+        <v>273</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>28</v>
@@ -5425,16 +4236,16 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>356</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>375</v>
+        <v>274</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>28</v>
@@ -5448,16 +4259,16 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>356</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>28</v>
@@ -5471,16 +4282,16 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>377</v>
+        <v>276</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>378</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>379</v>
+        <v>278</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>28</v>
@@ -5494,11 +4305,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>356</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -5508,7 +4319,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -5530,13 +4341,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>380</v>
+        <v>279</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>381</v>
+        <v>280</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>382</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5556,7 +4367,7 @@
         <v>21</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>383</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5564,104 +4375,104 @@
         <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>383</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>383</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>383</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>383</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>383</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>83</v>
@@ -5670,13 +4481,13 @@
         <v>90</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>383</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -5690,13 +4501,13 @@
         <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>95</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>383</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -5704,24 +4515,24 @@
         <v>101</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>383</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>114</v>
@@ -5730,213 +4541,13 @@
         <v>121</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>116</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>383</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -5951,16 +4562,6 @@
     <hyperlink ref="C9" r:id="rId8"/>
     <hyperlink ref="C10" r:id="rId9"/>
     <hyperlink ref="C11" r:id="rId10"/>
-    <hyperlink ref="C12" r:id="rId11"/>
-    <hyperlink ref="C13" r:id="rId12"/>
-    <hyperlink ref="C14" r:id="rId13"/>
-    <hyperlink ref="C15" r:id="rId14"/>
-    <hyperlink ref="C16" r:id="rId15"/>
-    <hyperlink ref="C17" r:id="rId16"/>
-    <hyperlink ref="C18" r:id="rId17"/>
-    <hyperlink ref="C19" r:id="rId18"/>
-    <hyperlink ref="C20" r:id="rId19"/>
-    <hyperlink ref="C21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5981,7 +4582,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>384</v>
+        <v>283</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5991,20 +4592,20 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>385</v>
+        <v>284</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>386</v>
+        <v>285</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>387</v>
+        <v>286</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>386</v>
+        <v>285</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>388</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6016,95 +4617,95 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>392</v>
+        <v>291</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>393</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>394</v>
+        <v>293</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>389</v>
+        <v>288</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>396</v>
+        <v>295</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>397</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>390</v>
+        <v>289</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>398</v>
+        <v>297</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>399</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>391</v>
+        <v>290</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>400</v>
+        <v>299</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>401</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>275</v>
+        <v>173</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -6130,98 +4731,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>301</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>403</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>404</v>
+        <v>303</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>405</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>406</v>
+        <v>305</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>407</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>408</v>
+        <v>307</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>409</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>410</v>
+        <v>309</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>411</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>412</v>
+        <v>311</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>413</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>414</v>
+        <v>313</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>415</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>416</v>
+        <v>315</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>417</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>418</v>
+        <v>317</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>419</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>283</v>
+        <v>181</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>420</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>421</v>
+        <v>320</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>422</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>423</v>
+        <v>322</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>424</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -6240,19 +4841,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>324</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>426</v>
+        <v>325</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>427</v>
+        <v>326</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>428</v>
+        <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>429</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -6260,7 +4861,7 @@
         <v>27</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2">
         <v>16</v>
@@ -6269,7 +4870,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>430</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="330">
   <si>
     <t>Rank</t>
   </si>
@@ -73,19 +73,214 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Top Home Roofers</t>
+  </si>
+  <si>
+    <t>Roofing / Repair / Replacement / Emergency</t>
+  </si>
+  <si>
+    <t>San Jose / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Official San Jose pages crawled Sep 15-16 publish a direct email, free on-site estimates, full roof inspections, detailed estimates, emergency leak work and a documented four-step estimate process.</t>
+  </si>
+  <si>
+    <t>408-443-2520</t>
+  </si>
+  <si>
+    <t>info@tophomeroofers.com</t>
+  </si>
+  <si>
+    <t>Direct email; free on-site estimate; local San Jose office</t>
+  </si>
+  <si>
+    <t>Turn inspection-first diagnosis and transparent estimate steps into a proof-before-purchase roofing campaign.</t>
+  </si>
+  <si>
+    <t>Inspection-to-estimate campaign idea for Top Home Roofers</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Top Home Roofers’ current San Jose pages and noticed your process already answers the question homeowners worry about most: what happens between noticing a roof problem and approving expensive work. Campaign angle: ‘Inspect the roof first. See the condition. Get the plan and price before deciding.’ I’d turn that into inspection posts, repair-vs-replacement FAQs, estimate follow-ups and emergency-leak education. Same-Day Customer Growth Pack: $150 flat. Want two Top Home-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://tophomeroofers.com/contact/</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>Skyline Roofing &amp; Construction</t>
+  </si>
+  <si>
+    <t>Residential / Commercial Roofing / Repair / Inspection</t>
+  </si>
+  <si>
+    <t>San Francisco Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official pages crawled Sep 14-16 publish direct email, free estimates, one-business-day inquiry response, written estimates, photographed inspections, commercial and residential roofing, and often same-day urgent leak repair.</t>
+  </si>
+  <si>
+    <t>(415) 209-5199</t>
+  </si>
+  <si>
+    <t>info@roofingbyskyline.com</t>
+  </si>
+  <si>
+    <t>Direct email; responds within one business day; free estimate</t>
+  </si>
+  <si>
+    <t>Use photographed inspection plus written fixed-scope estimate to reduce uncertainty before repair or replacement.</t>
+  </si>
+  <si>
+    <t>Photo-to-written-scope roofing campaign idea for Skyline</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Skyline Roofing’s current process and noticed a strong trust sequence: free inspection, photos of problem areas, then a written estimate with scope, materials, timeline and price. Campaign angle: ‘See what the roof is showing before choosing what to fix.’ I’d turn that into inspection posts, leak-vs-replacement FAQs, estimate follow-ups and commercial/property-manager content. Same-Day Customer Growth Pack: $150 flat. Want two Skyline-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://roofingbyskyline.com/contact</t>
+  </si>
+  <si>
+    <t>Valle Construction</t>
+  </si>
+  <si>
+    <t>Remodeling / ADU / Kitchen / Bathroom</t>
+  </si>
+  <si>
+    <t>San Jose / Santa Clara County, CA</t>
+  </si>
+  <si>
+    <t>Official San Jose page crawled Sep 13 publishes direct email, free estimates, ADU/kitchen/bath remodeling, local permit-process familiarity and a stated response within one business day.</t>
+  </si>
+  <si>
+    <t>(669) 225-3277</t>
+  </si>
+  <si>
+    <t>info@valle.construction</t>
+  </si>
+  <si>
+    <t>Direct email; one-business-day response; free estimate</t>
+  </si>
+  <si>
+    <t>Turn San Jose permit familiarity and project feasibility into a pre-estimate planning funnel for ADUs and remodels.</t>
+  </si>
+  <si>
+    <t>San Jose permit-to-estimate campaign idea for Valle</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Valle Construction’s San Jose page and noticed a useful marketing advantage: you handle ADUs and remodels while already understanding the local permit process. Campaign angle: ‘Before choosing finishes, know what the project can realistically permit, require and cost.’ I’d turn that into permit FAQs, ADU/remodel planning posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Valle-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://valle.construction/services/san-jose</t>
+  </si>
+  <si>
+    <t>Hertz Electric Inc</t>
+  </si>
+  <si>
+    <t>Electrical / EV / Panel / Battery</t>
+  </si>
+  <si>
+    <t>Official site crawled Sep 16 publishes direct email, same-day/emergency service, free estimates, EV charger and panel work, and PG&amp;E rebate/incentive assistance.</t>
+  </si>
+  <si>
+    <t>(415) 676-0598</t>
+  </si>
+  <si>
+    <t>arash@thehertzelectric.com</t>
+  </si>
+  <si>
+    <t>Direct email; same-day service; free estimate</t>
+  </si>
+  <si>
+    <t>Turn EV charger readiness plus rebate navigation into a fast, high-intent estimate funnel.</t>
+  </si>
+  <si>
+    <t>Same-day EV + rebate campaign idea for Hertz Electric</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Hertz Electric’s current San Jose page and saw you combine same-day service, EV charger expertise, panel work and PG&amp;E rebate guidance. Campaign angle: ‘Before installing the charger, know whether the panel is ready and which incentives may reduce the project cost.’ I’d turn that into readiness FAQs, rebate explainer posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Hertz-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://thehertzelectric.com/</t>
+  </si>
+  <si>
+    <t>Seltzer Restoration</t>
+  </si>
+  <si>
+    <t>Water Damage / Mold / Sewage Restoration</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>Official contact page crawled Sep 2 publishes direct email, San Jose office, seven-day office hours and explicit guidance for prospects to send photos, ZIP code, damage source, affected rooms and whether water is still present.</t>
+  </si>
+  <si>
+    <t>(669) 216-0503</t>
+  </si>
+  <si>
+    <t>seltzerbritton@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; seven-day office hours; emergency phone hours</t>
+  </si>
+  <si>
+    <t>Turn the existing damage-intake checklist into first-response educational content that helps prospects send useful information before assessment.</t>
+  </si>
+  <si>
+    <t>First-response damage checklist campaign idea for Seltzer</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Seltzer Restoration’s San Jose contact process and noticed you already tell customers exactly what helps you assess a loss: photos, ZIP code, damage source, affected rooms and whether water is still present. That can become a strong campaign: ‘Before the restoration team arrives, document the five details that make the first assessment faster and clearer.’ I’d turn that into emergency posts, homeowner FAQs and assessment follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Seltzer-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://seltzerrestorationllc.com/contact</t>
+  </si>
+  <si>
+    <t>Ozone Service</t>
+  </si>
+  <si>
+    <t>HVAC / Electrical / Heat Pump / Panel / EV</t>
+  </si>
+  <si>
+    <t>Official pages crawled Sep 14-16 publish direct email, 24/7 availability, free diagnostics and estimates, written scopes, financing, heat-pump rebates and in-house HVAC/electrical work under one license.</t>
+  </si>
+  <si>
+    <t>(669) 323-7077</t>
+  </si>
+  <si>
+    <t>go@serviceozone.com</t>
+  </si>
+  <si>
+    <t>Direct email; 24/7; free estimate and diagnostics</t>
+  </si>
+  <si>
+    <t>Turn one-team electrification plus rebates, written scope and financing into a high-ticket heat-pump decision funnel.</t>
+  </si>
+  <si>
+    <t>Heat-pump + electrical + rebate campaign idea for Ozone</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Ozone’s current HVAC/electrical pages and the strongest story is bigger than a heat-pump ad: one team can handle the HVAC, panel/circuit work, permits, rebate paperwork and written scope. Campaign angle: ‘Before upgrading the system, know the electrical work, incentives and total scope together.’ I’d turn that into rebate FAQs, electrification-readiness posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Ozone-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://serviceozone.com/</t>
+  </si>
+  <si>
     <t>Amex Roofing</t>
   </si>
   <si>
     <t>Roofing / Repair / Replacement / Inspection</t>
   </si>
   <si>
-    <t>San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Official site crawled within two weeks publishes a direct email, free roof inspections, written estimates, project photos, a public license record and 300+ permitted projects referenced through BuildZoom.</t>
+    <t>Official site reverified Sep 16 publishes direct email, free roof inspections, written scopes, completed-project photos, public CSLB license information and 300+ permitted projects referenced through BuildZoom.</t>
   </si>
   <si>
     <t>(510) 761-8120</t>
@@ -109,52 +304,13 @@
     <t>https://amex-roofing.com/</t>
   </si>
   <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
-    <t>Valle Construction</t>
-  </si>
-  <si>
-    <t>Remodeling / ADU / Kitchen / Bathroom</t>
-  </si>
-  <si>
-    <t>San Jose / Santa Clara County, CA</t>
-  </si>
-  <si>
-    <t>Official San Jose page crawled Sep 13 publishes direct email, free estimates, ADU/kitchen/bath remodeling, local permit-process familiarity and a stated response within one business day.</t>
-  </si>
-  <si>
-    <t>(669) 225-3277</t>
-  </si>
-  <si>
-    <t>info@valle.construction</t>
-  </si>
-  <si>
-    <t>Direct email; one-business-day response; free estimate</t>
-  </si>
-  <si>
-    <t>Turn San Jose permit familiarity and project feasibility into a pre-estimate planning funnel for ADUs and remodels.</t>
-  </si>
-  <si>
-    <t>San Jose permit-to-estimate campaign idea for Valle</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Valle Construction’s San Jose page and noticed a useful marketing advantage: you handle ADUs and remodels while already understanding the local permit process. Campaign angle: ‘Before choosing finishes, know what the project can realistically permit, require and cost.’ I’d turn that into permit FAQs, ADU/remodel planning posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Valle-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://valle.construction/services/san-jose</t>
-  </si>
-  <si>
     <t>California Bay Roofing Inc</t>
   </si>
   <si>
     <t>Residential / Commercial Roofing / Gutters</t>
   </si>
   <si>
-    <t>Official San Jose page crawled Sep 14 publishes two direct email addresses, a free inspection, residential and commercial roofing, flat-roof systems, coatings and seamless-gutter work.</t>
+    <t>Official San Jose page crawled Sep 14 publishes direct email, free no-obligation inspections, residential/commercial roofing, shingles, tile, metal, TPO, coatings, repairs and seamless gutters.</t>
   </si>
   <si>
     <t>(415) 684-4498</t>
@@ -172,142 +328,19 @@
     <t>Roof-system diagnosis campaign idea for California Bay Roofing</t>
   </si>
   <si>
-    <t>Hi — I reviewed California Bay Roofing’s San Jose services and noticed you work across shingles, flat roofs, coatings and seamless gutters. That supports a stronger campaign than generic roof replacement: ‘Find where the roof system is actually failing before choosing the repair.’ I’d build inspection posts, repair-path FAQs, drainage content and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two California Bay Roofing-specific examples first?</t>
+    <t>Hi — I reviewed California Bay Roofing’s San Jose services and noticed you work across shingles, tile, metal, TPO, coatings and seamless gutters. That supports a stronger campaign than generic roof replacement: ‘Find where the roof system is actually failing before choosing the repair.’ I’d build inspection posts, repair-path FAQs, drainage content and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two California Bay Roofing-specific examples first?</t>
   </si>
   <si>
     <t>https://www.californiabayroofinginc.net/san-jose-roofing</t>
   </si>
   <si>
-    <t>RCK Development</t>
-  </si>
-  <si>
-    <t>Remodeling / ADU / Additions / HVAC / Plumbing</t>
-  </si>
-  <si>
-    <t>Previously verified Sep 14 with direct email, free estimates, realistic estimate/timeline positioning, permit coordination and high-ticket remodel/ADU work.</t>
-  </si>
-  <si>
-    <t>(408) 982-7586</t>
-  </si>
-  <si>
-    <t>therckdevelopment@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; same-day message response; free estimate</t>
-  </si>
-  <si>
-    <t>Turn realistic scope, timeline and permit coordination into a no-pressure pre-estimate decision funnel.</t>
-  </si>
-  <si>
-    <t>Realistic remodel estimate campaign idea for RCK</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed RCK Development’s current site and noticed you make a useful promise most contractors avoid: realistic estimates and timelines, with permits and changes handled clearly. Campaign angle: ‘Before choosing finishes, know what the project can realistically cost, how long it can take, and what has to happen first.’ I’d turn that into planning FAQs, ADU/remodel posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two RCK-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.rckdevelopment.com/</t>
-  </si>
-  <si>
-    <t>2026-09-14</t>
-  </si>
-  <si>
-    <t>Fox Electric</t>
-  </si>
-  <si>
-    <t>Electrical / EV Charger / Panel Upgrade</t>
-  </si>
-  <si>
-    <t>Official San Jose panel page re-crawled Sep 11 publishes direct email, free on-site estimates, panel upgrades, EV charging and licensed C-10 service.</t>
-  </si>
-  <si>
-    <t>(650) 550-0719</t>
-  </si>
-  <si>
-    <t>info@foxelectrician.com</t>
-  </si>
-  <si>
-    <t>Direct email; free on-site estimate</t>
-  </si>
-  <si>
-    <t>Use load calculation and panel-readiness education to make EV/panel estimates more trustworthy.</t>
-  </si>
-  <si>
-    <t>EV + panel readiness campaign idea for Fox Electric</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Fox Electric’s San Jose panel and EV services and think the strongest customer question is simple: ‘Does this home actually need a panel upgrade for the next electrical load?’ I’d turn that into EV-readiness FAQs, load-management education, permit posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Fox-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://foxelectrician.com/services/panel-upgrade/san-jose/</t>
-  </si>
-  <si>
-    <t>Hertz Electric Inc</t>
-  </si>
-  <si>
-    <t>Electrical / EV / Panel / Battery</t>
-  </si>
-  <si>
-    <t>Official site crawled today publishes direct email, same-day/emergency service, free estimates, EV charger and panel work, and PG&amp;E rebate/incentive assistance.</t>
-  </si>
-  <si>
-    <t>(415) 676-0598</t>
-  </si>
-  <si>
-    <t>arash@thehertzelectric.com</t>
-  </si>
-  <si>
-    <t>Direct email; same-day service; free estimate</t>
-  </si>
-  <si>
-    <t>Turn EV charger readiness plus rebate navigation into a fast, high-intent estimate funnel.</t>
-  </si>
-  <si>
-    <t>Same-day EV + rebate campaign idea for Hertz Electric</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Hertz Electric’s current San Jose page today and saw you combine same-day service, EV charger expertise, panel work and PG&amp;E rebate guidance. Campaign angle: ‘Before installing the charger, know whether the panel is ready and which incentives may reduce the project cost.’ I’d turn that into readiness FAQs, rebate explainer posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Hertz-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://thehertzelectric.com/</t>
-  </si>
-  <si>
-    <t>Bayco Builders &amp; Restoration</t>
-  </si>
-  <si>
-    <t>Water / Fire / Mold / Sewage / Remodeling</t>
-  </si>
-  <si>
-    <t>Official site reverified this week with direct email, 24/7 emergency response and restoration-to-rebuild positioning.</t>
-  </si>
-  <si>
-    <t>(669) 770-5373</t>
-  </si>
-  <si>
-    <t>baycobuildersandrestoration@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; 24/7 emergency response</t>
-  </si>
-  <si>
-    <t>Explain first-hour mitigation and the rebuild path in calm plain language.</t>
-  </si>
-  <si>
-    <t>First-hour restoration campaign idea for Bayco</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Bayco’s current restoration pages and think the strongest campaign is the full path after an emergency: ‘Stop the damage first, document what happened, then keep the rebuild moving without starting over.’ I’d turn that into first-hour checklists, insurance FAQs, emergency posts and rebuild follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Bayco-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://baycobuildersandrestoration.com/</t>
-  </si>
-  <si>
     <t>Shefer Builder</t>
   </si>
   <si>
-    <t>Remodeling / ADU / Additions / New Construction</t>
-  </si>
-  <si>
-    <t>Official contact page reverified this week publishes direct email, free estimates, ADU/garage conversion, room additions and seven-day hours.</t>
+    <t>Remodeling / ADU / Additions / General Remodel</t>
+  </si>
+  <si>
+    <t>Official contact page crawled Sep 9 publishes direct email, free estimates, ADU/garage conversion, room additions, remodeling and seven-day hours.</t>
   </si>
   <si>
     <t>510-571-0060</t>
@@ -331,67 +364,34 @@
     <t>https://sheferbuilder.com/contact-us/</t>
   </si>
   <si>
-    <t>Ozone Service</t>
-  </si>
-  <si>
-    <t>HVAC / Electrical / Panel / EV</t>
-  </si>
-  <si>
-    <t>Official HVAC/electrical page reverified this week publishes direct email, free estimate, written scope/price, panel upgrades, EV chargers and heat pumps handled under one licensed team.</t>
-  </si>
-  <si>
-    <t>(310) 743-3364</t>
-  </si>
-  <si>
-    <t>info@serviceozone.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; 24/7 phone</t>
-  </si>
-  <si>
-    <t>Market one-team HVAC/electrical coordination for electrification projects that otherwise require multiple contractors.</t>
-  </si>
-  <si>
-    <t>One-team heat-pump + electrical campaign idea for Ozone</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Ozone’s current HVAC and electrical page and noticed a strong coordination angle: heat pumps, panel upgrades and EV charging can stay with one licensed team instead of being split between contractors. I’d turn that into electrification-readiness FAQs, scope explainers and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Ozone-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://serviceozone.com/ozone-hvac-electrical/</t>
-  </si>
-  <si>
-    <t>Silicon Valley Building Service and Repair</t>
-  </si>
-  <si>
-    <t>Remodeling / ADU / Additions</t>
-  </si>
-  <si>
-    <t>San Jose / South Bay, CA</t>
-  </si>
-  <si>
-    <t>Previously verified official pages publish free estimates, fixed-price written scopes, same-day replies during business hours, remodeling, ADUs and additions.</t>
-  </si>
-  <si>
-    <t>(408) 667-4946</t>
-  </si>
-  <si>
-    <t>info@siliconvalleybuilding.com</t>
-  </si>
-  <si>
-    <t>Direct email; usually same-day reply; free estimate</t>
-  </si>
-  <si>
-    <t>Turn scope-first fixed pricing into a high-ticket remodeling decision campaign.</t>
-  </si>
-  <si>
-    <t>Fixed-price remodeling decision-flow idea for SVBSR</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed SVBSR’s current process and noticed a strong trust angle: free estimate, written scope and fixed price before the work starts. Campaign idea: ‘Before committing to a remodel or ADU, make the scope and price understandable.’ I’d build planning FAQs, ADU/remodel posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two SVBSR-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://siliconvalleybuilding.com/</t>
+    <t>Simmitri Inc.</t>
+  </si>
+  <si>
+    <t>Roofing / Solar Energy</t>
+  </si>
+  <si>
+    <t>Official contact page crawled Sep 13 publishes direct email, free online estimates and combined roofing/solar service, with the company stating it has provided roofing and solar energy service since 1995.</t>
+  </si>
+  <si>
+    <t>(408) 779-3333</t>
+  </si>
+  <si>
+    <t>info@simmitri.com</t>
+  </si>
+  <si>
+    <t>Direct email; free online estimate</t>
+  </si>
+  <si>
+    <t>Use combined roof-and-solar planning to help homeowners evaluate the roof condition before committing to a solar project.</t>
+  </si>
+  <si>
+    <t>Roof-before-solar planning campaign idea for Simmitri</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Simmitri’s current roofing and solar positioning and think the combined service supports a useful planning campaign: ‘Before adding a long-life solar system, make sure the roof underneath it is ready for the same horizon.’ I’d turn that into roof-readiness FAQs, solar-planning posts, estimate follow-ups and roof-plus-solar decision content. Same-Day Customer Growth Pack: $150 flat. Want two Simmitri-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://simmitri.com/contact-us/</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -1662,34 +1662,34 @@
         <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>27</v>
@@ -1703,10 +1703,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>17</v>
@@ -1715,31 +1715,31 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1756,34 +1756,34 @@
         <v>62</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>17</v>
@@ -1809,28 +1809,28 @@
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1844,10 +1844,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>17</v>
@@ -1856,28 +1856,28 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1891,10 +1891,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>17</v>
@@ -1903,28 +1903,28 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -1938,10 +1938,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>17</v>
@@ -1950,28 +1950,28 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1985,13 +1985,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
@@ -2021,7 +2021,7 @@
         <v>121</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -2370,7 +2370,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2394,7 +2394,7 @@
         <v>27</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R4" s="3">
         <v>150</v>
@@ -2402,13 +2402,13 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -2426,13 +2426,15 @@
         <v>0</v>
       </c>
       <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+      <c r="N5" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="R5" s="3">
         <v>150</v>
@@ -2446,7 +2448,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2470,7 +2472,7 @@
         <v>27</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R6" s="3">
         <v>150</v>
@@ -2478,13 +2480,13 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2510,7 +2512,7 @@
         <v>27</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -2518,13 +2520,13 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2548,7 +2550,7 @@
         <v>27</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R8" s="3">
         <v>150</v>
@@ -2556,13 +2558,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2586,7 +2588,7 @@
         <v>27</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R9" s="3">
         <v>150</v>
@@ -2594,13 +2596,13 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2618,15 +2620,13 @@
         <v>0</v>
       </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -2634,7 +2634,7 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
@@ -2658,12 +2658,10 @@
         <v>0</v>
       </c>
       <c r="M11" s="2"/>
-      <c r="N11" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>121</v>
@@ -4395,16 +4393,16 @@
         <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>282</v>
@@ -4412,19 +4410,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>282</v>
@@ -4435,16 +4433,16 @@
         <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>282</v>
@@ -4452,19 +4450,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>282</v>
@@ -4472,19 +4470,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>282</v>
@@ -4492,19 +4490,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>282</v>
@@ -4512,19 +4510,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>282</v>
@@ -4532,7 +4530,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>114</v>
@@ -4541,7 +4539,7 @@
         <v>121</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>116</v>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="314">
   <si>
     <t>Rank</t>
   </si>
@@ -73,325 +73,289 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Top Home Roofers</t>
-  </si>
-  <si>
-    <t>Roofing / Repair / Replacement / Emergency</t>
+    <t>HB Design &amp; Construction</t>
+  </si>
+  <si>
+    <t>Design-Build / Remodeling / ADU</t>
+  </si>
+  <si>
+    <t>San Jose / South Bay, CA</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Official contact page currently advertises free on-site consultation, written estimates and usually same-day email replies, creating a fast-response path for high-value remodeling inquiries.</t>
+  </si>
+  <si>
+    <t>hello.hbdesignconstruction@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; usually same-day reply; free consultation</t>
+  </si>
+  <si>
+    <t>Turn the free consultation and written-estimate process into a pre-consultation content funnel that helps homeowners arrive with project scope, priorities and decision questions ready.</t>
+  </si>
+  <si>
+    <t>Pre-consultation remodeling campaign idea for HB Design</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed HB Design &amp; Construction’s current consultation process and noticed you already promise a free on-site consultation, written estimate and fast reply. I’d turn that into a customer-ready pre-consultation campaign that helps homeowners organize scope, priorities and questions before you arrive. The $150 Same-Day Customer Growth Pack can include social/Google posts, FAQs, inquiry follow-ups and estimate-ready messaging built around your actual services. Want two HB-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://hbdesignconstruction.com/contact</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>AYH Remodeling &amp; Construction Inc</t>
+  </si>
+  <si>
+    <t>Kitchen / Bathroom / ADU / Full Home Remodeling</t>
   </si>
   <si>
     <t>San Jose / Bay Area, CA</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Official San Jose pages crawled Sep 15-16 publish a direct email, free on-site estimates, full roof inspections, detailed estimates, emergency leak work and a documented four-step estimate process.</t>
-  </si>
-  <si>
-    <t>408-443-2520</t>
-  </si>
-  <si>
-    <t>info@tophomeroofers.com</t>
-  </si>
-  <si>
-    <t>Direct email; free on-site estimate; local San Jose office</t>
-  </si>
-  <si>
-    <t>Turn inspection-first diagnosis and transparent estimate steps into a proof-before-purchase roofing campaign.</t>
-  </si>
-  <si>
-    <t>Inspection-to-estimate campaign idea for Top Home Roofers</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Top Home Roofers’ current San Jose pages and noticed your process already answers the question homeowners worry about most: what happens between noticing a roof problem and approving expensive work. Campaign angle: ‘Inspect the roof first. See the condition. Get the plan and price before deciding.’ I’d turn that into inspection posts, repair-vs-replacement FAQs, estimate follow-ups and emergency-leak education. Same-Day Customer Growth Pack: $150 flat. Want two Top Home-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://tophomeroofers.com/contact/</t>
-  </si>
-  <si>
-    <t>2026-09-16</t>
-  </si>
-  <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
-    <t>Skyline Roofing &amp; Construction</t>
-  </si>
-  <si>
-    <t>Residential / Commercial Roofing / Repair / Inspection</t>
-  </si>
-  <si>
-    <t>San Francisco Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official pages crawled Sep 14-16 publish direct email, free estimates, one-business-day inquiry response, written estimates, photographed inspections, commercial and residential roofing, and often same-day urgent leak repair.</t>
-  </si>
-  <si>
-    <t>(415) 209-5199</t>
-  </si>
-  <si>
-    <t>info@roofingbyskyline.com</t>
-  </si>
-  <si>
-    <t>Direct email; responds within one business day; free estimate</t>
-  </si>
-  <si>
-    <t>Use photographed inspection plus written fixed-scope estimate to reduce uncertainty before repair or replacement.</t>
-  </si>
-  <si>
-    <t>Photo-to-written-scope roofing campaign idea for Skyline</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Skyline Roofing’s current process and noticed a strong trust sequence: free inspection, photos of problem areas, then a written estimate with scope, materials, timeline and price. Campaign angle: ‘See what the roof is showing before choosing what to fix.’ I’d turn that into inspection posts, leak-vs-replacement FAQs, estimate follow-ups and commercial/property-manager content. Same-Day Customer Growth Pack: $150 flat. Want two Skyline-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://roofingbyskyline.com/contact</t>
-  </si>
-  <si>
-    <t>Valle Construction</t>
-  </si>
-  <si>
-    <t>Remodeling / ADU / Kitchen / Bathroom</t>
-  </si>
-  <si>
-    <t>San Jose / Santa Clara County, CA</t>
-  </si>
-  <si>
-    <t>Official San Jose page crawled Sep 13 publishes direct email, free estimates, ADU/kitchen/bath remodeling, local permit-process familiarity and a stated response within one business day.</t>
-  </si>
-  <si>
-    <t>(669) 225-3277</t>
-  </si>
-  <si>
-    <t>info@valle.construction</t>
-  </si>
-  <si>
-    <t>Direct email; one-business-day response; free estimate</t>
-  </si>
-  <si>
-    <t>Turn San Jose permit familiarity and project feasibility into a pre-estimate planning funnel for ADUs and remodels.</t>
-  </si>
-  <si>
-    <t>San Jose permit-to-estimate campaign idea for Valle</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Valle Construction’s San Jose page and noticed a useful marketing advantage: you handle ADUs and remodels while already understanding the local permit process. Campaign angle: ‘Before choosing finishes, know what the project can realistically permit, require and cost.’ I’d turn that into permit FAQs, ADU/remodel planning posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Valle-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://valle.construction/services/san-jose</t>
-  </si>
-  <si>
-    <t>Hertz Electric Inc</t>
-  </si>
-  <si>
-    <t>Electrical / EV / Panel / Battery</t>
-  </si>
-  <si>
-    <t>Official site crawled Sep 16 publishes direct email, same-day/emergency service, free estimates, EV charger and panel work, and PG&amp;E rebate/incentive assistance.</t>
-  </si>
-  <si>
-    <t>(415) 676-0598</t>
-  </si>
-  <si>
-    <t>arash@thehertzelectric.com</t>
-  </si>
-  <si>
-    <t>Direct email; same-day service; free estimate</t>
-  </si>
-  <si>
-    <t>Turn EV charger readiness plus rebate navigation into a fast, high-intent estimate funnel.</t>
-  </si>
-  <si>
-    <t>Same-day EV + rebate campaign idea for Hertz Electric</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Hertz Electric’s current San Jose page and saw you combine same-day service, EV charger expertise, panel work and PG&amp;E rebate guidance. Campaign angle: ‘Before installing the charger, know whether the panel is ready and which incentives may reduce the project cost.’ I’d turn that into readiness FAQs, rebate explainer posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Hertz-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://thehertzelectric.com/</t>
-  </si>
-  <si>
-    <t>Seltzer Restoration</t>
-  </si>
-  <si>
-    <t>Water Damage / Mold / Sewage Restoration</t>
-  </si>
-  <si>
-    <t>San Jose, CA</t>
-  </si>
-  <si>
-    <t>Official contact page crawled Sep 2 publishes direct email, San Jose office, seven-day office hours and explicit guidance for prospects to send photos, ZIP code, damage source, affected rooms and whether water is still present.</t>
-  </si>
-  <si>
-    <t>(669) 216-0503</t>
-  </si>
-  <si>
-    <t>seltzerbritton@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; seven-day office hours; emergency phone hours</t>
-  </si>
-  <si>
-    <t>Turn the existing damage-intake checklist into first-response educational content that helps prospects send useful information before assessment.</t>
-  </si>
-  <si>
-    <t>First-response damage checklist campaign idea for Seltzer</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Seltzer Restoration’s San Jose contact process and noticed you already tell customers exactly what helps you assess a loss: photos, ZIP code, damage source, affected rooms and whether water is still present. That can become a strong campaign: ‘Before the restoration team arrives, document the five details that make the first assessment faster and clearer.’ I’d turn that into emergency posts, homeowner FAQs and assessment follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Seltzer-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://seltzerrestorationllc.com/contact</t>
-  </si>
-  <si>
-    <t>Ozone Service</t>
-  </si>
-  <si>
-    <t>HVAC / Electrical / Heat Pump / Panel / EV</t>
-  </si>
-  <si>
-    <t>Official pages crawled Sep 14-16 publish direct email, 24/7 availability, free diagnostics and estimates, written scopes, financing, heat-pump rebates and in-house HVAC/electrical work under one license.</t>
-  </si>
-  <si>
-    <t>(669) 323-7077</t>
-  </si>
-  <si>
-    <t>go@serviceozone.com</t>
-  </si>
-  <si>
-    <t>Direct email; 24/7; free estimate and diagnostics</t>
-  </si>
-  <si>
-    <t>Turn one-team electrification plus rebates, written scope and financing into a high-ticket heat-pump decision funnel.</t>
-  </si>
-  <si>
-    <t>Heat-pump + electrical + rebate campaign idea for Ozone</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Ozone’s current HVAC/electrical pages and the strongest story is bigger than a heat-pump ad: one team can handle the HVAC, panel/circuit work, permits, rebate paperwork and written scope. Campaign angle: ‘Before upgrading the system, know the electrical work, incentives and total scope together.’ I’d turn that into rebate FAQs, electrification-readiness posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Ozone-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://serviceozone.com/</t>
-  </si>
-  <si>
-    <t>Amex Roofing</t>
-  </si>
-  <si>
-    <t>Roofing / Repair / Replacement / Inspection</t>
-  </si>
-  <si>
-    <t>Official site reverified Sep 16 publishes direct email, free roof inspections, written scopes, completed-project photos, public CSLB license information and 300+ permitted projects referenced through BuildZoom.</t>
-  </si>
-  <si>
-    <t>(510) 761-8120</t>
-  </si>
-  <si>
-    <t>amexroofingca@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free inspection; written quote</t>
-  </si>
-  <si>
-    <t>Turn inspect-first documentation, written scope and completed-project photos into a proof-before-purchase campaign.</t>
-  </si>
-  <si>
-    <t>Proof-before-purchase roofing campaign idea for Amex</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Amex Roofing’s current site and noticed you already have the ingredients for a strong trust campaign: free inspection, written scope, clear pricing and completed-project photos. Campaign angle: ‘Inspect it. Put the scope in writing. See the work before you decide.’ I’d turn that into inspection posts, repair-vs-replacement FAQs, estimate follow-ups and project-proof content. Same-Day Customer Growth Pack: $150 flat. Want two Amex-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://amex-roofing.com/</t>
-  </si>
-  <si>
-    <t>California Bay Roofing Inc</t>
-  </si>
-  <si>
-    <t>Residential / Commercial Roofing / Gutters</t>
-  </si>
-  <si>
-    <t>Official San Jose page crawled Sep 14 publishes direct email, free no-obligation inspections, residential/commercial roofing, shingles, tile, metal, TPO, coatings, repairs and seamless gutters.</t>
-  </si>
-  <si>
-    <t>(415) 684-4498</t>
-  </si>
-  <si>
-    <t>californiabayroofinginc@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free inspection</t>
-  </si>
-  <si>
-    <t>Use roof-system diagnosis across shingles, flat roofs, coatings and drainage to create a repair-path decision campaign instead of generic replacement advertising.</t>
-  </si>
-  <si>
-    <t>Roof-system diagnosis campaign idea for California Bay Roofing</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed California Bay Roofing’s San Jose services and noticed you work across shingles, tile, metal, TPO, coatings and seamless gutters. That supports a stronger campaign than generic roof replacement: ‘Find where the roof system is actually failing before choosing the repair.’ I’d build inspection posts, repair-path FAQs, drainage content and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two California Bay Roofing-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.californiabayroofinginc.net/san-jose-roofing</t>
-  </si>
-  <si>
-    <t>Shefer Builder</t>
-  </si>
-  <si>
-    <t>Remodeling / ADU / Additions / General Remodel</t>
-  </si>
-  <si>
-    <t>Official contact page crawled Sep 9 publishes direct email, free estimates, ADU/garage conversion, room additions, remodeling and seven-day hours.</t>
-  </si>
-  <si>
-    <t>510-571-0060</t>
-  </si>
-  <si>
-    <t>sheferbuilder@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; seven-day hours; free estimate</t>
-  </si>
-  <si>
-    <t>Use one-contractor continuity across remodel, ADU and addition work to simplify a complex project decision.</t>
-  </si>
-  <si>
-    <t>ADU + addition decision-flow idea for Shefer Builder</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Shefer Builder’s current services and saw you handle remodeling, ADUs, garage conversions and room additions. Campaign angle: ‘Before choosing finishes, make the project path — scope, added space and build sequence — easy to understand.’ I’d turn that into ADU/addition FAQs, planning posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Shefer-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://sheferbuilder.com/contact-us/</t>
-  </si>
-  <si>
-    <t>Simmitri Inc.</t>
-  </si>
-  <si>
-    <t>Roofing / Solar Energy</t>
-  </si>
-  <si>
-    <t>Official contact page crawled Sep 13 publishes direct email, free online estimates and combined roofing/solar service, with the company stating it has provided roofing and solar energy service since 1995.</t>
-  </si>
-  <si>
-    <t>(408) 779-3333</t>
-  </si>
-  <si>
-    <t>info@simmitri.com</t>
-  </si>
-  <si>
-    <t>Direct email; free online estimate</t>
-  </si>
-  <si>
-    <t>Use combined roof-and-solar planning to help homeowners evaluate the roof condition before committing to a solar project.</t>
-  </si>
-  <si>
-    <t>Roof-before-solar planning campaign idea for Simmitri</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Simmitri’s current roofing and solar positioning and think the combined service supports a useful planning campaign: ‘Before adding a long-life solar system, make sure the roof underneath it is ready for the same horizon.’ I’d turn that into roof-readiness FAQs, solar-planning posts, estimate follow-ups and roof-plus-solar decision content. Same-Day Customer Growth Pack: $150 flat. Want two Simmitri-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://simmitri.com/contact-us/</t>
+    <t>Official site currently publishes a direct email, free estimates, 3D design support, an in-house licensed crew and broad remodeling/ADU services.</t>
+  </si>
+  <si>
+    <t>ayhremodelingandconstruction@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; long operating hours</t>
+  </si>
+  <si>
+    <t>Use 3D design support plus in-house construction as a visualize-before-you-build campaign for high-consideration remodel and ADU prospects.</t>
+  </si>
+  <si>
+    <t>3D-design-to-estimate campaign idea for AYH</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed AYH’s current San Jose site and noticed a strong customer story: 3D design support, an in-house licensed crew and free estimates across kitchens, bathrooms, ADUs and full-home work. I’d turn that into a ‘visualize it before you build it’ campaign with planning posts, remodel FAQs, inquiry follow-ups and estimate CTAs. Same-Day Customer Growth Pack: $150 flat. Want two AYH-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://ayhremodelingandconstruction.com/</t>
+  </si>
+  <si>
+    <t>Redwood Roofing</t>
+  </si>
+  <si>
+    <t>Roof Repair / Replacement / Inspection</t>
+  </si>
+  <si>
+    <t>San Jose / Los Gatos / Santa Cruz, CA</t>
+  </si>
+  <si>
+    <t>Official contact page crawled Sep 17 publishes a direct email, free estimates and a same-day or next-business-day response promise for estimate requests.</t>
+  </si>
+  <si>
+    <t>contact@redwoodroofing.com</t>
+  </si>
+  <si>
+    <t>Direct email; same-day/next-business-day response; free estimate</t>
+  </si>
+  <si>
+    <t>Turn fast estimate response plus inspection expertise into an urgency-without-pressure roof decision campaign.</t>
+  </si>
+  <si>
+    <t>Same-day roof-response campaign idea for Redwood Roofing</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Redwood Roofing’s current estimate page and noticed you already give homeowners something valuable during a stressful roof decision: a free estimate with same-day or next-business-day response. I’d turn that into an urgency-without-pressure campaign covering inspection, repair-vs-replacement questions, inquiry follow-ups and estimate CTAs. Same-Day Customer Growth Pack: $150 flat. Want two Redwood-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://redwoodroofing.com/contact-us/</t>
+  </si>
+  <si>
+    <t>Make It Simple Construction, Inc.</t>
+  </si>
+  <si>
+    <t>Full Home / Kitchen / Bathroom Remodeling</t>
+  </si>
+  <si>
+    <t>Official contact page publishes a direct named email, free estimates and broad Bay Area remodeling coverage, with positioning around guidance and no hidden costs.</t>
+  </si>
+  <si>
+    <t>jasmin@makeitsimpleinc.com</t>
+  </si>
+  <si>
+    <t>Direct named email; free estimate</t>
+  </si>
+  <si>
+    <t>Turn the company’s simplicity/no-hidden-cost positioning into a remodeling decision guide that reduces uncertainty before the estimate.</t>
+  </si>
+  <si>
+    <t>Make-the-remodel-simple campaign idea</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Make It Simple Construction’s current contact page and the strongest marketing angle is already in your name: helping homeowners understand what their remodel actually needs without hidden-cost anxiety. I’d turn that into planning posts, scope FAQs, inquiry follow-ups and estimate-ready messaging for kitchens, bathrooms and full-home projects. Same-Day Customer Growth Pack: $150 flat. Want two company-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://makeitsimpleinc.com/contact/</t>
+  </si>
+  <si>
+    <t>Top Tier Roofing</t>
+  </si>
+  <si>
+    <t>Roofing / Inspection / Replacement</t>
+  </si>
+  <si>
+    <t>Official contact page crawled Sep 13 publishes a direct named email, free roof inspections and free estimates, plus a prominent long-term warranty message.</t>
+  </si>
+  <si>
+    <t>david@toptierroofing.com</t>
+  </si>
+  <si>
+    <t>Direct named email; free inspection; free estimate</t>
+  </si>
+  <si>
+    <t>Turn free inspection plus long-term warranty positioning into a proof-and-protection campaign for homeowners comparing roof bids.</t>
+  </si>
+  <si>
+    <t>Inspection + warranty campaign idea for Top Tier Roofing</t>
+  </si>
+  <si>
+    <t>Hi David — I reviewed Top Tier Roofing’s current San Jose contact page and noticed a strong trust combination: free roof inspection, free estimate and prominent long-term warranty positioning. I’d turn that into inspection education, bid-comparison FAQs, warranty questions and estimate follow-ups that help homeowners evaluate more than price alone. Same-Day Customer Growth Pack: $150 flat. Want two Top Tier-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.toptierroofing.com/contact/</t>
+  </si>
+  <si>
+    <t>Silicon Valley Building Service and Repair</t>
+  </si>
+  <si>
+    <t>Remodeling / ADU / Additions / Garage Conversion</t>
+  </si>
+  <si>
+    <t>Official contact page currently publishes direct email, free estimates and online consultation booking for kitchens, bathrooms, whole-home remodeling, ADUs, additions and garage conversions.</t>
+  </si>
+  <si>
+    <t>info@siliconvalleybuilding.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; online booking</t>
+  </si>
+  <si>
+    <t>Use instant consultation booking plus broad design/build scope to create a project-readiness funnel that converts browsing homeowners into scheduled consultations.</t>
+  </si>
+  <si>
+    <t>Project-readiness booking campaign for Silicon Valley Building</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed your current San Jose contact flow and noticed prospects can move directly from project research to a free booked consultation. I’d build a project-readiness campaign around that path: ADU/remodel FAQs, scope-prep posts, inquiry follow-ups and clear booking CTAs. Same-Day Customer Growth Pack: $150 flat. Want two Silicon Valley Building-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://siliconvalleybuilding.com/contact</t>
+  </si>
+  <si>
+    <t>Eastman Roofing &amp; Waterproofing, Inc.</t>
+  </si>
+  <si>
+    <t>Roofing / Waterproofing / Inspection</t>
+  </si>
+  <si>
+    <t>San Jose / Silicon Valley, CA</t>
+  </si>
+  <si>
+    <t>Fresh local business data shows Eastman remains active in San Jose and emphasizes estimator photos, customer education, repair-versus-replacement options and a holistic roof/building approach.</t>
+  </si>
+  <si>
+    <t>Official website/contact route; local San Jose office</t>
+  </si>
+  <si>
+    <t>Turn estimator photos and repair-vs-replacement education into a diagnose-before-you-buy content campaign.</t>
+  </si>
+  <si>
+    <t>Photo-diagnosis roofing campaign idea for Eastman</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Eastman’s current positioning and the strongest customer-education story is the diagnostic process: inspect the roof, document what is happening, explain whether the issue is roofing or something broader, then discuss options. I’d turn that into photo-led inspection posts, repair-vs-replacement FAQs and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat.</t>
+  </si>
+  <si>
+    <t>https://www.eastmanroofing.com/</t>
+  </si>
+  <si>
+    <t>Los Gatos Roofing</t>
+  </si>
+  <si>
+    <t>Roofing / Gutters / Insulation</t>
+  </si>
+  <si>
+    <t>Fresh local business data shows a large active review footprint and company positioning around in-house crews, material choice and homeowner-specific roof recommendations.</t>
+  </si>
+  <si>
+    <t>Official website/contact route; San Jose office</t>
+  </si>
+  <si>
+    <t>Turn in-house crews and needs-based material selection into a craftsmanship-and-choice campaign for homeowners comparing roofing companies.</t>
+  </si>
+  <si>
+    <t>In-house crew + roof-choice campaign idea for Los Gatos Roofing</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Los Gatos Roofing’s current positioning and noticed two useful trust differentiators: in-house crews and choosing roofing systems around the homeowner’s actual needs rather than pushing one manufacturer. I’d turn that into comparison FAQs, material-choice posts, craftsmanship content and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat.</t>
+  </si>
+  <si>
+    <t>https://losgatosroofing.com/</t>
+  </si>
+  <si>
+    <t>Roof By Tom</t>
+  </si>
+  <si>
+    <t>Residential / Commercial Roofing</t>
+  </si>
+  <si>
+    <t>Official San Jose page currently advertises free estimates, inspection with explanation of findings, written estimates and same-day callbacks on most requests.</t>
+  </si>
+  <si>
+    <t>roofbytom@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; same-day callback on most requests; free estimate</t>
+  </si>
+  <si>
+    <t>Turn inspect-explain-write-the-estimate into a transparent roof decision campaign.</t>
+  </si>
+  <si>
+    <t>Inspect → explain → written estimate campaign for Roof By Tom</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Roof By Tom’s current San Jose page and noticed a clear customer-friendly sequence: inspect the roof, explain what you see and send a written estimate, with same-day callbacks on most requests. I’d turn that into inspection posts, repair/replacement FAQs and estimate follow-ups that reinforce that transparency. Same-Day Customer Growth Pack: $150 flat. Want two Roof By Tom-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://roofbytom.com/service-areas/san-jose/</t>
+  </si>
+  <si>
+    <t>Tomlinson Construction</t>
+  </si>
+  <si>
+    <t>Kitchen / Bathroom / Additions / Remodeling</t>
+  </si>
+  <si>
+    <t>Official contact page currently publishes a direct email, San Jose showroom and free estimates across kitchen, bathroom, interior/exterior remodeling, additions, cabinetry and related work.</t>
+  </si>
+  <si>
+    <t>info@tomlinsonconstruction.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; physical showroom</t>
+  </si>
+  <si>
+    <t>Use the showroom plus broad remodeling scope to create a see-options-first campaign that moves homeowners from inspiration to estimate.</t>
+  </si>
+  <si>
+    <t>Showroom-to-estimate remodeling campaign idea for Tomlinson</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Tomlinson Construction’s current San Jose contact page and noticed you have something many remodelers do not: a local showroom plus a broad range of kitchen, bath, addition and finish options. I’d turn that into a ‘see the options, narrow the scope, then estimate’ campaign with planning posts, FAQs and inquiry follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Tomlinson-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.tomlinsonconstruction.com/contact.html</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -573,6 +537,9 @@
     <t>New verified lead added 2026-09-12; no outreach recorded. Use individualized initial pitch.</t>
   </si>
   <si>
+    <t>Rotated out of fresh queue 2026-09-12; no outreach found in connected Gmail checks.</t>
+  </si>
+  <si>
     <t>FloodDry Water Damage Restoration</t>
   </si>
   <si>
@@ -798,18 +765,12 @@
     <t>2026-09-12</t>
   </si>
   <si>
-    <t>Rotated out of fresh queue 2026-09-12; no outreach found in connected Gmail checks.</t>
-  </si>
-  <si>
     <t>CostLess Heating &amp; Cooling</t>
   </si>
   <si>
     <t>2026-09-06</t>
   </si>
   <si>
-    <t>Los Gatos Roofing</t>
-  </si>
-  <si>
     <t>Roofs By Reveille, Inc</t>
   </si>
   <si>
@@ -843,15 +804,9 @@
     <t>South Bay Roofing CO</t>
   </si>
   <si>
-    <t>Eastman Roofing &amp; Waterproofing, Inc.</t>
-  </si>
-  <si>
     <t>The Roofer Bros</t>
   </si>
   <si>
-    <t>Roof By Tom</t>
-  </si>
-  <si>
     <t>FairPrice Heating &amp; Cooling</t>
   </si>
   <si>
@@ -865,9 +820,6 @@
   </si>
   <si>
     <t>Archived from active Top 10 on 2026-09-11; no outreach recorded.</t>
-  </si>
-  <si>
-    <t>Top Tier Roofing</t>
   </si>
   <si>
     <t>Verified Date</t>
@@ -1576,32 +1528,30 @@
       <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -1609,46 +1559,44 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="N3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1656,46 +1604,44 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="N4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1703,46 +1649,44 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="N5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1750,46 +1694,44 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="N6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1797,10 +1739,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>17</v>
@@ -1809,34 +1751,32 @@
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="N7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1844,46 +1784,42 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>86</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1891,10 +1827,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>17</v>
@@ -1903,34 +1839,30 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>96</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="N9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1938,46 +1870,44 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>105</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="N10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1985,10 +1915,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>17</v>
@@ -1997,34 +1927,32 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>115</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="N11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O11" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2063,142 +1991,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2232,58 +2160,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2294,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -2303,7 +2231,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -2315,10 +2243,10 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R2" s="3">
         <v>150</v>
@@ -2326,13 +2254,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2341,7 +2269,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -2350,13 +2278,15 @@
         <v>0</v>
       </c>
       <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="N3" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R3" s="3">
         <v>150</v>
@@ -2364,13 +2294,13 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2379,7 +2309,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -2391,10 +2321,10 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="R4" s="3">
         <v>150</v>
@@ -2402,13 +2332,13 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -2417,7 +2347,7 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -2426,15 +2356,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="2"/>
-      <c r="N5" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="R5" s="3">
         <v>150</v>
@@ -2442,13 +2370,13 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2457,7 +2385,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -2466,13 +2394,15 @@
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>168</v>
+      </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="R6" s="3">
         <v>150</v>
@@ -2480,13 +2410,13 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2495,7 +2425,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -2505,14 +2435,14 @@
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -2520,14 +2450,12 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>86</v>
-      </c>
+      <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -2535,7 +2463,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -2547,10 +2475,10 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="R8" s="3">
         <v>150</v>
@@ -2558,14 +2486,12 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -2573,7 +2499,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -2585,10 +2511,10 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="R9" s="3">
         <v>150</v>
@@ -2596,13 +2522,13 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2611,7 +2537,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -2620,13 +2546,15 @@
         <v>0</v>
       </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="N10" s="2" t="s">
+        <v>168</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -2634,13 +2562,13 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2649,7 +2577,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -2661,10 +2589,10 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="R11" s="3">
         <v>150</v>
@@ -2672,28 +2600,28 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -2703,7 +2631,7 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -2714,32 +2642,32 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -2749,7 +2677,7 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2760,26 +2688,26 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -2789,7 +2717,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2800,26 +2728,26 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -2829,7 +2757,7 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2840,26 +2768,26 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -2869,7 +2797,7 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -2880,26 +2808,26 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -2909,7 +2837,7 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -2920,26 +2848,26 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -2949,7 +2877,7 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -2960,26 +2888,26 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -2989,7 +2917,7 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -3000,26 +2928,26 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -3029,7 +2957,7 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -3040,26 +2968,26 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -3069,7 +2997,7 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3080,28 +3008,28 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3111,7 +3039,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3122,26 +3050,26 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3151,7 +3079,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3162,26 +3090,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3191,7 +3119,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3202,26 +3130,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -3231,7 +3159,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3242,26 +3170,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -3271,7 +3199,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -3335,67 +3263,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -3404,13 +3332,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3418,10 +3346,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -3430,13 +3358,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3444,10 +3372,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -3456,28 +3384,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -3486,13 +3414,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3500,10 +3428,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -3512,13 +3440,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3526,10 +3454,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -3538,13 +3466,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -3552,10 +3480,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -3564,28 +3492,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -3594,13 +3522,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3608,10 +3536,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -3620,13 +3548,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3634,10 +3562,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -3646,13 +3574,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -3660,10 +3588,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -3672,13 +3600,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -3686,10 +3614,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -3698,13 +3626,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -3712,10 +3640,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -3724,13 +3652,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -3738,10 +3666,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -3750,13 +3678,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -3764,10 +3692,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -3776,13 +3704,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -3790,10 +3718,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -3825,36 +3753,36 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -3865,19 +3793,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>255</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3888,17 +3816,17 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>258</v>
+        <v>84</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -3909,20 +3837,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -3932,19 +3860,19 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -3955,17 +3883,17 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -3976,17 +3904,17 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -3997,17 +3925,17 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -4018,17 +3946,17 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -4039,19 +3967,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -4062,17 +3990,17 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -4083,17 +4011,17 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -4104,17 +4032,17 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -4125,19 +4053,19 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>255</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -4148,17 +4076,17 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>270</v>
+        <v>75</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -4169,17 +4097,17 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -4190,17 +4118,17 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>272</v>
+        <v>92</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -4211,19 +4139,19 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>255</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -4234,19 +4162,19 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>255</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -4257,19 +4185,19 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>255</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -4280,19 +4208,19 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>278</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -4303,11 +4231,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>255</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -4339,13 +4267,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4356,196 +4284,192 @@
         <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>86</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>96</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4580,7 +4504,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -4590,120 +4514,120 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contact Ready")</f>
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -4729,98 +4653,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -4839,24 +4763,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="2">
         <v>10</v>
@@ -4868,7 +4792,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="321">
   <si>
     <t>Rank</t>
   </si>
@@ -85,7 +85,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>Official contact page currently advertises free on-site consultation, written estimates and usually same-day email replies, creating a fast-response path for high-value remodeling inquiries.</t>
+    <t>Official contact page offers a free on-site consultation, written estimate and usually same-day email reply, creating an unusually fast response path for high-value remodeling inquiries.</t>
   </si>
   <si>
     <t>hello.hbdesignconstruction@gmail.com</t>
@@ -100,85 +100,118 @@
     <t>Pre-consultation remodeling campaign idea for HB Design</t>
   </si>
   <si>
-    <t>Hi — I reviewed HB Design &amp; Construction’s current consultation process and noticed you already promise a free on-site consultation, written estimate and fast reply. I’d turn that into a customer-ready pre-consultation campaign that helps homeowners organize scope, priorities and questions before you arrive. The $150 Same-Day Customer Growth Pack can include social/Google posts, FAQs, inquiry follow-ups and estimate-ready messaging built around your actual services. Want two HB-specific examples first?</t>
+    <t>Hi — I reviewed HB Design &amp; Construction’s current consultation process and noticed you already offer a free on-site consultation, written estimate and usually same-day email reply. I’d turn that into a customer-ready pre-consultation campaign that helps homeowners organize scope, priorities and questions before you arrive. The $150 Same-Day Customer Growth Pack can include social/Google posts, FAQs, inquiry follow-ups and estimate-ready messaging built around your actual services. Want two HB-specific examples first?</t>
   </si>
   <si>
     <t>https://hbdesignconstruction.com/contact</t>
   </si>
   <si>
-    <t>2026-09-17</t>
+    <t>2026-09-18</t>
   </si>
   <si>
     <t>Contact Ready</t>
   </si>
   <si>
-    <t>AYH Remodeling &amp; Construction Inc</t>
-  </si>
-  <si>
-    <t>Kitchen / Bathroom / ADU / Full Home Remodeling</t>
+    <t>QualiBuild LLC</t>
+  </si>
+  <si>
+    <t>Kitchen / Bathroom / ADU Remodeling</t>
+  </si>
+  <si>
+    <t>Sunnyvale / San Jose / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official site was crawled four days ago and offers free estimates, owner-direct service, on-site visits usually within 1–2 days, written estimates and photo/video-based project scoping.</t>
+  </si>
+  <si>
+    <t>info@qualibuildca.com</t>
+  </si>
+  <si>
+    <t>Direct email; owners directly involved; on-site visits usually within 1–2 days</t>
+  </si>
+  <si>
+    <t>Turn the existing send-us-photos/video intake into a visual project-readiness campaign that pre-qualifies kitchen, bath and ADU prospects before the visit.</t>
+  </si>
+  <si>
+    <t>Photo-to-estimate campaign idea for QualiBuild</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed QualiBuild’s current project intake and noticed you already invite homeowners to send photos, video and rough dimensions before an on-site visit. I’d turn that into a simple visual project-readiness campaign with scope-prep posts, FAQs, inquiry follow-ups and estimate CTAs for kitchen, bath and ADU prospects. Same-Day Customer Growth Pack: $150 flat. Want two QualiBuild-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://qualibuildca.com/</t>
+  </si>
+  <si>
+    <t>Redwood Roofing</t>
+  </si>
+  <si>
+    <t>Roof Repair / Replacement / Inspection</t>
+  </si>
+  <si>
+    <t>Los Gatos / San Jose / Santa Cruz, CA</t>
+  </si>
+  <si>
+    <t>Official contact page crawled six days ago publishes a direct email, free estimates and a same-day callback promise, or next business day after hours.</t>
+  </si>
+  <si>
+    <t>contact@redwoodroofing.com</t>
+  </si>
+  <si>
+    <t>Direct email; same-day/next-business-day response; free estimate</t>
+  </si>
+  <si>
+    <t>Turn fast estimate response plus inspection expertise into an urgency-without-pressure roof decision campaign.</t>
+  </si>
+  <si>
+    <t>Same-day roof-response campaign idea for Redwood Roofing</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Redwood Roofing’s current estimate page and noticed you already give homeowners something valuable during a stressful roof decision: a free estimate with same-day or next-business-day response. I’d turn that into an urgency-without-pressure campaign covering inspection, repair-vs-replacement questions, inquiry follow-ups and estimate CTAs. Same-Day Customer Growth Pack: $150 flat. Want two Redwood-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://redwoodroofing.com/contact-us/</t>
+  </si>
+  <si>
+    <t>Premier Roofing &amp; Retro-Fit</t>
+  </si>
+  <si>
+    <t>Roofing / Retro-Fit</t>
+  </si>
+  <si>
+    <t>Santa Clara / South Bay, CA</t>
+  </si>
+  <si>
+    <t>Official contact page advertises a free same-day roofing quote, publishes a direct email and maintains weekday and Saturday business hours.</t>
+  </si>
+  <si>
+    <t>Info@premierroofingretrofit.com</t>
+  </si>
+  <si>
+    <t>Direct email; free same-day quote; Saturday hours</t>
+  </si>
+  <si>
+    <t>Build a same-day-quote campaign that tells homeowners exactly what to send before requesting a quote and reduces friction around urgent roof decisions.</t>
+  </si>
+  <si>
+    <t>Same-day quote campaign for Premier Roofing</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Premier Roofing &amp; Retro-Fit’s current Santa Clara contact page and noticed you already promote a free same-day roofing quote. I’d turn that speed promise into a customer-ready campaign showing homeowners what information to send, what to expect next and how to compare repair versus replacement. Same-Day Customer Growth Pack: $150 flat. Want two Premier-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://premierroofingretrofit.com/contact-us/</t>
+  </si>
+  <si>
+    <t>Make It Simple Construction, Inc.</t>
+  </si>
+  <si>
+    <t>Full Home / Kitchen / Bathroom Remodeling</t>
   </si>
   <si>
     <t>San Jose / Bay Area, CA</t>
   </si>
   <si>
-    <t>Official site currently publishes a direct email, free estimates, 3D design support, an in-house licensed crew and broad remodeling/ADU services.</t>
-  </si>
-  <si>
-    <t>ayhremodelingandconstruction@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; long operating hours</t>
-  </si>
-  <si>
-    <t>Use 3D design support plus in-house construction as a visualize-before-you-build campaign for high-consideration remodel and ADU prospects.</t>
-  </si>
-  <si>
-    <t>3D-design-to-estimate campaign idea for AYH</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed AYH’s current San Jose site and noticed a strong customer story: 3D design support, an in-house licensed crew and free estimates across kitchens, bathrooms, ADUs and full-home work. I’d turn that into a ‘visualize it before you build it’ campaign with planning posts, remodel FAQs, inquiry follow-ups and estimate CTAs. Same-Day Customer Growth Pack: $150 flat. Want two AYH-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://ayhremodelingandconstruction.com/</t>
-  </si>
-  <si>
-    <t>Redwood Roofing</t>
-  </si>
-  <si>
-    <t>Roof Repair / Replacement / Inspection</t>
-  </si>
-  <si>
-    <t>San Jose / Los Gatos / Santa Cruz, CA</t>
-  </si>
-  <si>
-    <t>Official contact page crawled Sep 17 publishes a direct email, free estimates and a same-day or next-business-day response promise for estimate requests.</t>
-  </si>
-  <si>
-    <t>contact@redwoodroofing.com</t>
-  </si>
-  <si>
-    <t>Direct email; same-day/next-business-day response; free estimate</t>
-  </si>
-  <si>
-    <t>Turn fast estimate response plus inspection expertise into an urgency-without-pressure roof decision campaign.</t>
-  </si>
-  <si>
-    <t>Same-day roof-response campaign idea for Redwood Roofing</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Redwood Roofing’s current estimate page and noticed you already give homeowners something valuable during a stressful roof decision: a free estimate with same-day or next-business-day response. I’d turn that into an urgency-without-pressure campaign covering inspection, repair-vs-replacement questions, inquiry follow-ups and estimate CTAs. Same-Day Customer Growth Pack: $150 flat. Want two Redwood-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://redwoodroofing.com/contact-us/</t>
-  </si>
-  <si>
-    <t>Make It Simple Construction, Inc.</t>
-  </si>
-  <si>
-    <t>Full Home / Kitchen / Bathroom Remodeling</t>
-  </si>
-  <si>
-    <t>Official contact page publishes a direct named email, free estimates and broad Bay Area remodeling coverage, with positioning around guidance and no hidden costs.</t>
+    <t>Official contact page publishes a direct named email, free estimates and positioning around guidance, no hidden costs and family ownership.</t>
   </si>
   <si>
     <t>jasmin@makeitsimpleinc.com</t>
@@ -187,7 +220,7 @@
     <t>Direct named email; free estimate</t>
   </si>
   <si>
-    <t>Turn the company’s simplicity/no-hidden-cost positioning into a remodeling decision guide that reduces uncertainty before the estimate.</t>
+    <t>Turn the simplicity/no-hidden-cost positioning into a remodeling decision guide that reduces uncertainty before the estimate.</t>
   </si>
   <si>
     <t>Make-the-remodel-simple campaign idea</t>
@@ -199,163 +232,142 @@
     <t>https://makeitsimpleinc.com/contact/</t>
   </si>
   <si>
-    <t>Top Tier Roofing</t>
-  </si>
-  <si>
-    <t>Roofing / Inspection / Replacement</t>
-  </si>
-  <si>
-    <t>Official contact page crawled Sep 13 publishes a direct named email, free roof inspections and free estimates, plus a prominent long-term warranty message.</t>
-  </si>
-  <si>
-    <t>david@toptierroofing.com</t>
-  </si>
-  <si>
-    <t>Direct named email; free inspection; free estimate</t>
-  </si>
-  <si>
-    <t>Turn free inspection plus long-term warranty positioning into a proof-and-protection campaign for homeowners comparing roof bids.</t>
-  </si>
-  <si>
-    <t>Inspection + warranty campaign idea for Top Tier Roofing</t>
-  </si>
-  <si>
-    <t>Hi David — I reviewed Top Tier Roofing’s current San Jose contact page and noticed a strong trust combination: free roof inspection, free estimate and prominent long-term warranty positioning. I’d turn that into inspection education, bid-comparison FAQs, warranty questions and estimate follow-ups that help homeowners evaluate more than price alone. Same-Day Customer Growth Pack: $150 flat. Want two Top Tier-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.toptierroofing.com/contact/</t>
-  </si>
-  <si>
-    <t>Silicon Valley Building Service and Repair</t>
-  </si>
-  <si>
-    <t>Remodeling / ADU / Additions / Garage Conversion</t>
-  </si>
-  <si>
-    <t>Official contact page currently publishes direct email, free estimates and online consultation booking for kitchens, bathrooms, whole-home remodeling, ADUs, additions and garage conversions.</t>
-  </si>
-  <si>
-    <t>info@siliconvalleybuilding.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; online booking</t>
-  </si>
-  <si>
-    <t>Use instant consultation booking plus broad design/build scope to create a project-readiness funnel that converts browsing homeowners into scheduled consultations.</t>
-  </si>
-  <si>
-    <t>Project-readiness booking campaign for Silicon Valley Building</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed your current San Jose contact flow and noticed prospects can move directly from project research to a free booked consultation. I’d build a project-readiness campaign around that path: ADU/remodel FAQs, scope-prep posts, inquiry follow-ups and clear booking CTAs. Same-Day Customer Growth Pack: $150 flat. Want two Silicon Valley Building-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://siliconvalleybuilding.com/contact</t>
-  </si>
-  <si>
-    <t>Eastman Roofing &amp; Waterproofing, Inc.</t>
-  </si>
-  <si>
-    <t>Roofing / Waterproofing / Inspection</t>
-  </si>
-  <si>
-    <t>San Jose / Silicon Valley, CA</t>
-  </si>
-  <si>
-    <t>Fresh local business data shows Eastman remains active in San Jose and emphasizes estimator photos, customer education, repair-versus-replacement options and a holistic roof/building approach.</t>
-  </si>
-  <si>
-    <t>Official website/contact route; local San Jose office</t>
-  </si>
-  <si>
-    <t>Turn estimator photos and repair-vs-replacement education into a diagnose-before-you-buy content campaign.</t>
-  </si>
-  <si>
-    <t>Photo-diagnosis roofing campaign idea for Eastman</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Eastman’s current positioning and the strongest customer-education story is the diagnostic process: inspect the roof, document what is happening, explain whether the issue is roofing or something broader, then discuss options. I’d turn that into photo-led inspection posts, repair-vs-replacement FAQs and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat.</t>
-  </si>
-  <si>
-    <t>https://www.eastmanroofing.com/</t>
-  </si>
-  <si>
-    <t>Los Gatos Roofing</t>
-  </si>
-  <si>
-    <t>Roofing / Gutters / Insulation</t>
-  </si>
-  <si>
-    <t>Fresh local business data shows a large active review footprint and company positioning around in-house crews, material choice and homeowner-specific roof recommendations.</t>
-  </si>
-  <si>
-    <t>Official website/contact route; San Jose office</t>
-  </si>
-  <si>
-    <t>Turn in-house crews and needs-based material selection into a craftsmanship-and-choice campaign for homeowners comparing roofing companies.</t>
-  </si>
-  <si>
-    <t>In-house crew + roof-choice campaign idea for Los Gatos Roofing</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Los Gatos Roofing’s current positioning and noticed two useful trust differentiators: in-house crews and choosing roofing systems around the homeowner’s actual needs rather than pushing one manufacturer. I’d turn that into comparison FAQs, material-choice posts, craftsmanship content and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat.</t>
-  </si>
-  <si>
-    <t>https://losgatosroofing.com/</t>
-  </si>
-  <si>
-    <t>Roof By Tom</t>
-  </si>
-  <si>
-    <t>Residential / Commercial Roofing</t>
-  </si>
-  <si>
-    <t>Official San Jose page currently advertises free estimates, inspection with explanation of findings, written estimates and same-day callbacks on most requests.</t>
-  </si>
-  <si>
-    <t>roofbytom@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; same-day callback on most requests; free estimate</t>
-  </si>
-  <si>
-    <t>Turn inspect-explain-write-the-estimate into a transparent roof decision campaign.</t>
-  </si>
-  <si>
-    <t>Inspect → explain → written estimate campaign for Roof By Tom</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Roof By Tom’s current San Jose page and noticed a clear customer-friendly sequence: inspect the roof, explain what you see and send a written estimate, with same-day callbacks on most requests. I’d turn that into inspection posts, repair/replacement FAQs and estimate follow-ups that reinforce that transparency. Same-Day Customer Growth Pack: $150 flat. Want two Roof By Tom-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://roofbytom.com/service-areas/san-jose/</t>
-  </si>
-  <si>
-    <t>Tomlinson Construction</t>
-  </si>
-  <si>
-    <t>Kitchen / Bathroom / Additions / Remodeling</t>
-  </si>
-  <si>
-    <t>Official contact page currently publishes a direct email, San Jose showroom and free estimates across kitchen, bathroom, interior/exterior remodeling, additions, cabinetry and related work.</t>
-  </si>
-  <si>
-    <t>info@tomlinsonconstruction.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; physical showroom</t>
-  </si>
-  <si>
-    <t>Use the showroom plus broad remodeling scope to create a see-options-first campaign that moves homeowners from inspiration to estimate.</t>
-  </si>
-  <si>
-    <t>Showroom-to-estimate remodeling campaign idea for Tomlinson</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Tomlinson Construction’s current San Jose contact page and noticed you have something many remodelers do not: a local showroom plus a broad range of kitchen, bath, addition and finish options. I’d turn that into a ‘see the options, narrow the scope, then estimate’ campaign with planning posts, FAQs and inquiry follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Tomlinson-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.tomlinsonconstruction.com/contact.html</t>
+    <t>BLUECON</t>
+  </si>
+  <si>
+    <t>Remodeling / ADU / Commercial Renovation</t>
+  </si>
+  <si>
+    <t>Official site crawled two days ago publishes a direct project email, San Jose office, free-estimate CTA and remodeling, ADU and commercial-renovation positioning.</t>
+  </si>
+  <si>
+    <t>build@blue-con.org</t>
+  </si>
+  <si>
+    <t>Direct project email; free estimate; San Jose office</t>
+  </si>
+  <si>
+    <t>Turn the broad remodel/ADU/commercial portfolio into a choose-your-project-path campaign that routes prospects to the right estimate conversation.</t>
+  </si>
+  <si>
+    <t>Project-path campaign idea for BLUECON</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed BLUECON’s current San Jose site and noticed you span home remodeling, ADUs and commercial renovation. I’d turn that breadth into a simple project-path campaign that helps prospects identify their project type, prepare the right details and move toward a free estimate. Same-Day Customer Growth Pack: $150 flat. Want two BLUECON-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://blueconbuilders.net/</t>
+  </si>
+  <si>
+    <t>Blues Bros</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>Official contact page publishes a direct email, financing availability, free in-home estimates and a stated response target within 24 hours.</t>
+  </si>
+  <si>
+    <t>info@bluesbros.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated response within 24 hours</t>
+  </si>
+  <si>
+    <t>Turn the 24-hour estimate response plus financing availability into a remodel-readiness campaign addressing scope, budget questions and next steps before the consultation.</t>
+  </si>
+  <si>
+    <t>24-hour remodel-response campaign idea for Blues Bros</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Blues Bros’ current San Jose contact page and noticed you combine free in-home estimates, a stated 24-hour response target and financing availability. I’d turn that into a remodel-readiness campaign covering scope questions, consultation prep, financing FAQs and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Blues Bros-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://bluesbros.com/contact/</t>
+  </si>
+  <si>
+    <t>Home Quality Remodeling</t>
+  </si>
+  <si>
+    <t>Home Remodeling</t>
+  </si>
+  <si>
+    <t>Official contact page publishes a direct San Jose email and a free on-site estimate intake that asks project type, financing interest and accepts plans or drawings.</t>
+  </si>
+  <si>
+    <t>inquiry@hqrpro.com</t>
+  </si>
+  <si>
+    <t>Direct email; San Jose office; free on-site estimate</t>
+  </si>
+  <si>
+    <t>Turn the existing estimate intake into a project-file-prep campaign that encourages prospects to submit plans, inspiration and financing questions before the visit.</t>
+  </si>
+  <si>
+    <t>Project-file prep campaign for HQR</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed HQR’s current San Jose estimate flow and noticed you already ask homeowners for project type, financing interest and even plans or drawings. I’d turn that into a project-file-prep campaign that helps prospects arrive with better information before the on-site estimate. Same-Day Customer Growth Pack: $150 flat. Want two HQR-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.homequalityremodeling.com/contact</t>
+  </si>
+  <si>
+    <t>Imperia Roofing &amp; Exteriors</t>
+  </si>
+  <si>
+    <t>Roofing / Siding / Stucco / Windows / Exterior Renovation</t>
+  </si>
+  <si>
+    <t>Santa Clara / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Recent official Santa Clara pages publish a direct email, free-estimate CTA and a broad roofing/exteriors mix including siding, stucco, painting and windows.</t>
+  </si>
+  <si>
+    <t>info@imperiare.com</t>
+  </si>
+  <si>
+    <t>Direct email; Santa Clara office; free estimate</t>
+  </si>
+  <si>
+    <t>Create an exterior-project selector campaign that helps property owners distinguish roof-only needs from broader siding, stucco, painting or window work before requesting an estimate.</t>
+  </si>
+  <si>
+    <t>Exterior project-selector campaign for Imperia</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Imperia’s current Santa Clara pages and noticed you cover far more than roofing: siding, stucco, painting and windows as well. I’d turn that into an exterior project-selector campaign that helps homeowners identify the right scope before requesting a free estimate, with FAQs and follow-up copy for cross-service opportunities. Same-Day Customer Growth Pack: $150 flat. Want two Imperia-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://imperiare.com/tpo/santa-clara/</t>
+  </si>
+  <si>
+    <t>Silicon Valley Chimney Sweep</t>
+  </si>
+  <si>
+    <t>Chimney Inspection / Cleaning / Repair</t>
+  </si>
+  <si>
+    <t>Official contact page crawled last week publishes a direct email, same-day replies, same-day appointments before noon, free written estimates and photo-based evaluation.</t>
+  </si>
+  <si>
+    <t>info@svchimneysweep.com</t>
+  </si>
+  <si>
+    <t>Direct email; same-day reply; photo intake; free written estimate</t>
+  </si>
+  <si>
+    <t>Turn send-us-a-photo plus same-day response into a visual chimney triage campaign that helps homeowners understand whether they need cleaning, inspection or repair.</t>
+  </si>
+  <si>
+    <t>Photo-first chimney campaign idea</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Silicon Valley Chimney Sweep’s current contact flow and noticed a strong customer-friendly combination: homeowners can email photos, receive a same-day reply and request a free written estimate. I’d turn that into a photo-first chimney triage campaign with symptom posts, FAQs, inquiry follow-ups and estimate CTAs. Same-Day Customer Growth Pack: $150 flat. Want two company-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://svchimneysweep.com/contact-us/</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -534,243 +546,243 @@
     <t>Offer Value $</t>
   </si>
   <si>
-    <t>New verified lead added 2026-09-12; no outreach recorded. Use individualized initial pitch.</t>
+    <t>FloodDry Water Damage Restoration</t>
+  </si>
+  <si>
+    <t>Follow-up</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:50:24-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-08T16:45:47-07:00</t>
+  </si>
+  <si>
+    <t>Contacted</t>
+  </si>
+  <si>
+    <t>Two verified outbound emails, no inbound reply found through 2026-09-12. Do not send another cold touch now.</t>
+  </si>
+  <si>
+    <t>Therma Tech</t>
+  </si>
+  <si>
+    <t>2026-09-05T20:01:38-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-07T13:35:02-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-07T14:19:35-07:00</t>
+  </si>
+  <si>
+    <t>Three verified outbound emails across two connected Gmail accounts; no inbound reply found through 2026-09-12. Stop cold follow-up unless they reply.</t>
+  </si>
+  <si>
+    <t>Dansel Restoration</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:49:58-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>One verified outbound email; no inbound reply found through 2026-09-12. One final respectful follow-up is permissible, then stop unless they reply.</t>
+  </si>
+  <si>
+    <t>California First Roofing</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:39:21-07:00</t>
+  </si>
+  <si>
+    <t>US Creative Restoration</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:53:01-07:00</t>
+  </si>
+  <si>
+    <t>One verified outbound email; no reply found through 2026-09-12. Eligible for at most one respectful follow-up.</t>
+  </si>
+  <si>
+    <t>WJM Builders</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:30:53-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>Clean Roofing</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:42:04-07:00</t>
+  </si>
+  <si>
+    <t>Solar Energy Consultants</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:25:44-07:00</t>
+  </si>
+  <si>
+    <t>Mayer's Construction</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:31:58-07:00</t>
+  </si>
+  <si>
+    <t>EVS Mechanical</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:32:27-07:00</t>
+  </si>
+  <si>
+    <t>Dueling Trowels Concrete Solutions</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:39:44-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:20:39-07:00</t>
+  </si>
+  <si>
+    <t>Two verified outbound emails; no reply found through 2026-09-12. Do not send another cold touch now.</t>
+  </si>
+  <si>
+    <t>GBD Concrete</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:54:30-07:00</t>
+  </si>
+  <si>
+    <t>John Molina Concrete</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:46:13-07:00</t>
+  </si>
+  <si>
+    <t>Precision Concrete Inc</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:40:53-07:00</t>
+  </si>
+  <si>
+    <t>One Day Complete Repipe</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:35:59-07:00</t>
+  </si>
+  <si>
+    <t>First Touch Evidence</t>
+  </si>
+  <si>
+    <t>FU1 Evidence</t>
+  </si>
+  <si>
+    <t>FU2 Evidence</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a074aa18c4a15e5</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07d94dc355abc7</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07dbda8027b039</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07537695be159d</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0753a7d53e5a5c</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0753ad793984cf</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0763c06f9e9dc5</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0753be59b49989</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07540c8b9fd4bc</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075443349aa830</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075449a2403271</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a08369d9f6b09c0</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0754701539a56d</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075485ca2a3fef</t>
+  </si>
+  <si>
+    <t>Precision Heating &amp; Cooling</t>
+  </si>
+  <si>
+    <t>2026-09-06T01:37:52-07:00</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075ddee6716e8a</t>
+  </si>
+  <si>
+    <t>Historical send discovered during Sep 12 audit; no reply found in connected Gmail search.</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07640ae5a69379</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a076456505c6304</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0764664a2b1202</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07646d6dbd3474</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0764fa024df1f4</t>
+  </si>
+  <si>
+    <t>Archived</t>
+  </si>
+  <si>
+    <t>Leader Restoration</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
   </si>
   <si>
     <t>Rotated out of fresh queue 2026-09-12; no outreach found in connected Gmail checks.</t>
   </si>
   <si>
-    <t>FloodDry Water Damage Restoration</t>
-  </si>
-  <si>
-    <t>Follow-up</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:50:24-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
-    <t>2026-09-08T16:45:47-07:00</t>
-  </si>
-  <si>
-    <t>Contacted</t>
-  </si>
-  <si>
-    <t>Two verified outbound emails, no inbound reply found through 2026-09-12. Do not send another cold touch now.</t>
-  </si>
-  <si>
-    <t>Therma Tech</t>
-  </si>
-  <si>
-    <t>2026-09-05T20:01:38-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-07T13:35:02-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-07T14:19:35-07:00</t>
-  </si>
-  <si>
-    <t>Three verified outbound emails across two connected Gmail accounts; no inbound reply found through 2026-09-12. Stop cold follow-up unless they reply.</t>
-  </si>
-  <si>
-    <t>Dansel Restoration</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:49:58-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>One verified outbound email; no inbound reply found through 2026-09-12. One final respectful follow-up is permissible, then stop unless they reply.</t>
-  </si>
-  <si>
-    <t>California First Roofing</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:39:21-07:00</t>
-  </si>
-  <si>
-    <t>US Creative Restoration</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:53:01-07:00</t>
-  </si>
-  <si>
-    <t>One verified outbound email; no reply found through 2026-09-12. Eligible for at most one respectful follow-up.</t>
-  </si>
-  <si>
-    <t>WJM Builders</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:30:53-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
-  </si>
-  <si>
-    <t>Clean Roofing</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:42:04-07:00</t>
-  </si>
-  <si>
-    <t>Solar Energy Consultants</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:25:44-07:00</t>
-  </si>
-  <si>
-    <t>Mayer's Construction</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:31:58-07:00</t>
-  </si>
-  <si>
-    <t>EVS Mechanical</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:32:27-07:00</t>
-  </si>
-  <si>
-    <t>Dueling Trowels Concrete Solutions</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:39:44-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:20:39-07:00</t>
-  </si>
-  <si>
-    <t>Two verified outbound emails; no reply found through 2026-09-12. Do not send another cold touch now.</t>
-  </si>
-  <si>
-    <t>GBD Concrete</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:54:30-07:00</t>
-  </si>
-  <si>
-    <t>John Molina Concrete</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:46:13-07:00</t>
-  </si>
-  <si>
-    <t>Precision Concrete Inc</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:40:53-07:00</t>
-  </si>
-  <si>
-    <t>One Day Complete Repipe</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:35:59-07:00</t>
-  </si>
-  <si>
-    <t>First Touch Evidence</t>
-  </si>
-  <si>
-    <t>FU1 Evidence</t>
-  </si>
-  <si>
-    <t>FU2 Evidence</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a074aa18c4a15e5</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07d94dc355abc7</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07dbda8027b039</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07537695be159d</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0753a7d53e5a5c</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0753ad793984cf</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0763c06f9e9dc5</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0753be59b49989</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07540c8b9fd4bc</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a075443349aa830</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a075449a2403271</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a08369d9f6b09c0</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0754701539a56d</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a075485ca2a3fef</t>
-  </si>
-  <si>
-    <t>Precision Heating &amp; Cooling</t>
-  </si>
-  <si>
-    <t>2026-09-06T01:37:52-07:00</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a075ddee6716e8a</t>
-  </si>
-  <si>
-    <t>Historical send discovered during Sep 12 audit; no reply found in connected Gmail search.</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07640ae5a69379</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a076456505c6304</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0764664a2b1202</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07646d6dbd3474</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0764fa024df1f4</t>
-  </si>
-  <si>
-    <t>Archived</t>
-  </si>
-  <si>
-    <t>Leader Restoration</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
     <t>CostLess Heating &amp; Cooling</t>
   </si>
   <si>
     <t>2026-09-06</t>
   </si>
   <si>
+    <t>Los Gatos Roofing</t>
+  </si>
+  <si>
     <t>Roofs By Reveille, Inc</t>
   </si>
   <si>
@@ -804,9 +816,15 @@
     <t>South Bay Roofing CO</t>
   </si>
   <si>
+    <t>Eastman Roofing &amp; Waterproofing, Inc.</t>
+  </si>
+  <si>
     <t>The Roofer Bros</t>
   </si>
   <si>
+    <t>Roof By Tom</t>
+  </si>
+  <si>
     <t>FairPrice Heating &amp; Cooling</t>
   </si>
   <si>
@@ -820,6 +838,9 @@
   </si>
   <si>
     <t>Archived from active Top 10 on 2026-09-11; no outreach recorded.</t>
+  </si>
+  <si>
+    <t>Top Tier Roofing</t>
   </si>
   <si>
     <t>Verified Date</t>
@@ -1655,32 +1676,32 @@
         <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>26</v>
@@ -1694,38 +1715,38 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>26</v>
@@ -1739,38 +1760,38 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>26</v>
@@ -1784,36 +1805,38 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="I8" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>26</v>
@@ -1827,36 +1850,38 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="I9" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
@@ -1870,38 +1895,38 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
@@ -1915,10 +1940,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>17</v>
@@ -1927,26 +1952,26 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>26</v>
@@ -1991,142 +2016,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2160,58 +2185,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2278,9 +2303,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="2"/>
-      <c r="N3" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
         <v>26</v>
@@ -2338,7 +2361,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -2362,7 +2385,7 @@
         <v>26</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R5" s="3">
         <v>150</v>
@@ -2370,13 +2393,13 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2394,15 +2417,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2" t="s">
-        <v>168</v>
-      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R6" s="3">
         <v>150</v>
@@ -2410,13 +2431,13 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2434,15 +2455,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -2450,12 +2469,14 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -2478,7 +2499,7 @@
         <v>26</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="R8" s="3">
         <v>150</v>
@@ -2486,12 +2507,14 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -2514,7 +2537,7 @@
         <v>26</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="R9" s="3">
         <v>150</v>
@@ -2522,13 +2545,13 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2546,15 +2569,13 @@
         <v>0</v>
       </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="2" t="s">
-        <v>168</v>
-      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -2562,13 +2583,13 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2592,7 +2613,7 @@
         <v>26</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="R11" s="3">
         <v>150</v>
@@ -2600,28 +2621,28 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -2631,7 +2652,7 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -2642,32 +2663,32 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -2677,7 +2698,7 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2688,26 +2709,26 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -2717,7 +2738,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2728,26 +2749,26 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -2757,7 +2778,7 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2768,26 +2789,26 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -2797,7 +2818,7 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -2808,26 +2829,26 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -2837,7 +2858,7 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -2848,26 +2869,26 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -2877,7 +2898,7 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -2888,26 +2909,26 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -2917,7 +2938,7 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -2928,26 +2949,26 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -2957,7 +2978,7 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -2968,26 +2989,26 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -2997,7 +3018,7 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3008,28 +3029,28 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3039,7 +3060,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3050,26 +3071,26 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3079,7 +3100,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3090,26 +3111,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3119,7 +3140,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3130,26 +3151,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -3159,7 +3180,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3170,26 +3191,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -3199,7 +3220,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -3263,67 +3284,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -3332,13 +3353,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3346,10 +3367,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -3358,13 +3379,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3372,10 +3393,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -3384,28 +3405,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -3414,13 +3435,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3428,10 +3449,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -3440,13 +3461,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3454,10 +3475,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -3466,13 +3487,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -3480,10 +3501,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -3492,28 +3513,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -3522,13 +3543,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3536,10 +3557,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -3548,13 +3569,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3562,10 +3583,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -3574,13 +3595,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -3588,10 +3609,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -3600,13 +3621,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -3614,10 +3635,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -3626,13 +3647,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -3640,10 +3661,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -3652,13 +3673,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -3666,10 +3687,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -3678,13 +3699,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -3692,10 +3713,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -3704,13 +3725,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -3718,10 +3739,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -3753,33 +3774,33 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -3793,16 +3814,16 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>27</v>
@@ -3816,14 +3837,14 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>84</v>
+        <v>249</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>27</v>
@@ -3837,20 +3858,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -3860,16 +3881,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>27</v>
@@ -3883,14 +3904,14 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>27</v>
@@ -3904,14 +3925,14 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -3925,14 +3946,14 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -3946,14 +3967,14 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>27</v>
@@ -3967,16 +3988,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>27</v>
@@ -3990,14 +4011,14 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>27</v>
@@ -4011,14 +4032,14 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>27</v>
@@ -4032,14 +4053,14 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>27</v>
@@ -4053,16 +4074,16 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>27</v>
@@ -4076,14 +4097,14 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>27</v>
@@ -4097,14 +4118,14 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>27</v>
@@ -4118,14 +4139,14 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>92</v>
+        <v>263</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>27</v>
@@ -4139,16 +4160,16 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>27</v>
@@ -4162,16 +4183,16 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>27</v>
@@ -4185,16 +4206,16 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>27</v>
@@ -4208,16 +4229,16 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>57</v>
+        <v>269</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>27</v>
@@ -4231,11 +4252,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -4267,13 +4288,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4293,7 +4314,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4313,7 +4334,7 @@
         <v>32</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4333,7 +4354,7 @@
         <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4341,135 +4362,139 @@
         <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="F8" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="F9" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -4504,7 +4529,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -4514,20 +4539,20 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4539,95 +4564,95 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -4653,98 +4678,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -4763,19 +4788,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4792,7 +4817,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="334">
   <si>
     <t>Rank</t>
   </si>
@@ -109,7 +109,7 @@
     <t>2026-09-18</t>
   </si>
   <si>
-    <t>Contact Ready</t>
+    <t>Contacted</t>
   </si>
   <si>
     <t>QualiBuild LLC</t>
@@ -546,6 +546,15 @@
     <t>Offer Value $</t>
   </si>
   <si>
+    <t>2026-09-18T16:24:00-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>Wait for reply. If no reply, eligible for respectful S02 follow-up on/after 2026-09-21; stop sooner on decline or opt-out.</t>
+  </si>
+  <si>
     <t>FloodDry Water Damage Restoration</t>
   </si>
   <si>
@@ -564,9 +573,6 @@
     <t>2026-09-08T16:45:47-07:00</t>
   </si>
   <si>
-    <t>Contacted</t>
-  </si>
-  <si>
     <t>Two verified outbound emails, no inbound reply found through 2026-09-12. Do not send another cold touch now.</t>
   </si>
   <si>
@@ -762,10 +768,43 @@
     <t>Gmail sent message 1a0764fa024df1f4</t>
   </si>
   <si>
+    <t>Gmail sent message 1a0b6d78c843ca6b</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7943740cae</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d79a6cdefdb</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7a193869fd</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7a978557f8</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7afc5b1de0</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7b4e0a0a3f</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7bd8a5e4c7</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7c520f4297</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7d1bb96f3a</t>
+  </si>
+  <si>
     <t>Archived</t>
   </si>
   <si>
     <t>Leader Restoration</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
   </si>
   <si>
     <t>2026-09-12</t>
@@ -2249,8 +2288,12 @@
       <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2265,7 +2308,9 @@
         <v>0</v>
       </c>
       <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="N2" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
         <v>26</v>
@@ -2287,8 +2332,12 @@
       <c r="C3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -2303,7 +2352,9 @@
         <v>0</v>
       </c>
       <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="N3" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
         <v>26</v>
@@ -2325,8 +2376,12 @@
       <c r="C4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -2341,7 +2396,9 @@
         <v>0</v>
       </c>
       <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
+      <c r="N4" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
         <v>26</v>
@@ -2363,8 +2420,12 @@
       <c r="C5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -2379,7 +2440,9 @@
         <v>0</v>
       </c>
       <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+      <c r="N5" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
         <v>26</v>
@@ -2401,8 +2464,12 @@
       <c r="C6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -2417,7 +2484,9 @@
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
         <v>26</v>
@@ -2439,8 +2508,12 @@
       <c r="C7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -2455,7 +2528,9 @@
         <v>0</v>
       </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+      <c r="N7" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
         <v>26</v>
@@ -2477,8 +2552,12 @@
       <c r="C8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -2493,7 +2572,9 @@
         <v>0</v>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
         <v>26</v>
@@ -2515,8 +2596,12 @@
       <c r="C9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -2531,7 +2616,9 @@
         <v>0</v>
       </c>
       <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+      <c r="N9" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
         <v>26</v>
@@ -2553,8 +2640,12 @@
       <c r="C10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -2569,7 +2660,9 @@
         <v>0</v>
       </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="N10" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
         <v>26</v>
@@ -2591,8 +2684,12 @@
       <c r="C11" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -2607,7 +2704,9 @@
         <v>0</v>
       </c>
       <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+      <c r="N11" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
         <v>26</v>
@@ -2621,28 +2720,28 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -2652,7 +2751,7 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -2663,32 +2762,32 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -2698,7 +2797,7 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2709,26 +2808,26 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -2738,7 +2837,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2749,26 +2848,26 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -2778,7 +2877,7 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2789,26 +2888,26 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -2818,7 +2917,7 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -2829,26 +2928,26 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -2858,7 +2957,7 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -2869,26 +2968,26 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -2898,7 +2997,7 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -2909,26 +3008,26 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -2938,7 +3037,7 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -2949,26 +3048,26 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -2978,7 +3077,7 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -2989,26 +3088,26 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -3018,7 +3117,7 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3029,28 +3128,28 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3060,7 +3159,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3071,26 +3170,26 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3100,7 +3199,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3111,26 +3210,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3140,7 +3239,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3151,26 +3250,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -3180,7 +3279,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3191,26 +3290,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -3220,7 +3319,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -3262,7 +3361,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -3287,19 +3386,19 @@
         <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>161</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>162</v>
@@ -3319,32 +3418,32 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -3353,13 +3452,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3367,10 +3466,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -3379,13 +3478,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3393,10 +3492,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -3405,28 +3504,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -3435,13 +3534,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3449,10 +3548,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -3461,13 +3560,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3475,10 +3574,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -3487,13 +3586,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -3501,10 +3600,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -3513,28 +3612,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -3543,13 +3642,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3557,10 +3656,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -3569,13 +3668,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3583,10 +3682,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -3595,13 +3694,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -3609,10 +3708,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -3621,13 +3720,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -3635,10 +3734,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -3647,13 +3746,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -3661,10 +3760,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -3673,13 +3772,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -3687,10 +3786,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -3699,13 +3798,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -3713,10 +3812,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -3725,13 +3824,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -3739,15 +3838,275 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
       </c>
       <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3789,7 +4148,7 @@
         <v>164</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>167</v>
@@ -3800,10 +4159,10 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -3814,19 +4173,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3837,17 +4196,17 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -3858,20 +4217,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -3881,19 +4240,19 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -3904,17 +4263,17 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -3925,17 +4284,17 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -3946,17 +4305,17 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -3967,17 +4326,17 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -3988,19 +4347,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -4011,17 +4370,17 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -4032,17 +4391,17 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -4053,17 +4412,17 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -4074,19 +4433,19 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -4097,17 +4456,17 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -4118,17 +4477,17 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -4139,17 +4498,17 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -4160,19 +4519,19 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -4183,19 +4542,19 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -4206,19 +4565,19 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -4229,19 +4588,19 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -4252,11 +4611,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -4288,13 +4647,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4314,7 +4673,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4334,7 +4693,7 @@
         <v>32</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4354,7 +4713,7 @@
         <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4374,7 +4733,7 @@
         <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4394,7 +4753,7 @@
         <v>62</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4414,7 +4773,7 @@
         <v>71</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4434,7 +4793,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4454,7 +4813,7 @@
         <v>89</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4474,7 +4833,7 @@
         <v>99</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4494,7 +4853,7 @@
         <v>108</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4529,7 +4888,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -4539,115 +4898,115 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contact Ready")</f>
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4678,98 +5037,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -4788,19 +5147,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4811,13 +5170,13 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D2" s="2">
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="336">
   <si>
     <t>Rank</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>https://svchimneysweep.com/contact-us/</t>
+  </si>
+  <si>
+    <t>Delivery Failed</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -553,6 +556,9 @@
   </si>
   <si>
     <t>Wait for reply. If no reply, eligible for respectful S02 follow-up on/after 2026-09-21; stop sooner on decline or opt-out.</t>
+  </si>
+  <si>
+    <t>Do not count as successfully contacted. Official site still publishes info@svchimneysweep.com, but Gmail returned a hard bounce. Reverify or use the official website inquiry route; do not resend to the bounced address.</t>
   </si>
   <si>
     <t>FloodDry Water Damage Restoration</t>
@@ -2016,7 +2022,7 @@
         <v>26</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2055,142 +2061,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2224,58 +2230,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2289,10 +2295,10 @@
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -2309,7 +2315,7 @@
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
@@ -2333,10 +2339,10 @@
         <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -2353,7 +2359,7 @@
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
@@ -2377,10 +2383,10 @@
         <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -2397,7 +2403,7 @@
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
@@ -2421,10 +2427,10 @@
         <v>52</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -2441,7 +2447,7 @@
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
@@ -2465,10 +2471,10 @@
         <v>62</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -2485,7 +2491,7 @@
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
@@ -2509,10 +2515,10 @@
         <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -2529,7 +2535,7 @@
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
@@ -2553,10 +2559,10 @@
         <v>80</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -2573,7 +2579,7 @@
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
@@ -2597,10 +2603,10 @@
         <v>89</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -2617,7 +2623,7 @@
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
@@ -2641,10 +2647,10 @@
         <v>99</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -2661,7 +2667,7 @@
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
@@ -2685,17 +2691,17 @@
         <v>108</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -2705,7 +2711,7 @@
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
@@ -2720,22 +2726,22 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -2751,7 +2757,7 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -2762,28 +2768,28 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
@@ -2797,7 +2803,7 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2808,19 +2814,19 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -2837,7 +2843,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2848,19 +2854,19 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -2877,7 +2883,7 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2888,19 +2894,19 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -2917,7 +2923,7 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -2928,19 +2934,19 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -2957,7 +2963,7 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -2968,19 +2974,19 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -2997,7 +3003,7 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -3008,19 +3014,19 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -3037,7 +3043,7 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -3048,19 +3054,19 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -3077,7 +3083,7 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -3088,19 +3094,19 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -3117,7 +3123,7 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3128,22 +3134,22 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -3159,7 +3165,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3170,19 +3176,19 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -3199,7 +3205,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3210,19 +3216,19 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -3239,7 +3245,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3250,19 +3256,19 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -3279,7 +3285,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3290,19 +3296,19 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -3319,7 +3325,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -3383,67 +3389,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -3452,13 +3458,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3469,7 +3475,7 @@
         <v>27</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -3478,13 +3484,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3495,7 +3501,7 @@
         <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -3504,19 +3510,19 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -3525,7 +3531,7 @@
         <v>27</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -3534,13 +3540,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3551,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -3560,13 +3566,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3577,7 +3583,7 @@
         <v>27</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -3586,13 +3592,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -3603,7 +3609,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -3612,19 +3618,19 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -3633,7 +3639,7 @@
         <v>27</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -3642,13 +3648,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3659,7 +3665,7 @@
         <v>27</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -3668,13 +3674,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3685,7 +3691,7 @@
         <v>27</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -3694,13 +3700,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -3711,7 +3717,7 @@
         <v>27</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -3720,13 +3726,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -3737,7 +3743,7 @@
         <v>27</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -3746,13 +3752,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -3763,7 +3769,7 @@
         <v>27</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -3772,13 +3778,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -3789,7 +3795,7 @@
         <v>27</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -3798,13 +3804,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -3815,7 +3821,7 @@
         <v>27</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -3824,13 +3830,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -3841,7 +3847,7 @@
         <v>27</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -3853,10 +3859,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -3867,7 +3873,7 @@
         <v>27</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -3879,10 +3885,10 @@
         <v>28</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -3893,7 +3899,7 @@
         <v>27</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -3905,10 +3911,10 @@
         <v>38</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -3919,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -3931,10 +3937,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -3945,7 +3951,7 @@
         <v>27</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -3957,10 +3963,10 @@
         <v>58</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -3971,7 +3977,7 @@
         <v>27</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3983,10 +3989,10 @@
         <v>68</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -3997,7 +4003,7 @@
         <v>27</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -4009,10 +4015,10 @@
         <v>77</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -4023,7 +4029,7 @@
         <v>27</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -4035,10 +4041,10 @@
         <v>86</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -4049,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -4061,10 +4067,10 @@
         <v>95</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -4075,7 +4081,7 @@
         <v>27</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -4087,10 +4093,10 @@
         <v>105</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -4098,10 +4104,10 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -4133,36 +4139,36 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4173,19 +4179,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4196,17 +4202,17 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -4217,20 +4223,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -4240,19 +4246,19 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -4263,17 +4269,17 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -4284,17 +4290,17 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -4305,17 +4311,17 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -4326,17 +4332,17 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -4347,19 +4353,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -4370,17 +4376,17 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -4391,17 +4397,17 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -4412,17 +4418,17 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -4433,19 +4439,19 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -4456,17 +4462,17 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -4477,17 +4483,17 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -4498,17 +4504,17 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -4519,19 +4525,19 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -4542,19 +4548,19 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -4565,19 +4571,19 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -4588,19 +4594,19 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -4611,11 +4617,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -4647,13 +4653,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4673,7 +4679,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4693,7 +4699,7 @@
         <v>32</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4713,7 +4719,7 @@
         <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4733,7 +4739,7 @@
         <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4753,7 +4759,7 @@
         <v>62</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4773,7 +4779,7 @@
         <v>71</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4793,7 +4799,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4813,7 +4819,7 @@
         <v>89</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4833,7 +4839,7 @@
         <v>99</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4853,7 +4859,7 @@
         <v>108</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -4888,7 +4894,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -4898,39 +4904,39 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contact Ready")</f>
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4942,76 +4948,76 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -5037,98 +5043,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -5147,19 +5153,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5176,7 +5182,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'New Lead Queue'!$A$1:$O$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Pipeline!$A$1:$R$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Pipeline!$A$1:$R$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="346">
   <si>
     <t>Rank</t>
   </si>
@@ -73,304 +73,301 @@
     <t>Status</t>
   </si>
   <si>
-    <t>HB Design &amp; Construction</t>
-  </si>
-  <si>
-    <t>Design-Build / Remodeling / ADU</t>
-  </si>
-  <si>
-    <t>San Jose / South Bay, CA</t>
+    <t>EDCO Heating &amp; Air</t>
+  </si>
+  <si>
+    <t>HVAC / Heating / Air Conditioning</t>
+  </si>
+  <si>
+    <t>San Jose / Bay Area, CA</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>Official contact page offers a free on-site consultation, written estimate and usually same-day email reply, creating an unusually fast response path for high-value remodeling inquiries.</t>
-  </si>
-  <si>
-    <t>hello.hbdesignconstruction@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; usually same-day reply; free consultation</t>
-  </si>
-  <si>
-    <t>Turn the free consultation and written-estimate process into a pre-consultation content funnel that helps homeowners arrive with project scope, priorities and decision questions ready.</t>
-  </si>
-  <si>
-    <t>Pre-consultation remodeling campaign idea for HB Design</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed HB Design &amp; Construction’s current consultation process and noticed you already offer a free on-site consultation, written estimate and usually same-day email reply. I’d turn that into a customer-ready pre-consultation campaign that helps homeowners organize scope, priorities and questions before you arrive. The $150 Same-Day Customer Growth Pack can include social/Google posts, FAQs, inquiry follow-ups and estimate-ready messaging built around your actual services. Want two HB-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://hbdesignconstruction.com/contact</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
-  </si>
-  <si>
-    <t>Contacted</t>
-  </si>
-  <si>
-    <t>QualiBuild LLC</t>
-  </si>
-  <si>
-    <t>Kitchen / Bathroom / ADU Remodeling</t>
-  </si>
-  <si>
-    <t>Sunnyvale / San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site was crawled four days ago and offers free estimates, owner-direct service, on-site visits usually within 1–2 days, written estimates and photo/video-based project scoping.</t>
-  </si>
-  <si>
-    <t>info@qualibuildca.com</t>
-  </si>
-  <si>
-    <t>Direct email; owners directly involved; on-site visits usually within 1–2 days</t>
-  </si>
-  <si>
-    <t>Turn the existing send-us-photos/video intake into a visual project-readiness campaign that pre-qualifies kitchen, bath and ADU prospects before the visit.</t>
-  </si>
-  <si>
-    <t>Photo-to-estimate campaign idea for QualiBuild</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed QualiBuild’s current project intake and noticed you already invite homeowners to send photos, video and rough dimensions before an on-site visit. I’d turn that into a simple visual project-readiness campaign with scope-prep posts, FAQs, inquiry follow-ups and estimate CTAs for kitchen, bath and ADU prospects. Same-Day Customer Growth Pack: $150 flat. Want two QualiBuild-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://qualibuildca.com/</t>
-  </si>
-  <si>
-    <t>Redwood Roofing</t>
-  </si>
-  <si>
-    <t>Roof Repair / Replacement / Inspection</t>
-  </si>
-  <si>
-    <t>Los Gatos / San Jose / Santa Cruz, CA</t>
-  </si>
-  <si>
-    <t>Official contact page crawled six days ago publishes a direct email, free estimates and a same-day callback promise, or next business day after hours.</t>
-  </si>
-  <si>
-    <t>contact@redwoodroofing.com</t>
-  </si>
-  <si>
-    <t>Direct email; same-day/next-business-day response; free estimate</t>
-  </si>
-  <si>
-    <t>Turn fast estimate response plus inspection expertise into an urgency-without-pressure roof decision campaign.</t>
-  </si>
-  <si>
-    <t>Same-day roof-response campaign idea for Redwood Roofing</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Redwood Roofing’s current estimate page and noticed you already give homeowners something valuable during a stressful roof decision: a free estimate with same-day or next-business-day response. I’d turn that into an urgency-without-pressure campaign covering inspection, repair-vs-replacement questions, inquiry follow-ups and estimate CTAs. Same-Day Customer Growth Pack: $150 flat. Want two Redwood-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://redwoodroofing.com/contact-us/</t>
-  </si>
-  <si>
-    <t>Premier Roofing &amp; Retro-Fit</t>
-  </si>
-  <si>
-    <t>Roofing / Retro-Fit</t>
-  </si>
-  <si>
-    <t>Santa Clara / South Bay, CA</t>
-  </si>
-  <si>
-    <t>Official contact page advertises a free same-day roofing quote, publishes a direct email and maintains weekday and Saturday business hours.</t>
-  </si>
-  <si>
-    <t>Info@premierroofingretrofit.com</t>
-  </si>
-  <si>
-    <t>Direct email; free same-day quote; Saturday hours</t>
-  </si>
-  <si>
-    <t>Build a same-day-quote campaign that tells homeowners exactly what to send before requesting a quote and reduces friction around urgent roof decisions.</t>
-  </si>
-  <si>
-    <t>Same-day quote campaign for Premier Roofing</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Premier Roofing &amp; Retro-Fit’s current Santa Clara contact page and noticed you already promote a free same-day roofing quote. I’d turn that speed promise into a customer-ready campaign showing homeowners what information to send, what to expect next and how to compare repair versus replacement. Same-Day Customer Growth Pack: $150 flat. Want two Premier-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://premierroofingretrofit.com/contact-us/</t>
-  </si>
-  <si>
-    <t>Make It Simple Construction, Inc.</t>
-  </si>
-  <si>
-    <t>Full Home / Kitchen / Bathroom Remodeling</t>
-  </si>
-  <si>
-    <t>San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official contact page publishes a direct named email, free estimates and positioning around guidance, no hidden costs and family ownership.</t>
-  </si>
-  <si>
-    <t>jasmin@makeitsimpleinc.com</t>
-  </si>
-  <si>
-    <t>Direct named email; free estimate</t>
-  </si>
-  <si>
-    <t>Turn the simplicity/no-hidden-cost positioning into a remodeling decision guide that reduces uncertainty before the estimate.</t>
-  </si>
-  <si>
-    <t>Make-the-remodel-simple campaign idea</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Make It Simple Construction’s current contact page and the strongest marketing angle is already in your name: helping homeowners understand what their remodel actually needs without hidden-cost anxiety. I’d turn that into planning posts, scope FAQs, inquiry follow-ups and estimate-ready messaging for kitchens, bathrooms and full-home projects. Same-Day Customer Growth Pack: $150 flat. Want two company-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://makeitsimpleinc.com/contact/</t>
-  </si>
-  <si>
-    <t>BLUECON</t>
-  </si>
-  <si>
-    <t>Remodeling / ADU / Commercial Renovation</t>
-  </si>
-  <si>
-    <t>Official site crawled two days ago publishes a direct project email, San Jose office, free-estimate CTA and remodeling, ADU and commercial-renovation positioning.</t>
-  </si>
-  <si>
-    <t>build@blue-con.org</t>
-  </si>
-  <si>
-    <t>Direct project email; free estimate; San Jose office</t>
-  </si>
-  <si>
-    <t>Turn the broad remodel/ADU/commercial portfolio into a choose-your-project-path campaign that routes prospects to the right estimate conversation.</t>
-  </si>
-  <si>
-    <t>Project-path campaign idea for BLUECON</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed BLUECON’s current San Jose site and noticed you span home remodeling, ADUs and commercial renovation. I’d turn that breadth into a simple project-path campaign that helps prospects identify their project type, prepare the right details and move toward a free estimate. Same-Day Customer Growth Pack: $150 flat. Want two BLUECON-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://blueconbuilders.net/</t>
-  </si>
-  <si>
-    <t>Blues Bros</t>
+    <t>Official contact page was crawled today and publishes a direct email, free consultation and estimate, Monday-Saturday hours, service across San Jose and surrounding Bay Area cities, and guaranteed-work positioning.</t>
+  </si>
+  <si>
+    <t>edcoheating@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; open Monday-Saturday; free consultation and estimate</t>
+  </si>
+  <si>
+    <t>Turn the free consultation plus broad Bay Area coverage into a system-replacement readiness campaign that helps homeowners organize comfort symptoms, system age and estimate questions before contacting EDCO.</t>
+  </si>
+  <si>
+    <t>HVAC estimate-readiness campaign idea for EDCO</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed EDCO Heating &amp; Air’s current contact flow and noticed you already offer free consultations and estimates while serving San Jose and the surrounding Bay Area. I’d turn that into an HVAC estimate-readiness campaign that helps homeowners organize comfort symptoms, system age and replacement questions before reaching out. The $150 Same-Day Customer Growth Pack can include Google/social posts, FAQs, inquiry follow-ups and estimate-ready messaging built around your actual services. Want two EDCO-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.edcoheating.com/contact</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>Engrave Concrete Design</t>
+  </si>
+  <si>
+    <t>Decorative Concrete / Flooring / Remodeling</t>
+  </si>
+  <si>
+    <t>Official site was crawled four days ago and publishes a direct email, Monday-Saturday hours, a free-estimate CTA, residential/commercial/industrial positioning, daily photo updates and an on-time guarantee.</t>
+  </si>
+  <si>
+    <t>engraveconcretedesign@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; Monday-Saturday hours; free estimate</t>
+  </si>
+  <si>
+    <t>Turn the residential/commercial/industrial range and visual nature of decorative concrete into a before-and-after project-selector campaign that routes prospects by surface and use case.</t>
+  </si>
+  <si>
+    <t>Visual project-selector campaign for Engrave Concrete Design</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Engrave Concrete Design’s current site and noticed you span residential, commercial and industrial decorative flooring while already emphasizing free estimates and daily project updates. I’d turn that visual work into a project-selector campaign that helps prospects identify the right surface, finish and use case before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two Engrave-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://engraveconcretedesign.com/</t>
+  </si>
+  <si>
+    <t>Good Vibes Roofing and Siding Inc.</t>
+  </si>
+  <si>
+    <t>Roofing / Siding</t>
   </si>
   <si>
     <t>San Jose, CA</t>
   </si>
   <si>
-    <t>Official contact page publishes a direct email, financing availability, free in-home estimates and a stated response target within 24 hours.</t>
-  </si>
-  <si>
-    <t>info@bluesbros.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated response within 24 hours</t>
-  </si>
-  <si>
-    <t>Turn the 24-hour estimate response plus financing availability into a remodel-readiness campaign addressing scope, budget questions and next steps before the consultation.</t>
-  </si>
-  <si>
-    <t>24-hour remodel-response campaign idea for Blues Bros</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Blues Bros’ current San Jose contact page and noticed you combine free in-home estimates, a stated 24-hour response target and financing availability. I’d turn that into a remodel-readiness campaign covering scope questions, consultation prep, financing FAQs and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Blues Bros-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://bluesbros.com/contact/</t>
-  </si>
-  <si>
-    <t>Home Quality Remodeling</t>
-  </si>
-  <si>
-    <t>Home Remodeling</t>
-  </si>
-  <si>
-    <t>Official contact page publishes a direct San Jose email and a free on-site estimate intake that asks project type, financing interest and accepts plans or drawings.</t>
-  </si>
-  <si>
-    <t>inquiry@hqrpro.com</t>
-  </si>
-  <si>
-    <t>Direct email; San Jose office; free on-site estimate</t>
-  </si>
-  <si>
-    <t>Turn the existing estimate intake into a project-file-prep campaign that encourages prospects to submit plans, inspiration and financing questions before the visit.</t>
-  </si>
-  <si>
-    <t>Project-file prep campaign for HQR</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed HQR’s current San Jose estimate flow and noticed you already ask homeowners for project type, financing interest and even plans or drawings. I’d turn that into a project-file-prep campaign that helps prospects arrive with better information before the on-site estimate. Same-Day Customer Growth Pack: $150 flat. Want two HQR-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.homequalityremodeling.com/contact</t>
-  </si>
-  <si>
-    <t>Imperia Roofing &amp; Exteriors</t>
-  </si>
-  <si>
-    <t>Roofing / Siding / Stucco / Windows / Exterior Renovation</t>
-  </si>
-  <si>
-    <t>Santa Clara / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Recent official Santa Clara pages publish a direct email, free-estimate CTA and a broad roofing/exteriors mix including siding, stucco, painting and windows.</t>
-  </si>
-  <si>
-    <t>info@imperiare.com</t>
-  </si>
-  <si>
-    <t>Direct email; Santa Clara office; free estimate</t>
-  </si>
-  <si>
-    <t>Create an exterior-project selector campaign that helps property owners distinguish roof-only needs from broader siding, stucco, painting or window work before requesting an estimate.</t>
-  </si>
-  <si>
-    <t>Exterior project-selector campaign for Imperia</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Imperia’s current Santa Clara pages and noticed you cover far more than roofing: siding, stucco, painting and windows as well. I’d turn that into an exterior project-selector campaign that helps homeowners identify the right scope before requesting a free estimate, with FAQs and follow-up copy for cross-service opportunities. Same-Day Customer Growth Pack: $150 flat. Want two Imperia-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://imperiare.com/tpo/santa-clara/</t>
-  </si>
-  <si>
-    <t>Silicon Valley Chimney Sweep</t>
-  </si>
-  <si>
-    <t>Chimney Inspection / Cleaning / Repair</t>
-  </si>
-  <si>
-    <t>Official contact page crawled last week publishes a direct email, same-day replies, same-day appointments before noon, free written estimates and photo-based evaluation.</t>
-  </si>
-  <si>
-    <t>info@svchimneysweep.com</t>
-  </si>
-  <si>
-    <t>Direct email; same-day reply; photo intake; free written estimate</t>
-  </si>
-  <si>
-    <t>Turn send-us-a-photo plus same-day response into a visual chimney triage campaign that helps homeowners understand whether they need cleaning, inspection or repair.</t>
-  </si>
-  <si>
-    <t>Photo-first chimney campaign idea</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Silicon Valley Chimney Sweep’s current contact flow and noticed a strong customer-friendly combination: homeowners can email photos, receive a same-day reply and request a free written estimate. I’d turn that into a photo-first chimney triage campaign with symptom posts, FAQs, inquiry follow-ups and estimate CTAs. Same-Day Customer Growth Pack: $150 flat. Want two company-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://svchimneysweep.com/contact-us/</t>
-  </si>
-  <si>
-    <t>Delivery Failed</t>
+    <t>Official site was crawled last week and publishes a direct email, free-estimate CTA, San Jose roofing positioning and GAF Certified contractor status.</t>
+  </si>
+  <si>
+    <t>cmclaudio0415@icloud.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; San Jose</t>
+  </si>
+  <si>
+    <t>Turn roofing-plus-siding capability into an exterior-condition campaign that helps homeowners distinguish roof-only problems from broader exterior work before requesting an estimate.</t>
+  </si>
+  <si>
+    <t>Roof-or-siding project campaign idea for Good Vibes</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Good Vibes Roofing and Siding’s current San Jose site and noticed you combine roofing and siding with a free-estimate path. I’d turn that into an exterior-condition campaign that helps homeowners distinguish roof-only concerns from projects that may involve siding too, with FAQs, estimate-prep posts and inquiry follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Good Vibes-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://goodvibesroofingandsidinginc.com/</t>
+  </si>
+  <si>
+    <t>Sami &amp; Sons</t>
+  </si>
+  <si>
+    <t>Custom Homes / ADUs / Remodeling</t>
+  </si>
+  <si>
+    <t>San Jose / Peninsula / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official site currently says it is booking 2026 builds, offers free on-site estimates, uses a project intake that asks project type, timing and budget, and says quotes are usually returned within 24 hours.</t>
+  </si>
+  <si>
+    <t>info@samiandsons.com</t>
+  </si>
+  <si>
+    <t>Direct email; free on-site estimate; stated under-24-hour quote response</t>
+  </si>
+  <si>
+    <t>Turn the existing project-type/timing/budget intake into a pre-qualification content funnel for custom homes, ADUs, additions and remodels.</t>
+  </si>
+  <si>
+    <t>24-hour project-readiness campaign idea for Sami &amp; Sons</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Sami &amp; Sons’ current project intake and noticed you already ask prospects about project type, timing and budget before a free on-site estimate, with quotes usually returned within 24 hours. I’d turn that into a project-readiness campaign that helps custom-home, ADU and remodeling prospects arrive better prepared before the consultation. Same-Day Customer Growth Pack: $150 flat. Want two Sami &amp; Sons-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://samiandsons.com/</t>
+  </si>
+  <si>
+    <t>Carrillo Construction &amp; Remodeling LLC</t>
+  </si>
+  <si>
+    <t>General Contracting / Remodeling / Additions</t>
+  </si>
+  <si>
+    <t>Official San Jose page was crawled five days ago and offers free on-site written estimates, says a project lead can visit the same week, and advertises 5–15% off depending on project.</t>
+  </si>
+  <si>
+    <t>contact@carrilloconstruction.com</t>
+  </si>
+  <si>
+    <t>Direct email; free written estimate; same-week visit positioning</t>
+  </si>
+  <si>
+    <t>Turn same-week visits plus written estimates into a scope-readiness campaign that prepares homeowners for additions, kitchens, baths and whole-home projects before the site visit.</t>
+  </si>
+  <si>
+    <t>Same-week estimate campaign idea for Carrillo Construction</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Carrillo Construction &amp; Remodeling’s current San Jose page and noticed you already offer free on-site written estimates and say a project lead can often visit the same week. I’d turn that speed and clarity into a scope-readiness campaign for additions and remodels, with planning posts, FAQs, inquiry follow-ups and estimate CTAs. Same-Day Customer Growth Pack: $150 flat. Want two Carrillo-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://carrilloconstructionandremodelingllc.com/locations/san-jose</t>
+  </si>
+  <si>
+    <t>TrenchFree</t>
+  </si>
+  <si>
+    <t>Trenchless Plumbing / Sewer / Water Main</t>
+  </si>
+  <si>
+    <t>San Jose / Santa Clara County / San Mateo County, CA</t>
+  </si>
+  <si>
+    <t>Official contact page was crawled four days ago and publishes a direct service email, free-quote CTA and project routing for water mains, sewer lines, electrical conduit and underground gas lines.</t>
+  </si>
+  <si>
+    <t>service@trenchfree.com</t>
+  </si>
+  <si>
+    <t>Direct service email; free quote; project-type routing</t>
+  </si>
+  <si>
+    <t>Turn the four underground-line project types into a symptom-to-solution campaign that helps property owners identify which trenchless service they likely need before requesting a quote.</t>
+  </si>
+  <si>
+    <t>Project-routing campaign idea for TrenchFree</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed TrenchFree’s current contact flow and noticed you already route prospects by water main, sewer, conduit and underground gas-line needs. I’d turn that into a symptom-to-solution campaign that helps property owners identify the right service and prepare useful project details before requesting a free quote. Same-Day Customer Growth Pack: $150 flat. Want two TrenchFree-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://trenchfree.com/contact-trenchfree/</t>
+  </si>
+  <si>
+    <t>Americool Comfort</t>
+  </si>
+  <si>
+    <t>HVAC / Heating / Cooling / Indoor Air Quality</t>
+  </si>
+  <si>
+    <t>South San Jose / Santa Clara County / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official contact page was crawled two weeks ago and publishes a direct email, free-estimate offer, preferred-contact and appointment fields, urgent/not-urgent routing and 24/7 emergency-service positioning.</t>
+  </si>
+  <si>
+    <t>contact@americool.us</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; urgency routing; 24/7 emergency positioning</t>
+  </si>
+  <si>
+    <t>Turn the existing urgent/not-urgent intake into a repair-versus-replacement triage campaign that gives homeowners a clearer path before booking service.</t>
+  </si>
+  <si>
+    <t>HVAC triage campaign idea for Americool Comfort</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Americool Comfort’s current contact flow and noticed you already distinguish urgent from non-urgent requests while offering free estimates and emergency service. I’d turn that into an HVAC triage campaign that helps homeowners sort repair, replacement and air-quality needs before they book. Same-Day Customer Growth Pack: $150 flat. Want two Americool-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://americool.us/contact-us/</t>
+  </si>
+  <si>
+    <t>AC Concrete</t>
+  </si>
+  <si>
+    <t>Concrete / Sidewalk Repair / Landscaping</t>
+  </si>
+  <si>
+    <t>Official site was crawled last week and publishes a direct email, free-estimate CTA, financing availability, concrete and landscaping licensing, and service across San Jose and numerous Bay Area cities.</t>
+  </si>
+  <si>
+    <t>info@acconcretesj.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; financing available</t>
+  </si>
+  <si>
+    <t>Turn concrete-plus-landscaping capability and financing into a property-improvement project selector that separates repair, replacement and broader outdoor upgrades.</t>
+  </si>
+  <si>
+    <t>Concrete project-selector campaign for AC Concrete</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed AC Concrete’s current site and noticed you combine concrete construction, sidewalk repair and landscaping while offering free estimates and financing options. I’d turn that breadth into a project-selector campaign that helps property owners distinguish repair, replacement and larger outdoor upgrades before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two AC Concrete-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://acconcretesj.com/</t>
+  </si>
+  <si>
+    <t>Stones Landscaping Inc.</t>
+  </si>
+  <si>
+    <t>Landscaping / Concrete-Related Services</t>
+  </si>
+  <si>
+    <t>Official contact page was crawled two days ago and publishes a direct email, free on-site consultation, detailed proposal within 48 hours of the site visit and financing availability for qualifying projects.</t>
+  </si>
+  <si>
+    <t>stoneslandscapinginc1201@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free consultation; proposal within 48 hours of site visit</t>
+  </si>
+  <si>
+    <t>Turn the free consultation and 48-hour proposal process into a landscape-project prep campaign that gets scope, priorities and financing questions organized before the visit.</t>
+  </si>
+  <si>
+    <t>48-hour proposal campaign idea for Stones Landscaping</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Stones Landscaping’s current estimate process and noticed you already offer a free on-site consultation followed by a detailed proposal within 48 hours of the visit. I’d turn that into a project-prep campaign that helps homeowners organize scope, priorities and financing questions before you arrive. Same-Day Customer Growth Pack: $150 flat. Want two Stones-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://stoneslandscapinginc.com/contact/</t>
+  </si>
+  <si>
+    <t>Water's Fault</t>
+  </si>
+  <si>
+    <t>Water Damage Restoration</t>
+  </si>
+  <si>
+    <t>South San Francisco / Peninsula / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official site was crawled today and publishes a direct email, Bay Area water-damage-restoration positioning, an online contact form and service coverage extending through the Peninsula toward San Jose.</t>
+  </si>
+  <si>
+    <t>info@watersfault.com</t>
+  </si>
+  <si>
+    <t>Direct email; online contact form; Bay Area restoration service</t>
+  </si>
+  <si>
+    <t>Turn urgent water-damage uncertainty into a first-hour homeowner information campaign covering what to document, what not to disturb and what details to send before an assessment.</t>
+  </si>
+  <si>
+    <t>First-hour water-damage campaign idea for Water's Fault</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Water’s Fault’s current Bay Area contact flow and noticed you provide a direct email plus an online route for water-damage inquiries. I’d turn the urgency of those situations into a first-hour homeowner information campaign covering what to document, what details to send and how to prepare for an assessment. Same-Day Customer Growth Pack: $150 flat. Want two Water’s Fault-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://watersfault.com/</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -549,6 +546,147 @@
     <t>Offer Value $</t>
   </si>
   <si>
+    <t>FloodDry Water Damage Restoration</t>
+  </si>
+  <si>
+    <t>Follow-up</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:50:24-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-08T16:45:47-07:00</t>
+  </si>
+  <si>
+    <t>Contacted</t>
+  </si>
+  <si>
+    <t>Two verified outbound emails, no inbound reply found through 2026-09-12. Do not send another cold touch now.</t>
+  </si>
+  <si>
+    <t>Therma Tech</t>
+  </si>
+  <si>
+    <t>2026-09-05T20:01:38-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-07T13:35:02-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-07T14:19:35-07:00</t>
+  </si>
+  <si>
+    <t>Three verified outbound emails across two connected Gmail accounts; no inbound reply found through 2026-09-12. Stop cold follow-up unless they reply.</t>
+  </si>
+  <si>
+    <t>Dansel Restoration</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:49:58-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>One verified outbound email; no inbound reply found through 2026-09-12. One final respectful follow-up is permissible, then stop unless they reply.</t>
+  </si>
+  <si>
+    <t>California First Roofing</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:39:21-07:00</t>
+  </si>
+  <si>
+    <t>US Creative Restoration</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:53:01-07:00</t>
+  </si>
+  <si>
+    <t>One verified outbound email; no reply found through 2026-09-12. Eligible for at most one respectful follow-up.</t>
+  </si>
+  <si>
+    <t>WJM Builders</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:30:53-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>Clean Roofing</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:42:04-07:00</t>
+  </si>
+  <si>
+    <t>Solar Energy Consultants</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:25:44-07:00</t>
+  </si>
+  <si>
+    <t>Mayer's Construction</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:31:58-07:00</t>
+  </si>
+  <si>
+    <t>EVS Mechanical</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:32:27-07:00</t>
+  </si>
+  <si>
+    <t>Dueling Trowels Concrete Solutions</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:39:44-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:20:39-07:00</t>
+  </si>
+  <si>
+    <t>Two verified outbound emails; no reply found through 2026-09-12. Do not send another cold touch now.</t>
+  </si>
+  <si>
+    <t>GBD Concrete</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:54:30-07:00</t>
+  </si>
+  <si>
+    <t>John Molina Concrete</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:46:13-07:00</t>
+  </si>
+  <si>
+    <t>Precision Concrete Inc</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:40:53-07:00</t>
+  </si>
+  <si>
+    <t>One Day Complete Repipe</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:35:59-07:00</t>
+  </si>
+  <si>
+    <t>HB Design &amp; Construction</t>
+  </si>
+  <si>
     <t>2026-09-18T16:24:00-07:00</t>
   </si>
   <si>
@@ -558,259 +696,151 @@
     <t>Wait for reply. If no reply, eligible for respectful S02 follow-up on/after 2026-09-21; stop sooner on decline or opt-out.</t>
   </si>
   <si>
+    <t>QualiBuild LLC</t>
+  </si>
+  <si>
+    <t>Redwood Roofing</t>
+  </si>
+  <si>
+    <t>Premier Roofing &amp; Retro-Fit</t>
+  </si>
+  <si>
+    <t>Make It Simple Construction, Inc.</t>
+  </si>
+  <si>
+    <t>BLUECON</t>
+  </si>
+  <si>
+    <t>Blues Bros</t>
+  </si>
+  <si>
+    <t>Home Quality Remodeling</t>
+  </si>
+  <si>
+    <t>Imperia Roofing &amp; Exteriors</t>
+  </si>
+  <si>
+    <t>First Touch Evidence</t>
+  </si>
+  <si>
+    <t>FU1 Evidence</t>
+  </si>
+  <si>
+    <t>FU2 Evidence</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a074aa18c4a15e5</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07d94dc355abc7</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07dbda8027b039</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07537695be159d</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0753a7d53e5a5c</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0753ad793984cf</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0763c06f9e9dc5</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0753be59b49989</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07540c8b9fd4bc</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075443349aa830</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075449a2403271</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a08369d9f6b09c0</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0754701539a56d</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075485ca2a3fef</t>
+  </si>
+  <si>
+    <t>Precision Heating &amp; Cooling</t>
+  </si>
+  <si>
+    <t>2026-09-06T01:37:52-07:00</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075ddee6716e8a</t>
+  </si>
+  <si>
+    <t>Historical send discovered during Sep 12 audit; no reply found in connected Gmail search.</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07640ae5a69379</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a076456505c6304</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0764664a2b1202</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07646d6dbd3474</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0764fa024df1f4</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d78c843ca6b</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7943740cae</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d79a6cdefdb</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7a193869fd</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7a978557f8</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7afc5b1de0</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7b4e0a0a3f</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7bd8a5e4c7</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7c520f4297</t>
+  </si>
+  <si>
+    <t>Silicon Valley Chimney Sweep</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7d1bb96f3a</t>
+  </si>
+  <si>
+    <t>Delivery Failed</t>
+  </si>
+  <si>
     <t>Do not count as successfully contacted. Official site still publishes info@svchimneysweep.com, but Gmail returned a hard bounce. Reverify or use the official website inquiry route; do not resend to the bounced address.</t>
   </si>
   <si>
-    <t>FloodDry Water Damage Restoration</t>
-  </si>
-  <si>
-    <t>Follow-up</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:50:24-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
-    <t>2026-09-08T16:45:47-07:00</t>
-  </si>
-  <si>
-    <t>Two verified outbound emails, no inbound reply found through 2026-09-12. Do not send another cold touch now.</t>
-  </si>
-  <si>
-    <t>Therma Tech</t>
-  </si>
-  <si>
-    <t>2026-09-05T20:01:38-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-07T13:35:02-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-07T14:19:35-07:00</t>
-  </si>
-  <si>
-    <t>Three verified outbound emails across two connected Gmail accounts; no inbound reply found through 2026-09-12. Stop cold follow-up unless they reply.</t>
-  </si>
-  <si>
-    <t>Dansel Restoration</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:49:58-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>One verified outbound email; no inbound reply found through 2026-09-12. One final respectful follow-up is permissible, then stop unless they reply.</t>
-  </si>
-  <si>
-    <t>California First Roofing</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:39:21-07:00</t>
-  </si>
-  <si>
-    <t>US Creative Restoration</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:53:01-07:00</t>
-  </si>
-  <si>
-    <t>One verified outbound email; no reply found through 2026-09-12. Eligible for at most one respectful follow-up.</t>
-  </si>
-  <si>
-    <t>WJM Builders</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:30:53-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
-  </si>
-  <si>
-    <t>Clean Roofing</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:42:04-07:00</t>
-  </si>
-  <si>
-    <t>Solar Energy Consultants</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:25:44-07:00</t>
-  </si>
-  <si>
-    <t>Mayer's Construction</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:31:58-07:00</t>
-  </si>
-  <si>
-    <t>EVS Mechanical</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:32:27-07:00</t>
-  </si>
-  <si>
-    <t>Dueling Trowels Concrete Solutions</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:39:44-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:20:39-07:00</t>
-  </si>
-  <si>
-    <t>Two verified outbound emails; no reply found through 2026-09-12. Do not send another cold touch now.</t>
-  </si>
-  <si>
-    <t>GBD Concrete</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:54:30-07:00</t>
-  </si>
-  <si>
-    <t>John Molina Concrete</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:46:13-07:00</t>
-  </si>
-  <si>
-    <t>Precision Concrete Inc</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:40:53-07:00</t>
-  </si>
-  <si>
-    <t>One Day Complete Repipe</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:35:59-07:00</t>
-  </si>
-  <si>
-    <t>First Touch Evidence</t>
-  </si>
-  <si>
-    <t>FU1 Evidence</t>
-  </si>
-  <si>
-    <t>FU2 Evidence</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a074aa18c4a15e5</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07d94dc355abc7</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07dbda8027b039</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07537695be159d</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0753a7d53e5a5c</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0753ad793984cf</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0763c06f9e9dc5</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0753be59b49989</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07540c8b9fd4bc</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a075443349aa830</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a075449a2403271</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a08369d9f6b09c0</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0754701539a56d</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a075485ca2a3fef</t>
-  </si>
-  <si>
-    <t>Precision Heating &amp; Cooling</t>
-  </si>
-  <si>
-    <t>2026-09-06T01:37:52-07:00</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a075ddee6716e8a</t>
-  </si>
-  <si>
-    <t>Historical send discovered during Sep 12 audit; no reply found in connected Gmail search.</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07640ae5a69379</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a076456505c6304</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0764664a2b1202</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07646d6dbd3474</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0764fa024df1f4</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d78c843ca6b</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7943740cae</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d79a6cdefdb</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7a193869fd</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7a978557f8</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7afc5b1de0</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7b4e0a0a3f</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7bd8a5e4c7</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7c520f4297</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7d1bb96f3a</t>
-  </si>
-  <si>
     <t>Archived</t>
   </si>
   <si>
     <t>Leader Restoration</t>
-  </si>
-  <si>
-    <t>Contact Ready</t>
   </si>
   <si>
     <t>2026-09-12</t>
@@ -1631,32 +1661,32 @@
         <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>26</v>
@@ -1670,38 +1700,38 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>26</v>
@@ -1715,38 +1745,38 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>26</v>
@@ -1760,38 +1790,38 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>26</v>
@@ -1805,38 +1835,38 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>26</v>
@@ -1850,10 +1880,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>78</v>
@@ -1901,7 +1931,7 @@
         <v>87</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
@@ -1946,32 +1976,32 @@
         <v>96</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
@@ -1985,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
@@ -2022,7 +2052,7 @@
         <v>26</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2061,142 +2091,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2206,7 +2236,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -2230,58 +2260,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2294,12 +2324,8 @@
       <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>173</v>
-      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2314,9 +2340,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
         <v>26</v>
@@ -2336,14 +2360,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>173</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -2358,15 +2378,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="2"/>
-      <c r="N3" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R3" s="3">
         <v>150</v>
@@ -2374,20 +2392,16 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>173</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -2402,15 +2416,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="2"/>
-      <c r="N4" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R4" s="3">
         <v>150</v>
@@ -2418,20 +2430,16 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>173</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -2446,15 +2454,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="2"/>
-      <c r="N5" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R5" s="3">
         <v>150</v>
@@ -2462,20 +2468,16 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>173</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -2490,15 +2492,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R6" s="3">
         <v>150</v>
@@ -2506,20 +2506,16 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>173</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -2534,15 +2530,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -2550,7 +2544,7 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
@@ -2558,12 +2552,8 @@
       <c r="C8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>173</v>
-      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -2578,9 +2568,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
         <v>26</v>
@@ -2602,12 +2590,8 @@
       <c r="C9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>173</v>
-      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -2622,9 +2606,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2"/>
-      <c r="N9" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
         <v>26</v>
@@ -2644,14 +2626,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>173</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -2666,15 +2644,13 @@
         <v>0</v>
       </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -2682,7 +2658,7 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
@@ -2690,18 +2666,14 @@
       <c r="C11" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>173</v>
-      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -2710,9 +2682,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="2"/>
-      <c r="N11" s="2" t="s">
-        <v>175</v>
-      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
         <v>26</v>
@@ -2726,28 +2696,28 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -2757,7 +2727,7 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -2768,32 +2738,32 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -2803,7 +2773,7 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2814,26 +2784,26 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -2843,7 +2813,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2854,26 +2824,26 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -2883,7 +2853,7 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2894,26 +2864,26 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -2923,7 +2893,7 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -2934,26 +2904,26 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -2963,7 +2933,7 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -2974,26 +2944,26 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -3003,7 +2973,7 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -3014,26 +2984,26 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -3043,7 +3013,7 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -3054,26 +3024,26 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -3083,7 +3053,7 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -3094,26 +3064,26 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -3123,7 +3093,7 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3134,28 +3104,28 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3165,7 +3135,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3176,26 +3146,26 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3205,7 +3175,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3216,26 +3186,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3245,7 +3215,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3256,26 +3226,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -3285,7 +3255,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3296,26 +3266,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -3325,7 +3295,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -3334,8 +3304,368 @@
         <v>150</v>
       </c>
     </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="3">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R26"/>
+  <autoFilter ref="A1:R35"/>
   <conditionalFormatting sqref="J2:J501">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Won/Paid">
       <formula>NOT(ISERROR(SEARCH("Won/Paid",J2)))</formula>
@@ -3389,67 +3719,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -3458,13 +3788,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3472,10 +3802,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -3484,13 +3814,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3498,10 +3828,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -3510,28 +3840,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -3540,13 +3870,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3554,10 +3884,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -3566,13 +3896,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3580,10 +3910,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -3592,13 +3922,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -3606,10 +3936,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -3618,28 +3948,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -3648,13 +3978,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3662,10 +3992,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -3674,13 +4004,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3688,10 +4018,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -3700,13 +4030,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -3714,10 +4044,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -3726,13 +4056,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -3740,10 +4070,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -3752,13 +4082,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -3766,10 +4096,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -3778,13 +4108,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -3792,10 +4122,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -3804,13 +4134,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -3818,10 +4148,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -3830,13 +4160,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -3844,10 +4174,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -3856,13 +4186,13 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
-        <v>15</v>
+        <v>217</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -3870,10 +4200,10 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -3882,13 +4212,13 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>221</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -3896,10 +4226,10 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -3908,13 +4238,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
-        <v>38</v>
+        <v>222</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -3922,10 +4252,10 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -3934,13 +4264,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -3948,10 +4278,10 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -3960,13 +4290,13 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>58</v>
+        <v>224</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -3974,10 +4304,10 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3986,13 +4316,13 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
-        <v>68</v>
+        <v>225</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -4000,10 +4330,10 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -4012,13 +4342,13 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -4026,10 +4356,10 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -4038,13 +4368,13 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>86</v>
+        <v>227</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -4052,10 +4382,10 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -4064,13 +4394,13 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
-        <v>95</v>
+        <v>228</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -4078,10 +4408,10 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -4090,13 +4420,13 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>105</v>
+        <v>264</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -4104,10 +4434,10 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>114</v>
+        <v>266</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>175</v>
+        <v>267</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -4139,36 +4469,36 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>165</v>
-      </c>
       <c r="G1" s="4" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4179,19 +4509,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4202,17 +4532,17 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -4223,20 +4553,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -4246,19 +4576,19 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -4269,17 +4599,17 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -4290,17 +4620,17 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -4311,17 +4641,17 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -4332,17 +4662,17 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -4353,19 +4683,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -4376,17 +4706,17 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -4397,17 +4727,17 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -4418,17 +4748,17 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -4439,19 +4769,19 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -4462,17 +4792,17 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -4483,17 +4813,17 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -4504,17 +4834,17 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -4525,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -4548,19 +4878,19 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -4571,19 +4901,19 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -4594,19 +4924,19 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -4617,11 +4947,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -4653,13 +4983,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4679,7 +5009,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4687,104 +5017,104 @@
         <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>79</v>
@@ -4799,7 +5129,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4819,7 +5149,7 @@
         <v>89</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4827,24 +5157,24 @@
         <v>95</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>107</v>
@@ -4859,7 +5189,7 @@
         <v>108</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -4894,7 +5224,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -4904,120 +5234,120 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contact Ready")</f>
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -5043,98 +5373,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -5153,19 +5483,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5182,7 +5512,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -73,301 +73,301 @@
     <t>Status</t>
   </si>
   <si>
-    <t>EDCO Heating &amp; Air</t>
-  </si>
-  <si>
-    <t>HVAC / Heating / Air Conditioning</t>
+    <t>Precision Pavings</t>
+  </si>
+  <si>
+    <t>Hardscaping / Pavers / Outdoor Construction</t>
+  </si>
+  <si>
+    <t>San Jose / Silicon Valley, CA</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Official contact page publishes a direct email, free-estimate intake, 24-hour response promise, project-type and budget fields, and an 18-year warranty positioning.</t>
+  </si>
+  <si>
+    <t>ricardo@precisionpavings.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated 24-hour response</t>
+  </si>
+  <si>
+    <t>Turn the existing project-type and budget intake into a visual hardscape project-planning campaign that helps prospects arrive with scope, budget band and material preferences organized before the estimate.</t>
+  </si>
+  <si>
+    <t>24-hour hardscape estimate campaign for Precision Pavings</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Precision Pavings’ current estimate flow and noticed you already ask prospects for project type and budget while promising a detailed response within 24 hours. I’d turn that into a visual project-planning campaign that helps homeowners organize scope, budget band and material preferences before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two Precision-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://precisionpavings.com/contact</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>Innovation Heating &amp; Air Inc.</t>
+  </si>
+  <si>
+    <t>HVAC / Heating / Air Conditioning / Ductwork</t>
+  </si>
+  <si>
+    <t>San Jose / Santa Clara County, CA</t>
+  </si>
+  <si>
+    <t>Official site was crawled yesterday and publishes a direct email, Monday-Saturday hours, free estimates, transparent-pricing positioning and repair, furnace, AC and ductwork services.</t>
+  </si>
+  <si>
+    <t>innovationheatingandair@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; Monday-Saturday hours; free estimate</t>
+  </si>
+  <si>
+    <t>Turn the free-estimate and transparent-pricing promise into a repair-versus-replacement readiness campaign that helps homeowners document symptoms and system age before booking.</t>
+  </si>
+  <si>
+    <t>HVAC repair-vs-replace campaign for Innovation Heating &amp; Air</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Innovation Heating &amp; Air’s current San Jose site and noticed you already emphasize free estimates, transparent pricing and flexible Monday-Saturday scheduling. I’d turn that into a repair-versus-replacement readiness campaign that helps homeowners document symptoms, system age and comfort problems before booking. Same-Day Customer Growth Pack: $150 flat. Want two Innovation-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://innovationheatingandairinc.com/</t>
+  </si>
+  <si>
+    <t>Electrica Inc</t>
+  </si>
+  <si>
+    <t>Electrical / EV Chargers / Panels / Generators</t>
   </si>
   <si>
     <t>San Jose / Bay Area, CA</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Official contact page was crawled today and publishes a direct email, free consultation and estimate, Monday-Saturday hours, service across San Jose and surrounding Bay Area cities, and guaranteed-work positioning.</t>
-  </si>
-  <si>
-    <t>edcoheating@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; open Monday-Saturday; free consultation and estimate</t>
-  </si>
-  <si>
-    <t>Turn the free consultation plus broad Bay Area coverage into a system-replacement readiness campaign that helps homeowners organize comfort symptoms, system age and estimate questions before contacting EDCO.</t>
-  </si>
-  <si>
-    <t>HVAC estimate-readiness campaign idea for EDCO</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed EDCO Heating &amp; Air’s current contact flow and noticed you already offer free consultations and estimates while serving San Jose and the surrounding Bay Area. I’d turn that into an HVAC estimate-readiness campaign that helps homeowners organize comfort symptoms, system age and replacement questions before reaching out. The $150 Same-Day Customer Growth Pack can include Google/social posts, FAQs, inquiry follow-ups and estimate-ready messaging built around your actual services. Want two EDCO-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.edcoheating.com/contact</t>
-  </si>
-  <si>
-    <t>2026-09-19</t>
-  </si>
-  <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
-    <t>Engrave Concrete Design</t>
-  </si>
-  <si>
-    <t>Decorative Concrete / Flooring / Remodeling</t>
-  </si>
-  <si>
-    <t>Official site was crawled four days ago and publishes a direct email, Monday-Saturday hours, a free-estimate CTA, residential/commercial/industrial positioning, daily photo updates and an on-time guarantee.</t>
-  </si>
-  <si>
-    <t>engraveconcretedesign@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; Monday-Saturday hours; free estimate</t>
-  </si>
-  <si>
-    <t>Turn the residential/commercial/industrial range and visual nature of decorative concrete into a before-and-after project-selector campaign that routes prospects by surface and use case.</t>
-  </si>
-  <si>
-    <t>Visual project-selector campaign for Engrave Concrete Design</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Engrave Concrete Design’s current site and noticed you span residential, commercial and industrial decorative flooring while already emphasizing free estimates and daily project updates. I’d turn that visual work into a project-selector campaign that helps prospects identify the right surface, finish and use case before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two Engrave-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://engraveconcretedesign.com/</t>
-  </si>
-  <si>
-    <t>Good Vibes Roofing and Siding Inc.</t>
-  </si>
-  <si>
-    <t>Roofing / Siding</t>
-  </si>
-  <si>
-    <t>San Jose, CA</t>
-  </si>
-  <si>
-    <t>Official site was crawled last week and publishes a direct email, free-estimate CTA, San Jose roofing positioning and GAF Certified contractor status.</t>
-  </si>
-  <si>
-    <t>cmclaudio0415@icloud.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; San Jose</t>
-  </si>
-  <si>
-    <t>Turn roofing-plus-siding capability into an exterior-condition campaign that helps homeowners distinguish roof-only problems from broader exterior work before requesting an estimate.</t>
-  </si>
-  <si>
-    <t>Roof-or-siding project campaign idea for Good Vibes</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Good Vibes Roofing and Siding’s current San Jose site and noticed you combine roofing and siding with a free-estimate path. I’d turn that into an exterior-condition campaign that helps homeowners distinguish roof-only concerns from projects that may involve siding too, with FAQs, estimate-prep posts and inquiry follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Good Vibes-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://goodvibesroofingandsidinginc.com/</t>
-  </si>
-  <si>
-    <t>Sami &amp; Sons</t>
-  </si>
-  <si>
-    <t>Custom Homes / ADUs / Remodeling</t>
-  </si>
-  <si>
-    <t>San Jose / Peninsula / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site currently says it is booking 2026 builds, offers free on-site estimates, uses a project intake that asks project type, timing and budget, and says quotes are usually returned within 24 hours.</t>
-  </si>
-  <si>
-    <t>info@samiandsons.com</t>
-  </si>
-  <si>
-    <t>Direct email; free on-site estimate; stated under-24-hour quote response</t>
-  </si>
-  <si>
-    <t>Turn the existing project-type/timing/budget intake into a pre-qualification content funnel for custom homes, ADUs, additions and remodels.</t>
-  </si>
-  <si>
-    <t>24-hour project-readiness campaign idea for Sami &amp; Sons</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Sami &amp; Sons’ current project intake and noticed you already ask prospects about project type, timing and budget before a free on-site estimate, with quotes usually returned within 24 hours. I’d turn that into a project-readiness campaign that helps custom-home, ADU and remodeling prospects arrive better prepared before the consultation. Same-Day Customer Growth Pack: $150 flat. Want two Sami &amp; Sons-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://samiandsons.com/</t>
-  </si>
-  <si>
-    <t>Carrillo Construction &amp; Remodeling LLC</t>
-  </si>
-  <si>
-    <t>General Contracting / Remodeling / Additions</t>
-  </si>
-  <si>
-    <t>Official San Jose page was crawled five days ago and offers free on-site written estimates, says a project lead can visit the same week, and advertises 5–15% off depending on project.</t>
-  </si>
-  <si>
-    <t>contact@carrilloconstruction.com</t>
-  </si>
-  <si>
-    <t>Direct email; free written estimate; same-week visit positioning</t>
-  </si>
-  <si>
-    <t>Turn same-week visits plus written estimates into a scope-readiness campaign that prepares homeowners for additions, kitchens, baths and whole-home projects before the site visit.</t>
-  </si>
-  <si>
-    <t>Same-week estimate campaign idea for Carrillo Construction</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Carrillo Construction &amp; Remodeling’s current San Jose page and noticed you already offer free on-site written estimates and say a project lead can often visit the same week. I’d turn that speed and clarity into a scope-readiness campaign for additions and remodels, with planning posts, FAQs, inquiry follow-ups and estimate CTAs. Same-Day Customer Growth Pack: $150 flat. Want two Carrillo-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://carrilloconstructionandremodelingllc.com/locations/san-jose</t>
-  </si>
-  <si>
-    <t>TrenchFree</t>
-  </si>
-  <si>
-    <t>Trenchless Plumbing / Sewer / Water Main</t>
-  </si>
-  <si>
-    <t>San Jose / Santa Clara County / San Mateo County, CA</t>
-  </si>
-  <si>
-    <t>Official contact page was crawled four days ago and publishes a direct service email, free-quote CTA and project routing for water mains, sewer lines, electrical conduit and underground gas lines.</t>
-  </si>
-  <si>
-    <t>service@trenchfree.com</t>
-  </si>
-  <si>
-    <t>Direct service email; free quote; project-type routing</t>
-  </si>
-  <si>
-    <t>Turn the four underground-line project types into a symptom-to-solution campaign that helps property owners identify which trenchless service they likely need before requesting a quote.</t>
-  </si>
-  <si>
-    <t>Project-routing campaign idea for TrenchFree</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed TrenchFree’s current contact flow and noticed you already route prospects by water main, sewer, conduit and underground gas-line needs. I’d turn that into a symptom-to-solution campaign that helps property owners identify the right service and prepare useful project details before requesting a free quote. Same-Day Customer Growth Pack: $150 flat. Want two TrenchFree-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://trenchfree.com/contact-trenchfree/</t>
-  </si>
-  <si>
-    <t>Americool Comfort</t>
-  </si>
-  <si>
-    <t>HVAC / Heating / Cooling / Indoor Air Quality</t>
-  </si>
-  <si>
-    <t>South San Jose / Santa Clara County / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official contact page was crawled two weeks ago and publishes a direct email, free-estimate offer, preferred-contact and appointment fields, urgent/not-urgent routing and 24/7 emergency-service positioning.</t>
-  </si>
-  <si>
-    <t>contact@americool.us</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; urgency routing; 24/7 emergency positioning</t>
-  </si>
-  <si>
-    <t>Turn the existing urgent/not-urgent intake into a repair-versus-replacement triage campaign that gives homeowners a clearer path before booking service.</t>
-  </si>
-  <si>
-    <t>HVAC triage campaign idea for Americool Comfort</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Americool Comfort’s current contact flow and noticed you already distinguish urgent from non-urgent requests while offering free estimates and emergency service. I’d turn that into an HVAC triage campaign that helps homeowners sort repair, replacement and air-quality needs before they book. Same-Day Customer Growth Pack: $150 flat. Want two Americool-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://americool.us/contact-us/</t>
-  </si>
-  <si>
-    <t>AC Concrete</t>
-  </si>
-  <si>
-    <t>Concrete / Sidewalk Repair / Landscaping</t>
-  </si>
-  <si>
-    <t>Official site was crawled last week and publishes a direct email, free-estimate CTA, financing availability, concrete and landscaping licensing, and service across San Jose and numerous Bay Area cities.</t>
-  </si>
-  <si>
-    <t>info@acconcretesj.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; financing available</t>
-  </si>
-  <si>
-    <t>Turn concrete-plus-landscaping capability and financing into a property-improvement project selector that separates repair, replacement and broader outdoor upgrades.</t>
-  </si>
-  <si>
-    <t>Concrete project-selector campaign for AC Concrete</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed AC Concrete’s current site and noticed you combine concrete construction, sidewalk repair and landscaping while offering free estimates and financing options. I’d turn that breadth into a project-selector campaign that helps property owners distinguish repair, replacement and larger outdoor upgrades before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two AC Concrete-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://acconcretesj.com/</t>
-  </si>
-  <si>
-    <t>Stones Landscaping Inc.</t>
-  </si>
-  <si>
-    <t>Landscaping / Concrete-Related Services</t>
-  </si>
-  <si>
-    <t>Official contact page was crawled two days ago and publishes a direct email, free on-site consultation, detailed proposal within 48 hours of the site visit and financing availability for qualifying projects.</t>
-  </si>
-  <si>
-    <t>stoneslandscapinginc1201@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free consultation; proposal within 48 hours of site visit</t>
-  </si>
-  <si>
-    <t>Turn the free consultation and 48-hour proposal process into a landscape-project prep campaign that gets scope, priorities and financing questions organized before the visit.</t>
-  </si>
-  <si>
-    <t>48-hour proposal campaign idea for Stones Landscaping</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Stones Landscaping’s current estimate process and noticed you already offer a free on-site consultation followed by a detailed proposal within 48 hours of the visit. I’d turn that into a project-prep campaign that helps homeowners organize scope, priorities and financing questions before you arrive. Same-Day Customer Growth Pack: $150 flat. Want two Stones-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://stoneslandscapinginc.com/contact/</t>
-  </si>
-  <si>
-    <t>Water's Fault</t>
-  </si>
-  <si>
-    <t>Water Damage Restoration</t>
-  </si>
-  <si>
-    <t>South San Francisco / Peninsula / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site was crawled today and publishes a direct email, Bay Area water-damage-restoration positioning, an online contact form and service coverage extending through the Peninsula toward San Jose.</t>
-  </si>
-  <si>
-    <t>info@watersfault.com</t>
-  </si>
-  <si>
-    <t>Direct email; online contact form; Bay Area restoration service</t>
-  </si>
-  <si>
-    <t>Turn urgent water-damage uncertainty into a first-hour homeowner information campaign covering what to document, what not to disturb and what details to send before an assessment.</t>
-  </si>
-  <si>
-    <t>First-hour water-damage campaign idea for Water's Fault</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Water’s Fault’s current Bay Area contact flow and noticed you provide a direct email plus an online route for water-damage inquiries. I’d turn the urgency of those situations into a first-hour homeowner information campaign covering what to document, what details to send and how to prepare for an assessment. Same-Day Customer Growth Pack: $150 flat. Want two Water’s Fault-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://watersfault.com/</t>
+    <t>Official site was crawled yesterday and publishes a direct email, free-estimate intake, photo-by-email option, Saturday hours and services spanning EV chargers, panel upgrades, generators, lighting and commercial electrical work.</t>
+  </si>
+  <si>
+    <t>info@electrica-inc.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; accepts project photos; Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the photo-enabled intake and multiple high-value electrical services into a project-readiness selector that routes homeowners by EV charger, panel, generator or lighting need.</t>
+  </si>
+  <si>
+    <t>Photo-first electrical project campaign for Electrica</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Electrica’s current estimate flow and noticed you already let prospects email project photos while covering EV chargers, panel upgrades, generators and other electrical work. I’d turn that into a photo-first project-readiness campaign that helps homeowners identify the right service and send useful details before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two Electrica-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.electrica-inc.com/</t>
+  </si>
+  <si>
+    <t>Cal Painting Plus</t>
+  </si>
+  <si>
+    <t>Residential / Commercial Painting</t>
+  </si>
+  <si>
+    <t>San Jose / South Bay, CA</t>
+  </si>
+  <si>
+    <t>Official contact page was crawled three days ago and publishes a named direct email, free-estimate offer, Monday-Saturday hours and a stated response target within 24 hours.</t>
+  </si>
+  <si>
+    <t>chris@calpaintingplus.com</t>
+  </si>
+  <si>
+    <t>Named direct email; free estimate; stated 24-hour response; Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the fast response and interior/exterior service split into a color-and-scope preparation campaign that gets homeowners ready with rooms, surfaces, timing and finish priorities.</t>
+  </si>
+  <si>
+    <t>24-hour painting estimate campaign for Cal Painting Plus</t>
+  </si>
+  <si>
+    <t>Hi Chris — I reviewed Cal Painting Plus’s current contact flow and noticed you already promise a response within 24 hours and offer free estimates across interior and exterior painting. I’d turn that into a color-and-scope preparation campaign that helps homeowners organize rooms, surfaces, timing and finish priorities before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two Cal Painting Plus-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.calpaintingplus.com/contact</t>
+  </si>
+  <si>
+    <t>SolidRise Garage Door Repair</t>
+  </si>
+  <si>
+    <t>Garage Door Repair / Installation</t>
+  </si>
+  <si>
+    <t>San Jose / Santa Clara / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official site was crawled last week and publishes a direct email, free estimates, same-day service, 24/7 emergency positioning and a stated 30-minute quote response.</t>
+  </si>
+  <si>
+    <t>contact@solidrisegaragedoorrepair.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; 30-minute quote positioning; same-day/24-7 service</t>
+  </si>
+  <si>
+    <t>Turn the fast-response promise into a symptom-to-service triage campaign covering springs, openers, cables, off-track doors and replacement decisions.</t>
+  </si>
+  <si>
+    <t>30-minute garage-door triage campaign for SolidRise</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed SolidRise’s current Bay Area site and noticed you already position around same-day service, free estimates and a 30-minute quote response. I’d turn that speed into a symptom-to-service campaign that helps homeowners distinguish spring, opener, cable, off-track and replacement needs before requesting service. Same-Day Customer Growth Pack: $150 flat. Want two SolidRise-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.solidrisegaragedoorrepair.com/</t>
+  </si>
+  <si>
+    <t>Bay Best Garage Door</t>
+  </si>
+  <si>
+    <t>San Jose to San Francisco, CA</t>
+  </si>
+  <si>
+    <t>Official contact page publishes a direct email, free-estimate CTA, 24/7 hours, same-day-service positioning and transparent-pricing messaging.</t>
+  </si>
+  <si>
+    <t>info@baybestgaragedoorca.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; 24/7; same-day service</t>
+  </si>
+  <si>
+    <t>Turn same-day availability and transparent pricing into an emergency-versus-planned-service campaign that helps prospects quickly classify repair, opener and replacement needs.</t>
+  </si>
+  <si>
+    <t>Same-day garage-door campaign for Bay Best</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Bay Best Garage Door’s current contact flow and noticed you already emphasize 24/7 availability, same-day service and transparent pricing. I’d turn that into an emergency-versus-planned-service campaign that helps homeowners quickly classify repair, opener and replacement needs before booking. Same-Day Customer Growth Pack: $150 flat. Want two Bay Best-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://baybestgaragedoorca.com/contact-us/</t>
+  </si>
+  <si>
+    <t>ZGREEN Restoration</t>
+  </si>
+  <si>
+    <t>Water / Fire Damage Restoration</t>
+  </si>
+  <si>
+    <t>Official Silicon Valley page publishes a direct email, 24/7 emergency availability, free no-obligation estimates, insurance-company coordination and a stated 45-minute response time.</t>
+  </si>
+  <si>
+    <t>info@zgreenrestoration.com</t>
+  </si>
+  <si>
+    <t>Direct email; 24/7; free estimate; stated 45-minute response</t>
+  </si>
+  <si>
+    <t>Turn the emergency response and insurance coordination into a first-hour damage-preparation campaign covering documentation, safety, insurance information and what to expect on arrival.</t>
+  </si>
+  <si>
+    <t>First-hour restoration campaign idea for ZGREEN</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed ZGREEN’s current Silicon Valley restoration page and noticed you already emphasize 24/7 availability, free estimates, insurance coordination and a 45-minute response target. I’d turn that into a first-hour homeowner campaign covering what to document, what information to prepare and what to expect before the restoration team arrives. Same-Day Customer Growth Pack: $150 flat. Want two ZGREEN-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.zgreenrestoration.com/cupertino-property-restoration/</t>
+  </si>
+  <si>
+    <t>Cal's Garage Doors</t>
+  </si>
+  <si>
+    <t>Garage Doors / Openers / Repair / Installation</t>
+  </si>
+  <si>
+    <t>Campbell / San Jose / South Bay, CA</t>
+  </si>
+  <si>
+    <t>Official contact page was crawled last week and publishes a direct email, free-estimate offer, Saturday hours and service history dating to 1965 across San Jose and the South Bay.</t>
+  </si>
+  <si>
+    <t>info@calsgaragedoors.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the long service history and repair-plus-installation range into a repair-or-replace decision campaign that helps homeowners identify symptoms, door age and opener needs before the estimate.</t>
+  </si>
+  <si>
+    <t>Repair-or-replace campaign idea for Cal's Garage Doors</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Cal’s Garage Doors’ current contact page and noticed you combine repair, opener and new-door services with free estimates across San Jose and the South Bay. I’d turn that into a repair-or-replace decision campaign that helps homeowners organize symptoms, door age and opener needs before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two Cal’s-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://calsgaragedoors.com/contact-us/</t>
+  </si>
+  <si>
+    <t>Around The Clock Garage Doors</t>
+  </si>
+  <si>
+    <t>Garage Door Repair / Installation / Replacement</t>
+  </si>
+  <si>
+    <t>Official site publishes a direct office email, free-estimate CTA and repair, installation and replacement positioning for Bay Area homeowners and businesses.</t>
+  </si>
+  <si>
+    <t>office@aroundtheclockgaragedoors.com</t>
+  </si>
+  <si>
+    <t>Direct office email; free estimate</t>
+  </si>
+  <si>
+    <t>Turn the repair-install-replace service range into a simple door-problem selector that helps prospects identify likely service needs before requesting an estimate.</t>
+  </si>
+  <si>
+    <t>Garage-door project selector for Around The Clock</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Around The Clock Garage Doors’ current Bay Area site and noticed you cover repair, installation and replacement with a free-estimate path. I’d turn that into a simple door-problem selector that helps homeowners identify likely repair versus replacement needs before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two company-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://aroundtheclockgaragedoors.com/</t>
+  </si>
+  <si>
+    <t>Península Arbor Inc.</t>
+  </si>
+  <si>
+    <t>Tree Care / Tree Removal / Emergency Arbor Services</t>
+  </si>
+  <si>
+    <t>Official site was crawled three days ago and publishes a direct email, free-consultation CTA, emergency service, insured/warranty positioning and residential/commercial tree-care coverage including San Jose.</t>
+  </si>
+  <si>
+    <t>peninsulaarbor@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free consultation; emergency service</t>
+  </si>
+  <si>
+    <t>Turn emergency plus routine tree care into a risk-and-maintenance triage campaign that helps property owners distinguish urgent hazards, removals and preventive care before requesting a consultation.</t>
+  </si>
+  <si>
+    <t>Tree-risk triage campaign for Península Arbor</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Península Arbor’s current site and noticed you combine emergency service with routine tree care and removal while offering a free consultation. I’d turn that into a risk-and-maintenance triage campaign that helps property owners distinguish urgent hazards, removal needs and preventive care before reaching out. Same-Day Customer Growth Pack: $150 flat. Want two Península Arbor-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://peninsulaarborinc.com/</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -1661,32 +1661,32 @@
         <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>26</v>
@@ -1700,38 +1700,38 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>26</v>
@@ -1745,38 +1745,38 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>26</v>
@@ -1790,38 +1790,38 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>26</v>
@@ -1835,38 +1835,38 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>26</v>
@@ -1880,13 +1880,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
@@ -1931,32 +1931,32 @@
         <v>87</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
@@ -1970,38 +1970,38 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
@@ -2360,7 +2360,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2384,7 +2384,7 @@
         <v>26</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R3" s="3">
         <v>150</v>
@@ -2392,13 +2392,13 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2422,7 +2422,7 @@
         <v>26</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R4" s="3">
         <v>150</v>
@@ -2430,13 +2430,13 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -2460,7 +2460,7 @@
         <v>26</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R5" s="3">
         <v>150</v>
@@ -2468,13 +2468,13 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2498,7 +2498,7 @@
         <v>26</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R6" s="3">
         <v>150</v>
@@ -2506,13 +2506,13 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2536,7 +2536,7 @@
         <v>26</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2612,7 +2612,7 @@
         <v>26</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R9" s="3">
         <v>150</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2650,7 +2650,7 @@
         <v>26</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
@@ -5017,16 +5017,16 @@
         <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>298</v>
@@ -5034,19 +5034,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>298</v>
@@ -5054,19 +5054,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>298</v>
@@ -5074,19 +5074,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>298</v>
@@ -5094,19 +5094,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>298</v>
@@ -5114,7 +5114,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>79</v>
@@ -5137,16 +5137,16 @@
         <v>86</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>298</v>
@@ -5154,19 +5154,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>298</v>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>107</v>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="342">
   <si>
     <t>Rank</t>
   </si>
@@ -73,301 +73,292 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Precision Pavings</t>
-  </si>
-  <si>
-    <t>Hardscaping / Pavers / Outdoor Construction</t>
-  </si>
-  <si>
-    <t>San Jose / Silicon Valley, CA</t>
+    <t>OK Mechanical Services</t>
+  </si>
+  <si>
+    <t>HVAC / Heating / Air Conditioning / Heat Pumps</t>
+  </si>
+  <si>
+    <t>San Jose / Bay Area, CA</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>Official contact page publishes a direct email, free-estimate intake, 24-hour response promise, project-type and budget fields, and an 18-year warranty positioning.</t>
-  </si>
-  <si>
-    <t>ricardo@precisionpavings.com</t>
+    <t>Official site was crawled last month and advertises free estimates, same-week installation, emergency HVAC service, financing for new systems and an average response time under one hour.</t>
+  </si>
+  <si>
+    <t>ok.hvac.ca@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated under-one-hour average response; emergency service</t>
+  </si>
+  <si>
+    <t>Turn the fast-response and financing positioning into a repair-versus-replacement readiness campaign that helps homeowners organize system age, symptoms, comfort problems and financing questions before requesting an estimate.</t>
+  </si>
+  <si>
+    <t>Under-one-hour HVAC response campaign for OK Mechanical</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed OK Mechanical Services’ current San Jose site and noticed you already emphasize free estimates, same-week installation, financing and an average response time under one hour. I’d turn that into a repair-versus-replacement readiness campaign that helps homeowners organize system age, symptoms, comfort problems and financing questions before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two OK Mechanical-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.ok-ms.com/</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>AAA Construction Management</t>
+  </si>
+  <si>
+    <t>General Contracting / Home Remodeling</t>
+  </si>
+  <si>
+    <t>Official contact page offers a free consultation and estimate, publishes a direct sales email, states a response within 24 hours and lists Saturday hours.</t>
+  </si>
+  <si>
+    <t>sales@aaa-cm.com</t>
+  </si>
+  <si>
+    <t>Direct sales email; free estimate; stated 24-hour response; Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the 24-hour estimate path into a project-readiness campaign that helps remodeling prospects organize scope, priorities, budget and site questions before the consultation.</t>
+  </si>
+  <si>
+    <t>24-hour remodel estimate campaign for AAA Construction Management</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed AAA Construction Management’s current contact flow and noticed you already offer free consultations and estimates with a stated response within 24 hours. I’d turn that into a project-readiness campaign that helps homeowners organize scope, priorities, budget and site questions before the consultation. Same-Day Customer Growth Pack: $150 flat. Want two AAA-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.aaa-cm.com/contact</t>
+  </si>
+  <si>
+    <t>Atra Construction</t>
+  </si>
+  <si>
+    <t>ADU / General Construction</t>
+  </si>
+  <si>
+    <t>Official contact page specializes in Bay Area ADUs, offers consultations and free estimates, publishes a direct email and states the team will respond within 24 hours.</t>
+  </si>
+  <si>
+    <t>info@atraconstruction.com</t>
   </si>
   <si>
     <t>Direct email; free estimate; stated 24-hour response</t>
   </si>
   <si>
-    <t>Turn the existing project-type and budget intake into a visual hardscape project-planning campaign that helps prospects arrive with scope, budget band and material preferences organized before the estimate.</t>
-  </si>
-  <si>
-    <t>24-hour hardscape estimate campaign for Precision Pavings</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Precision Pavings’ current estimate flow and noticed you already ask prospects for project type and budget while promising a detailed response within 24 hours. I’d turn that into a visual project-planning campaign that helps homeowners organize scope, budget band and material preferences before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two Precision-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://precisionpavings.com/contact</t>
-  </si>
-  <si>
-    <t>2026-09-20</t>
-  </si>
-  <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
-    <t>Innovation Heating &amp; Air Inc.</t>
-  </si>
-  <si>
-    <t>HVAC / Heating / Air Conditioning / Ductwork</t>
-  </si>
-  <si>
-    <t>San Jose / Santa Clara County, CA</t>
-  </si>
-  <si>
-    <t>Official site was crawled yesterday and publishes a direct email, Monday-Saturday hours, free estimates, transparent-pricing positioning and repair, furnace, AC and ductwork services.</t>
-  </si>
-  <si>
-    <t>innovationheatingandair@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; Monday-Saturday hours; free estimate</t>
-  </si>
-  <si>
-    <t>Turn the free-estimate and transparent-pricing promise into a repair-versus-replacement readiness campaign that helps homeowners document symptoms and system age before booking.</t>
-  </si>
-  <si>
-    <t>HVAC repair-vs-replace campaign for Innovation Heating &amp; Air</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Innovation Heating &amp; Air’s current San Jose site and noticed you already emphasize free estimates, transparent pricing and flexible Monday-Saturday scheduling. I’d turn that into a repair-versus-replacement readiness campaign that helps homeowners document symptoms, system age and comfort problems before booking. Same-Day Customer Growth Pack: $150 flat. Want two Innovation-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://innovationheatingandairinc.com/</t>
-  </si>
-  <si>
-    <t>Electrica Inc</t>
-  </si>
-  <si>
-    <t>Electrical / EV Chargers / Panels / Generators</t>
-  </si>
-  <si>
-    <t>San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site was crawled yesterday and publishes a direct email, free-estimate intake, photo-by-email option, Saturday hours and services spanning EV chargers, panel upgrades, generators, lighting and commercial electrical work.</t>
-  </si>
-  <si>
-    <t>info@electrica-inc.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; accepts project photos; Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the photo-enabled intake and multiple high-value electrical services into a project-readiness selector that routes homeowners by EV charger, panel, generator or lighting need.</t>
-  </si>
-  <si>
-    <t>Photo-first electrical project campaign for Electrica</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Electrica’s current estimate flow and noticed you already let prospects email project photos while covering EV chargers, panel upgrades, generators and other electrical work. I’d turn that into a photo-first project-readiness campaign that helps homeowners identify the right service and send useful details before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two Electrica-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.electrica-inc.com/</t>
-  </si>
-  <si>
-    <t>Cal Painting Plus</t>
-  </si>
-  <si>
-    <t>Residential / Commercial Painting</t>
+    <t>Turn the ADU specialization into a pre-consultation campaign that helps homeowners identify ADU purpose, site constraints, project location and planning questions before requesting an estimate.</t>
+  </si>
+  <si>
+    <t>24-hour ADU consultation campaign for Atra Construction</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Atra Construction’s current Bay Area ADU contact flow and noticed you already offer free estimates and state that your team gets back to prospects within 24 hours. I’d turn that into an ADU pre-consultation campaign that helps homeowners organize intended use, site constraints, location and planning questions before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two Atra-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.atraconstruction.com/contact</t>
+  </si>
+  <si>
+    <t>Valle Construction</t>
+  </si>
+  <si>
+    <t>Remodeling / ADUs / Home Repairs</t>
+  </si>
+  <si>
+    <t>Official San Jose page was crawled last week and publishes a direct email, free-estimate CTA, one-business-day response positioning and services spanning bathrooms, kitchens, ADUs and home repairs.</t>
+  </si>
+  <si>
+    <t>info@valle.construction</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated one-business-day response</t>
+  </si>
+  <si>
+    <t>Turn the broad remodel-and-ADU range into a project-type selector that helps homeowners identify scope, likely permit complexity and preparation needs before the estimate.</t>
+  </si>
+  <si>
+    <t>One-day project-readiness campaign for Valle Construction</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Valle Construction’s current San Jose page and noticed you cover bathrooms, kitchens, ADUs and home repairs while offering free estimates and a one-business-day response. I’d turn that into a project-type readiness campaign that helps homeowners identify scope, likely permit questions and preparation needs before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two Valle-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://valle.construction/services/san-jose</t>
+  </si>
+  <si>
+    <t>Gladiator Repipe &amp; Plumbing</t>
+  </si>
+  <si>
+    <t>Plumbing / Repiping / Emergency Plumbing</t>
+  </si>
+  <si>
+    <t>Official service-area page was crawled last week and publishes a direct email, free-estimate intake, 24/7 emergency availability and plumbing/repiping coverage across 20+ Bay Area cities.</t>
+  </si>
+  <si>
+    <t>gladiatorrepipe@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; 24/7 emergency availability</t>
+  </si>
+  <si>
+    <t>Turn the repipe-plus-emergency positioning into a symptom-to-project campaign that helps homeowners distinguish urgent leaks from whole-home repipe planning and prepare useful property details before requesting an estimate.</t>
+  </si>
+  <si>
+    <t>Plumbing symptom-to-project campaign for Gladiator Repipe</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Gladiator Repipe &amp; Plumbing’s current Bay Area service page and noticed you combine free estimates, 24/7 emergency availability and whole-home repiping. I’d turn that into a symptom-to-project campaign that helps homeowners distinguish urgent leak issues from repipe planning and prepare useful property details before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two Gladiator-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://gladiatorrepipe.com/service-areas/</t>
+  </si>
+  <si>
+    <t>Jade Landscape Management</t>
+  </si>
+  <si>
+    <t>Landscaping / Property Care</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>Official site was crawled last month and publishes a direct email, free-estimate intake, Monday-Saturday hours and a promise to respond to every inquiry within 24 hours.</t>
+  </si>
+  <si>
+    <t>Contact@JadeLM.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated 24-hour response; Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the fast estimate response into a property-priority campaign that helps residential and commercial prospects organize desired work, maintenance priorities and site details before the estimate.</t>
+  </si>
+  <si>
+    <t>24-hour landscape estimate campaign for Jade</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Jade Landscape Management’s current San Jose estimate flow and noticed you already promise to respond to every inquiry within 24 hours while serving both residential and commercial properties. I’d turn that into a property-priority campaign that helps prospects organize desired work, maintenance priorities and site details before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two Jade-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.jadelm.com/</t>
+  </si>
+  <si>
+    <t>The JS Fencing</t>
+  </si>
+  <si>
+    <t>Fencing / Gates</t>
   </si>
   <si>
     <t>San Jose / South Bay, CA</t>
   </si>
   <si>
-    <t>Official contact page was crawled three days ago and publishes a named direct email, free-estimate offer, Monday-Saturday hours and a stated response target within 24 hours.</t>
-  </si>
-  <si>
-    <t>chris@calpaintingplus.com</t>
-  </si>
-  <si>
-    <t>Named direct email; free estimate; stated 24-hour response; Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the fast response and interior/exterior service split into a color-and-scope preparation campaign that gets homeowners ready with rooms, surfaces, timing and finish priorities.</t>
-  </si>
-  <si>
-    <t>24-hour painting estimate campaign for Cal Painting Plus</t>
-  </si>
-  <si>
-    <t>Hi Chris — I reviewed Cal Painting Plus’s current contact flow and noticed you already promise a response within 24 hours and offer free estimates across interior and exterior painting. I’d turn that into a color-and-scope preparation campaign that helps homeowners organize rooms, surfaces, timing and finish priorities before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two Cal Painting Plus-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.calpaintingplus.com/contact</t>
-  </si>
-  <si>
-    <t>SolidRise Garage Door Repair</t>
-  </si>
-  <si>
-    <t>Garage Door Repair / Installation</t>
-  </si>
-  <si>
-    <t>San Jose / Santa Clara / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site was crawled last week and publishes a direct email, free estimates, same-day service, 24/7 emergency positioning and a stated 30-minute quote response.</t>
-  </si>
-  <si>
-    <t>contact@solidrisegaragedoorrepair.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; 30-minute quote positioning; same-day/24-7 service</t>
-  </si>
-  <si>
-    <t>Turn the fast-response promise into a symptom-to-service triage campaign covering springs, openers, cables, off-track doors and replacement decisions.</t>
-  </si>
-  <si>
-    <t>30-minute garage-door triage campaign for SolidRise</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed SolidRise’s current Bay Area site and noticed you already position around same-day service, free estimates and a 30-minute quote response. I’d turn that speed into a symptom-to-service campaign that helps homeowners distinguish spring, opener, cable, off-track and replacement needs before requesting service. Same-Day Customer Growth Pack: $150 flat. Want two SolidRise-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.solidrisegaragedoorrepair.com/</t>
-  </si>
-  <si>
-    <t>Bay Best Garage Door</t>
-  </si>
-  <si>
-    <t>San Jose to San Francisco, CA</t>
-  </si>
-  <si>
-    <t>Official contact page publishes a direct email, free-estimate CTA, 24/7 hours, same-day-service positioning and transparent-pricing messaging.</t>
-  </si>
-  <si>
-    <t>info@baybestgaragedoorca.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; 24/7; same-day service</t>
-  </si>
-  <si>
-    <t>Turn same-day availability and transparent pricing into an emergency-versus-planned-service campaign that helps prospects quickly classify repair, opener and replacement needs.</t>
-  </si>
-  <si>
-    <t>Same-day garage-door campaign for Bay Best</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Bay Best Garage Door’s current contact flow and noticed you already emphasize 24/7 availability, same-day service and transparent pricing. I’d turn that into an emergency-versus-planned-service campaign that helps homeowners quickly classify repair, opener and replacement needs before booking. Same-Day Customer Growth Pack: $150 flat. Want two Bay Best-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://baybestgaragedoorca.com/contact-us/</t>
-  </si>
-  <si>
-    <t>ZGREEN Restoration</t>
-  </si>
-  <si>
-    <t>Water / Fire Damage Restoration</t>
-  </si>
-  <si>
-    <t>Official Silicon Valley page publishes a direct email, 24/7 emergency availability, free no-obligation estimates, insurance-company coordination and a stated 45-minute response time.</t>
-  </si>
-  <si>
-    <t>info@zgreenrestoration.com</t>
-  </si>
-  <si>
-    <t>Direct email; 24/7; free estimate; stated 45-minute response</t>
-  </si>
-  <si>
-    <t>Turn the emergency response and insurance coordination into a first-hour damage-preparation campaign covering documentation, safety, insurance information and what to expect on arrival.</t>
-  </si>
-  <si>
-    <t>First-hour restoration campaign idea for ZGREEN</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed ZGREEN’s current Silicon Valley restoration page and noticed you already emphasize 24/7 availability, free estimates, insurance coordination and a 45-minute response target. I’d turn that into a first-hour homeowner campaign covering what to document, what information to prepare and what to expect before the restoration team arrives. Same-Day Customer Growth Pack: $150 flat. Want two ZGREEN-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.zgreenrestoration.com/cupertino-property-restoration/</t>
-  </si>
-  <si>
-    <t>Cal's Garage Doors</t>
-  </si>
-  <si>
-    <t>Garage Doors / Openers / Repair / Installation</t>
-  </si>
-  <si>
-    <t>Campbell / San Jose / South Bay, CA</t>
-  </si>
-  <si>
-    <t>Official contact page was crawled last week and publishes a direct email, free-estimate offer, Saturday hours and service history dating to 1965 across San Jose and the South Bay.</t>
-  </si>
-  <si>
-    <t>info@calsgaragedoors.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the long service history and repair-plus-installation range into a repair-or-replace decision campaign that helps homeowners identify symptoms, door age and opener needs before the estimate.</t>
-  </si>
-  <si>
-    <t>Repair-or-replace campaign idea for Cal's Garage Doors</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Cal’s Garage Doors’ current contact page and noticed you combine repair, opener and new-door services with free estimates across San Jose and the South Bay. I’d turn that into a repair-or-replace decision campaign that helps homeowners organize symptoms, door age and opener needs before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two Cal’s-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://calsgaragedoors.com/contact-us/</t>
-  </si>
-  <si>
-    <t>Around The Clock Garage Doors</t>
-  </si>
-  <si>
-    <t>Garage Door Repair / Installation / Replacement</t>
-  </si>
-  <si>
-    <t>Official site publishes a direct office email, free-estimate CTA and repair, installation and replacement positioning for Bay Area homeowners and businesses.</t>
-  </si>
-  <si>
-    <t>office@aroundtheclockgaragedoors.com</t>
-  </si>
-  <si>
-    <t>Direct office email; free estimate</t>
-  </si>
-  <si>
-    <t>Turn the repair-install-replace service range into a simple door-problem selector that helps prospects identify likely service needs before requesting an estimate.</t>
-  </si>
-  <si>
-    <t>Garage-door project selector for Around The Clock</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Around The Clock Garage Doors’ current Bay Area site and noticed you cover repair, installation and replacement with a free-estimate path. I’d turn that into a simple door-problem selector that helps homeowners identify likely repair versus replacement needs before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two company-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://aroundtheclockgaragedoors.com/</t>
-  </si>
-  <si>
-    <t>Península Arbor Inc.</t>
-  </si>
-  <si>
-    <t>Tree Care / Tree Removal / Emergency Arbor Services</t>
-  </si>
-  <si>
-    <t>Official site was crawled three days ago and publishes a direct email, free-consultation CTA, emergency service, insured/warranty positioning and residential/commercial tree-care coverage including San Jose.</t>
-  </si>
-  <si>
-    <t>peninsulaarbor@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free consultation; emergency service</t>
-  </si>
-  <si>
-    <t>Turn emergency plus routine tree care into a risk-and-maintenance triage campaign that helps property owners distinguish urgent hazards, removals and preventive care before requesting a consultation.</t>
-  </si>
-  <si>
-    <t>Tree-risk triage campaign for Península Arbor</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Península Arbor’s current site and noticed you combine emergency service with routine tree care and removal while offering a free consultation. I’d turn that into a risk-and-maintenance triage campaign that helps property owners distinguish urgent hazards, removal needs and preventive care before reaching out. Same-Day Customer Growth Pack: $150 flat. Want two Península Arbor-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://peninsulaarborinc.com/</t>
+    <t>Official contact page was crawled three weeks ago and publishes a direct email, free no-obligation estimate, seven-day hours and an intake specifically asking for rough fence length, desired height and city.</t>
+  </si>
+  <si>
+    <t>thejsfencing@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; open seven days</t>
+  </si>
+  <si>
+    <t>Turn the existing rough-length and height intake into a fence-planning campaign that helps homeowners prepare boundary, material, gate and neighbor-sharing questions before measurement.</t>
+  </si>
+  <si>
+    <t>Fence-planning estimate campaign for The JS Fencing</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed The JS Fencing’s current estimate flow and noticed you already tell homeowners that rough fence length, desired height and city are enough to get started. I’d turn that into a fence-planning campaign that helps prospects prepare boundary, material, gate and neighbor-sharing questions before measurement. Same-Day Customer Growth Pack: $150 flat. Want two JS Fencing-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.thejsfencing.com/contact</t>
+  </si>
+  <si>
+    <t>San Jose Concrete</t>
+  </si>
+  <si>
+    <t>Concrete / Driveways / Patios / Foundations</t>
+  </si>
+  <si>
+    <t>Official contact page was crawled last month and publishes a direct email, free estimates, a 24-hour response target and seven-day 7am-7pm availability across high-value concrete services.</t>
+  </si>
+  <si>
+    <t>info@san-jose-concrete.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated 24-hour response; seven-day availability</t>
+  </si>
+  <si>
+    <t>Turn the broad concrete service menu into a project-scope selector that helps prospects identify driveway, patio, foundation, repair or decorative needs before the site visit.</t>
+  </si>
+  <si>
+    <t>24-hour concrete project-selector campaign</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed San Jose Concrete’s current contact flow and noticed you already offer free estimates, a 24-hour response target and seven-day availability across driveways, patios, foundations and other concrete work. I’d turn that into a project-scope selector that helps prospects identify the right service and prepare useful site details before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two company-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://san-jose-concrete.com/contact/</t>
+  </si>
+  <si>
+    <t>Avis Builders and Design</t>
+  </si>
+  <si>
+    <t>Decks / Outdoor Construction / General Building</t>
+  </si>
+  <si>
+    <t>Official site was crawled four days ago and publishes a direct email, San Jose location, contractor license and free in-home consultation/free-estimate CTA.</t>
+  </si>
+  <si>
+    <t>info@avisbuildersanddesign.com</t>
+  </si>
+  <si>
+    <t>Direct email; free in-home consultation; free estimate</t>
+  </si>
+  <si>
+    <t>Turn the free in-home consultation into an outdoor-project preparation campaign that helps homeowners organize deck size, use, materials, site conditions and design priorities before the visit.</t>
+  </si>
+  <si>
+    <t>Deck consultation prep campaign for Avis Builders</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Avis Builders and Design’s current San Jose site and noticed you already offer a free in-home consultation for deck and outdoor projects. I’d turn that into a consultation-prep campaign that helps homeowners organize desired size, use, materials, site conditions and design priorities before the visit. Same-Day Customer Growth Pack: $150 flat. Want two Avis-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://avisbuildersanddesign.com/</t>
+  </si>
+  <si>
+    <t>Tomlinson Construction</t>
+  </si>
+  <si>
+    <t>Kitchen / Bathroom / Interior / Exterior Remodeling</t>
+  </si>
+  <si>
+    <t>Official contact page publishes a direct email, free-estimate intake and a detailed service selector covering kitchens, bathrooms, interior/exterior remodeling, accessibility, room additions, cabinetry and flooring.</t>
+  </si>
+  <si>
+    <t>info@tomlinsonconstruction.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; detailed project-type intake</t>
+  </si>
+  <si>
+    <t>Turn the detailed remodeling service selector into a project-planning campaign that helps prospects organize rooms, accessibility needs, additions, finishes and priorities before requesting an estimate.</t>
+  </si>
+  <si>
+    <t>Remodel project-planning campaign for Tomlinson Construction</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Tomlinson Construction’s current San Jose estimate flow and noticed you already let homeowners identify kitchen, bathroom, interior, exterior, accessibility, addition and finish-related needs up front. I’d turn that into a project-planning campaign that helps prospects organize rooms, priorities and finish decisions before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two Tomlinson-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.tomlinsonconstruction.com/contact.html</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -688,9 +679,6 @@
   </si>
   <si>
     <t>2026-09-18T16:24:00-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
   </si>
   <si>
     <t>Wait for reply. If no reply, eligible for respectful S02 follow-up on/after 2026-09-21; stop sooner on decline or opt-out.</t>
@@ -1661,32 +1649,32 @@
         <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>26</v>
@@ -1700,38 +1688,38 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>26</v>
@@ -1745,38 +1733,38 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>26</v>
@@ -1790,38 +1778,38 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>26</v>
@@ -1835,38 +1823,38 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>26</v>
@@ -1880,38 +1868,38 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>26</v>
@@ -1925,38 +1913,38 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
@@ -1970,38 +1958,38 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
@@ -2015,38 +2003,38 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>26</v>
@@ -2091,142 +2079,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2260,58 +2248,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2360,7 +2348,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2384,7 +2372,7 @@
         <v>26</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R3" s="3">
         <v>150</v>
@@ -2392,13 +2380,13 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2422,7 +2410,7 @@
         <v>26</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R4" s="3">
         <v>150</v>
@@ -2430,13 +2418,13 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -2460,7 +2448,7 @@
         <v>26</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="R5" s="3">
         <v>150</v>
@@ -2468,13 +2456,13 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2498,7 +2486,7 @@
         <v>26</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="R6" s="3">
         <v>150</v>
@@ -2506,13 +2494,13 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2536,7 +2524,7 @@
         <v>26</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -2544,13 +2532,13 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2574,7 +2562,7 @@
         <v>26</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R8" s="3">
         <v>150</v>
@@ -2582,13 +2570,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2612,7 +2600,7 @@
         <v>26</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="R9" s="3">
         <v>150</v>
@@ -2620,13 +2608,13 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2650,7 +2638,7 @@
         <v>26</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -2658,13 +2646,13 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2688,7 +2676,7 @@
         <v>26</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="R11" s="3">
         <v>150</v>
@@ -2696,28 +2684,28 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -2727,7 +2715,7 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -2738,32 +2726,32 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="G13" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -2773,7 +2761,7 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2784,26 +2772,26 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -2813,7 +2801,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2824,26 +2812,26 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -2853,7 +2841,7 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2864,26 +2852,26 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -2893,7 +2881,7 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -2904,26 +2892,26 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -2933,7 +2921,7 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -2944,26 +2932,26 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -2973,7 +2961,7 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -2984,26 +2972,26 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -3013,7 +3001,7 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -3024,26 +3012,26 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -3053,7 +3041,7 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -3064,26 +3052,26 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -3093,7 +3081,7 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3104,28 +3092,28 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3135,7 +3123,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3146,26 +3134,26 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3175,7 +3163,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3186,26 +3174,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3215,7 +3203,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3226,26 +3214,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -3255,7 +3243,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3266,26 +3254,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -3295,7 +3283,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -3306,26 +3294,26 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>219</v>
+        <v>26</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -3335,7 +3323,7 @@
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -3346,26 +3334,26 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>219</v>
+        <v>26</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
@@ -3375,7 +3363,7 @@
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -3386,26 +3374,26 @@
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>219</v>
+        <v>26</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -3415,7 +3403,7 @@
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -3426,26 +3414,26 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>219</v>
+        <v>26</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K30" s="3">
         <v>0</v>
@@ -3455,7 +3443,7 @@
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -3466,26 +3454,26 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>219</v>
+        <v>26</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K31" s="3">
         <v>0</v>
@@ -3495,7 +3483,7 @@
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -3506,26 +3494,26 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>219</v>
+        <v>26</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3535,7 +3523,7 @@
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -3546,26 +3534,26 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>219</v>
+        <v>26</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -3575,7 +3563,7 @@
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -3586,26 +3574,26 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>219</v>
+        <v>26</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -3615,7 +3603,7 @@
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -3626,26 +3614,26 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>219</v>
+        <v>26</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -3655,7 +3643,7 @@
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -3719,67 +3707,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -3788,13 +3776,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3802,10 +3790,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -3814,13 +3802,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3828,10 +3816,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -3840,28 +3828,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -3870,13 +3858,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3884,10 +3872,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -3896,13 +3884,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3910,10 +3898,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -3922,13 +3910,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -3936,10 +3924,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -3948,28 +3936,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -3978,13 +3966,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3992,10 +3980,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -4004,13 +3992,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -4018,10 +4006,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -4030,13 +4018,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -4044,10 +4032,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -4056,13 +4044,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -4070,10 +4058,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -4082,13 +4070,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -4096,10 +4084,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -4108,13 +4096,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -4122,10 +4110,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -4134,13 +4122,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -4148,10 +4136,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -4160,13 +4148,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -4174,10 +4162,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -4186,13 +4174,13 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -4200,10 +4188,10 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -4212,13 +4200,13 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -4226,10 +4214,10 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -4238,13 +4226,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -4252,10 +4240,10 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -4264,13 +4252,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -4278,10 +4266,10 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -4290,13 +4278,13 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -4304,10 +4292,10 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -4316,13 +4304,13 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -4330,10 +4318,10 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -4342,13 +4330,13 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -4356,10 +4344,10 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -4368,13 +4356,13 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -4382,10 +4370,10 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -4394,13 +4382,13 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -4408,10 +4396,10 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -4420,13 +4408,13 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -4434,10 +4422,10 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -4469,33 +4457,33 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -4509,16 +4497,16 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>27</v>
@@ -4532,14 +4520,14 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>27</v>
@@ -4553,20 +4541,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -4576,16 +4564,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>27</v>
@@ -4599,14 +4587,14 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>27</v>
@@ -4620,14 +4608,14 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -4641,14 +4629,14 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -4662,14 +4650,14 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>27</v>
@@ -4683,16 +4671,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>27</v>
@@ -4706,14 +4694,14 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>27</v>
@@ -4727,14 +4715,14 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>27</v>
@@ -4748,14 +4736,14 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>27</v>
@@ -4769,16 +4757,16 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>27</v>
@@ -4792,14 +4780,14 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>27</v>
@@ -4813,14 +4801,14 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>27</v>
@@ -4834,14 +4822,14 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>27</v>
@@ -4855,16 +4843,16 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>27</v>
@@ -4878,16 +4866,16 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>27</v>
@@ -4901,16 +4889,16 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>27</v>
@@ -4924,16 +4912,16 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>27</v>
@@ -4947,11 +4935,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -4983,13 +4971,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5009,7 +4997,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5017,179 +5005,179 @@
         <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -5224,7 +5212,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5234,20 +5222,20 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5259,95 +5247,95 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -5373,98 +5361,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -5483,19 +5471,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5512,7 +5500,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="346">
   <si>
     <t>Rank</t>
   </si>
@@ -73,292 +73,301 @@
     <t>Status</t>
   </si>
   <si>
-    <t>OK Mechanical Services</t>
-  </si>
-  <si>
-    <t>HVAC / Heating / Air Conditioning / Heat Pumps</t>
+    <t>Souza &amp; Son's Inc</t>
+  </si>
+  <si>
+    <t>Hardscape / Landscape / Pavers / Retaining Walls</t>
+  </si>
+  <si>
+    <t>Bay Area, CA</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Official contact page was crawled three days ago and publishes a direct sales email, free on-site estimates, a 24-hour email response target, site visits within 48 hours, written quotes within 24 hours of the visit and Saturday hours.</t>
+  </si>
+  <si>
+    <t>sales@souzasonsinc.com</t>
+  </si>
+  <si>
+    <t>Direct sales email; stated 24-hour response; free on-site estimate; Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the 48-hour site-visit and 24-hour written-quote process into a project-readiness campaign that helps homeowners send photos, measurements, material preferences and access details before the visit.</t>
+  </si>
+  <si>
+    <t>48-hour hardscape estimate campaign for Souza &amp; Son's</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Souza &amp; Son's current Bay Area estimate flow and noticed you already offer free on-site estimates, visits within 48 hours and written quotes within 24 hours afterward. I’d turn that speed into a project-readiness campaign that helps homeowners organize photos, measurements, material preferences and access details before the visit. Same-Day Customer Growth Pack: $150 flat. Want two Souza &amp; Son's-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://souzasonsinc.com/contact/</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>ViewPoint Roofing</t>
+  </si>
+  <si>
+    <t>Roofing / Roof Replacement / Repair / Inspections</t>
+  </si>
+  <si>
+    <t>Official site was crawled today and publishes a direct email, free estimates, same-day estimates, a 24-hour response promise and a typical two-hour business-hours response across high-value roofing services.</t>
+  </si>
+  <si>
+    <t>info@viewpointroofing.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; same-day estimates; stated two-hour typical response</t>
+  </si>
+  <si>
+    <t>Turn the fast estimate path into a roof-decision campaign that helps homeowners organize leak symptoms, roof age, visible damage, project urgency and replacement-versus-repair questions before inspection.</t>
+  </si>
+  <si>
+    <t>Two-hour roof-response campaign for ViewPoint Roofing</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed ViewPoint Roofing’s current Bay Area site and noticed you already promote free estimates, same-day estimates and a typical two-hour response during business hours. I’d turn that into a roof-decision campaign that helps homeowners organize roof age, leak symptoms, visible damage and repair-versus-replacement questions before inspection. Same-Day Customer Growth Pack: $150 flat. Want two ViewPoint-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://viewpointroofing.com/</t>
+  </si>
+  <si>
+    <t>Legend Remodeling &amp; Improvement</t>
+  </si>
+  <si>
+    <t>Kitchen / Bathroom / Deck / Whole-Home Remodeling</t>
+  </si>
+  <si>
+    <t>Concord / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official site was crawled this month and publishes a direct email, free written estimates, seven-day 6am-11pm hours and a stated 24-hour response for bathroom, kitchen and deck projects.</t>
+  </si>
+  <si>
+    <t>infolegendremodeling@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated 24-hour response; seven-day extended hours</t>
+  </si>
+  <si>
+    <t>Turn the detailed consultation and itemized-estimate process into a remodel-planning campaign that helps prospects organize room goals, layout changes, materials, budget priorities and permit questions before the visit.</t>
+  </si>
+  <si>
+    <t>24-hour remodel planning campaign for Legend</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Legend Remodeling &amp; Improvement’s current Bay Area site and noticed you already offer free detailed estimates, extended seven-day hours and a stated 24-hour response. I’d turn that into a remodel-planning campaign that helps homeowners organize room goals, layout changes, material preferences and permit questions before the consultation. Same-Day Customer Growth Pack: $150 flat. Want two Legend-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.legendremodel.com/</t>
+  </si>
+  <si>
+    <t>Murgreen Environmental Company</t>
+  </si>
+  <si>
+    <t>Plumbing / Residential / Commercial / Municipal</t>
+  </si>
+  <si>
+    <t>Tracy / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official plumbing site was crawled yesterday and publishes a direct named email, free-estimate intake, 24/7 emergency service and a promise to respond to every inquiry within two business hours.</t>
+  </si>
+  <si>
+    <t>felix@murgreen.com</t>
+  </si>
+  <si>
+    <t>Direct named email; free estimate; stated two-business-hour response; 24/7 emergencies</t>
+  </si>
+  <si>
+    <t>Turn the two-hour response and broad residential/commercial/municipal coverage into an urgency-and-scope campaign that helps prospects identify service type, symptoms, property context and emergency status before dispatch.</t>
+  </si>
+  <si>
+    <t>Two-hour plumbing inquiry campaign for Murgreen</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Murgreen’s current plumbing site and noticed you already offer free estimates, 24/7 emergency coverage and a stated two-business-hour response to every inquiry. I’d turn that into an urgency-and-scope campaign that helps prospects identify service type, symptoms, property context and emergency status before dispatch. Same-Day Customer Growth Pack: $150 flat. Want two Murgreen-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://plumbing.murgreen.com/</t>
+  </si>
+  <si>
+    <t>Green Hard Landscape Construction</t>
+  </si>
+  <si>
+    <t>Landscaping / Hardscaping / Outdoor Construction</t>
   </si>
   <si>
     <t>San Jose / Bay Area, CA</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Official site was crawled last month and advertises free estimates, same-week installation, emergency HVAC service, financing for new systems and an average response time under one hour.</t>
-  </si>
-  <si>
-    <t>ok.hvac.ca@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated under-one-hour average response; emergency service</t>
-  </si>
-  <si>
-    <t>Turn the fast-response and financing positioning into a repair-versus-replacement readiness campaign that helps homeowners organize system age, symptoms, comfort problems and financing questions before requesting an estimate.</t>
-  </si>
-  <si>
-    <t>Under-one-hour HVAC response campaign for OK Mechanical</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed OK Mechanical Services’ current San Jose site and noticed you already emphasize free estimates, same-week installation, financing and an average response time under one hour. I’d turn that into a repair-versus-replacement readiness campaign that helps homeowners organize system age, symptoms, comfort problems and financing questions before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two OK Mechanical-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.ok-ms.com/</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
-  </si>
-  <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
-    <t>AAA Construction Management</t>
-  </si>
-  <si>
-    <t>General Contracting / Home Remodeling</t>
-  </si>
-  <si>
-    <t>Official contact page offers a free consultation and estimate, publishes a direct sales email, states a response within 24 hours and lists Saturday hours.</t>
-  </si>
-  <si>
-    <t>sales@aaa-cm.com</t>
-  </si>
-  <si>
-    <t>Direct sales email; free estimate; stated 24-hour response; Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the 24-hour estimate path into a project-readiness campaign that helps remodeling prospects organize scope, priorities, budget and site questions before the consultation.</t>
-  </si>
-  <si>
-    <t>24-hour remodel estimate campaign for AAA Construction Management</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed AAA Construction Management’s current contact flow and noticed you already offer free consultations and estimates with a stated response within 24 hours. I’d turn that into a project-readiness campaign that helps homeowners organize scope, priorities, budget and site questions before the consultation. Same-Day Customer Growth Pack: $150 flat. Want two AAA-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.aaa-cm.com/contact</t>
-  </si>
-  <si>
-    <t>Atra Construction</t>
-  </si>
-  <si>
-    <t>ADU / General Construction</t>
-  </si>
-  <si>
-    <t>Official contact page specializes in Bay Area ADUs, offers consultations and free estimates, publishes a direct email and states the team will respond within 24 hours.</t>
-  </si>
-  <si>
-    <t>info@atraconstruction.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated 24-hour response</t>
-  </si>
-  <si>
-    <t>Turn the ADU specialization into a pre-consultation campaign that helps homeowners identify ADU purpose, site constraints, project location and planning questions before requesting an estimate.</t>
-  </si>
-  <si>
-    <t>24-hour ADU consultation campaign for Atra Construction</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Atra Construction’s current Bay Area ADU contact flow and noticed you already offer free estimates and state that your team gets back to prospects within 24 hours. I’d turn that into an ADU pre-consultation campaign that helps homeowners organize intended use, site constraints, location and planning questions before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two Atra-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.atraconstruction.com/contact</t>
-  </si>
-  <si>
-    <t>Valle Construction</t>
-  </si>
-  <si>
-    <t>Remodeling / ADUs / Home Repairs</t>
-  </si>
-  <si>
-    <t>Official San Jose page was crawled last week and publishes a direct email, free-estimate CTA, one-business-day response positioning and services spanning bathrooms, kitchens, ADUs and home repairs.</t>
-  </si>
-  <si>
-    <t>info@valle.construction</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated one-business-day response</t>
-  </si>
-  <si>
-    <t>Turn the broad remodel-and-ADU range into a project-type selector that helps homeowners identify scope, likely permit complexity and preparation needs before the estimate.</t>
-  </si>
-  <si>
-    <t>One-day project-readiness campaign for Valle Construction</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Valle Construction’s current San Jose page and noticed you cover bathrooms, kitchens, ADUs and home repairs while offering free estimates and a one-business-day response. I’d turn that into a project-type readiness campaign that helps homeowners identify scope, likely permit questions and preparation needs before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two Valle-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://valle.construction/services/san-jose</t>
-  </si>
-  <si>
-    <t>Gladiator Repipe &amp; Plumbing</t>
-  </si>
-  <si>
-    <t>Plumbing / Repiping / Emergency Plumbing</t>
-  </si>
-  <si>
-    <t>Official service-area page was crawled last week and publishes a direct email, free-estimate intake, 24/7 emergency availability and plumbing/repiping coverage across 20+ Bay Area cities.</t>
-  </si>
-  <si>
-    <t>gladiatorrepipe@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; 24/7 emergency availability</t>
-  </si>
-  <si>
-    <t>Turn the repipe-plus-emergency positioning into a symptom-to-project campaign that helps homeowners distinguish urgent leaks from whole-home repipe planning and prepare useful property details before requesting an estimate.</t>
-  </si>
-  <si>
-    <t>Plumbing symptom-to-project campaign for Gladiator Repipe</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Gladiator Repipe &amp; Plumbing’s current Bay Area service page and noticed you combine free estimates, 24/7 emergency availability and whole-home repiping. I’d turn that into a symptom-to-project campaign that helps homeowners distinguish urgent leak issues from repipe planning and prepare useful property details before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two Gladiator-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://gladiatorrepipe.com/service-areas/</t>
-  </si>
-  <si>
-    <t>Jade Landscape Management</t>
-  </si>
-  <si>
-    <t>Landscaping / Property Care</t>
-  </si>
-  <si>
-    <t>San Jose, CA</t>
-  </si>
-  <si>
-    <t>Official site was crawled last month and publishes a direct email, free-estimate intake, Monday-Saturday hours and a promise to respond to every inquiry within 24 hours.</t>
-  </si>
-  <si>
-    <t>Contact@JadeLM.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated 24-hour response; Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the fast estimate response into a property-priority campaign that helps residential and commercial prospects organize desired work, maintenance priorities and site details before the estimate.</t>
-  </si>
-  <si>
-    <t>24-hour landscape estimate campaign for Jade</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Jade Landscape Management’s current San Jose estimate flow and noticed you already promise to respond to every inquiry within 24 hours while serving both residential and commercial properties. I’d turn that into a property-priority campaign that helps prospects organize desired work, maintenance priorities and site details before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two Jade-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.jadelm.com/</t>
-  </si>
-  <si>
-    <t>The JS Fencing</t>
-  </si>
-  <si>
-    <t>Fencing / Gates</t>
-  </si>
-  <si>
-    <t>San Jose / South Bay, CA</t>
-  </si>
-  <si>
-    <t>Official contact page was crawled three weeks ago and publishes a direct email, free no-obligation estimate, seven-day hours and an intake specifically asking for rough fence length, desired height and city.</t>
-  </si>
-  <si>
-    <t>thejsfencing@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; open seven days</t>
-  </si>
-  <si>
-    <t>Turn the existing rough-length and height intake into a fence-planning campaign that helps homeowners prepare boundary, material, gate and neighbor-sharing questions before measurement.</t>
-  </si>
-  <si>
-    <t>Fence-planning estimate campaign for The JS Fencing</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed The JS Fencing’s current estimate flow and noticed you already tell homeowners that rough fence length, desired height and city are enough to get started. I’d turn that into a fence-planning campaign that helps prospects prepare boundary, material, gate and neighbor-sharing questions before measurement. Same-Day Customer Growth Pack: $150 flat. Want two JS Fencing-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.thejsfencing.com/contact</t>
-  </si>
-  <si>
-    <t>San Jose Concrete</t>
-  </si>
-  <si>
-    <t>Concrete / Driveways / Patios / Foundations</t>
-  </si>
-  <si>
-    <t>Official contact page was crawled last month and publishes a direct email, free estimates, a 24-hour response target and seven-day 7am-7pm availability across high-value concrete services.</t>
-  </si>
-  <si>
-    <t>info@san-jose-concrete.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated 24-hour response; seven-day availability</t>
-  </si>
-  <si>
-    <t>Turn the broad concrete service menu into a project-scope selector that helps prospects identify driveway, patio, foundation, repair or decorative needs before the site visit.</t>
-  </si>
-  <si>
-    <t>24-hour concrete project-selector campaign</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed San Jose Concrete’s current contact flow and noticed you already offer free estimates, a 24-hour response target and seven-day availability across driveways, patios, foundations and other concrete work. I’d turn that into a project-scope selector that helps prospects identify the right service and prepare useful site details before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two company-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://san-jose-concrete.com/contact/</t>
-  </si>
-  <si>
-    <t>Avis Builders and Design</t>
-  </si>
-  <si>
-    <t>Decks / Outdoor Construction / General Building</t>
-  </si>
-  <si>
-    <t>Official site was crawled four days ago and publishes a direct email, San Jose location, contractor license and free in-home consultation/free-estimate CTA.</t>
-  </si>
-  <si>
-    <t>info@avisbuildersanddesign.com</t>
-  </si>
-  <si>
-    <t>Direct email; free in-home consultation; free estimate</t>
-  </si>
-  <si>
-    <t>Turn the free in-home consultation into an outdoor-project preparation campaign that helps homeowners organize deck size, use, materials, site conditions and design priorities before the visit.</t>
-  </si>
-  <si>
-    <t>Deck consultation prep campaign for Avis Builders</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Avis Builders and Design’s current San Jose site and noticed you already offer a free in-home consultation for deck and outdoor projects. I’d turn that into a consultation-prep campaign that helps homeowners organize desired size, use, materials, site conditions and design priorities before the visit. Same-Day Customer Growth Pack: $150 flat. Want two Avis-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://avisbuildersanddesign.com/</t>
-  </si>
-  <si>
-    <t>Tomlinson Construction</t>
-  </si>
-  <si>
-    <t>Kitchen / Bathroom / Interior / Exterior Remodeling</t>
-  </si>
-  <si>
-    <t>Official contact page publishes a direct email, free-estimate intake and a detailed service selector covering kitchens, bathrooms, interior/exterior remodeling, accessibility, room additions, cabinetry and flooring.</t>
-  </si>
-  <si>
-    <t>info@tomlinsonconstruction.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; detailed project-type intake</t>
-  </si>
-  <si>
-    <t>Turn the detailed remodeling service selector into a project-planning campaign that helps prospects organize rooms, accessibility needs, additions, finishes and priorities before requesting an estimate.</t>
-  </si>
-  <si>
-    <t>Remodel project-planning campaign for Tomlinson Construction</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Tomlinson Construction’s current San Jose estimate flow and noticed you already let homeowners identify kitchen, bathroom, interior, exterior, accessibility, addition and finish-related needs up front. I’d turn that into a project-planning campaign that helps prospects organize rooms, priorities and finish decisions before requesting an estimate. Same-Day Customer Growth Pack: $150 flat. Want two Tomlinson-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.tomlinsonconstruction.com/contact.html</t>
+    <t>Official site was crawled this month and publishes a direct email, free on-site consultation, free estimates and a stated response within 24 hours across San Jose and the wider Bay Area.</t>
+  </si>
+  <si>
+    <t>greenhardscaping@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated 24-hour response; free on-site walkthrough</t>
+  </si>
+  <si>
+    <t>Turn the free walkthrough into an outdoor-project readiness campaign that helps homeowners organize project type, timeline, drainage, hardscape, planting and maintenance priorities before the site visit.</t>
+  </si>
+  <si>
+    <t>24-hour landscape walkthrough campaign for Green Hard</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Green Hard Landscape Construction’s current Bay Area estimate flow and noticed you already offer free on-site walkthroughs and state that you respond within 24 hours. I’d turn that into an outdoor-project readiness campaign that helps homeowners organize project type, timeline, drainage, hardscape and planting priorities before the visit. Same-Day Customer Growth Pack: $150 flat. Want two Green Hard-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.greenhardconstruction.com/</t>
+  </si>
+  <si>
+    <t>Orozco &amp; Sons Concrete</t>
+  </si>
+  <si>
+    <t>Concrete / Driveways / Patios / Retaining Walls / Commercial</t>
+  </si>
+  <si>
+    <t>Official contact page was crawled two weeks ago and publishes a direct quote email, free no-obligation estimates and a stated 24-hour response across residential and commercial concrete work.</t>
+  </si>
+  <si>
+    <t>Orozcoandsonsconcrete@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct quote email; free estimate; stated 24-hour response</t>
+  </si>
+  <si>
+    <t>Turn the broad concrete menu into a project-selector campaign that helps prospects identify installation versus repair, surface type, approximate dimensions, finish preferences and commercial-versus-residential needs before estimating.</t>
+  </si>
+  <si>
+    <t>24-hour concrete estimate campaign for Orozco &amp; Sons</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Orozco &amp; Sons Concrete’s current Bay Area contact flow and noticed you already offer free estimates with a stated 24-hour response across residential and commercial work. I’d turn that into a project-selector campaign that helps prospects identify installation versus repair, approximate dimensions, finish preferences and property type before estimating. Same-Day Customer Growth Pack: $150 flat. Want two Orozco-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://orozcoandsonsconcrete.com/contact</t>
+  </si>
+  <si>
+    <t>DD's Construction</t>
+  </si>
+  <si>
+    <t>General Contracting / Renovations / Custom Homes / Commercial</t>
+  </si>
+  <si>
+    <t>Sacramento / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official site was crawled last week and publishes a direct email, free no-obligation estimates and a typical 24-hour response across renovations, custom builds and commercial projects, including San Jose and Santa Clara service coverage.</t>
+  </si>
+  <si>
+    <t>info@ddsconstructionca.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated typical 24-hour response</t>
+  </si>
+  <si>
+    <t>Turn the broad build-and-renovation range into a project-readiness campaign that helps prospects organize scope, site-visit needs, timeline and residential-versus-commercial requirements before the estimate.</t>
+  </si>
+  <si>
+    <t>24-hour project-readiness campaign for DD's Construction</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed DD's Construction’s current estimate flow and noticed you offer free no-obligation estimates and typically respond within 24 hours across renovations, custom builds and commercial work. I’d turn that into a project-readiness campaign that helps prospects organize scope, site-visit needs, timeline and property type before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two DD's-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://ddsconstructionca.com/</t>
+  </si>
+  <si>
+    <t>JC Construction Pro Services</t>
+  </si>
+  <si>
+    <t>Residential / Commercial Construction / Remodeling</t>
+  </si>
+  <si>
+    <t>Official contact page was crawled today and publishes a direct email, free estimates, Saturday hours and a stated usual response within 24 hours for residential and commercial construction projects.</t>
+  </si>
+  <si>
+    <t>JCConstruction89gb@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated usual 24-hour response; Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the residential-and-commercial intake into a scope-preparation campaign that helps prospects organize service type, project details, property use and scheduling priorities before the estimate.</t>
+  </si>
+  <si>
+    <t>24-hour construction inquiry campaign for JC Construction</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed JC Construction Pro Services’ current Bay Area contact flow and noticed you already offer free estimates, Saturday availability and usually respond within 24 hours. I’d turn that into a scope-preparation campaign that helps residential and commercial prospects organize service type, project details, property use and scheduling priorities before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two JC-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://jcconstructionproservices.com/contact.php</t>
+  </si>
+  <si>
+    <t>Willow Wash</t>
+  </si>
+  <si>
+    <t>Exterior Cleaning / Roof Cleaning / Commercial Property Maintenance</t>
+  </si>
+  <si>
+    <t>Official site was crawled today and publishes a direct email, free estimates, same-week availability and a stated 24-hour quote target for residential and commercial exterior cleaning across 36+ Bay Area communities.</t>
+  </si>
+  <si>
+    <t>Burch@willowwashllc.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; quotes within 24 hours; same-week availability</t>
+  </si>
+  <si>
+    <t>Turn the residential/commercial service breadth into a property-care selector that helps prospects identify surfaces, building type, access, recurring-maintenance needs and urgency before quoting.</t>
+  </si>
+  <si>
+    <t>24-hour property-care quote campaign for Willow Wash</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Willow Wash’s current San Jose and Bay Area site and noticed you already offer free estimates, same-week availability and most quotes within 24 hours for residential and commercial exterior cleaning. I’d turn that into a property-care selector that helps prospects identify surfaces, property type, access and recurring-maintenance needs before quoting. Same-Day Customer Growth Pack: $150 flat. Want two Willow Wash-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://willowwashllc.com/</t>
+  </si>
+  <si>
+    <t>Fortino Cisneros Landscaping</t>
+  </si>
+  <si>
+    <t>Landscaping / Irrigation / Turf / Tree Work</t>
+  </si>
+  <si>
+    <t>San Jose / Peninsula / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official site was crawled last month and publishes a direct email, free estimates, same-week scheduling for most jobs, 24/7 emergency help and quotes usually scheduled within 24 hours across landscaping, irrigation, turf and tree services.</t>
+  </si>
+  <si>
+    <t>contact@fortinocisneroslandscaping.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; quotes usually scheduled within 24 hours; same-week scheduling</t>
+  </si>
+  <si>
+    <t>Turn the owner-direct, multi-service yard offering into a yard-priority campaign that helps homeowners distinguish maintenance, irrigation, turf, tree and cleanup needs and prepare photos/site details before the estimate.</t>
+  </si>
+  <si>
+    <t>24-hour yard-priority campaign for Fortino Cisneros Landscaping</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Fortino Cisneros Landscaping’s current Bay Area site and noticed you already offer free estimates, same-week scheduling for most jobs and quotes usually scheduled within 24 hours. I’d turn that into a yard-priority campaign that helps homeowners distinguish maintenance, irrigation, turf, tree and cleanup needs and prepare useful site details before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two Fortino-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.fortinocisneroslandscaping.com/</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -679,6 +688,9 @@
   </si>
   <si>
     <t>2026-09-18T16:24:00-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
   </si>
   <si>
     <t>Wait for reply. If no reply, eligible for respectful S02 follow-up on/after 2026-09-21; stop sooner on decline or opt-out.</t>
@@ -1694,32 +1706,32 @@
         <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>26</v>
@@ -1733,38 +1745,38 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>26</v>
@@ -1778,38 +1790,38 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>26</v>
@@ -1823,38 +1835,38 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>26</v>
@@ -1868,38 +1880,38 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>26</v>
@@ -1913,38 +1925,38 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
@@ -1958,38 +1970,38 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
@@ -2003,38 +2015,38 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>26</v>
@@ -2079,142 +2091,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2248,58 +2260,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2386,7 +2398,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2410,7 +2422,7 @@
         <v>26</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R4" s="3">
         <v>150</v>
@@ -2418,13 +2430,13 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -2448,7 +2460,7 @@
         <v>26</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R5" s="3">
         <v>150</v>
@@ -2456,13 +2468,13 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2486,7 +2498,7 @@
         <v>26</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="R6" s="3">
         <v>150</v>
@@ -2494,13 +2506,13 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2524,7 +2536,7 @@
         <v>26</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -2532,13 +2544,13 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2562,7 +2574,7 @@
         <v>26</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="R8" s="3">
         <v>150</v>
@@ -2570,13 +2582,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2600,7 +2612,7 @@
         <v>26</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="R9" s="3">
         <v>150</v>
@@ -2608,13 +2620,13 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2638,7 +2650,7 @@
         <v>26</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -2646,13 +2658,13 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2676,7 +2688,7 @@
         <v>26</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="R11" s="3">
         <v>150</v>
@@ -2684,28 +2696,28 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -2715,7 +2727,7 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -2726,32 +2738,32 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -2761,7 +2773,7 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2772,26 +2784,26 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -2801,7 +2813,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2812,26 +2824,26 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -2841,7 +2853,7 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2852,26 +2864,26 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -2881,7 +2893,7 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -2892,26 +2904,26 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -2921,7 +2933,7 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -2932,26 +2944,26 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -2961,7 +2973,7 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -2972,26 +2984,26 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -3001,7 +3013,7 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -3012,26 +3024,26 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -3041,7 +3053,7 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -3052,26 +3064,26 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -3081,7 +3093,7 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3092,28 +3104,28 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3123,7 +3135,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3134,26 +3146,26 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3163,7 +3175,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3174,26 +3186,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3203,7 +3215,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3214,26 +3226,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -3243,7 +3255,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3254,26 +3266,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -3283,7 +3295,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -3294,26 +3306,26 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -3323,7 +3335,7 @@
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -3334,26 +3346,26 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
@@ -3363,7 +3375,7 @@
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -3374,26 +3386,26 @@
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="E29" s="2" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -3403,7 +3415,7 @@
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -3414,26 +3426,26 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K30" s="3">
         <v>0</v>
@@ -3443,7 +3455,7 @@
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -3454,26 +3466,26 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K31" s="3">
         <v>0</v>
@@ -3483,7 +3495,7 @@
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -3494,26 +3506,26 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3523,7 +3535,7 @@
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -3534,26 +3546,26 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -3563,7 +3575,7 @@
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -3574,26 +3586,26 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -3603,7 +3615,7 @@
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -3614,26 +3626,26 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -3643,7 +3655,7 @@
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -3707,67 +3719,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -3776,13 +3788,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3790,10 +3802,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -3802,13 +3814,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3816,10 +3828,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -3828,28 +3840,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -3858,13 +3870,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3872,10 +3884,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -3884,13 +3896,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3898,10 +3910,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -3910,13 +3922,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -3924,10 +3936,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -3936,28 +3948,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -3966,13 +3978,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3980,10 +3992,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -3992,13 +4004,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -4006,10 +4018,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -4018,13 +4030,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -4032,10 +4044,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -4044,13 +4056,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -4058,10 +4070,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -4070,13 +4082,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -4084,10 +4096,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -4096,13 +4108,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -4110,10 +4122,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -4122,13 +4134,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -4136,10 +4148,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -4148,13 +4160,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -4162,10 +4174,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -4174,13 +4186,13 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -4188,10 +4200,10 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -4200,13 +4212,13 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -4214,10 +4226,10 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -4226,13 +4238,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -4240,10 +4252,10 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -4252,13 +4264,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -4266,10 +4278,10 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -4278,13 +4290,13 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -4292,10 +4304,10 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -4304,13 +4316,13 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -4318,10 +4330,10 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -4330,13 +4342,13 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -4344,10 +4356,10 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -4356,13 +4368,13 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -4370,10 +4382,10 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -4382,13 +4394,13 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -4396,10 +4408,10 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -4408,13 +4420,13 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -4422,10 +4434,10 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -4457,33 +4469,33 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -4497,16 +4509,16 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>27</v>
@@ -4520,14 +4532,14 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>27</v>
@@ -4541,20 +4553,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -4564,16 +4576,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>27</v>
@@ -4587,14 +4599,14 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>27</v>
@@ -4608,14 +4620,14 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -4629,14 +4641,14 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -4650,14 +4662,14 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>27</v>
@@ -4671,16 +4683,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>27</v>
@@ -4694,14 +4706,14 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>27</v>
@@ -4715,14 +4727,14 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>27</v>
@@ -4736,14 +4748,14 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>27</v>
@@ -4757,16 +4769,16 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>27</v>
@@ -4780,14 +4792,14 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>27</v>
@@ -4801,14 +4813,14 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>27</v>
@@ -4822,14 +4834,14 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>27</v>
@@ -4843,16 +4855,16 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>27</v>
@@ -4866,16 +4878,16 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>27</v>
@@ -4889,16 +4901,16 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>27</v>
@@ -4912,16 +4924,16 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>27</v>
@@ -4935,11 +4947,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -4971,13 +4983,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4997,7 +5009,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5017,7 +5029,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5025,159 +5037,159 @@
         <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -5212,7 +5224,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5222,20 +5234,20 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5247,95 +5259,95 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -5361,98 +5373,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -5471,19 +5483,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5500,7 +5512,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -73,301 +73,301 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Souza &amp; Son's Inc</t>
-  </si>
-  <si>
-    <t>Hardscape / Landscape / Pavers / Retaining Walls</t>
+    <t>Bay HVAC Masters</t>
+  </si>
+  <si>
+    <t>HVAC / Heating / Cooling / System Installation</t>
+  </si>
+  <si>
+    <t>San Jose / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Official contact page publishes service@bayhvacmasters.com, same-day appointments, free installation estimates, 24/7 emergency dispatch and a stated one-business-hour response to inquiries and email.</t>
+  </si>
+  <si>
+    <t>service@bayhvacmasters.com</t>
+  </si>
+  <si>
+    <t>Direct service email; stated one-business-hour response; same-day appointments; free installation estimates</t>
+  </si>
+  <si>
+    <t>Turn the one-hour response and same-day availability into a repair-versus-replacement readiness campaign that helps homeowners identify symptoms, equipment age, comfort problems and installation goals before dispatch.</t>
+  </si>
+  <si>
+    <t>One-hour HVAC response campaign for Bay HVAC Masters</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Bay HVAC Masters’ current San Jose contact flow and noticed you already offer same-day appointments, free installation estimates and a stated one-business-hour email response. I’d turn that speed into a repair-versus-replacement readiness campaign that helps homeowners organize symptoms, equipment age, comfort issues and installation goals before dispatch. Same-Day Customer Growth Pack: $150 flat. Want two Bay HVAC Masters-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.bayhvacmasters.com/contact/</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>JS Overhead Garage Door</t>
+  </si>
+  <si>
+    <t>Garage Door Repair / Installation / Openers / Emergency Service</t>
+  </si>
+  <si>
+    <t>Bay Area / Sacramento, CA</t>
+  </si>
+  <si>
+    <t>Official contact page publishes info@jsogaragedoor.com, same-day service, free estimates and a stated response within one hour during business hours.</t>
+  </si>
+  <si>
+    <t>info@jsogaragedoor.com</t>
+  </si>
+  <si>
+    <t>Direct email; stated one-hour business-hours response; same-day service; free estimate</t>
+  </si>
+  <si>
+    <t>Turn the one-hour response into a garage-door triage campaign that helps prospects identify door versus opener issues, safety symptoms, urgency and replacement-versus-repair needs before service.</t>
+  </si>
+  <si>
+    <t>One-hour garage-door triage campaign for JS Overhead</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed JS Overhead Garage Door’s current contact flow and noticed you already offer same-day service, free estimates and a stated one-hour response during business hours. I’d turn that into a garage-door triage campaign that helps prospects identify door versus opener issues, safety symptoms, urgency and repair-versus-replacement needs before service. Same-Day Customer Growth Pack: $150 flat. Want two JS Overhead-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.jsogaragedoor.com/contact</t>
+  </si>
+  <si>
+    <t>Elite Unit Group</t>
+  </si>
+  <si>
+    <t>Apartment Turnovers / Property Maintenance / Multi-Service Renovation</t>
+  </si>
+  <si>
+    <t>Bay Area / Sacramento / Central Valley, CA</t>
+  </si>
+  <si>
+    <t>Official contact page was crawled today and publishes info@eliteunitgroup.com, free turnover quotes, responses within a few hours and 24–48 hour unit turns with one crew handling multiple services.</t>
+  </si>
+  <si>
+    <t>info@eliteunitgroup.com</t>
+  </si>
+  <si>
+    <t>Direct email; free quote; stated response within hours; 24–48 hour unit turns</t>
+  </si>
+  <si>
+    <t>Turn the fast multi-service turnover model into a property-manager intake campaign that organizes unit condition, required trades, vacancy deadline, photos and scope before quoting.</t>
+  </si>
+  <si>
+    <t>Fast unit-turn intake campaign for Elite Unit Group</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Elite Unit Group’s current California turnover flow and noticed you already offer free quotes, responses within a few hours and 24–48 hour unit turns using one crew across multiple services. I’d turn that into a property-manager intake campaign that organizes unit condition, required trades, vacancy deadline, photos and scope before quoting. Same-Day Customer Growth Pack: $150 flat. Want two Elite Unit-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://eliteunitgroup.com/contact</t>
+  </si>
+  <si>
+    <t>Pristine Construction LLC</t>
+  </si>
+  <si>
+    <t>Design-Build / Kitchens / Bathrooms / ADUs / Whole-Home Remodeling</t>
+  </si>
+  <si>
+    <t>Official site publishes office@pristineconstructionllc.com, free no-obligation consultations, a stated response within 24 hours and a design-build focus on kitchens, baths, ADUs and full-home remodels.</t>
+  </si>
+  <si>
+    <t>office@pristineconstructionllc.com</t>
+  </si>
+  <si>
+    <t>Direct office email; free consultation; stated 24-hour response; Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the design-build consultation into a project-direction campaign that helps homeowners organize vision, timeline, goals, project type and site-visit readiness before the first call.</t>
+  </si>
+  <si>
+    <t>24-hour design-build intake campaign for Pristine</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Pristine Construction’s current San Jose consultation flow and noticed you already offer free consultations with a stated 24-hour response for kitchens, baths, ADUs and full-home remodels. I’d turn that into a project-direction campaign that helps homeowners organize vision, timeline, goals and site-visit readiness before the first call. Same-Day Customer Growth Pack: $150 flat. Want two Pristine-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://pristineconstructionllc.com/</t>
+  </si>
+  <si>
+    <t>Maison Remodeling Group</t>
+  </si>
+  <si>
+    <t>Kitchen / Bathroom / ADU / Additions / Whole-Home Remodeling</t>
+  </si>
+  <si>
+    <t>Santa Clara / San Jose / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official contact page publishes office@maisonremodeling.com, free 30-minute consultations and a stated 24-hour response for kitchen, bathroom, ADU, addition, whole-home and outdoor remodeling inquiries.</t>
+  </si>
+  <si>
+    <t>office@maisonremodeling.com</t>
+  </si>
+  <si>
+    <t>Direct office email; free consultation; stated 24-hour response</t>
+  </si>
+  <si>
+    <t>Turn the 30-minute consultation into a pre-call planning campaign that helps homeowners organize project type, priorities, budget questions, timeline and existing plans before speaking with the team.</t>
+  </si>
+  <si>
+    <t>30-minute consultation prep campaign for Maison Remodeling</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Maison Remodeling Group’s current Santa Clara consultation flow and noticed you already offer free 30-minute consultations and state that written inquiries receive a response within 24 hours. I’d turn that into a pre-call planning campaign that helps homeowners organize project type, priorities, budget questions, timeline and existing plans before speaking with your team. Same-Day Customer Growth Pack: $150 flat. Want two Maison-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://maisonremodeling.com/contact</t>
+  </si>
+  <si>
+    <t>Atlantis Remodeling</t>
+  </si>
+  <si>
+    <t>Official contact page publishes contact@atlantis-remodeling.com, free no-obligation consultations, Monday-Saturday hours and a stated response within 24 hours for premium remodeling projects.</t>
+  </si>
+  <si>
+    <t>contact@atlantis-remodeling.com</t>
+  </si>
+  <si>
+    <t>Direct email; free consultation; stated 24-hour response; Monday-Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the design-build consultation into a dream-project readiness campaign that helps prospects organize vision, project type, decision priorities and questions before the consultation.</t>
+  </si>
+  <si>
+    <t>24-hour consultation campaign for Atlantis Remodeling</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Atlantis Remodeling’s current San Jose contact flow and noticed you already offer free no-obligation consultations, Monday-Saturday availability and a stated 24-hour response. I’d turn that into a dream-project readiness campaign that helps prospects organize vision, project type, decision priorities and questions before the consultation. Same-Day Customer Growth Pack: $150 flat. Want two Atlantis-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.atlantis-remodeling.com/contact</t>
+  </si>
+  <si>
+    <t>Silicon Prime Painting</t>
+  </si>
+  <si>
+    <t>Residential / Commercial Painting</t>
+  </si>
+  <si>
+    <t>Official contact page offers free estimates, states a response within one business day and serves San Jose and the surrounding Bay Area with licensed and insured painting services.</t>
+  </si>
+  <si>
+    <t>contact-form-first</t>
+  </si>
+  <si>
+    <t>Official free-estimate form; stated one-business-day response; San Jose address published</t>
+  </si>
+  <si>
+    <t>Turn the fast estimate process into a paint-project preparation campaign that helps prospects organize interior-versus-exterior scope, surfaces, rooms, finish goals, timing and property details before estimating.</t>
+  </si>
+  <si>
+    <t>One-day paint estimate campaign for Silicon Prime</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Silicon Prime Painting’s current San Jose estimate flow and noticed you offer free estimates with a stated response within one business day. I’d turn that into a paint-project preparation campaign that helps prospects organize interior-versus-exterior scope, surfaces, rooms, finish goals and timing before estimating. Same-Day Customer Growth Pack: $150 flat. Want two Silicon Prime-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.siliconprimepainting.org/contact.html</t>
+  </si>
+  <si>
+    <t>Otto &amp; Sons Construction</t>
+  </si>
+  <si>
+    <t>Residential Remodeling / Commercial Tenant Improvements / Construction</t>
+  </si>
+  <si>
+    <t>Bay Area / Antioch, CA</t>
+  </si>
+  <si>
+    <t>Official contact page publishes alani@ottoandsonsco.com, free no-obligation estimates, a typical 24-hour business-day response and Saturday hours for residential remodels and commercial work.</t>
+  </si>
+  <si>
+    <t>alani@ottoandsonsco.com</t>
+  </si>
+  <si>
+    <t>Direct named email; free estimate; typical 24-hour response; Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the residential-and-commercial range into a project-routing campaign that helps prospects identify remodel, tenant-improvement, small-build or service-call needs and prepare useful scope details before quoting.</t>
+  </si>
+  <si>
+    <t>24-hour project-routing campaign for Otto &amp; Sons</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Otto &amp; Sons Construction’s current Bay Area quote flow and noticed you already offer free estimates, typically respond within 24 business hours and handle both residential remodels and commercial work. I’d turn that into a project-routing campaign that helps prospects identify remodel, tenant-improvement, small-build or service-call needs and prepare useful scope details before quoting. Same-Day Customer Growth Pack: $150 flat. Want two Otto &amp; Sons-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.ottoandsonsco.com/contact</t>
+  </si>
+  <si>
+    <t>SBH Construction</t>
+  </si>
+  <si>
+    <t>Foundation Repair / Residential Construction / Remodeling</t>
+  </si>
+  <si>
+    <t>Walnut Creek / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official services page publishes info@sbhconstruction.com, free no-obligation consultations, detailed estimates and a stated one-business-day response, with permit applications and inspections handled for clients.</t>
+  </si>
+  <si>
+    <t>info@sbhconstruction.com</t>
+  </si>
+  <si>
+    <t>Direct email; free consultation; stated 24-hour response; Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the consultation and permit-handling process into a foundation/project readiness campaign that helps homeowners organize symptoms, project goals, property context and permit questions before the site visit.</t>
+  </si>
+  <si>
+    <t>Foundation project-readiness campaign for SBH Construction</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed SBH Construction’s current Bay Area service flow and noticed you already offer free consultations, detailed estimates, permit handling and a stated response within one business day. I’d turn that into a project-readiness campaign that helps homeowners organize symptoms, project goals, property context and permit questions before the site visit. Same-Day Customer Growth Pack: $150 flat. Want two SBH-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://sbhconstructioninc.com/services/</t>
+  </si>
+  <si>
+    <t>Bay Area Fabrication &amp; Repair</t>
+  </si>
+  <si>
+    <t>Welding / Metal Fabrication / Mobile Repair / Commercial &amp; Residential</t>
   </si>
   <si>
     <t>Bay Area, CA</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Official contact page was crawled three days ago and publishes a direct sales email, free on-site estimates, a 24-hour email response target, site visits within 48 hours, written quotes within 24 hours of the visit and Saturday hours.</t>
-  </si>
-  <si>
-    <t>sales@souzasonsinc.com</t>
-  </si>
-  <si>
-    <t>Direct sales email; stated 24-hour response; free on-site estimate; Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the 48-hour site-visit and 24-hour written-quote process into a project-readiness campaign that helps homeowners send photos, measurements, material preferences and access details before the visit.</t>
-  </si>
-  <si>
-    <t>48-hour hardscape estimate campaign for Souza &amp; Son's</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Souza &amp; Son's current Bay Area estimate flow and noticed you already offer free on-site estimates, visits within 48 hours and written quotes within 24 hours afterward. I’d turn that speed into a project-readiness campaign that helps homeowners organize photos, measurements, material preferences and access details before the visit. Same-Day Customer Growth Pack: $150 flat. Want two Souza &amp; Son's-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://souzasonsinc.com/contact/</t>
-  </si>
-  <si>
-    <t>2026-09-22</t>
-  </si>
-  <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
-    <t>ViewPoint Roofing</t>
-  </si>
-  <si>
-    <t>Roofing / Roof Replacement / Repair / Inspections</t>
-  </si>
-  <si>
-    <t>Official site was crawled today and publishes a direct email, free estimates, same-day estimates, a 24-hour response promise and a typical two-hour business-hours response across high-value roofing services.</t>
-  </si>
-  <si>
-    <t>info@viewpointroofing.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; same-day estimates; stated two-hour typical response</t>
-  </si>
-  <si>
-    <t>Turn the fast estimate path into a roof-decision campaign that helps homeowners organize leak symptoms, roof age, visible damage, project urgency and replacement-versus-repair questions before inspection.</t>
-  </si>
-  <si>
-    <t>Two-hour roof-response campaign for ViewPoint Roofing</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed ViewPoint Roofing’s current Bay Area site and noticed you already promote free estimates, same-day estimates and a typical two-hour response during business hours. I’d turn that into a roof-decision campaign that helps homeowners organize roof age, leak symptoms, visible damage and repair-versus-replacement questions before inspection. Same-Day Customer Growth Pack: $150 flat. Want two ViewPoint-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://viewpointroofing.com/</t>
-  </si>
-  <si>
-    <t>Legend Remodeling &amp; Improvement</t>
-  </si>
-  <si>
-    <t>Kitchen / Bathroom / Deck / Whole-Home Remodeling</t>
-  </si>
-  <si>
-    <t>Concord / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site was crawled this month and publishes a direct email, free written estimates, seven-day 6am-11pm hours and a stated 24-hour response for bathroom, kitchen and deck projects.</t>
-  </si>
-  <si>
-    <t>infolegendremodeling@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated 24-hour response; seven-day extended hours</t>
-  </si>
-  <si>
-    <t>Turn the detailed consultation and itemized-estimate process into a remodel-planning campaign that helps prospects organize room goals, layout changes, materials, budget priorities and permit questions before the visit.</t>
-  </si>
-  <si>
-    <t>24-hour remodel planning campaign for Legend</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Legend Remodeling &amp; Improvement’s current Bay Area site and noticed you already offer free detailed estimates, extended seven-day hours and a stated 24-hour response. I’d turn that into a remodel-planning campaign that helps homeowners organize room goals, layout changes, material preferences and permit questions before the consultation. Same-Day Customer Growth Pack: $150 flat. Want two Legend-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.legendremodel.com/</t>
-  </si>
-  <si>
-    <t>Murgreen Environmental Company</t>
-  </si>
-  <si>
-    <t>Plumbing / Residential / Commercial / Municipal</t>
-  </si>
-  <si>
-    <t>Tracy / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official plumbing site was crawled yesterday and publishes a direct named email, free-estimate intake, 24/7 emergency service and a promise to respond to every inquiry within two business hours.</t>
-  </si>
-  <si>
-    <t>felix@murgreen.com</t>
-  </si>
-  <si>
-    <t>Direct named email; free estimate; stated two-business-hour response; 24/7 emergencies</t>
-  </si>
-  <si>
-    <t>Turn the two-hour response and broad residential/commercial/municipal coverage into an urgency-and-scope campaign that helps prospects identify service type, symptoms, property context and emergency status before dispatch.</t>
-  </si>
-  <si>
-    <t>Two-hour plumbing inquiry campaign for Murgreen</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Murgreen’s current plumbing site and noticed you already offer free estimates, 24/7 emergency coverage and a stated two-business-hour response to every inquiry. I’d turn that into an urgency-and-scope campaign that helps prospects identify service type, symptoms, property context and emergency status before dispatch. Same-Day Customer Growth Pack: $150 flat. Want two Murgreen-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://plumbing.murgreen.com/</t>
-  </si>
-  <si>
-    <t>Green Hard Landscape Construction</t>
-  </si>
-  <si>
-    <t>Landscaping / Hardscaping / Outdoor Construction</t>
-  </si>
-  <si>
-    <t>San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site was crawled this month and publishes a direct email, free on-site consultation, free estimates and a stated response within 24 hours across San Jose and the wider Bay Area.</t>
-  </si>
-  <si>
-    <t>greenhardscaping@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated 24-hour response; free on-site walkthrough</t>
-  </si>
-  <si>
-    <t>Turn the free walkthrough into an outdoor-project readiness campaign that helps homeowners organize project type, timeline, drainage, hardscape, planting and maintenance priorities before the site visit.</t>
-  </si>
-  <si>
-    <t>24-hour landscape walkthrough campaign for Green Hard</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Green Hard Landscape Construction’s current Bay Area estimate flow and noticed you already offer free on-site walkthroughs and state that you respond within 24 hours. I’d turn that into an outdoor-project readiness campaign that helps homeowners organize project type, timeline, drainage, hardscape and planting priorities before the visit. Same-Day Customer Growth Pack: $150 flat. Want two Green Hard-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.greenhardconstruction.com/</t>
-  </si>
-  <si>
-    <t>Orozco &amp; Sons Concrete</t>
-  </si>
-  <si>
-    <t>Concrete / Driveways / Patios / Retaining Walls / Commercial</t>
-  </si>
-  <si>
-    <t>Official contact page was crawled two weeks ago and publishes a direct quote email, free no-obligation estimates and a stated 24-hour response across residential and commercial concrete work.</t>
-  </si>
-  <si>
-    <t>Orozcoandsonsconcrete@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct quote email; free estimate; stated 24-hour response</t>
-  </si>
-  <si>
-    <t>Turn the broad concrete menu into a project-selector campaign that helps prospects identify installation versus repair, surface type, approximate dimensions, finish preferences and commercial-versus-residential needs before estimating.</t>
-  </si>
-  <si>
-    <t>24-hour concrete estimate campaign for Orozco &amp; Sons</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Orozco &amp; Sons Concrete’s current Bay Area contact flow and noticed you already offer free estimates with a stated 24-hour response across residential and commercial work. I’d turn that into a project-selector campaign that helps prospects identify installation versus repair, approximate dimensions, finish preferences and property type before estimating. Same-Day Customer Growth Pack: $150 flat. Want two Orozco-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://orozcoandsonsconcrete.com/contact</t>
-  </si>
-  <si>
-    <t>DD's Construction</t>
-  </si>
-  <si>
-    <t>General Contracting / Renovations / Custom Homes / Commercial</t>
-  </si>
-  <si>
-    <t>Sacramento / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site was crawled last week and publishes a direct email, free no-obligation estimates and a typical 24-hour response across renovations, custom builds and commercial projects, including San Jose and Santa Clara service coverage.</t>
-  </si>
-  <si>
-    <t>info@ddsconstructionca.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated typical 24-hour response</t>
-  </si>
-  <si>
-    <t>Turn the broad build-and-renovation range into a project-readiness campaign that helps prospects organize scope, site-visit needs, timeline and residential-versus-commercial requirements before the estimate.</t>
-  </si>
-  <si>
-    <t>24-hour project-readiness campaign for DD's Construction</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed DD's Construction’s current estimate flow and noticed you offer free no-obligation estimates and typically respond within 24 hours across renovations, custom builds and commercial work. I’d turn that into a project-readiness campaign that helps prospects organize scope, site-visit needs, timeline and property type before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two DD's-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://ddsconstructionca.com/</t>
-  </si>
-  <si>
-    <t>JC Construction Pro Services</t>
-  </si>
-  <si>
-    <t>Residential / Commercial Construction / Remodeling</t>
-  </si>
-  <si>
-    <t>Official contact page was crawled today and publishes a direct email, free estimates, Saturday hours and a stated usual response within 24 hours for residential and commercial construction projects.</t>
-  </si>
-  <si>
-    <t>JCConstruction89gb@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated usual 24-hour response; Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the residential-and-commercial intake into a scope-preparation campaign that helps prospects organize service type, project details, property use and scheduling priorities before the estimate.</t>
-  </si>
-  <si>
-    <t>24-hour construction inquiry campaign for JC Construction</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed JC Construction Pro Services’ current Bay Area contact flow and noticed you already offer free estimates, Saturday availability and usually respond within 24 hours. I’d turn that into a scope-preparation campaign that helps residential and commercial prospects organize service type, project details, property use and scheduling priorities before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two JC-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://jcconstructionproservices.com/contact.php</t>
-  </si>
-  <si>
-    <t>Willow Wash</t>
-  </si>
-  <si>
-    <t>Exterior Cleaning / Roof Cleaning / Commercial Property Maintenance</t>
-  </si>
-  <si>
-    <t>Official site was crawled today and publishes a direct email, free estimates, same-week availability and a stated 24-hour quote target for residential and commercial exterior cleaning across 36+ Bay Area communities.</t>
-  </si>
-  <si>
-    <t>Burch@willowwashllc.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; quotes within 24 hours; same-week availability</t>
-  </si>
-  <si>
-    <t>Turn the residential/commercial service breadth into a property-care selector that helps prospects identify surfaces, building type, access, recurring-maintenance needs and urgency before quoting.</t>
-  </si>
-  <si>
-    <t>24-hour property-care quote campaign for Willow Wash</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Willow Wash’s current San Jose and Bay Area site and noticed you already offer free estimates, same-week availability and most quotes within 24 hours for residential and commercial exterior cleaning. I’d turn that into a property-care selector that helps prospects identify surfaces, property type, access and recurring-maintenance needs before quoting. Same-Day Customer Growth Pack: $150 flat. Want two Willow Wash-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://willowwashllc.com/</t>
-  </si>
-  <si>
-    <t>Fortino Cisneros Landscaping</t>
-  </si>
-  <si>
-    <t>Landscaping / Irrigation / Turf / Tree Work</t>
-  </si>
-  <si>
-    <t>San Jose / Peninsula / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site was crawled last month and publishes a direct email, free estimates, same-week scheduling for most jobs, 24/7 emergency help and quotes usually scheduled within 24 hours across landscaping, irrigation, turf and tree services.</t>
-  </si>
-  <si>
-    <t>contact@fortinocisneroslandscaping.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; quotes usually scheduled within 24 hours; same-week scheduling</t>
-  </si>
-  <si>
-    <t>Turn the owner-direct, multi-service yard offering into a yard-priority campaign that helps homeowners distinguish maintenance, irrigation, turf, tree and cleanup needs and prepare photos/site details before the estimate.</t>
-  </si>
-  <si>
-    <t>24-hour yard-priority campaign for Fortino Cisneros Landscaping</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Fortino Cisneros Landscaping’s current Bay Area site and noticed you already offer free estimates, same-week scheduling for most jobs and quotes usually scheduled within 24 hours. I’d turn that into a yard-priority campaign that helps homeowners distinguish maintenance, irrigation, turf, tree and cleanup needs and prepare useful site details before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two Fortino-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.fortinocisneroslandscaping.com/</t>
+    <t>Official site publishes bayareafabrications@gmail.com, free estimates, Monday-Saturday hours and a stated 24-hour response across welding, structural fabrication, mobile repair and custom metalwork.</t>
+  </si>
+  <si>
+    <t>bayareafabrications@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated 24-hour response; Monday-Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the broad fabrication menu into a job-scope selector that helps prospects identify mobile repair versus shop fabrication, material, dimensions, location and urgency before estimating.</t>
+  </si>
+  <si>
+    <t>24-hour fabrication quote campaign for Bay Area Fabrication</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Bay Area Fabrication &amp; Repair’s current service flow and noticed you offer free estimates, Monday-Saturday availability and a stated 24-hour response across welding, fabrication and mobile repair. I’d turn that into a job-scope selector that helps prospects identify mobile repair versus shop fabrication, material, dimensions, location and urgency before estimating. Same-Day Customer Growth Pack: $150 flat. Want two business-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://bayareafabrications.com/</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -1661,32 +1661,32 @@
         <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>26</v>
@@ -1700,38 +1700,38 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>26</v>
@@ -1745,13 +1745,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -1838,7 +1838,7 @@
         <v>67</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>17</v>
@@ -1847,26 +1847,26 @@
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>26</v>
@@ -1880,38 +1880,38 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>26</v>
@@ -1925,38 +1925,38 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
@@ -1970,13 +1970,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
@@ -2360,7 +2360,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2384,7 +2384,7 @@
         <v>26</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R3" s="3">
         <v>150</v>
@@ -2392,13 +2392,13 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2422,7 +2422,7 @@
         <v>26</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R4" s="3">
         <v>150</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
@@ -2512,7 +2512,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2536,7 +2536,7 @@
         <v>26</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -2544,13 +2544,13 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2574,7 +2574,7 @@
         <v>26</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R8" s="3">
         <v>150</v>
@@ -2582,13 +2582,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2612,7 +2612,7 @@
         <v>26</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R9" s="3">
         <v>150</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
@@ -5017,16 +5017,16 @@
         <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>298</v>
@@ -5034,19 +5034,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>298</v>
@@ -5054,7 +5054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>50</v>
@@ -5097,16 +5097,16 @@
         <v>67</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>298</v>
@@ -5114,19 +5114,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>298</v>
@@ -5134,19 +5134,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>298</v>
@@ -5154,7 +5154,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>97</v>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="347">
   <si>
     <t>Rank</t>
   </si>
@@ -253,31 +253,34 @@
     <t>https://www.atlantis-remodeling.com/contact</t>
   </si>
   <si>
-    <t>Silicon Prime Painting</t>
-  </si>
-  <si>
-    <t>Residential / Commercial Painting</t>
-  </si>
-  <si>
-    <t>Official contact page offers free estimates, states a response within one business day and serves San Jose and the surrounding Bay Area with licensed and insured painting services.</t>
-  </si>
-  <si>
-    <t>contact-form-first</t>
-  </si>
-  <si>
-    <t>Official free-estimate form; stated one-business-day response; San Jose address published</t>
-  </si>
-  <si>
-    <t>Turn the fast estimate process into a paint-project preparation campaign that helps prospects organize interior-versus-exterior scope, surfaces, rooms, finish goals, timing and property details before estimating.</t>
-  </si>
-  <si>
-    <t>One-day paint estimate campaign for Silicon Prime</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Silicon Prime Painting’s current San Jose estimate flow and noticed you offer free estimates with a stated response within one business day. I’d turn that into a paint-project preparation campaign that helps prospects organize interior-versus-exterior scope, surfaces, rooms, finish goals and timing before estimating. Same-Day Customer Growth Pack: $150 flat. Want two Silicon Prime-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.siliconprimepainting.org/contact.html</t>
+    <t>ValGreg Construction</t>
+  </si>
+  <si>
+    <t>Residential Remodeling / Renovations / General Construction</t>
+  </si>
+  <si>
+    <t>San Francisco / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official contact page publishes Valgregconstruction@gmail.com, free estimates and a stated 24-hour response for Bay Area residential remodeling, renovation and construction inquiries.</t>
+  </si>
+  <si>
+    <t>Valgregconstruction@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated 24-hour response</t>
+  </si>
+  <si>
+    <t>Turn the free-estimate path into a remodel scope-preparation campaign that helps homeowners organize project type, existing conditions, priorities, timeline and photos before estimating.</t>
+  </si>
+  <si>
+    <t>24-hour remodel estimate campaign for ValGreg Construction</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed ValGreg Construction’s current Bay Area estimate flow and noticed you already offer free estimates with a stated 24-hour response. I’d turn that into a remodel scope-preparation campaign that helps homeowners organize project type, existing conditions, priorities, timeline and useful photos before estimating. Same-Day Customer Growth Pack: $150 flat. Want two ValGreg-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.valgregconstruction.com/free-estimate</t>
   </si>
   <si>
     <t>Otto &amp; Sons Construction</t>
@@ -1886,32 +1889,32 @@
         <v>76</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>26</v>
@@ -1925,38 +1928,38 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
@@ -1970,38 +1973,38 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
@@ -2015,38 +2018,38 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>26</v>
@@ -2091,142 +2094,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2260,58 +2263,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2550,7 +2553,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2574,7 +2577,7 @@
         <v>26</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R8" s="3">
         <v>150</v>
@@ -2582,13 +2585,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2612,7 +2615,7 @@
         <v>26</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R9" s="3">
         <v>150</v>
@@ -2620,13 +2623,13 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2650,7 +2653,7 @@
         <v>26</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -2658,13 +2661,13 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2688,7 +2691,7 @@
         <v>26</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R11" s="3">
         <v>150</v>
@@ -2696,28 +2699,28 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -2727,7 +2730,7 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -2738,32 +2741,32 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -2773,7 +2776,7 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2784,26 +2787,26 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -2813,7 +2816,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2824,26 +2827,26 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -2853,7 +2856,7 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2864,26 +2867,26 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -2893,7 +2896,7 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -2904,26 +2907,26 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -2933,7 +2936,7 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -2944,26 +2947,26 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -2973,7 +2976,7 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -2984,26 +2987,26 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -3013,7 +3016,7 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -3024,26 +3027,26 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -3053,7 +3056,7 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -3064,26 +3067,26 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -3093,7 +3096,7 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3104,28 +3107,28 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3135,7 +3138,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3146,26 +3149,26 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3175,7 +3178,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3186,26 +3189,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3215,7 +3218,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3226,26 +3229,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -3255,7 +3258,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3266,26 +3269,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -3295,7 +3298,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -3306,26 +3309,26 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -3335,7 +3338,7 @@
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -3346,26 +3349,26 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
@@ -3375,7 +3378,7 @@
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -3386,26 +3389,26 @@
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -3415,7 +3418,7 @@
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -3426,26 +3429,26 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K30" s="3">
         <v>0</v>
@@ -3455,7 +3458,7 @@
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -3466,26 +3469,26 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K31" s="3">
         <v>0</v>
@@ -3495,7 +3498,7 @@
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -3506,26 +3509,26 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3535,7 +3538,7 @@
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -3546,26 +3549,26 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -3575,7 +3578,7 @@
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -3586,26 +3589,26 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -3615,7 +3618,7 @@
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -3626,26 +3629,26 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -3655,7 +3658,7 @@
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -3719,67 +3722,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -3788,13 +3791,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3802,10 +3805,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -3814,13 +3817,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3828,10 +3831,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -3840,28 +3843,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -3870,13 +3873,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3884,10 +3887,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -3896,13 +3899,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3910,10 +3913,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -3922,13 +3925,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -3936,10 +3939,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -3948,28 +3951,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -3978,13 +3981,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3992,10 +3995,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -4004,13 +4007,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -4018,10 +4021,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -4030,13 +4033,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -4044,10 +4047,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -4056,13 +4059,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -4070,10 +4073,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -4082,13 +4085,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -4096,10 +4099,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -4108,13 +4111,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -4122,10 +4125,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -4134,13 +4137,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -4148,10 +4151,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -4160,13 +4163,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -4174,10 +4177,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -4186,13 +4189,13 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -4200,10 +4203,10 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -4212,13 +4215,13 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -4226,10 +4229,10 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -4238,13 +4241,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -4252,10 +4255,10 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -4264,13 +4267,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -4278,10 +4281,10 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -4290,13 +4293,13 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -4304,10 +4307,10 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -4316,13 +4319,13 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -4330,10 +4333,10 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -4342,13 +4345,13 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -4356,10 +4359,10 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -4368,13 +4371,13 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -4382,10 +4385,10 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -4394,13 +4397,13 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -4408,10 +4411,10 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -4420,13 +4423,13 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -4434,10 +4437,10 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -4469,33 +4472,33 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -4509,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>27</v>
@@ -4532,14 +4535,14 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>27</v>
@@ -4553,20 +4556,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -4576,16 +4579,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>27</v>
@@ -4599,14 +4602,14 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>27</v>
@@ -4620,14 +4623,14 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -4641,14 +4644,14 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -4662,14 +4665,14 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>27</v>
@@ -4683,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>27</v>
@@ -4706,14 +4709,14 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>27</v>
@@ -4727,14 +4730,14 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>27</v>
@@ -4748,14 +4751,14 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>27</v>
@@ -4769,16 +4772,16 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>27</v>
@@ -4792,14 +4795,14 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>27</v>
@@ -4813,14 +4816,14 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>27</v>
@@ -4834,14 +4837,14 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>27</v>
@@ -4855,16 +4858,16 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>27</v>
@@ -4878,16 +4881,16 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>27</v>
@@ -4901,16 +4904,16 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>27</v>
@@ -4924,16 +4927,16 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>27</v>
@@ -4947,11 +4950,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -4983,13 +4986,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5009,7 +5012,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5029,7 +5032,7 @@
         <v>32</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5049,7 +5052,7 @@
         <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5069,7 +5072,7 @@
         <v>51</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5089,7 +5092,7 @@
         <v>61</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -5109,7 +5112,7 @@
         <v>69</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -5117,79 +5120,79 @@
         <v>75</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -5224,7 +5227,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5234,20 +5237,20 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5259,95 +5262,95 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -5373,98 +5376,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -5483,19 +5486,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5512,7 +5515,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="349">
   <si>
     <t>Rank</t>
   </si>
@@ -73,304 +73,310 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Bay HVAC Masters</t>
-  </si>
-  <si>
-    <t>HVAC / Heating / Cooling / System Installation</t>
+    <t>JH Construction</t>
+  </si>
+  <si>
+    <t>General Construction / Remodeling / Residential &amp; Commercial</t>
+  </si>
+  <si>
+    <t>San Francisco Bay Area, CA</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Official contact page publishes jh13remodeling@gmail.com, free no-obligation estimates, Monday-Saturday availability and a stated response within 24 hours.</t>
+  </si>
+  <si>
+    <t>jh13remodeling@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; stated 24-hour response; Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the 24-hour estimate response into a project-readiness campaign that helps prospects organize project type, scope, timeline, budget questions and permit concerns before the estimate.</t>
+  </si>
+  <si>
+    <t>24-hour project-readiness campaign for JH Construction</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed JH Construction’s current Bay Area estimate flow and noticed you already offer free no-obligation estimates with a stated 24-hour response. I’d turn that into a project-readiness campaign that helps homeowners organize project type, scope, timeline, budget questions and permit concerns before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two JH-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://jhremodel.com/contact</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>Valdivia Roofing</t>
+  </si>
+  <si>
+    <t>Roof Replacement / Repair / Emergency Roofing</t>
+  </si>
+  <si>
+    <t>Morgan Hill / San Jose / Gilroy / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official site publishes humberto@valdiviaroofing.com, free estimates, 24/7 emergency service and fast same-day callbacks for estimate requests.</t>
+  </si>
+  <si>
+    <t>humberto@valdiviaroofing.com</t>
+  </si>
+  <si>
+    <t>Direct named email; free estimate; same-day callbacks; 24/7 emergency service</t>
+  </si>
+  <si>
+    <t>Turn the fast-response roofing process into a repair-versus-replacement readiness campaign that helps homeowners identify leaks, roof age, urgency, material questions and inspection needs before the callback.</t>
+  </si>
+  <si>
+    <t>Same-day roofing response campaign for Valdivia Roofing</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Valdivia Roofing’s current Bay Area estimate flow and noticed you already offer free estimates, 24/7 emergency service and fast same-day callbacks. I’d turn that into a repair-versus-replacement readiness campaign that helps homeowners organize leak symptoms, roof age, urgency and inspection questions before the callback. Same-Day Customer Growth Pack: $150 flat. Want two Valdivia-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://valdiviaroofing.com/services</t>
+  </si>
+  <si>
+    <t>Alderstone Remodeling &amp; Exteriors</t>
+  </si>
+  <si>
+    <t>Remodeling / Exteriors / Home Improvement</t>
+  </si>
+  <si>
+    <t>Northern California</t>
+  </si>
+  <si>
+    <t>Official contact page publishes info@alderstoneremodel.com, free no-obligation in-home consultations and estimates, and says responses arrive within one business day, usually the same day.</t>
+  </si>
+  <si>
+    <t>info@alderstoneremodel.com</t>
+  </si>
+  <si>
+    <t>Direct email; free consultation/estimate; usually same-business-day response</t>
+  </si>
+  <si>
+    <t>Turn the same-day consultation response into an interior-versus-exterior project scoping campaign that helps homeowners organize priorities, existing conditions, desired improvements and timeline before the visit.</t>
+  </si>
+  <si>
+    <t>Same-day project-scoping campaign for Alderstone</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Alderstone Remodeling &amp; Exteriors’ current consultation flow and noticed you already offer free in-home consultations and usually respond the same business day. I’d turn that into a project-scoping campaign that helps homeowners organize interior versus exterior priorities, existing conditions, desired improvements and timeline before the visit. Same-Day Customer Growth Pack: $150 flat. Want two Alderstone-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://alderstoneremodel.com/contact</t>
+  </si>
+  <si>
+    <t>Visionable Landscaping</t>
+  </si>
+  <si>
+    <t>Landscape Design / Hardscaping / Complete Backyard Remodeling</t>
+  </si>
+  <si>
+    <t>Fremont / East Bay / South Bay / Peninsula, CA</t>
+  </si>
+  <si>
+    <t>Official contact page publishes info@visionablelandscaping.com, free consultations with 3D renderings, consultations seven days a week and a stated response within 24 hours. Complete backyard remodels are listed at a typical $20K–$60K+ range.</t>
+  </si>
+  <si>
+    <t>info@visionablelandscaping.com</t>
+  </si>
+  <si>
+    <t>Direct email; free 3D consultation; stated 24-hour response; seven-day consultations</t>
+  </si>
+  <si>
+    <t>Turn the free 3D consultation into a backyard-project preparation campaign that helps homeowners organize use cases, budget range, photos, desired features and priorities before the design visit.</t>
+  </si>
+  <si>
+    <t>3D backyard consultation campaign for Visionable</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Visionable Landscaping’s current Fremont consultation flow and noticed you already offer free consultations with 3D renderings and a stated 24-hour response. I’d turn that into a backyard-project preparation campaign that helps homeowners organize use cases, budget range, photos, desired features and priorities before the design visit. Same-Day Customer Growth Pack: $150 flat. Want two Visionable-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://visionablelandscaping.com/contact</t>
+  </si>
+  <si>
+    <t>Seal Home Remodeling</t>
+  </si>
+  <si>
+    <t>Kitchen / Bathroom / Additions / Full-Home Renovations</t>
+  </si>
+  <si>
+    <t>Official site publishes Pham@sealhomeremodeling.com, free consultations and estimates, premium remodeling services and a stated response within 24 hours.</t>
+  </si>
+  <si>
+    <t>Pham@sealhomeremodeling.com</t>
+  </si>
+  <si>
+    <t>Direct named email; free consultation/estimate; stated 24-hour response</t>
+  </si>
+  <si>
+    <t>Turn the premium-remodel consultation into a decision-preparation campaign that helps homeowners organize room priorities, desired finishes, addition needs, timeline and proposal questions before consultation.</t>
+  </si>
+  <si>
+    <t>24-hour remodel consultation campaign for Seal Home Remodeling</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Seal Home Remodeling’s current Bay Area consultation flow and noticed you already offer free consultations and estimates with a stated 24-hour response. I’d turn that into a remodel decision-preparation campaign that helps homeowners organize room priorities, desired finishes, addition needs, timeline and proposal questions before consultation. Same-Day Customer Growth Pack: $150 flat. Want two Seal-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://sealhomeremodeling.com/</t>
+  </si>
+  <si>
+    <t>ProMan California</t>
+  </si>
+  <si>
+    <t>Construction / Remodeling / Roofing / Siding / Restoration / Home Services</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Official contact page publishes info@promancalifornia.com, free in-home estimates, callback-in-minutes positioning, 24/7 emergency service and a broad construction/home-services menu.</t>
+  </si>
+  <si>
+    <t>info@promancalifornia.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; callback-in-minutes positioning; 24/7 emergency service</t>
+  </si>
+  <si>
+    <t>Turn the broad service menu into a service-routing campaign that helps prospects identify project category, urgency, property details and estimate needs before booking.</t>
+  </si>
+  <si>
+    <t>Fast service-routing campaign for ProMan California</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed ProMan California’s current booking flow and noticed you already offer free in-home estimates, callback-in-minutes positioning and a broad construction and home-services menu. I’d turn that into a service-routing campaign that helps prospects identify project category, urgency, property details and estimate needs before booking. Same-Day Customer Growth Pack: $150 flat. Want two ProMan-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://promansiding.com/contact</t>
+  </si>
+  <si>
+    <t>Green Hard Landscape Construction</t>
+  </si>
+  <si>
+    <t>Landscaping / Hardscaping / Outdoor Construction</t>
   </si>
   <si>
     <t>San Jose / Bay Area, CA</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Official contact page publishes service@bayhvacmasters.com, same-day appointments, free installation estimates, 24/7 emergency dispatch and a stated one-business-hour response to inquiries and email.</t>
-  </si>
-  <si>
-    <t>service@bayhvacmasters.com</t>
-  </si>
-  <si>
-    <t>Direct service email; stated one-business-hour response; same-day appointments; free installation estimates</t>
-  </si>
-  <si>
-    <t>Turn the one-hour response and same-day availability into a repair-versus-replacement readiness campaign that helps homeowners identify symptoms, equipment age, comfort problems and installation goals before dispatch.</t>
-  </si>
-  <si>
-    <t>One-hour HVAC response campaign for Bay HVAC Masters</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Bay HVAC Masters’ current San Jose contact flow and noticed you already offer same-day appointments, free installation estimates and a stated one-business-hour email response. I’d turn that speed into a repair-versus-replacement readiness campaign that helps homeowners organize symptoms, equipment age, comfort issues and installation goals before dispatch. Same-Day Customer Growth Pack: $150 flat. Want two Bay HVAC Masters-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.bayhvacmasters.com/contact/</t>
-  </si>
-  <si>
-    <t>2026-09-23</t>
-  </si>
-  <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
-    <t>JS Overhead Garage Door</t>
-  </si>
-  <si>
-    <t>Garage Door Repair / Installation / Openers / Emergency Service</t>
-  </si>
-  <si>
-    <t>Bay Area / Sacramento, CA</t>
-  </si>
-  <si>
-    <t>Official contact page publishes info@jsogaragedoor.com, same-day service, free estimates and a stated response within one hour during business hours.</t>
-  </si>
-  <si>
-    <t>info@jsogaragedoor.com</t>
-  </si>
-  <si>
-    <t>Direct email; stated one-hour business-hours response; same-day service; free estimate</t>
-  </si>
-  <si>
-    <t>Turn the one-hour response into a garage-door triage campaign that helps prospects identify door versus opener issues, safety symptoms, urgency and replacement-versus-repair needs before service.</t>
-  </si>
-  <si>
-    <t>One-hour garage-door triage campaign for JS Overhead</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed JS Overhead Garage Door’s current contact flow and noticed you already offer same-day service, free estimates and a stated one-hour response during business hours. I’d turn that into a garage-door triage campaign that helps prospects identify door versus opener issues, safety symptoms, urgency and repair-versus-replacement needs before service. Same-Day Customer Growth Pack: $150 flat. Want two JS Overhead-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.jsogaragedoor.com/contact</t>
-  </si>
-  <si>
-    <t>Elite Unit Group</t>
-  </si>
-  <si>
-    <t>Apartment Turnovers / Property Maintenance / Multi-Service Renovation</t>
-  </si>
-  <si>
-    <t>Bay Area / Sacramento / Central Valley, CA</t>
-  </si>
-  <si>
-    <t>Official contact page was crawled today and publishes info@eliteunitgroup.com, free turnover quotes, responses within a few hours and 24–48 hour unit turns with one crew handling multiple services.</t>
-  </si>
-  <si>
-    <t>info@eliteunitgroup.com</t>
-  </si>
-  <si>
-    <t>Direct email; free quote; stated response within hours; 24–48 hour unit turns</t>
-  </si>
-  <si>
-    <t>Turn the fast multi-service turnover model into a property-manager intake campaign that organizes unit condition, required trades, vacancy deadline, photos and scope before quoting.</t>
-  </si>
-  <si>
-    <t>Fast unit-turn intake campaign for Elite Unit Group</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Elite Unit Group’s current California turnover flow and noticed you already offer free quotes, responses within a few hours and 24–48 hour unit turns using one crew across multiple services. I’d turn that into a property-manager intake campaign that organizes unit condition, required trades, vacancy deadline, photos and scope before quoting. Same-Day Customer Growth Pack: $150 flat. Want two Elite Unit-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://eliteunitgroup.com/contact</t>
-  </si>
-  <si>
-    <t>Pristine Construction LLC</t>
-  </si>
-  <si>
-    <t>Design-Build / Kitchens / Bathrooms / ADUs / Whole-Home Remodeling</t>
-  </si>
-  <si>
-    <t>Official site publishes office@pristineconstructionllc.com, free no-obligation consultations, a stated response within 24 hours and a design-build focus on kitchens, baths, ADUs and full-home remodels.</t>
-  </si>
-  <si>
-    <t>office@pristineconstructionllc.com</t>
-  </si>
-  <si>
-    <t>Direct office email; free consultation; stated 24-hour response; Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the design-build consultation into a project-direction campaign that helps homeowners organize vision, timeline, goals, project type and site-visit readiness before the first call.</t>
-  </si>
-  <si>
-    <t>24-hour design-build intake campaign for Pristine</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Pristine Construction’s current San Jose consultation flow and noticed you already offer free consultations with a stated 24-hour response for kitchens, baths, ADUs and full-home remodels. I’d turn that into a project-direction campaign that helps homeowners organize vision, timeline, goals and site-visit readiness before the first call. Same-Day Customer Growth Pack: $150 flat. Want two Pristine-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://pristineconstructionllc.com/</t>
-  </si>
-  <si>
-    <t>Maison Remodeling Group</t>
-  </si>
-  <si>
-    <t>Kitchen / Bathroom / ADU / Additions / Whole-Home Remodeling</t>
-  </si>
-  <si>
-    <t>Santa Clara / San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official contact page publishes office@maisonremodeling.com, free 30-minute consultations and a stated 24-hour response for kitchen, bathroom, ADU, addition, whole-home and outdoor remodeling inquiries.</t>
-  </si>
-  <si>
-    <t>office@maisonremodeling.com</t>
-  </si>
-  <si>
-    <t>Direct office email; free consultation; stated 24-hour response</t>
-  </si>
-  <si>
-    <t>Turn the 30-minute consultation into a pre-call planning campaign that helps homeowners organize project type, priorities, budget questions, timeline and existing plans before speaking with the team.</t>
-  </si>
-  <si>
-    <t>30-minute consultation prep campaign for Maison Remodeling</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Maison Remodeling Group’s current Santa Clara consultation flow and noticed you already offer free 30-minute consultations and state that written inquiries receive a response within 24 hours. I’d turn that into a pre-call planning campaign that helps homeowners organize project type, priorities, budget questions, timeline and existing plans before speaking with your team. Same-Day Customer Growth Pack: $150 flat. Want two Maison-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://maisonremodeling.com/contact</t>
-  </si>
-  <si>
-    <t>Atlantis Remodeling</t>
-  </si>
-  <si>
-    <t>Official contact page publishes contact@atlantis-remodeling.com, free no-obligation consultations, Monday-Saturday hours and a stated response within 24 hours for premium remodeling projects.</t>
-  </si>
-  <si>
-    <t>contact@atlantis-remodeling.com</t>
-  </si>
-  <si>
-    <t>Direct email; free consultation; stated 24-hour response; Monday-Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the design-build consultation into a dream-project readiness campaign that helps prospects organize vision, project type, decision priorities and questions before the consultation.</t>
-  </si>
-  <si>
-    <t>24-hour consultation campaign for Atlantis Remodeling</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Atlantis Remodeling’s current San Jose contact flow and noticed you already offer free no-obligation consultations, Monday-Saturday availability and a stated 24-hour response. I’d turn that into a dream-project readiness campaign that helps prospects organize vision, project type, decision priorities and questions before the consultation. Same-Day Customer Growth Pack: $150 flat. Want two Atlantis-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.atlantis-remodeling.com/contact</t>
-  </si>
-  <si>
-    <t>ValGreg Construction</t>
-  </si>
-  <si>
-    <t>Residential Remodeling / Renovations / General Construction</t>
-  </si>
-  <si>
-    <t>San Francisco / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official contact page publishes Valgregconstruction@gmail.com, free estimates and a stated 24-hour response for Bay Area residential remodeling, renovation and construction inquiries.</t>
-  </si>
-  <si>
-    <t>Valgregconstruction@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated 24-hour response</t>
-  </si>
-  <si>
-    <t>Turn the free-estimate path into a remodel scope-preparation campaign that helps homeowners organize project type, existing conditions, priorities, timeline and photos before estimating.</t>
-  </si>
-  <si>
-    <t>24-hour remodel estimate campaign for ValGreg Construction</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed ValGreg Construction’s current Bay Area estimate flow and noticed you already offer free estimates with a stated 24-hour response. I’d turn that into a remodel scope-preparation campaign that helps homeowners organize project type, existing conditions, priorities, timeline and useful photos before estimating. Same-Day Customer Growth Pack: $150 flat. Want two ValGreg-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.valgregconstruction.com/free-estimate</t>
-  </si>
-  <si>
-    <t>Otto &amp; Sons Construction</t>
-  </si>
-  <si>
-    <t>Residential Remodeling / Commercial Tenant Improvements / Construction</t>
-  </si>
-  <si>
-    <t>Bay Area / Antioch, CA</t>
-  </si>
-  <si>
-    <t>Official contact page publishes alani@ottoandsonsco.com, free no-obligation estimates, a typical 24-hour business-day response and Saturday hours for residential remodels and commercial work.</t>
-  </si>
-  <si>
-    <t>alani@ottoandsonsco.com</t>
-  </si>
-  <si>
-    <t>Direct named email; free estimate; typical 24-hour response; Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the residential-and-commercial range into a project-routing campaign that helps prospects identify remodel, tenant-improvement, small-build or service-call needs and prepare useful scope details before quoting.</t>
-  </si>
-  <si>
-    <t>24-hour project-routing campaign for Otto &amp; Sons</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Otto &amp; Sons Construction’s current Bay Area quote flow and noticed you already offer free estimates, typically respond within 24 business hours and handle both residential remodels and commercial work. I’d turn that into a project-routing campaign that helps prospects identify remodel, tenant-improvement, small-build or service-call needs and prepare useful scope details before quoting. Same-Day Customer Growth Pack: $150 flat. Want two Otto &amp; Sons-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.ottoandsonsco.com/contact</t>
-  </si>
-  <si>
-    <t>SBH Construction</t>
-  </si>
-  <si>
-    <t>Foundation Repair / Residential Construction / Remodeling</t>
-  </si>
-  <si>
-    <t>Walnut Creek / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official services page publishes info@sbhconstruction.com, free no-obligation consultations, detailed estimates and a stated one-business-day response, with permit applications and inspections handled for clients.</t>
-  </si>
-  <si>
-    <t>info@sbhconstruction.com</t>
-  </si>
-  <si>
-    <t>Direct email; free consultation; stated 24-hour response; Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the consultation and permit-handling process into a foundation/project readiness campaign that helps homeowners organize symptoms, project goals, property context and permit questions before the site visit.</t>
-  </si>
-  <si>
-    <t>Foundation project-readiness campaign for SBH Construction</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed SBH Construction’s current Bay Area service flow and noticed you already offer free consultations, detailed estimates, permit handling and a stated response within one business day. I’d turn that into a project-readiness campaign that helps homeowners organize symptoms, project goals, property context and permit questions before the site visit. Same-Day Customer Growth Pack: $150 flat. Want two SBH-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://sbhconstructioninc.com/services/</t>
-  </si>
-  <si>
-    <t>Bay Area Fabrication &amp; Repair</t>
-  </si>
-  <si>
-    <t>Welding / Metal Fabrication / Mobile Repair / Commercial &amp; Residential</t>
-  </si>
-  <si>
-    <t>Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site publishes bayareafabrications@gmail.com, free estimates, Monday-Saturday hours and a stated 24-hour response across welding, structural fabrication, mobile repair and custom metalwork.</t>
-  </si>
-  <si>
-    <t>bayareafabrications@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated 24-hour response; Monday-Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the broad fabrication menu into a job-scope selector that helps prospects identify mobile repair versus shop fabrication, material, dimensions, location and urgency before estimating.</t>
-  </si>
-  <si>
-    <t>24-hour fabrication quote campaign for Bay Area Fabrication</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Bay Area Fabrication &amp; Repair’s current service flow and noticed you offer free estimates, Monday-Saturday availability and a stated 24-hour response across welding, fabrication and mobile repair. I’d turn that into a job-scope selector that helps prospects identify mobile repair versus shop fabrication, material, dimensions, location and urgency before estimating. Same-Day Customer Growth Pack: $150 flat. Want two business-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://bayareafabrications.com/</t>
+    <t>Official site publishes greenhardscaping@gmail.com, free estimates, free on-site walkthroughs and a stated response within 24 hours across the Bay Area.</t>
+  </si>
+  <si>
+    <t>greenhardscaping@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; free on-site walkthrough; stated 24-hour response</t>
+  </si>
+  <si>
+    <t>Turn the free walkthrough into an outdoor-project preparation campaign that helps prospects organize service type, preferred timeline, property conditions, desired features and project priorities before the visit.</t>
+  </si>
+  <si>
+    <t>24-hour outdoor-project campaign for Green Hard</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Green Hard Landscape Construction’s current Bay Area estimate flow and noticed you already offer free on-site walkthroughs and a stated 24-hour response. I’d turn that into an outdoor-project preparation campaign that helps prospects organize service type, preferred timeline, property conditions, desired features and priorities before the visit. Same-Day Customer Growth Pack: $150 flat. Want two Green Hard-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.greenhardconstruction.com/</t>
+  </si>
+  <si>
+    <t>Bay Stone Depot</t>
+  </si>
+  <si>
+    <t>Natural Stone / Countertops / Fabrication / Premium Surfaces</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>Official contact page publishes baystonedepotinc@gmail.com, free consultations and personalized quotes within 24 hours for premium stone, countertops, fabrication and specialty surfaces.</t>
+  </si>
+  <si>
+    <t>baystonedepotinc@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free consultation; personalized quote within 24 hours; Saturday showroom hours</t>
+  </si>
+  <si>
+    <t>Turn the specialist quote process into a premium-surface selection campaign that helps prospects organize project type, approximate budget, material preferences and measurements before consultation.</t>
+  </si>
+  <si>
+    <t>24-hour surface-selection campaign for Bay Stone Depot</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Bay Stone Depot’s current San Jose quote flow and noticed you already offer free consultations and personalized quotes within 24 hours. I’d turn that into a premium-surface selection campaign that helps prospects organize project type, approximate budget, material preferences and measurements before consultation. Same-Day Customer Growth Pack: $150 flat. Want two Bay Stone-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://baystonedepot.com/contact</t>
+  </si>
+  <si>
+    <t>Home Pro NW</t>
+  </si>
+  <si>
+    <t>Kitchen / Bathroom / ADU / New Construction / Full-Home Renovation</t>
+  </si>
+  <si>
+    <t>Seattle / King County, WA</t>
+  </si>
+  <si>
+    <t>Official site publishes Info@homepronw.com, says it responds to every inquiry within 24 hours, offers complimentary consultations, accepts plans and inspiration files before calls, and states projects start at $50,000.</t>
+  </si>
+  <si>
+    <t>Info@homepronw.com</t>
+  </si>
+  <si>
+    <t>Direct email; stated 24-hour response; complimentary consultation; projects start at $50K</t>
+  </si>
+  <si>
+    <t>Turn the $50K+ consultation process into a high-ticket project-readiness campaign that helps prospects organize plans, inspiration, project type, budget, timeline and investment questions before the call.</t>
+  </si>
+  <si>
+    <t>$50K+ consultation-prep campaign for Home Pro NW</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Home Pro NW’s current consultation flow and noticed you already focus on projects starting at $50,000, offer complimentary consultations and respond within 24 hours. I’d turn that into a high-ticket project-readiness campaign that helps prospects organize plans, inspiration, project type, budget and timeline before the call. Same-Day Customer Growth Pack: $150 flat. Want two Home Pro NW-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://homepronw.com/</t>
+  </si>
+  <si>
+    <t>Silicon Prime Painting Inc</t>
+  </si>
+  <si>
+    <t>Residential / Commercial Painting / Cabinet Refinishing / Drywall</t>
+  </si>
+  <si>
+    <t>San Jose / Silicon Valley / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official site publishes spp@siliconprimepainting.com, free written estimates, Monday-Saturday hours and residential/commercial painting, cabinet refinishing, drywall repair and related services.</t>
+  </si>
+  <si>
+    <t>spp@siliconprimepainting.com</t>
+  </si>
+  <si>
+    <t>Direct email; free written estimate; Monday-Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn the free written-estimate process into a painting-project selector that helps prospects organize surface type, rooms or exterior areas, repair needs, color decisions and scheduling requirements before quoting.</t>
+  </si>
+  <si>
+    <t>Written-estimate campaign for Silicon Prime Painting</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Silicon Prime Painting’s current Bay Area estimate flow and noticed you already offer free written estimates across residential, commercial, cabinet and drywall work. I’d turn that into a painting-project selector that helps prospects organize surface type, rooms or exterior areas, repair needs, color decisions and scheduling requirements before quoting. Same-Day Customer Growth Pack: $150 flat. Want two Silicon Prime-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://siliconprimepaintinginc.com/</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -1754,32 +1760,32 @@
         <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>26</v>
@@ -1793,13 +1799,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
@@ -1841,35 +1847,35 @@
         <v>67</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>26</v>
@@ -1883,38 +1889,38 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>26</v>
@@ -1928,38 +1934,38 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
@@ -1973,38 +1979,38 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
@@ -2018,38 +2024,38 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>26</v>
@@ -2094,142 +2100,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -2263,58 +2269,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2439,7 +2445,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -2463,7 +2469,7 @@
         <v>26</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R5" s="3">
         <v>150</v>
@@ -2471,7 +2477,7 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -2515,7 +2521,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2539,7 +2545,7 @@
         <v>26</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -2547,13 +2553,13 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2577,7 +2583,7 @@
         <v>26</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R8" s="3">
         <v>150</v>
@@ -2585,13 +2591,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2615,7 +2621,7 @@
         <v>26</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="R9" s="3">
         <v>150</v>
@@ -2623,13 +2629,13 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2653,7 +2659,7 @@
         <v>26</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -2661,13 +2667,13 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2691,7 +2697,7 @@
         <v>26</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R11" s="3">
         <v>150</v>
@@ -2699,28 +2705,28 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -2730,7 +2736,7 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -2741,32 +2747,32 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -2776,7 +2782,7 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2787,26 +2793,26 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -2816,7 +2822,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2827,26 +2833,26 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -2856,7 +2862,7 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2867,26 +2873,26 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -2896,7 +2902,7 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -2907,26 +2913,26 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -2936,7 +2942,7 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -2947,26 +2953,26 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -2976,7 +2982,7 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -2987,26 +2993,26 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -3016,7 +3022,7 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -3027,26 +3033,26 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -3056,7 +3062,7 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -3067,26 +3073,26 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -3096,7 +3102,7 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3107,28 +3113,28 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3138,7 +3144,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3149,26 +3155,26 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3178,7 +3184,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3189,26 +3195,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3218,7 +3224,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3229,26 +3235,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -3258,7 +3264,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3269,26 +3275,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -3298,7 +3304,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -3309,26 +3315,26 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -3338,7 +3344,7 @@
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -3349,26 +3355,26 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
@@ -3378,7 +3384,7 @@
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -3389,26 +3395,26 @@
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -3418,7 +3424,7 @@
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -3429,26 +3435,26 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K30" s="3">
         <v>0</v>
@@ -3458,7 +3464,7 @@
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -3469,26 +3475,26 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K31" s="3">
         <v>0</v>
@@ -3498,7 +3504,7 @@
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -3509,26 +3515,26 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3538,7 +3544,7 @@
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -3549,26 +3555,26 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -3578,7 +3584,7 @@
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -3589,26 +3595,26 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -3618,7 +3624,7 @@
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -3629,26 +3635,26 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -3658,7 +3664,7 @@
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -3722,67 +3728,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -3791,13 +3797,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3805,10 +3811,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -3817,13 +3823,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3831,10 +3837,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -3843,28 +3849,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -3873,13 +3879,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3887,10 +3893,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -3899,13 +3905,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3913,10 +3919,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -3925,13 +3931,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -3939,10 +3945,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -3951,28 +3957,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -3981,13 +3987,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3995,10 +4001,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -4007,13 +4013,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -4021,10 +4027,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -4033,13 +4039,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -4047,10 +4053,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -4059,13 +4065,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -4073,10 +4079,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -4085,13 +4091,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -4099,10 +4105,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -4111,13 +4117,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -4125,10 +4131,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -4137,13 +4143,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -4151,10 +4157,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -4163,13 +4169,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -4177,10 +4183,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -4189,13 +4195,13 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -4203,10 +4209,10 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -4215,13 +4221,13 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -4229,10 +4235,10 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -4241,13 +4247,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -4255,10 +4261,10 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -4267,13 +4273,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -4281,10 +4287,10 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -4293,13 +4299,13 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -4307,10 +4313,10 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -4319,13 +4325,13 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -4333,10 +4339,10 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -4345,13 +4351,13 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -4359,10 +4365,10 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -4371,13 +4377,13 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -4385,10 +4391,10 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -4397,13 +4403,13 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -4411,10 +4417,10 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -4423,13 +4429,13 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -4437,10 +4443,10 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -4472,33 +4478,33 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -4512,16 +4518,16 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>27</v>
@@ -4535,14 +4541,14 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>27</v>
@@ -4556,20 +4562,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -4579,16 +4585,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>27</v>
@@ -4602,14 +4608,14 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>27</v>
@@ -4623,14 +4629,14 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -4644,14 +4650,14 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -4665,14 +4671,14 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>27</v>
@@ -4686,16 +4692,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>27</v>
@@ -4709,14 +4715,14 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>27</v>
@@ -4730,14 +4736,14 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>27</v>
@@ -4751,14 +4757,14 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>27</v>
@@ -4772,16 +4778,16 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>27</v>
@@ -4795,14 +4801,14 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>27</v>
@@ -4816,14 +4822,14 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>27</v>
@@ -4837,14 +4843,14 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>27</v>
@@ -4858,16 +4864,16 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>27</v>
@@ -4881,16 +4887,16 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>27</v>
@@ -4904,16 +4910,16 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>27</v>
@@ -4927,16 +4933,16 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>27</v>
@@ -4950,11 +4956,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -4986,13 +4992,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5012,7 +5018,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5032,7 +5038,7 @@
         <v>32</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5052,7 +5058,7 @@
         <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5060,24 +5066,24 @@
         <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>60</v>
@@ -5092,7 +5098,7 @@
         <v>61</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -5100,99 +5106,99 @@
         <v>67</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -5227,7 +5233,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5237,20 +5243,20 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5262,95 +5268,95 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -5376,98 +5382,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -5486,19 +5492,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5515,7 +5521,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="369">
   <si>
     <t>Rank</t>
   </si>
@@ -109,7 +109,7 @@
     <t>2026-09-25</t>
   </si>
   <si>
-    <t>Contact Ready</t>
+    <t>Contacted</t>
   </si>
   <si>
     <t>Valdivia Roofing</t>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>https://alderstoneremodel.com/contact</t>
+  </si>
+  <si>
+    <t>Delivery Failed</t>
   </si>
   <si>
     <t>Visionable Landscaping</t>
@@ -555,6 +558,36 @@
     <t>Offer Value $</t>
   </si>
   <si>
+    <t>2026-09-25T05:28:57-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>Wait for an actual reply. Check delivery failures and opt-outs before a single respectful follow-up on or after 2026-09-29.</t>
+  </si>
+  <si>
+    <t>2026-09-25T05:28:58-07:00</t>
+  </si>
+  <si>
+    <t>Do not resend to the bounced address. Find a verified alternative contact route; initial email did not deliver.</t>
+  </si>
+  <si>
+    <t>2026-09-25T05:28:59-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-25T05:29:00-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-25T05:29:01-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-25T05:29:02-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-25T05:29:03-07:00</t>
+  </si>
+  <si>
     <t>FloodDry Water Damage Restoration</t>
   </si>
   <si>
@@ -573,9 +606,6 @@
     <t>2026-09-08T16:45:47-07:00</t>
   </si>
   <si>
-    <t>Contacted</t>
-  </si>
-  <si>
     <t>Two verified outbound emails, no inbound reply found through 2026-09-12. Do not send another cold touch now.</t>
   </si>
   <si>
@@ -840,16 +870,46 @@
     <t>Gmail sent message 1a0b6d7d1bb96f3a</t>
   </si>
   <si>
-    <t>Delivery Failed</t>
-  </si>
-  <si>
     <t>Do not count as successfully contacted. Official site still publishes info@svchimneysweep.com, but Gmail returned a hard bounce. Reverify or use the official website inquiry route; do not resend to the bounced address.</t>
   </si>
   <si>
+    <t>Gmail sent message 1a0d88a4fad08ed7</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0d88a4f2e3d368</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0d88a53a1c7431</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0d88a55fbcdab6</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0d88a575f61927</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0d88a58e14836f</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0d88a5c75c4bb9</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0d88a5f653c17b</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0d88a617a05989</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0d88a63f26b6c8</t>
+  </si>
+  <si>
     <t>Archived</t>
   </si>
   <si>
     <t>Leader Restoration</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
   </si>
   <si>
     <t>2026-09-12</t>
@@ -1746,7 +1806,7 @@
         <v>26</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1754,38 +1814,38 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>26</v>
@@ -1799,10 +1859,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>17</v>
@@ -1811,26 +1871,26 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>26</v>
@@ -1844,38 +1904,38 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>26</v>
@@ -1889,38 +1949,38 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>26</v>
@@ -1934,38 +1994,38 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
@@ -1979,38 +2039,38 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
@@ -2024,38 +2084,38 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>26</v>
@@ -2100,142 +2160,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2269,58 +2329,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2333,8 +2393,12 @@
       <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2349,7 +2413,9 @@
         <v>0</v>
       </c>
       <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="N2" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
         <v>26</v>
@@ -2371,8 +2437,12 @@
       <c r="C3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -2387,7 +2457,9 @@
         <v>0</v>
       </c>
       <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="N3" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
         <v>26</v>
@@ -2409,14 +2481,16 @@
       <c r="C4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>178</v>
+      </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -2425,7 +2499,9 @@
         <v>0</v>
       </c>
       <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
+      <c r="N4" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
         <v>26</v>
@@ -2439,16 +2515,20 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -2463,13 +2543,15 @@
         <v>0</v>
       </c>
       <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+      <c r="N5" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R5" s="3">
         <v>150</v>
@@ -2477,16 +2559,20 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -2501,13 +2587,15 @@
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R6" s="3">
         <v>150</v>
@@ -2515,16 +2603,20 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -2539,13 +2631,15 @@
         <v>0</v>
       </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+      <c r="N7" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R7" s="3">
         <v>150</v>
@@ -2553,16 +2647,20 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -2577,13 +2675,15 @@
         <v>0</v>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R8" s="3">
         <v>150</v>
@@ -2591,16 +2691,20 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -2615,13 +2719,15 @@
         <v>0</v>
       </c>
       <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+      <c r="N9" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R9" s="3">
         <v>150</v>
@@ -2629,16 +2735,20 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -2653,13 +2763,15 @@
         <v>0</v>
       </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="N10" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -2667,16 +2779,20 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -2691,13 +2807,15 @@
         <v>0</v>
       </c>
       <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+      <c r="N11" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R11" s="3">
         <v>150</v>
@@ -2705,28 +2823,28 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -2736,7 +2854,7 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -2747,32 +2865,32 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -2782,7 +2900,7 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2793,26 +2911,26 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -2822,7 +2940,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2833,26 +2951,26 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -2862,7 +2980,7 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2873,26 +2991,26 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -2902,7 +3020,7 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -2913,26 +3031,26 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -2942,7 +3060,7 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -2953,26 +3071,26 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -2982,7 +3100,7 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -2993,26 +3111,26 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -3022,7 +3140,7 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -3033,26 +3151,26 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -3062,7 +3180,7 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -3073,26 +3191,26 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -3102,7 +3220,7 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3113,28 +3231,28 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3144,7 +3262,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3155,26 +3273,26 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3184,7 +3302,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3195,26 +3313,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3224,7 +3342,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3235,26 +3353,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -3264,7 +3382,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3275,26 +3393,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -3304,7 +3422,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -3315,26 +3433,26 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -3344,7 +3462,7 @@
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -3355,26 +3473,26 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
@@ -3384,7 +3502,7 @@
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -3395,26 +3513,26 @@
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -3424,7 +3542,7 @@
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -3435,26 +3553,26 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K30" s="3">
         <v>0</v>
@@ -3464,7 +3582,7 @@
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -3475,26 +3593,26 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K31" s="3">
         <v>0</v>
@@ -3504,7 +3622,7 @@
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -3515,26 +3633,26 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3544,7 +3662,7 @@
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -3555,26 +3673,26 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -3584,7 +3702,7 @@
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -3595,26 +3713,26 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -3624,7 +3742,7 @@
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -3635,26 +3753,26 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="E35" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -3664,7 +3782,7 @@
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -3706,7 +3824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -3728,67 +3846,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -3797,13 +3915,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3811,10 +3929,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -3823,13 +3941,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3837,10 +3955,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -3849,28 +3967,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -3879,13 +3997,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3893,10 +4011,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -3905,13 +4023,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3919,10 +4037,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -3931,13 +4049,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -3945,10 +4063,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -3957,28 +4075,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -3987,13 +4105,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -4001,10 +4119,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -4013,13 +4131,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -4027,10 +4145,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -4039,13 +4157,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -4053,10 +4171,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -4065,13 +4183,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -4079,10 +4197,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -4091,13 +4209,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -4105,10 +4223,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -4117,13 +4235,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -4131,10 +4249,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -4143,13 +4261,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -4157,10 +4275,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -4169,13 +4287,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -4183,10 +4301,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -4195,13 +4313,13 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -4209,10 +4327,10 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -4221,13 +4339,13 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -4235,10 +4353,10 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -4247,13 +4365,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -4261,10 +4379,10 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -4273,13 +4391,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -4287,10 +4405,10 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -4299,13 +4417,13 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -4313,10 +4431,10 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -4325,13 +4443,13 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -4339,10 +4457,10 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -4351,13 +4469,13 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -4365,10 +4483,10 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -4377,13 +4495,13 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -4391,10 +4509,10 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -4403,13 +4521,13 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="C26" s="2" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -4417,10 +4535,10 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -4429,13 +4547,13 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -4443,15 +4561,275 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>269</v>
+        <v>48</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
       </c>
       <c r="L27" s="2"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K37" s="3">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4478,36 +4856,36 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4518,19 +4896,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4541,17 +4919,17 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -4562,20 +4940,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -4585,19 +4963,19 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -4608,17 +4986,17 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -4629,17 +5007,17 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -4650,17 +5028,17 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -4671,17 +5049,17 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -4692,19 +5070,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -4715,17 +5093,17 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -4736,17 +5114,17 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -4757,17 +5135,17 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -4778,19 +5156,19 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -4801,17 +5179,17 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -4822,17 +5200,17 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -4843,17 +5221,17 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -4864,19 +5242,19 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -4887,19 +5265,19 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -4910,19 +5288,19 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -4933,19 +5311,19 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -4956,11 +5334,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -4992,13 +5370,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5018,7 +5396,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5038,7 +5416,7 @@
         <v>32</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5058,147 +5436,147 @@
         <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -5233,7 +5611,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5243,120 +5621,120 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contact Ready")</f>
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -5382,98 +5760,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -5492,19 +5870,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5515,13 +5893,13 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D2" s="2">
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'New Lead Queue'!$A$1:$O$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Pipeline!$A$1:$R$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Pipeline!$A$1:$R$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="378">
   <si>
     <t>Rank</t>
   </si>
@@ -73,313 +73,310 @@
     <t>Status</t>
   </si>
   <si>
-    <t>JH Construction</t>
-  </si>
-  <si>
-    <t>General Construction / Remodeling / Residential &amp; Commercial</t>
-  </si>
-  <si>
-    <t>San Francisco Bay Area, CA</t>
+    <t>Roof Geeks</t>
+  </si>
+  <si>
+    <t>Roofing / Residential &amp; Commercial</t>
+  </si>
+  <si>
+    <t>Shingle Springs / Greater Sacramento, CA</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>Official contact page publishes jh13remodeling@gmail.com, free no-obligation estimates, Monday-Saturday availability and a stated response within 24 hours.</t>
-  </si>
-  <si>
-    <t>jh13remodeling@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; stated 24-hour response; Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the 24-hour estimate response into a project-readiness campaign that helps prospects organize project type, scope, timeline, budget questions and permit concerns before the estimate.</t>
-  </si>
-  <si>
-    <t>24-hour project-readiness campaign for JH Construction</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed JH Construction’s current Bay Area estimate flow and noticed you already offer free no-obligation estimates with a stated 24-hour response. I’d turn that into a project-readiness campaign that helps homeowners organize project type, scope, timeline, budget questions and permit concerns before the estimate. Same-Day Customer Growth Pack: $150 flat. Want two JH-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://jhremodel.com/contact</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>Contacted</t>
-  </si>
-  <si>
-    <t>Valdivia Roofing</t>
-  </si>
-  <si>
-    <t>Roof Replacement / Repair / Emergency Roofing</t>
-  </si>
-  <si>
-    <t>Morgan Hill / San Jose / Gilroy / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site publishes humberto@valdiviaroofing.com, free estimates, 24/7 emergency service and fast same-day callbacks for estimate requests.</t>
-  </si>
-  <si>
-    <t>humberto@valdiviaroofing.com</t>
-  </si>
-  <si>
-    <t>Direct named email; free estimate; same-day callbacks; 24/7 emergency service</t>
-  </si>
-  <si>
-    <t>Turn the fast-response roofing process into a repair-versus-replacement readiness campaign that helps homeowners identify leaks, roof age, urgency, material questions and inspection needs before the callback.</t>
-  </si>
-  <si>
-    <t>Same-day roofing response campaign for Valdivia Roofing</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Valdivia Roofing’s current Bay Area estimate flow and noticed you already offer free estimates, 24/7 emergency service and fast same-day callbacks. I’d turn that into a repair-versus-replacement readiness campaign that helps homeowners organize leak symptoms, roof age, urgency and inspection questions before the callback. Same-Day Customer Growth Pack: $150 flat. Want two Valdivia-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://valdiviaroofing.com/services</t>
-  </si>
-  <si>
-    <t>Alderstone Remodeling &amp; Exteriors</t>
-  </si>
-  <si>
-    <t>Remodeling / Exteriors / Home Improvement</t>
-  </si>
-  <si>
-    <t>Northern California</t>
-  </si>
-  <si>
-    <t>Official contact page publishes info@alderstoneremodel.com, free no-obligation in-home consultations and estimates, and says responses arrive within one business day, usually the same day.</t>
-  </si>
-  <si>
-    <t>info@alderstoneremodel.com</t>
-  </si>
-  <si>
-    <t>Direct email; free consultation/estimate; usually same-business-day response</t>
-  </si>
-  <si>
-    <t>Turn the same-day consultation response into an interior-versus-exterior project scoping campaign that helps homeowners organize priorities, existing conditions, desired improvements and timeline before the visit.</t>
-  </si>
-  <si>
-    <t>Same-day project-scoping campaign for Alderstone</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Alderstone Remodeling &amp; Exteriors’ current consultation flow and noticed you already offer free in-home consultations and usually respond the same business day. I’d turn that into a project-scoping campaign that helps homeowners organize interior versus exterior priorities, existing conditions, desired improvements and timeline before the visit. Same-Day Customer Growth Pack: $150 flat. Want two Alderstone-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://alderstoneremodel.com/contact</t>
-  </si>
-  <si>
-    <t>Delivery Failed</t>
-  </si>
-  <si>
-    <t>Visionable Landscaping</t>
-  </si>
-  <si>
-    <t>Landscape Design / Hardscaping / Complete Backyard Remodeling</t>
-  </si>
-  <si>
-    <t>Fremont / East Bay / South Bay / Peninsula, CA</t>
-  </si>
-  <si>
-    <t>Official contact page publishes info@visionablelandscaping.com, free consultations with 3D renderings, consultations seven days a week and a stated response within 24 hours. Complete backyard remodels are listed at a typical $20K–$60K+ range.</t>
-  </si>
-  <si>
-    <t>info@visionablelandscaping.com</t>
-  </si>
-  <si>
-    <t>Direct email; free 3D consultation; stated 24-hour response; seven-day consultations</t>
-  </si>
-  <si>
-    <t>Turn the free 3D consultation into a backyard-project preparation campaign that helps homeowners organize use cases, budget range, photos, desired features and priorities before the design visit.</t>
-  </si>
-  <si>
-    <t>3D backyard consultation campaign for Visionable</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Visionable Landscaping’s current Fremont consultation flow and noticed you already offer free consultations with 3D renderings and a stated 24-hour response. I’d turn that into a backyard-project preparation campaign that helps homeowners organize use cases, budget range, photos, desired features and priorities before the design visit. Same-Day Customer Growth Pack: $150 flat. Want two Visionable-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://visionablelandscaping.com/contact</t>
-  </si>
-  <si>
-    <t>Seal Home Remodeling</t>
-  </si>
-  <si>
-    <t>Kitchen / Bathroom / Additions / Full-Home Renovations</t>
-  </si>
-  <si>
-    <t>Official site publishes Pham@sealhomeremodeling.com, free consultations and estimates, premium remodeling services and a stated response within 24 hours.</t>
-  </si>
-  <si>
-    <t>Pham@sealhomeremodeling.com</t>
-  </si>
-  <si>
-    <t>Direct named email; free consultation/estimate; stated 24-hour response</t>
-  </si>
-  <si>
-    <t>Turn the premium-remodel consultation into a decision-preparation campaign that helps homeowners organize room priorities, desired finishes, addition needs, timeline and proposal questions before consultation.</t>
-  </si>
-  <si>
-    <t>24-hour remodel consultation campaign for Seal Home Remodeling</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Seal Home Remodeling’s current Bay Area consultation flow and noticed you already offer free consultations and estimates with a stated 24-hour response. I’d turn that into a remodel decision-preparation campaign that helps homeowners organize room priorities, desired finishes, addition needs, timeline and proposal questions before consultation. Same-Day Customer Growth Pack: $150 flat. Want two Seal-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://sealhomeremodeling.com/</t>
-  </si>
-  <si>
-    <t>ProMan California</t>
-  </si>
-  <si>
-    <t>Construction / Remodeling / Roofing / Siding / Restoration / Home Services</t>
-  </si>
-  <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>Official contact page publishes info@promancalifornia.com, free in-home estimates, callback-in-minutes positioning, 24/7 emergency service and a broad construction/home-services menu.</t>
-  </si>
-  <si>
-    <t>info@promancalifornia.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; callback-in-minutes positioning; 24/7 emergency service</t>
-  </si>
-  <si>
-    <t>Turn the broad service menu into a service-routing campaign that helps prospects identify project category, urgency, property details and estimate needs before booking.</t>
-  </si>
-  <si>
-    <t>Fast service-routing campaign for ProMan California</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed ProMan California’s current booking flow and noticed you already offer free in-home estimates, callback-in-minutes positioning and a broad construction and home-services menu. I’d turn that into a service-routing campaign that helps prospects identify project category, urgency, property details and estimate needs before booking. Same-Day Customer Growth Pack: $150 flat. Want two ProMan-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://promansiding.com/contact</t>
-  </si>
-  <si>
-    <t>Green Hard Landscape Construction</t>
-  </si>
-  <si>
-    <t>Landscaping / Hardscaping / Outdoor Construction</t>
-  </si>
-  <si>
-    <t>San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site publishes greenhardscaping@gmail.com, free estimates, free on-site walkthroughs and a stated response within 24 hours across the Bay Area.</t>
-  </si>
-  <si>
-    <t>greenhardscaping@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free estimate; free on-site walkthrough; stated 24-hour response</t>
-  </si>
-  <si>
-    <t>Turn the free walkthrough into an outdoor-project preparation campaign that helps prospects organize service type, preferred timeline, property conditions, desired features and project priorities before the visit.</t>
-  </si>
-  <si>
-    <t>24-hour outdoor-project campaign for Green Hard</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Green Hard Landscape Construction’s current Bay Area estimate flow and noticed you already offer free on-site walkthroughs and a stated 24-hour response. I’d turn that into an outdoor-project preparation campaign that helps prospects organize service type, preferred timeline, property conditions, desired features and priorities before the visit. Same-Day Customer Growth Pack: $150 flat. Want two Green Hard-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.greenhardconstruction.com/</t>
-  </si>
-  <si>
-    <t>Bay Stone Depot</t>
-  </si>
-  <si>
-    <t>Natural Stone / Countertops / Fabrication / Premium Surfaces</t>
-  </si>
-  <si>
-    <t>San Jose, CA</t>
-  </si>
-  <si>
-    <t>Official contact page publishes baystonedepotinc@gmail.com, free consultations and personalized quotes within 24 hours for premium stone, countertops, fabrication and specialty surfaces.</t>
-  </si>
-  <si>
-    <t>baystonedepotinc@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; free consultation; personalized quote within 24 hours; Saturday showroom hours</t>
-  </si>
-  <si>
-    <t>Turn the specialist quote process into a premium-surface selection campaign that helps prospects organize project type, approximate budget, material preferences and measurements before consultation.</t>
-  </si>
-  <si>
-    <t>24-hour surface-selection campaign for Bay Stone Depot</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Bay Stone Depot’s current San Jose quote flow and noticed you already offer free consultations and personalized quotes within 24 hours. I’d turn that into a premium-surface selection campaign that helps prospects organize project type, approximate budget, material preferences and measurements before consultation. Same-Day Customer Growth Pack: $150 flat. Want two Bay Stone-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://baystonedepot.com/contact</t>
-  </si>
-  <si>
-    <t>Home Pro NW</t>
-  </si>
-  <si>
-    <t>Kitchen / Bathroom / ADU / New Construction / Full-Home Renovation</t>
-  </si>
-  <si>
-    <t>Seattle / King County, WA</t>
-  </si>
-  <si>
-    <t>Official site publishes Info@homepronw.com, says it responds to every inquiry within 24 hours, offers complimentary consultations, accepts plans and inspiration files before calls, and states projects start at $50,000.</t>
-  </si>
-  <si>
-    <t>Info@homepronw.com</t>
-  </si>
-  <si>
-    <t>Direct email; stated 24-hour response; complimentary consultation; projects start at $50K</t>
-  </si>
-  <si>
-    <t>Turn the $50K+ consultation process into a high-ticket project-readiness campaign that helps prospects organize plans, inspiration, project type, budget, timeline and investment questions before the call.</t>
-  </si>
-  <si>
-    <t>$50K+ consultation-prep campaign for Home Pro NW</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Home Pro NW’s current consultation flow and noticed you already focus on projects starting at $50,000, offer complimentary consultations and respond within 24 hours. I’d turn that into a high-ticket project-readiness campaign that helps prospects organize plans, inspiration, project type, budget and timeline before the call. Same-Day Customer Growth Pack: $150 flat. Want two Home Pro NW-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://homepronw.com/</t>
-  </si>
-  <si>
-    <t>Silicon Prime Painting Inc</t>
-  </si>
-  <si>
-    <t>Residential / Commercial Painting / Cabinet Refinishing / Drywall</t>
-  </si>
-  <si>
-    <t>San Jose / Silicon Valley / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site publishes spp@siliconprimepainting.com, free written estimates, Monday-Saturday hours and residential/commercial painting, cabinet refinishing, drywall repair and related services.</t>
-  </si>
-  <si>
-    <t>spp@siliconprimepainting.com</t>
-  </si>
-  <si>
-    <t>Direct email; free written estimate; Monday-Saturday hours</t>
-  </si>
-  <si>
-    <t>Turn the free written-estimate process into a painting-project selector that helps prospects organize surface type, rooms or exterior areas, repair needs, color decisions and scheduling requirements before quoting.</t>
-  </si>
-  <si>
-    <t>Written-estimate campaign for Silicon Prime Painting</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Silicon Prime Painting’s current Bay Area estimate flow and noticed you already offer free written estimates across residential, commercial, cabinet and drywall work. I’d turn that into a painting-project selector that helps prospects organize surface type, rooms or exterior areas, repair needs, color decisions and scheduling requirements before quoting. Same-Day Customer Growth Pack: $150 flat. Want two Silicon Prime-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://siliconprimepaintinginc.com/</t>
+    <t>Official contact page publishes info@roofgeeksca.com, free roofing estimates, emergency leak response, Monday-Saturday hours, and same-day responses during business hours.</t>
+  </si>
+  <si>
+    <t>info@roofgeeksca.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; same-day business-hours response; emergency leak service</t>
+  </si>
+  <si>
+    <t>Turn fast estimate response into repair-vs-replacement readiness that captures roof age, leak location, urgency, property type and photos before inspection.</t>
+  </si>
+  <si>
+    <t>Same-day roof-readiness campaign for Roof Geeks</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Roof Geeks’ current estimate flow and noticed you offer free estimates, emergency leak response and same-day replies during business hours. I’d turn that into a repair-versus-replacement readiness campaign that helps property owners organize roof age, leak location, urgency, property type and photos before your team responds. Same-Day Customer Growth Pack: $150 flat. Want two Roof Geeks-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://roofgeeksca.com/contact</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>Elite HVAC</t>
+  </si>
+  <si>
+    <t>HVAC / Heating &amp; Air Conditioning</t>
+  </si>
+  <si>
+    <t>Agoura Hills / Los Angeles &amp; Ventura Counties, CA</t>
+  </si>
+  <si>
+    <t>Official contact page publishes info@elitehvac.us, free estimates, online scheduling with confirmation within minutes, a stated 24-hour email response, Monday-Saturday hours and 24/7 emergency service.</t>
+  </si>
+  <si>
+    <t>info@elitehvac.us</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; booking confirmation within minutes; 24-hour email response; 24/7 emergency service</t>
+  </si>
+  <si>
+    <t>Separate emergency repair from planned replacement and collect system type, symptoms, property type, equipment age and urgency before dispatch.</t>
+  </si>
+  <si>
+    <t>Fast HVAC lead-routing campaign for Elite HVAC</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Elite HVAC’s current booking flow and noticed you offer free estimates, appointment confirmation within minutes and 24/7 emergency service. I’d turn that into an emergency-versus-planned HVAC routing campaign that captures system type, symptoms, property type, equipment age and urgency before dispatch. Same-Day Customer Growth Pack: $150 flat. Want two Elite-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.elitehvac.us/contact</t>
+  </si>
+  <si>
+    <t>Smart Choice</t>
+  </si>
+  <si>
+    <t>HVAC / Construction / Property Improvements</t>
+  </si>
+  <si>
+    <t>Palmdale / Los Angeles County, CA</t>
+  </si>
+  <si>
+    <t>Official contact page publishes hvacsmartchoice@gmail.com, free estimates, same-day response positioning, seven-day hours and a licensed project-manager callback within 24 hours.</t>
+  </si>
+  <si>
+    <t>hvacsmartchoice@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; same-day positioning; project-manager callback within 24 hours; seven-day hours</t>
+  </si>
+  <si>
+    <t>Route HVAC, remodeling and commercial inquiries by service type, urgency, property type, scope and timeline before the project-manager callback.</t>
+  </si>
+  <si>
+    <t>Same-day service-routing campaign for Smart Choice</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Smart Choice’s current estimate flow and noticed you offer free estimates, same-day response positioning and a licensed project-manager follow-up within 24 hours. I’d turn that into a service-routing campaign that separates HVAC, remodeling and commercial inquiries while collecting urgency, property type, scope and timeline before the callback. Same-Day Customer Growth Pack: $150 flat. Want two Smart Choice-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://smartchoicegeneral.com/contact</t>
+  </si>
+  <si>
+    <t>Sacramento Roofing Inc</t>
+  </si>
+  <si>
+    <t>Roofing / Repair &amp; Replacement</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>Official site publishes sacramentoroofinginc@gmail.com, free inspections and estimates, same-day response, emergency routing and current financing offers for roof replacement.</t>
+  </si>
+  <si>
+    <t>sacramentoroofinginc@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free inspection/estimate; same-day response; emergency routing</t>
+  </si>
+  <si>
+    <t>Qualify repair-vs-replacement inquiries by roof age, leak symptoms, visible damage, urgency and financing interest before estimate follow-up.</t>
+  </si>
+  <si>
+    <t>Same-day roofing qualification campaign for Sacramento Roofing</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Sacramento Roofing Inc’s current estimate flow and noticed you offer free inspections, same-day responses and emergency routing. I’d turn that into a repair-versus-replacement qualification campaign that captures roof age, leak symptoms, visible damage, urgency and financing interest before the estimate follow-up. Same-Day Customer Growth Pack: $150 flat. Want two Sacramento Roofing-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://sacramento-roofing.com/contact</t>
+  </si>
+  <si>
+    <t>Hernandez Quality Painting</t>
+  </si>
+  <si>
+    <t>Painting / Residential &amp; Commercial</t>
+  </si>
+  <si>
+    <t>Lompoc / Central Coast, CA</t>
+  </si>
+  <si>
+    <t>Official site publishes qualitypaintingsb@gmail.com, states Armando personally reviews inquiries and responds within 24 hours, then schedules an on-site consultation and written quote.</t>
+  </si>
+  <si>
+    <t>qualitypaintingsb@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; owner-reviewed inquiry; 24-hour response; on-site consultation; written quote</t>
+  </si>
+  <si>
+    <t>Pre-qualify painting inquiries with surface type, rooms/areas, repair needs, finish/color decisions, photos and timing before the site visit.</t>
+  </si>
+  <si>
+    <t>24-hour painting project-prep campaign for Hernandez</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Hernandez Quality Painting’s current inquiry flow and noticed Armando personally reviews inquiries within 24 hours before the on-site consultation and written quote. I’d turn that into a painting project-prep campaign that captures surface type, rooms or exterior areas, repair needs, finish decisions, photos and timing before the visit. Same-Day Customer Growth Pack: $150 flat. Want two Hernandez-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://hernandezqualitypaintingsb.com/contact/</t>
+  </si>
+  <si>
+    <t>VMK Construction</t>
+  </si>
+  <si>
+    <t>General Construction / ADU / Remodeling</t>
+  </si>
+  <si>
+    <t>SF Bay Area &amp; Greater Sacramento, CA</t>
+  </si>
+  <si>
+    <t>Official contact page publishes vmkconstruction4u@gmail.com, a free consultation, stated response within 24 hours and ADU/remodel specialization.</t>
+  </si>
+  <si>
+    <t>vmkconstruction4u@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; free consultation; stated 24-hour response; Saturday by appointment</t>
+  </si>
+  <si>
+    <t>Prepare ADU/remodel prospects with project type, property constraints, approximate scope, timeline, budget questions and permit concerns before consultation.</t>
+  </si>
+  <si>
+    <t>24-hour ADU readiness campaign for VMK Construction</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed VMK Construction’s current consultation flow and noticed you offer free ADU/remodel consultations with a stated 24-hour response. I’d turn that into a project-readiness campaign that helps prospects organize project type, property constraints, approximate scope, timeline, budget questions and permit concerns before consultation. Same-Day Customer Growth Pack: $150 flat. Want two VMK-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.vmk-construction.com/contact</t>
+  </si>
+  <si>
+    <t>SoCal ADU Pro</t>
+  </si>
+  <si>
+    <t>ADU / Design-Build Construction</t>
+  </si>
+  <si>
+    <t>Southern California</t>
+  </si>
+  <si>
+    <t>Official site publishes info@socaladupro.com, a free ADU consultation, stated 24-hour response and turnkey design, permits and construction.</t>
+  </si>
+  <si>
+    <t>info@socaladupro.com</t>
+  </si>
+  <si>
+    <t>Direct email; free consultation; stated 24-hour response; Saturday hours</t>
+  </si>
+  <si>
+    <t>Turn free consultations into ADU feasibility briefs covering lot/property basics, desired size/use, budget range, timeline and permit questions.</t>
+  </si>
+  <si>
+    <t>24-hour ADU feasibility campaign for SoCal ADU Pro</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed SoCal ADU Pro’s current consultation flow and noticed you offer free consultations with a stated 24-hour response across turnkey design, permits and construction. I’d turn that into an ADU feasibility campaign that helps homeowners organize property basics, desired size and use, budget range, timeline and permit questions before your team responds. Same-Day Customer Growth Pack: $150 flat. Want two SoCal ADU Pro-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.socaladupro.com/</t>
+  </si>
+  <si>
+    <t>Yealpha Construction &amp; Energy</t>
+  </si>
+  <si>
+    <t>Construction / ADU / Remodeling / Energy</t>
+  </si>
+  <si>
+    <t>Official site publishes cs@yealpha.com, free consultation and estimate, response within 24 hours and usually same day across ADU, remodeling, solar, battery and electrical services.</t>
+  </si>
+  <si>
+    <t>cs@yealpha.com</t>
+  </si>
+  <si>
+    <t>Direct email; free consultation/estimate; usually same-day response; multiple high-ticket services</t>
+  </si>
+  <si>
+    <t>Route construction-versus-energy inquiries and capture project type, property details, goals, urgency, budget range and timeline before consultation.</t>
+  </si>
+  <si>
+    <t>Same-day project-routing campaign for Yealpha</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Yealpha’s current inquiry flow and noticed you offer free consultations and estimates with responses usually the same day across ADUs, remodeling and energy projects. I’d turn that into a project-routing campaign that separates construction from energy inquiries while collecting property details, goals, urgency, budget range and timeline before consultation. Same-Day Customer Growth Pack: $150 flat. Want two Yealpha-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.yealpha.com/</t>
+  </si>
+  <si>
+    <t>Priority One Builders</t>
+  </si>
+  <si>
+    <t>General Construction / ADU / Additions / Multifamily</t>
+  </si>
+  <si>
+    <t>Pasadena / Greater Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>Official site publishes info@p1build.com, free consultation and estimate, stated 24-hour response, Saturday hours and high-ticket ADU/addition/multifamily services.</t>
+  </si>
+  <si>
+    <t>info@p1build.com</t>
+  </si>
+  <si>
+    <t>Direct email; free consultation/estimate; stated 24-hour response; Saturday hours</t>
+  </si>
+  <si>
+    <t>Create a project-readiness intake around build type, property conditions, desired outcome, budget range, timeline and permit questions.</t>
+  </si>
+  <si>
+    <t>24-hour project-readiness campaign for Priority One</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Priority One Builders’ current consultation flow and noticed you offer free consultations and estimates with a stated 24-hour response for ADUs, additions and larger construction projects. I’d turn that into a project-readiness campaign that captures build type, property conditions, desired outcome, budget range, timeline and permit questions before consultation. Same-Day Customer Growth Pack: $150 flat. Want two Priority One-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://p1build.com/</t>
+  </si>
+  <si>
+    <t>Hammertime 24/7 Inc.</t>
+  </si>
+  <si>
+    <t>General Construction / ADU / Design-Build</t>
+  </si>
+  <si>
+    <t>Temecula / Southern California</t>
+  </si>
+  <si>
+    <t>Official site publishes joey@hammertime247.com, free on-site consultation, stated one-business-day/24-hour response, itemized fixed-price proposals and a direct line to the owner.</t>
+  </si>
+  <si>
+    <t>joey@hammertime247.com</t>
+  </si>
+  <si>
+    <t>Direct owner email; free on-site consultation; 24-hour response; itemized fixed-price proposal</t>
+  </si>
+  <si>
+    <t>Prepare construction prospects with project type, site conditions, goals, approximate scope, timeline and budget before the owner consultation.</t>
+  </si>
+  <si>
+    <t>24-hour consultation-prep campaign for Hammertime 24/7</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Hammertime 24/7’s current project flow and noticed you offer free on-site consultations, itemized fixed-price proposals and responses within one business day. I’d turn that into a consultation-prep campaign that helps prospects organize project type, site conditions, goals, approximate scope, timeline and budget before the owner conversation. Same-Day Customer Growth Pack: $150 flat. Want two Hammertime-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.hammertime247inc.com/</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -558,330 +555,363 @@
     <t>Offer Value $</t>
   </si>
   <si>
+    <t>FloodDry Water Damage Restoration</t>
+  </si>
+  <si>
+    <t>Follow-up</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:50:24-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-08T16:45:47-07:00</t>
+  </si>
+  <si>
+    <t>Contacted</t>
+  </si>
+  <si>
+    <t>Two verified outbound emails, no inbound reply found through 2026-09-12. Do not send another cold touch now.</t>
+  </si>
+  <si>
+    <t>Therma Tech</t>
+  </si>
+  <si>
+    <t>2026-09-05T20:01:38-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-07T13:35:02-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-07T14:19:35-07:00</t>
+  </si>
+  <si>
+    <t>Three verified outbound emails across two connected Gmail accounts; no inbound reply found through 2026-09-12. Stop cold follow-up unless they reply.</t>
+  </si>
+  <si>
+    <t>Dansel Restoration</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:49:58-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>One verified outbound email; no inbound reply found through 2026-09-12. One final respectful follow-up is permissible, then stop unless they reply.</t>
+  </si>
+  <si>
+    <t>California First Roofing</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:39:21-07:00</t>
+  </si>
+  <si>
+    <t>US Creative Restoration</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:53:01-07:00</t>
+  </si>
+  <si>
+    <t>One verified outbound email; no reply found through 2026-09-12. Eligible for at most one respectful follow-up.</t>
+  </si>
+  <si>
+    <t>WJM Builders</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:30:53-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>Clean Roofing</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:42:04-07:00</t>
+  </si>
+  <si>
+    <t>Solar Energy Consultants</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:25:44-07:00</t>
+  </si>
+  <si>
+    <t>Mayer's Construction</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:31:58-07:00</t>
+  </si>
+  <si>
+    <t>EVS Mechanical</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:32:27-07:00</t>
+  </si>
+  <si>
+    <t>Dueling Trowels Concrete Solutions</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:39:44-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:20:39-07:00</t>
+  </si>
+  <si>
+    <t>Two verified outbound emails; no reply found through 2026-09-12. Do not send another cold touch now.</t>
+  </si>
+  <si>
+    <t>GBD Concrete</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:54:30-07:00</t>
+  </si>
+  <si>
+    <t>John Molina Concrete</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:46:13-07:00</t>
+  </si>
+  <si>
+    <t>Precision Concrete Inc</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:40:53-07:00</t>
+  </si>
+  <si>
+    <t>One Day Complete Repipe</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:35:59-07:00</t>
+  </si>
+  <si>
+    <t>HB Design &amp; Construction</t>
+  </si>
+  <si>
+    <t>2026-09-18T16:24:00-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>Wait for reply. If no reply, eligible for respectful S02 follow-up on/after 2026-09-21; stop sooner on decline or opt-out.</t>
+  </si>
+  <si>
+    <t>QualiBuild LLC</t>
+  </si>
+  <si>
+    <t>Redwood Roofing</t>
+  </si>
+  <si>
+    <t>Premier Roofing &amp; Retro-Fit</t>
+  </si>
+  <si>
+    <t>Make It Simple Construction, Inc.</t>
+  </si>
+  <si>
+    <t>BLUECON</t>
+  </si>
+  <si>
+    <t>Blues Bros</t>
+  </si>
+  <si>
+    <t>Home Quality Remodeling</t>
+  </si>
+  <si>
+    <t>Imperia Roofing &amp; Exteriors</t>
+  </si>
+  <si>
+    <t>JH Construction</t>
+  </si>
+  <si>
     <t>2026-09-25T05:28:57-07:00</t>
   </si>
   <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
     <t>Wait for an actual reply. Check delivery failures and opt-outs before a single respectful follow-up on or after 2026-09-29.</t>
   </si>
   <si>
+    <t>Valdivia Roofing</t>
+  </si>
+  <si>
     <t>2026-09-25T05:28:58-07:00</t>
   </si>
   <si>
+    <t>Visionable Landscaping</t>
+  </si>
+  <si>
+    <t>2026-09-25T05:28:59-07:00</t>
+  </si>
+  <si>
+    <t>Seal Home Remodeling</t>
+  </si>
+  <si>
+    <t>ProMan California</t>
+  </si>
+  <si>
+    <t>2026-09-25T05:29:00-07:00</t>
+  </si>
+  <si>
+    <t>Green Hard Landscape Construction</t>
+  </si>
+  <si>
+    <t>2026-09-25T05:29:01-07:00</t>
+  </si>
+  <si>
+    <t>Bay Stone Depot</t>
+  </si>
+  <si>
+    <t>2026-09-25T05:29:02-07:00</t>
+  </si>
+  <si>
+    <t>Home Pro NW</t>
+  </si>
+  <si>
+    <t>Silicon Prime Painting Inc</t>
+  </si>
+  <si>
+    <t>2026-09-25T05:29:03-07:00</t>
+  </si>
+  <si>
+    <t>First Touch Evidence</t>
+  </si>
+  <si>
+    <t>FU1 Evidence</t>
+  </si>
+  <si>
+    <t>FU2 Evidence</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a074aa18c4a15e5</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07d94dc355abc7</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07dbda8027b039</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07537695be159d</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0753a7d53e5a5c</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0753ad793984cf</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0763c06f9e9dc5</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0753be59b49989</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07540c8b9fd4bc</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075443349aa830</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075449a2403271</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a08369d9f6b09c0</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0754701539a56d</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075485ca2a3fef</t>
+  </si>
+  <si>
+    <t>Precision Heating &amp; Cooling</t>
+  </si>
+  <si>
+    <t>2026-09-06T01:37:52-07:00</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075ddee6716e8a</t>
+  </si>
+  <si>
+    <t>Historical send discovered during Sep 12 audit; no reply found in connected Gmail search.</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07640ae5a69379</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a076456505c6304</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0764664a2b1202</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07646d6dbd3474</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0764fa024df1f4</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d78c843ca6b</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7943740cae</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d79a6cdefdb</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7a193869fd</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7a978557f8</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7afc5b1de0</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7b4e0a0a3f</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7bd8a5e4c7</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7c520f4297</t>
+  </si>
+  <si>
+    <t>Silicon Valley Chimney Sweep</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0b6d7d1bb96f3a</t>
+  </si>
+  <si>
+    <t>Delivery Failed</t>
+  </si>
+  <si>
+    <t>Do not count as successfully contacted. Official site still publishes info@svchimneysweep.com, but Gmail returned a hard bounce. Reverify or use the official website inquiry route; do not resend to the bounced address.</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0d88a4fad08ed7</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0d88a4f2e3d368</t>
+  </si>
+  <si>
+    <t>Alderstone Remodeling &amp; Exteriors</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0d88a53a1c7431</t>
+  </si>
+  <si>
     <t>Do not resend to the bounced address. Find a verified alternative contact route; initial email did not deliver.</t>
   </si>
   <si>
-    <t>2026-09-25T05:28:59-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-25T05:29:00-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-25T05:29:01-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-25T05:29:02-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-25T05:29:03-07:00</t>
-  </si>
-  <si>
-    <t>FloodDry Water Damage Restoration</t>
-  </si>
-  <si>
-    <t>Follow-up</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:50:24-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
-    <t>2026-09-08T16:45:47-07:00</t>
-  </si>
-  <si>
-    <t>Two verified outbound emails, no inbound reply found through 2026-09-12. Do not send another cold touch now.</t>
-  </si>
-  <si>
-    <t>Therma Tech</t>
-  </si>
-  <si>
-    <t>2026-09-05T20:01:38-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-07T13:35:02-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-07T14:19:35-07:00</t>
-  </si>
-  <si>
-    <t>Three verified outbound emails across two connected Gmail accounts; no inbound reply found through 2026-09-12. Stop cold follow-up unless they reply.</t>
-  </si>
-  <si>
-    <t>Dansel Restoration</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:49:58-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>One verified outbound email; no inbound reply found through 2026-09-12. One final respectful follow-up is permissible, then stop unless they reply.</t>
-  </si>
-  <si>
-    <t>California First Roofing</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:39:21-07:00</t>
-  </si>
-  <si>
-    <t>US Creative Restoration</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:53:01-07:00</t>
-  </si>
-  <si>
-    <t>One verified outbound email; no reply found through 2026-09-12. Eligible for at most one respectful follow-up.</t>
-  </si>
-  <si>
-    <t>WJM Builders</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:30:53-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
-  </si>
-  <si>
-    <t>Clean Roofing</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:42:04-07:00</t>
-  </si>
-  <si>
-    <t>Solar Energy Consultants</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:25:44-07:00</t>
-  </si>
-  <si>
-    <t>Mayer's Construction</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:31:58-07:00</t>
-  </si>
-  <si>
-    <t>EVS Mechanical</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:32:27-07:00</t>
-  </si>
-  <si>
-    <t>Dueling Trowels Concrete Solutions</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:39:44-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-06T03:20:39-07:00</t>
-  </si>
-  <si>
-    <t>Two verified outbound emails; no reply found through 2026-09-12. Do not send another cold touch now.</t>
-  </si>
-  <si>
-    <t>GBD Concrete</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:54:30-07:00</t>
-  </si>
-  <si>
-    <t>John Molina Concrete</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:46:13-07:00</t>
-  </si>
-  <si>
-    <t>Precision Concrete Inc</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:40:53-07:00</t>
-  </si>
-  <si>
-    <t>One Day Complete Repipe</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:35:59-07:00</t>
-  </si>
-  <si>
-    <t>HB Design &amp; Construction</t>
-  </si>
-  <si>
-    <t>2026-09-18T16:24:00-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
-  </si>
-  <si>
-    <t>Wait for reply. If no reply, eligible for respectful S02 follow-up on/after 2026-09-21; stop sooner on decline or opt-out.</t>
-  </si>
-  <si>
-    <t>QualiBuild LLC</t>
-  </si>
-  <si>
-    <t>Redwood Roofing</t>
-  </si>
-  <si>
-    <t>Premier Roofing &amp; Retro-Fit</t>
-  </si>
-  <si>
-    <t>Make It Simple Construction, Inc.</t>
-  </si>
-  <si>
-    <t>BLUECON</t>
-  </si>
-  <si>
-    <t>Blues Bros</t>
-  </si>
-  <si>
-    <t>Home Quality Remodeling</t>
-  </si>
-  <si>
-    <t>Imperia Roofing &amp; Exteriors</t>
-  </si>
-  <si>
-    <t>First Touch Evidence</t>
-  </si>
-  <si>
-    <t>FU1 Evidence</t>
-  </si>
-  <si>
-    <t>FU2 Evidence</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a074aa18c4a15e5</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07d94dc355abc7</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07dbda8027b039</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07537695be159d</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0753a7d53e5a5c</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0753ad793984cf</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0763c06f9e9dc5</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0753be59b49989</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07540c8b9fd4bc</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a075443349aa830</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a075449a2403271</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a08369d9f6b09c0</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0754701539a56d</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a075485ca2a3fef</t>
-  </si>
-  <si>
-    <t>Precision Heating &amp; Cooling</t>
-  </si>
-  <si>
-    <t>2026-09-06T01:37:52-07:00</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a075ddee6716e8a</t>
-  </si>
-  <si>
-    <t>Historical send discovered during Sep 12 audit; no reply found in connected Gmail search.</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07640ae5a69379</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a076456505c6304</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0764664a2b1202</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a07646d6dbd3474</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0764fa024df1f4</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d78c843ca6b</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7943740cae</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d79a6cdefdb</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7a193869fd</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7a978557f8</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7afc5b1de0</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7b4e0a0a3f</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7bd8a5e4c7</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7c520f4297</t>
-  </si>
-  <si>
-    <t>Silicon Valley Chimney Sweep</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0b6d7d1bb96f3a</t>
-  </si>
-  <si>
-    <t>Do not count as successfully contacted. Official site still publishes info@svchimneysweep.com, but Gmail returned a hard bounce. Reverify or use the official website inquiry route; do not resend to the bounced address.</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0d88a4fad08ed7</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0d88a4f2e3d368</t>
-  </si>
-  <si>
-    <t>Gmail sent message 1a0d88a53a1c7431</t>
-  </si>
-  <si>
     <t>Gmail sent message 1a0d88a55fbcdab6</t>
   </si>
   <si>
@@ -907,9 +937,6 @@
   </si>
   <si>
     <t>Leader Restoration</t>
-  </si>
-  <si>
-    <t>Contact Ready</t>
   </si>
   <si>
     <t>2026-09-12</t>
@@ -1806,7 +1833,7 @@
         <v>26</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1814,38 +1841,38 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>26</v>
@@ -1859,13 +1886,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
@@ -2000,32 +2027,32 @@
         <v>89</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
@@ -2039,38 +2066,38 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
@@ -2084,38 +2111,38 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>26</v>
@@ -2160,142 +2187,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2305,7 +2332,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -2329,58 +2356,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2393,12 +2420,8 @@
       <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>176</v>
-      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2413,9 +2436,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
         <v>26</v>
@@ -2437,12 +2458,8 @@
       <c r="C3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>176</v>
-      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -2457,9 +2474,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="2"/>
-      <c r="N3" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
         <v>26</v>
@@ -2481,16 +2496,14 @@
       <c r="C4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>178</v>
-      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -2499,9 +2512,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2"/>
-      <c r="N4" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
         <v>26</v>
@@ -2515,20 +2526,16 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>176</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -2543,15 +2550,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="2"/>
-      <c r="N5" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R5" s="3">
         <v>150</v>
@@ -2559,7 +2564,7 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -2567,12 +2572,8 @@
       <c r="C6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>176</v>
-      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -2587,9 +2588,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
         <v>26</v>
@@ -2611,12 +2610,8 @@
       <c r="C7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>176</v>
-      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -2631,9 +2626,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
         <v>26</v>
@@ -2655,12 +2648,8 @@
       <c r="C8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>176</v>
-      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -2675,9 +2664,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
         <v>26</v>
@@ -2697,14 +2684,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>176</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -2719,15 +2702,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="2"/>
-      <c r="N9" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R9" s="3">
         <v>150</v>
@@ -2735,20 +2716,16 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>176</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -2763,15 +2740,13 @@
         <v>0</v>
       </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="R10" s="3">
         <v>150</v>
@@ -2779,20 +2754,16 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>176</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -2807,15 +2778,13 @@
         <v>0</v>
       </c>
       <c r="M11" s="2"/>
-      <c r="N11" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R11" s="3">
         <v>150</v>
@@ -2823,28 +2792,28 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -2854,7 +2823,7 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -2865,32 +2834,32 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -2900,7 +2869,7 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2911,26 +2880,26 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -2940,7 +2909,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2951,26 +2920,26 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -2980,7 +2949,7 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2991,26 +2960,26 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -3020,7 +2989,7 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -3031,26 +3000,26 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -3060,7 +3029,7 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -3071,26 +3040,26 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -3100,7 +3069,7 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -3111,26 +3080,26 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -3140,7 +3109,7 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -3151,26 +3120,26 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -3180,7 +3149,7 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -3191,26 +3160,26 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -3220,7 +3189,7 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3231,28 +3200,28 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3262,7 +3231,7 @@
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3273,26 +3242,26 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -3302,7 +3271,7 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3313,26 +3282,26 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3342,7 +3311,7 @@
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3353,26 +3322,26 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -3382,7 +3351,7 @@
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3393,26 +3362,26 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -3422,7 +3391,7 @@
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -3433,26 +3402,26 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="2" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -3462,7 +3431,7 @@
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -3473,26 +3442,26 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="2" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
@@ -3502,7 +3471,7 @@
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -3513,26 +3482,26 @@
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="2" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -3542,7 +3511,7 @@
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -3553,26 +3522,26 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="2" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K30" s="3">
         <v>0</v>
@@ -3582,7 +3551,7 @@
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -3593,26 +3562,26 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K31" s="3">
         <v>0</v>
@@ -3622,7 +3591,7 @@
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -3633,26 +3602,26 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3662,7 +3631,7 @@
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -3673,26 +3642,26 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="2" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -3702,7 +3671,7 @@
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -3713,26 +3682,26 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="2" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -3742,7 +3711,7 @@
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -3753,26 +3722,26 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="2" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -3782,7 +3751,7 @@
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -3791,8 +3760,368 @@
         <v>150</v>
       </c>
     </row>
+    <row r="36" spans="1:18">
+      <c r="A36" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K37" s="3">
+        <v>0</v>
+      </c>
+      <c r="L37" s="3">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K38" s="3">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K39" s="3">
+        <v>0</v>
+      </c>
+      <c r="L39" s="3">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K40" s="3">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="3">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R35"/>
+  <autoFilter ref="A1:R44"/>
   <conditionalFormatting sqref="J2:J501">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Won/Paid">
       <formula>NOT(ISERROR(SEARCH("Won/Paid",J2)))</formula>
@@ -3846,67 +4175,67 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -3915,13 +4244,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3929,10 +4258,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -3941,13 +4270,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3955,10 +4284,10 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -3967,28 +4296,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -3997,13 +4326,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -4011,10 +4340,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -4023,13 +4352,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -4037,10 +4366,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -4049,13 +4378,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -4063,10 +4392,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -4075,28 +4404,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -4105,13 +4434,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -4119,10 +4448,10 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -4131,13 +4460,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -4145,10 +4474,10 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -4157,13 +4486,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -4171,10 +4500,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -4183,13 +4512,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -4197,10 +4526,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -4209,13 +4538,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -4223,10 +4552,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -4235,13 +4564,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -4249,10 +4578,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -4261,13 +4590,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -4275,10 +4604,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -4287,13 +4616,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -4301,10 +4630,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -4313,13 +4642,13 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -4327,10 +4656,10 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -4339,13 +4668,13 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -4353,10 +4682,10 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -4365,13 +4694,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -4379,10 +4708,10 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -4391,13 +4720,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -4405,10 +4734,10 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -4417,13 +4746,13 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -4431,10 +4760,10 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -4443,13 +4772,13 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -4457,10 +4786,10 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -4469,13 +4798,13 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -4483,10 +4812,10 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -4495,13 +4824,13 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -4509,10 +4838,10 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -4521,13 +4850,13 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -4535,10 +4864,10 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -4547,13 +4876,13 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -4561,10 +4890,10 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>48</v>
+        <v>286</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -4573,13 +4902,13 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
-        <v>15</v>
+        <v>232</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -4587,10 +4916,10 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
@@ -4599,13 +4928,13 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="2" t="s">
-        <v>28</v>
+        <v>235</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
@@ -4613,10 +4942,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -4625,13 +4954,13 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="2" t="s">
-        <v>38</v>
+        <v>290</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -4639,10 +4968,10 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
-        <v>48</v>
+        <v>286</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>179</v>
+        <v>292</v>
       </c>
       <c r="K30" s="3">
         <v>0</v>
@@ -4651,13 +4980,13 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="2" t="s">
-        <v>49</v>
+        <v>237</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -4665,10 +4994,10 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="K31" s="3">
         <v>0</v>
@@ -4677,13 +5006,13 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="2" t="s">
-        <v>59</v>
+        <v>239</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -4691,10 +5020,10 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -4703,13 +5032,13 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="2" t="s">
-        <v>68</v>
+        <v>240</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>181</v>
+        <v>241</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -4717,10 +5046,10 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -4729,13 +5058,13 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="2" t="s">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -4743,10 +5072,10 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -4755,13 +5084,13 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="2" t="s">
-        <v>88</v>
+        <v>244</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -4769,10 +5098,10 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -4781,13 +5110,13 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="2" t="s">
-        <v>98</v>
+        <v>246</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -4795,10 +5124,10 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="K36" s="3">
         <v>0</v>
@@ -4807,13 +5136,13 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="2" t="s">
-        <v>108</v>
+        <v>247</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>184</v>
+        <v>248</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -4821,10 +5150,10 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="K37" s="3">
         <v>0</v>
@@ -4856,36 +5185,36 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="G1" s="4" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4896,19 +5225,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4919,17 +5248,17 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -4940,20 +5269,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -4963,19 +5292,19 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -4986,17 +5315,17 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -5007,17 +5336,17 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -5028,17 +5357,17 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -5049,17 +5378,17 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -5070,19 +5399,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -5093,17 +5422,17 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -5114,17 +5443,17 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -5135,17 +5464,17 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -5156,19 +5485,19 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -5179,17 +5508,17 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -5200,17 +5529,17 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -5221,17 +5550,17 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -5242,19 +5571,19 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -5265,19 +5594,19 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -5288,19 +5617,19 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -5311,19 +5640,19 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -5334,11 +5663,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -5370,13 +5699,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5396,7 +5725,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5416,7 +5745,7 @@
         <v>32</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5436,32 +5765,32 @@
         <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>61</v>
@@ -5476,7 +5805,7 @@
         <v>62</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -5496,7 +5825,7 @@
         <v>72</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -5516,7 +5845,7 @@
         <v>82</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -5524,59 +5853,59 @@
         <v>88</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -5611,7 +5940,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5621,120 +5950,120 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>292</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contact Ready")</f>
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!R:R)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!K:K)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="E6" s="3">
         <f>SUM(Pipeline!L:L)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="E8" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -5760,98 +6089,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -5870,19 +6199,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5899,7 +6228,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
